--- a/source/bin/excel/achievement.xlsx
+++ b/source/bin/excel/achievement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D29A9AD-680D-4F2D-A182-C7F8BDDC941E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABC02A0-4414-422B-9F2E-307AFD1F185F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="badge_group" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$499</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6617" uniqueCount="5706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6628" uniqueCount="5717">
   <si>
     <t>sheet</t>
   </si>
@@ -38255,6 +38255,333 @@
   </si>
   <si>
     <t>段位場中，和出役滿「四槓子」</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>泽尼娅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守护者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>澤尼婭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ジニア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Protector of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Xenia</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지니아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수호자</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解锁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>泽尼娅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传记中的所有结局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解鎖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>澤尼婭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>傳記中的所有結局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ジニア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の物語のエンディングをすべて解放する</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlock all endings in Xenia's Story</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지니아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스토리의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엔딩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오픈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>30740019-1</t>
+    <phoneticPr fontId="38" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -39021,7 +39348,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -39330,6 +39657,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="76" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -40364,7 +40707,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM559"/>
+  <dimension ref="A1:AM560"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -72601,309 +72944,297 @@
       <c r="Z479" s="27"/>
       <c r="AA479" s="27"/>
     </row>
-    <row r="480" spans="1:31" s="59" customFormat="1" ht="16.5">
-      <c r="B480" s="130">
+    <row r="480" spans="1:31" s="144" customFormat="1" ht="16.5">
+      <c r="B480" s="144">
         <v>100482</v>
       </c>
-      <c r="C480" s="59" t="s">
+      <c r="C480" s="144" t="s">
         <v>5684</v>
       </c>
-      <c r="D480" s="87" t="s">
+      <c r="D480" s="145" t="s">
         <v>5507</v>
       </c>
-      <c r="E480" s="132" t="s">
+      <c r="E480" s="146" t="s">
         <v>5686</v>
       </c>
-      <c r="F480" s="133" t="s">
+      <c r="F480" s="147" t="s">
         <v>5688</v>
       </c>
-      <c r="G480" s="138" t="s">
+      <c r="G480" s="148" t="s">
         <v>5690</v>
       </c>
-      <c r="H480" s="87" t="s">
+      <c r="H480" s="145" t="s">
         <v>5509</v>
       </c>
-      <c r="I480" s="87" t="s">
+      <c r="I480" s="145" t="s">
         <v>5510</v>
       </c>
-      <c r="J480" s="133" t="s">
+      <c r="J480" s="147" t="s">
         <v>5692</v>
       </c>
-      <c r="K480" s="135" t="s">
+      <c r="K480" s="149" t="s">
         <v>5694</v>
       </c>
-      <c r="L480" s="139" t="s">
+      <c r="L480" s="150" t="s">
         <v>5696</v>
       </c>
-      <c r="M480" s="59">
+      <c r="M480" s="144">
         <v>2</v>
       </c>
-      <c r="N480" s="59">
-        <v>0</v>
-      </c>
-      <c r="O480" s="59">
+      <c r="N480" s="144">
+        <v>0</v>
+      </c>
+      <c r="O480" s="144">
         <v>10</v>
       </c>
-      <c r="P480" s="85">
+      <c r="P480" s="144">
         <v>169</v>
       </c>
-      <c r="R480" s="130">
+      <c r="R480" s="144">
         <v>99170</v>
       </c>
-      <c r="T480" s="59">
-        <v>0</v>
-      </c>
-      <c r="U480" s="59">
-        <v>0</v>
-      </c>
-      <c r="X480" s="27"/>
-      <c r="Y480" s="27"/>
-      <c r="Z480" s="27"/>
-      <c r="AA480" s="27"/>
+      <c r="T480" s="144">
+        <v>0</v>
+      </c>
+      <c r="U480" s="144">
+        <v>0</v>
+      </c>
+      <c r="X480" s="151"/>
+      <c r="Y480" s="151"/>
+      <c r="Z480" s="151"/>
+      <c r="AA480" s="151"/>
     </row>
-    <row r="481" spans="1:39" s="59" customFormat="1" ht="16.5">
-      <c r="B481" s="130">
+    <row r="481" spans="1:39" s="144" customFormat="1" ht="16.5">
+      <c r="B481" s="144">
         <v>100483</v>
       </c>
-      <c r="C481" s="59" t="s">
+      <c r="C481" s="144" t="s">
         <v>5685</v>
       </c>
-      <c r="D481" s="87" t="s">
+      <c r="D481" s="145" t="s">
         <v>5508</v>
       </c>
-      <c r="E481" s="132" t="s">
+      <c r="E481" s="146" t="s">
         <v>5687</v>
       </c>
-      <c r="F481" s="133" t="s">
+      <c r="F481" s="147" t="s">
         <v>5689</v>
       </c>
-      <c r="G481" s="138" t="s">
+      <c r="G481" s="148" t="s">
         <v>5691</v>
       </c>
-      <c r="H481" s="87" t="s">
+      <c r="H481" s="145" t="s">
         <v>5511</v>
       </c>
-      <c r="I481" s="87" t="s">
+      <c r="I481" s="145" t="s">
         <v>5512</v>
       </c>
-      <c r="J481" s="133" t="s">
+      <c r="J481" s="147" t="s">
         <v>5693</v>
       </c>
-      <c r="K481" s="131" t="s">
+      <c r="K481" s="145" t="s">
         <v>5695</v>
       </c>
-      <c r="L481" s="134" t="s">
+      <c r="L481" s="152" t="s">
         <v>5697</v>
       </c>
-      <c r="M481" s="59">
+      <c r="M481" s="144">
         <v>2</v>
       </c>
-      <c r="N481" s="59">
-        <v>0</v>
-      </c>
-      <c r="O481" s="59">
+      <c r="N481" s="144">
+        <v>0</v>
+      </c>
+      <c r="O481" s="144">
         <v>10</v>
       </c>
-      <c r="P481" s="86">
+      <c r="P481" s="144">
         <v>371</v>
       </c>
-      <c r="R481" s="130">
+      <c r="R481" s="144">
         <v>99171</v>
       </c>
-      <c r="T481" s="59">
-        <v>0</v>
-      </c>
-      <c r="U481" s="59">
-        <v>0</v>
-      </c>
-      <c r="X481" s="27"/>
-      <c r="Y481" s="27"/>
-      <c r="Z481" s="27"/>
-      <c r="AA481" s="27"/>
+      <c r="T481" s="144">
+        <v>0</v>
+      </c>
+      <c r="U481" s="144">
+        <v>0</v>
+      </c>
+      <c r="X481" s="151"/>
+      <c r="Y481" s="151"/>
+      <c r="Z481" s="151"/>
+      <c r="AA481" s="151"/>
     </row>
-    <row r="482" spans="1:39" s="59" customFormat="1" ht="16.5">
-      <c r="A482" s="59">
+    <row r="482" spans="1:39" s="144" customFormat="1" ht="16.5">
+      <c r="A482" s="144">
         <v>18</v>
       </c>
-      <c r="B482" s="130">
+      <c r="B482" s="144">
         <v>100484</v>
       </c>
-      <c r="C482" s="87" t="s">
+      <c r="C482" s="145" t="s">
         <v>5513</v>
       </c>
-      <c r="D482" s="87" t="s">
+      <c r="D482" s="145" t="s">
         <v>5514</v>
       </c>
-      <c r="E482" s="88" t="s">
+      <c r="E482" s="146" t="s">
         <v>5515</v>
       </c>
-      <c r="F482" s="89" t="s">
+      <c r="F482" s="147" t="s">
         <v>5516</v>
       </c>
-      <c r="G482" s="93" t="s">
+      <c r="G482" s="152" t="s">
         <v>5517</v>
       </c>
-      <c r="H482" s="90" t="s">
+      <c r="H482" s="149" t="s">
         <v>5518</v>
       </c>
-      <c r="I482" s="87" t="s">
+      <c r="I482" s="145" t="s">
         <v>5519</v>
       </c>
-      <c r="J482" s="89" t="s">
+      <c r="J482" s="147" t="s">
         <v>5520</v>
       </c>
-      <c r="K482" s="87" t="s">
+      <c r="K482" s="145" t="s">
         <v>5521</v>
       </c>
-      <c r="L482" s="93" t="s">
+      <c r="L482" s="152" t="s">
         <v>5522</v>
       </c>
-      <c r="M482" s="91">
+      <c r="M482" s="153">
         <v>1</v>
       </c>
-      <c r="N482" s="59">
-        <v>0</v>
-      </c>
-      <c r="O482" s="59">
+      <c r="N482" s="144">
+        <v>0</v>
+      </c>
+      <c r="O482" s="144">
         <v>10</v>
       </c>
       <c r="P482" s="142">
         <v>518</v>
       </c>
-      <c r="R482" s="130">
+      <c r="R482" s="144">
         <v>99172</v>
       </c>
-      <c r="S482" s="92" t="s">
+      <c r="S482" s="151" t="s">
         <v>5523</v>
       </c>
-      <c r="T482" s="59">
-        <v>0</v>
-      </c>
-      <c r="U482" s="59">
-        <v>0</v>
-      </c>
-      <c r="X482" s="27"/>
-      <c r="Y482" s="27"/>
-      <c r="Z482" s="27"/>
-      <c r="AA482" s="27"/>
+      <c r="T482" s="144">
+        <v>0</v>
+      </c>
+      <c r="U482" s="144">
+        <v>0</v>
+      </c>
+      <c r="X482" s="151"/>
+      <c r="Y482" s="151"/>
+      <c r="Z482" s="151"/>
+      <c r="AA482" s="151"/>
     </row>
-    <row r="483" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="A483" s="1" t="s">
-        <v>4234</v>
-      </c>
-      <c r="B483" s="1">
-        <v>800011</v>
-      </c>
-      <c r="C483" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D483" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E483" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F483" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G483" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H483" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I483" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J483" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="K483" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="L483" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="M483" s="47">
+    <row r="483" spans="1:39" s="59" customFormat="1">
+      <c r="A483" s="59">
+        <v>19</v>
+      </c>
+      <c r="B483" s="144">
+        <v>100485</v>
+      </c>
+      <c r="C483" s="87" t="s">
+        <v>5706</v>
+      </c>
+      <c r="D483" s="87" t="s">
+        <v>5707</v>
+      </c>
+      <c r="E483" s="88" t="s">
+        <v>5708</v>
+      </c>
+      <c r="F483" s="89" t="s">
+        <v>5709</v>
+      </c>
+      <c r="G483" s="93" t="s">
+        <v>5710</v>
+      </c>
+      <c r="H483" s="90" t="s">
+        <v>5711</v>
+      </c>
+      <c r="I483" s="87" t="s">
+        <v>5712</v>
+      </c>
+      <c r="J483" s="89" t="s">
+        <v>5713</v>
+      </c>
+      <c r="K483" s="87" t="s">
+        <v>5714</v>
+      </c>
+      <c r="L483" s="93" t="s">
+        <v>5715</v>
+      </c>
+      <c r="M483" s="91">
         <v>1</v>
       </c>
-      <c r="N483" s="1">
-        <v>0</v>
-      </c>
-      <c r="O483" s="1">
-        <v>12</v>
-      </c>
-      <c r="P483" s="1">
-        <v>1</v>
-      </c>
-      <c r="R483" s="1">
-        <v>90501</v>
-      </c>
-      <c r="T483" s="1">
-        <v>0</v>
-      </c>
-      <c r="U483" s="1">
-        <v>0</v>
-      </c>
-      <c r="X483" s="1">
-        <v>90501</v>
-      </c>
-      <c r="Y483" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z483" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA483" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB483" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE483" s="51"/>
-      <c r="AF483" s="51"/>
-      <c r="AG483" s="51"/>
-      <c r="AH483" s="51"/>
-      <c r="AI483" s="51"/>
-      <c r="AL483" s="51"/>
-      <c r="AM483" s="51"/>
+      <c r="N483" s="59">
+        <v>0</v>
+      </c>
+      <c r="O483" s="59">
+        <v>10</v>
+      </c>
+      <c r="P483" s="142">
+        <v>519</v>
+      </c>
+      <c r="R483" s="130">
+        <v>99173</v>
+      </c>
+      <c r="S483" s="92" t="s">
+        <v>5716</v>
+      </c>
+      <c r="T483" s="59">
+        <v>0</v>
+      </c>
+      <c r="U483" s="59">
+        <v>0</v>
+      </c>
+      <c r="X483" s="27"/>
+      <c r="Y483" s="27"/>
+      <c r="Z483" s="27"/>
+      <c r="AA483" s="27"/>
     </row>
     <row r="484" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="A484" s="1" t="s">
+        <v>4234</v>
+      </c>
       <c r="B484" s="1">
-        <v>800012</v>
+        <v>800011</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E484" s="41" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="H484" s="42" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="I484" s="42" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J484" s="46" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="K484" s="42" t="s">
-        <v>4235</v>
+        <v>235</v>
       </c>
       <c r="L484" s="42" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="M484" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N484" s="1">
         <v>0</v>
@@ -72912,10 +73243,10 @@
         <v>12</v>
       </c>
       <c r="P484" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R484" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="T484" s="1">
         <v>0</v>
@@ -72924,57 +73255,64 @@
         <v>0</v>
       </c>
       <c r="X484" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="Y484" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z484" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA484" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB484" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="AE484" s="51"/>
+      <c r="AF484" s="51"/>
+      <c r="AG484" s="51"/>
+      <c r="AH484" s="51"/>
+      <c r="AI484" s="51"/>
+      <c r="AL484" s="51"/>
+      <c r="AM484" s="51"/>
     </row>
     <row r="485" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B485" s="1">
-        <v>800013</v>
+        <v>800012</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E485" s="41" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F485" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H485" s="42" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I485" s="42" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="J485" s="46" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="K485" s="42" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
       <c r="L485" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="M485" s="48">
-        <v>3</v>
+        <v>249</v>
+      </c>
+      <c r="M485" s="47">
+        <v>2</v>
       </c>
       <c r="N485" s="1">
         <v>0</v>
@@ -72983,10 +73321,10 @@
         <v>12</v>
       </c>
       <c r="P485" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R485" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="T485" s="1">
         <v>0</v>
@@ -72995,7 +73333,7 @@
         <v>0</v>
       </c>
       <c r="X485" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="Y485" s="1" t="s">
         <v>237</v>
@@ -73004,7 +73342,7 @@
         <v>250</v>
       </c>
       <c r="AA485" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB485" s="1" t="s">
         <v>239</v>
@@ -73012,40 +73350,40 @@
     </row>
     <row r="486" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B486" s="1">
-        <v>800014</v>
+        <v>800013</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E486" s="41" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H486" s="42" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I486" s="42" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="J486" s="46" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="K486" s="42" t="s">
-        <v>269</v>
+        <v>4236</v>
       </c>
       <c r="L486" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M486" s="47">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="M486" s="48">
+        <v>3</v>
       </c>
       <c r="N486" s="1">
         <v>0</v>
@@ -73054,10 +73392,10 @@
         <v>12</v>
       </c>
       <c r="P486" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R486" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="T486" s="1">
         <v>0</v>
@@ -73066,57 +73404,57 @@
         <v>0</v>
       </c>
       <c r="X486" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="Y486" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z486" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA486" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB486" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="487" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B487" s="1">
-        <v>800015</v>
+        <v>800014</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="E487" s="41" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="H487" s="42" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I487" s="42" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="J487" s="46" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="K487" s="42" t="s">
-        <v>4237</v>
+        <v>269</v>
       </c>
       <c r="L487" s="42" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="M487" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N487" s="1">
         <v>0</v>
@@ -73125,10 +73463,10 @@
         <v>12</v>
       </c>
       <c r="P487" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R487" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="T487" s="1">
         <v>0</v>
@@ -73137,16 +73475,16 @@
         <v>0</v>
       </c>
       <c r="X487" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="Y487" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z487" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA487" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB487" s="1" t="s">
         <v>271</v>
@@ -73154,40 +73492,40 @@
     </row>
     <row r="488" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B488" s="1">
-        <v>800016</v>
+        <v>800015</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E488" s="43" t="s">
-        <v>284</v>
+        <v>273</v>
+      </c>
+      <c r="E488" s="41" t="s">
+        <v>274</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H488" s="42" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I488" s="42" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J488" s="46" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K488" s="42" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
       <c r="L488" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="M488" s="48">
-        <v>3</v>
+        <v>281</v>
+      </c>
+      <c r="M488" s="47">
+        <v>2</v>
       </c>
       <c r="N488" s="1">
         <v>0</v>
@@ -73196,10 +73534,10 @@
         <v>12</v>
       </c>
       <c r="P488" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R488" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="T488" s="1">
         <v>0</v>
@@ -73208,7 +73546,7 @@
         <v>0</v>
       </c>
       <c r="X488" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="Y488" s="1" t="s">
         <v>237</v>
@@ -73217,7 +73555,7 @@
         <v>250</v>
       </c>
       <c r="AA488" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB488" s="1" t="s">
         <v>271</v>
@@ -73225,40 +73563,40 @@
     </row>
     <row r="489" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B489" s="1">
-        <v>800017</v>
+        <v>800016</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E489" s="43" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="H489" s="42" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I489" s="42" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J489" s="46" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="K489" s="42" t="s">
-        <v>300</v>
+        <v>4238</v>
       </c>
       <c r="L489" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="M489" s="47">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="M489" s="48">
+        <v>3</v>
       </c>
       <c r="N489" s="1">
         <v>0</v>
@@ -73267,10 +73605,10 @@
         <v>12</v>
       </c>
       <c r="P489" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R489" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="T489" s="1">
         <v>0</v>
@@ -73279,54 +73617,54 @@
         <v>0</v>
       </c>
       <c r="X489" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="Y489" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z489" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA489" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB489" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="490" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B490" s="1">
-        <v>800018</v>
+        <v>800017</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E490" s="41" t="s">
-        <v>305</v>
+        <v>293</v>
+      </c>
+      <c r="E490" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="H490" s="42" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="I490" s="42" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="J490" s="46" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="K490" s="42" t="s">
-        <v>4239</v>
+        <v>300</v>
       </c>
       <c r="L490" s="42" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="M490" s="47">
         <v>1</v>
@@ -73338,10 +73676,10 @@
         <v>12</v>
       </c>
       <c r="P490" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R490" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="T490" s="1">
         <v>0</v>
@@ -73350,16 +73688,16 @@
         <v>0</v>
       </c>
       <c r="X490" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="Y490" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z490" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA490" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB490" s="1" t="s">
         <v>302</v>
@@ -73367,40 +73705,40 @@
     </row>
     <row r="491" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B491" s="1">
-        <v>800019</v>
+        <v>800018</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E491" s="41" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H491" s="42" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I491" s="42" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J491" s="46" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="K491" s="42" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
       <c r="L491" s="42" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M491" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N491" s="1">
         <v>0</v>
@@ -73409,10 +73747,10 @@
         <v>12</v>
       </c>
       <c r="P491" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R491" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="T491" s="1">
         <v>0</v>
@@ -73421,7 +73759,7 @@
         <v>0</v>
       </c>
       <c r="X491" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="Y491" s="1" t="s">
         <v>237</v>
@@ -73430,7 +73768,7 @@
         <v>250</v>
       </c>
       <c r="AA491" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB491" s="1" t="s">
         <v>302</v>
@@ -73438,40 +73776,40 @@
     </row>
     <row r="492" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B492" s="1">
-        <v>800020</v>
+        <v>800019</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E492" s="41" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="H492" s="42" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="I492" s="42" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="J492" s="46" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="K492" s="42" t="s">
-        <v>331</v>
+        <v>4240</v>
       </c>
       <c r="L492" s="42" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="M492" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N492" s="1">
         <v>0</v>
@@ -73480,10 +73818,10 @@
         <v>12</v>
       </c>
       <c r="P492" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R492" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="T492" s="1">
         <v>0</v>
@@ -73492,57 +73830,57 @@
         <v>0</v>
       </c>
       <c r="X492" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="Y492" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z492" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA492" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB492" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="493" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B493" s="1">
-        <v>800021</v>
+        <v>800020</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E493" s="41" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="H493" s="42" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I493" s="42" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="J493" s="46" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="K493" s="42" t="s">
-        <v>4241</v>
+        <v>331</v>
       </c>
       <c r="L493" s="42" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="M493" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N493" s="1">
         <v>0</v>
@@ -73551,10 +73889,10 @@
         <v>12</v>
       </c>
       <c r="P493" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R493" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="T493" s="1">
         <v>0</v>
@@ -73563,7 +73901,7 @@
         <v>0</v>
       </c>
       <c r="X493" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="Y493" s="1" t="s">
         <v>237</v>
@@ -73572,7 +73910,7 @@
         <v>333</v>
       </c>
       <c r="AA493" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB493" s="1" t="s">
         <v>239</v>
@@ -73580,40 +73918,40 @@
     </row>
     <row r="494" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B494" s="1">
-        <v>800022</v>
+        <v>800021</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E494" s="41" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="H494" s="42" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I494" s="42" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J494" s="46" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="K494" s="42" t="s">
-        <v>4242</v>
+        <v>4241</v>
       </c>
       <c r="L494" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="M494" s="48">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="M494" s="47">
+        <v>2</v>
       </c>
       <c r="N494" s="1">
         <v>0</v>
@@ -73622,10 +73960,10 @@
         <v>12</v>
       </c>
       <c r="P494" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R494" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="T494" s="1">
         <v>0</v>
@@ -73634,7 +73972,7 @@
         <v>0</v>
       </c>
       <c r="X494" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="Y494" s="1" t="s">
         <v>237</v>
@@ -73643,7 +73981,7 @@
         <v>333</v>
       </c>
       <c r="AA494" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB494" s="1" t="s">
         <v>239</v>
@@ -73651,40 +73989,40 @@
     </row>
     <row r="495" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B495" s="1">
-        <v>800023</v>
+        <v>800022</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E495" s="41" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H495" s="42" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I495" s="42" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="J495" s="46" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="K495" s="42" t="s">
-        <v>362</v>
+        <v>4242</v>
       </c>
       <c r="L495" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="M495" s="47">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="M495" s="48">
+        <v>3</v>
       </c>
       <c r="N495" s="1">
         <v>0</v>
@@ -73693,10 +74031,10 @@
         <v>12</v>
       </c>
       <c r="P495" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R495" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="T495" s="1">
         <v>0</v>
@@ -73705,7 +74043,7 @@
         <v>0</v>
       </c>
       <c r="X495" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="Y495" s="1" t="s">
         <v>237</v>
@@ -73714,45 +74052,45 @@
         <v>333</v>
       </c>
       <c r="AA495" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB495" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="496" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B496" s="1">
-        <v>800024</v>
+        <v>800023</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E496" s="41" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="H496" s="42" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I496" s="42" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J496" s="46" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="K496" s="42" t="s">
-        <v>4243</v>
+        <v>362</v>
       </c>
       <c r="L496" s="42" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M496" s="47">
         <v>1</v>
@@ -73764,10 +74102,10 @@
         <v>12</v>
       </c>
       <c r="P496" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R496" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="T496" s="1">
         <v>0</v>
@@ -73776,7 +74114,7 @@
         <v>0</v>
       </c>
       <c r="X496" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="Y496" s="1" t="s">
         <v>237</v>
@@ -73785,7 +74123,7 @@
         <v>333</v>
       </c>
       <c r="AA496" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB496" s="1" t="s">
         <v>271</v>
@@ -73793,40 +74131,40 @@
     </row>
     <row r="497" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B497" s="1">
-        <v>800025</v>
+        <v>800024</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E497" s="41" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="H497" s="42" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I497" s="42" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="J497" s="46" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K497" s="42" t="s">
-        <v>4244</v>
+        <v>4243</v>
       </c>
       <c r="L497" s="42" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="M497" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N497" s="1">
         <v>0</v>
@@ -73835,10 +74173,10 @@
         <v>12</v>
       </c>
       <c r="P497" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R497" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="T497" s="1">
         <v>0</v>
@@ -73847,7 +74185,7 @@
         <v>0</v>
       </c>
       <c r="X497" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="Y497" s="1" t="s">
         <v>237</v>
@@ -73856,116 +74194,119 @@
         <v>333</v>
       </c>
       <c r="AA497" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB497" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="498" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="A498" s="94" t="s">
-        <v>4838</v>
-      </c>
-      <c r="B498" s="85">
-        <v>800031</v>
-      </c>
-      <c r="C498" s="95" t="s">
-        <v>4839</v>
-      </c>
-      <c r="D498" s="95" t="s">
-        <v>4840</v>
-      </c>
-      <c r="E498" s="108" t="s">
-        <v>5325</v>
-      </c>
-      <c r="F498" s="108" t="s">
-        <v>5078</v>
-      </c>
-      <c r="G498" s="108" t="s">
-        <v>5079</v>
-      </c>
-      <c r="H498" s="97" t="s">
-        <v>4841</v>
-      </c>
-      <c r="I498" s="114" t="s">
-        <v>5343</v>
-      </c>
-      <c r="J498" s="116" t="s">
-        <v>5337</v>
-      </c>
-      <c r="K498" s="108" t="s">
-        <v>5082</v>
-      </c>
-      <c r="L498" s="109" t="s">
-        <v>5083</v>
-      </c>
-      <c r="M498" s="99">
-        <v>1</v>
-      </c>
-      <c r="N498" s="85">
-        <v>0</v>
-      </c>
-      <c r="O498" s="85">
-        <v>13</v>
-      </c>
-      <c r="P498" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q498">
-        <v>1059</v>
-      </c>
-      <c r="R498" s="100">
-        <v>94501</v>
-      </c>
-      <c r="T498" s="85">
-        <v>0</v>
-      </c>
-      <c r="U498" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z498" s="101"/>
-      <c r="AA498" s="101"/>
-      <c r="AE498" s="102"/>
-      <c r="AF498" s="102"/>
-      <c r="AG498" s="102"/>
-      <c r="AH498" s="102"/>
-      <c r="AI498" s="102"/>
-      <c r="AL498" s="102"/>
-      <c r="AM498" s="102"/>
+    <row r="498" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B498" s="1">
+        <v>800025</v>
+      </c>
+      <c r="C498" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E498" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F498" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G498" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H498" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="I498" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="J498" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="K498" s="42" t="s">
+        <v>4244</v>
+      </c>
+      <c r="L498" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="M498" s="47">
+        <v>2</v>
+      </c>
+      <c r="N498" s="1">
+        <v>0</v>
+      </c>
+      <c r="O498" s="1">
+        <v>12</v>
+      </c>
+      <c r="P498" s="1">
+        <v>15</v>
+      </c>
+      <c r="R498" s="1">
+        <v>90515</v>
+      </c>
+      <c r="T498" s="1">
+        <v>0</v>
+      </c>
+      <c r="U498" s="1">
+        <v>0</v>
+      </c>
+      <c r="X498" s="1">
+        <v>90515</v>
+      </c>
+      <c r="Y498" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z498" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA498" s="42">
+        <v>10</v>
+      </c>
+      <c r="AB498" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="499" spans="1:39" s="85" customFormat="1" ht="33">
+      <c r="A499" s="94" t="s">
+        <v>4838</v>
+      </c>
       <c r="B499" s="85">
-        <v>800032</v>
+        <v>800031</v>
       </c>
       <c r="C499" s="95" t="s">
-        <v>4842</v>
+        <v>4839</v>
       </c>
       <c r="D499" s="95" t="s">
-        <v>4843</v>
+        <v>4840</v>
       </c>
       <c r="E499" s="108" t="s">
-        <v>5327</v>
+        <v>5325</v>
       </c>
       <c r="F499" s="108" t="s">
-        <v>5086</v>
+        <v>5078</v>
       </c>
       <c r="G499" s="108" t="s">
-        <v>5080</v>
+        <v>5079</v>
       </c>
       <c r="H499" s="97" t="s">
-        <v>4844</v>
-      </c>
-      <c r="I499" s="97" t="s">
-        <v>4845</v>
+        <v>4841</v>
+      </c>
+      <c r="I499" s="114" t="s">
+        <v>5343</v>
       </c>
       <c r="J499" s="116" t="s">
-        <v>5338</v>
+        <v>5337</v>
       </c>
       <c r="K499" s="108" t="s">
-        <v>5092</v>
+        <v>5082</v>
       </c>
       <c r="L499" s="109" t="s">
-        <v>5094</v>
+        <v>5083</v>
       </c>
       <c r="M499" s="99">
         <v>1</v>
@@ -73977,13 +74318,13 @@
         <v>13</v>
       </c>
       <c r="P499" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q499">
         <v>1059</v>
       </c>
       <c r="R499" s="100">
-        <v>94502</v>
+        <v>94501</v>
       </c>
       <c r="T499" s="85">
         <v>0</v>
@@ -73993,43 +74334,50 @@
       </c>
       <c r="Z499" s="101"/>
       <c r="AA499" s="101"/>
+      <c r="AE499" s="102"/>
+      <c r="AF499" s="102"/>
+      <c r="AG499" s="102"/>
+      <c r="AH499" s="102"/>
+      <c r="AI499" s="102"/>
+      <c r="AL499" s="102"/>
+      <c r="AM499" s="102"/>
     </row>
-    <row r="500" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="500" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B500" s="85">
-        <v>800033</v>
+        <v>800032</v>
       </c>
       <c r="C500" s="95" t="s">
-        <v>4846</v>
+        <v>4842</v>
       </c>
       <c r="D500" s="95" t="s">
-        <v>4847</v>
+        <v>4843</v>
       </c>
       <c r="E500" s="108" t="s">
-        <v>5329</v>
+        <v>5327</v>
       </c>
       <c r="F500" s="108" t="s">
-        <v>5089</v>
+        <v>5086</v>
       </c>
       <c r="G500" s="108" t="s">
-        <v>5081</v>
+        <v>5080</v>
       </c>
       <c r="H500" s="97" t="s">
-        <v>4848</v>
+        <v>4844</v>
       </c>
       <c r="I500" s="97" t="s">
-        <v>4849</v>
+        <v>4845</v>
       </c>
       <c r="J500" s="116" t="s">
-        <v>5339</v>
+        <v>5338</v>
       </c>
       <c r="K500" s="108" t="s">
-        <v>5093</v>
+        <v>5092</v>
       </c>
       <c r="L500" s="109" t="s">
-        <v>5095</v>
-      </c>
-      <c r="M500" s="103">
-        <v>2</v>
+        <v>5094</v>
+      </c>
+      <c r="M500" s="99">
+        <v>1</v>
       </c>
       <c r="N500" s="85">
         <v>0</v>
@@ -74038,13 +74386,13 @@
         <v>13</v>
       </c>
       <c r="P500" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q500">
         <v>1059</v>
       </c>
       <c r="R500" s="100">
-        <v>94503</v>
+        <v>94502</v>
       </c>
       <c r="T500" s="85">
         <v>0</v>
@@ -74055,42 +74403,42 @@
       <c r="Z500" s="101"/>
       <c r="AA500" s="101"/>
     </row>
-    <row r="501" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="501" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B501" s="85">
-        <v>800034</v>
+        <v>800033</v>
       </c>
       <c r="C501" s="95" t="s">
-        <v>4850</v>
+        <v>4846</v>
       </c>
       <c r="D501" s="95" t="s">
-        <v>4851</v>
-      </c>
-      <c r="E501" s="117" t="s">
-        <v>5326</v>
+        <v>4847</v>
+      </c>
+      <c r="E501" s="108" t="s">
+        <v>5329</v>
       </c>
       <c r="F501" s="108" t="s">
-        <v>5084</v>
+        <v>5089</v>
       </c>
       <c r="G501" s="108" t="s">
-        <v>5085</v>
+        <v>5081</v>
       </c>
       <c r="H501" s="97" t="s">
-        <v>4852</v>
+        <v>4848</v>
       </c>
       <c r="I501" s="97" t="s">
-        <v>4853</v>
+        <v>4849</v>
       </c>
       <c r="J501" s="116" t="s">
-        <v>5331</v>
-      </c>
-      <c r="K501" s="98" t="s">
-        <v>5096</v>
-      </c>
-      <c r="L501" s="110" t="s">
-        <v>5099</v>
-      </c>
-      <c r="M501" s="99">
-        <v>1</v>
+        <v>5339</v>
+      </c>
+      <c r="K501" s="108" t="s">
+        <v>5093</v>
+      </c>
+      <c r="L501" s="109" t="s">
+        <v>5095</v>
+      </c>
+      <c r="M501" s="103">
+        <v>2</v>
       </c>
       <c r="N501" s="85">
         <v>0</v>
@@ -74099,13 +74447,13 @@
         <v>13</v>
       </c>
       <c r="P501" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q501">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R501" s="100">
-        <v>94504</v>
+        <v>94503</v>
       </c>
       <c r="T501" s="85">
         <v>0</v>
@@ -74118,37 +74466,37 @@
     </row>
     <row r="502" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B502" s="85">
-        <v>800035</v>
+        <v>800034</v>
       </c>
       <c r="C502" s="95" t="s">
-        <v>4854</v>
+        <v>4850</v>
       </c>
       <c r="D502" s="95" t="s">
-        <v>4855</v>
+        <v>4851</v>
       </c>
       <c r="E502" s="117" t="s">
-        <v>5328</v>
+        <v>5326</v>
       </c>
       <c r="F502" s="108" t="s">
-        <v>5087</v>
-      </c>
-      <c r="G502" s="109" t="s">
-        <v>5088</v>
+        <v>5084</v>
+      </c>
+      <c r="G502" s="108" t="s">
+        <v>5085</v>
       </c>
       <c r="H502" s="97" t="s">
-        <v>4856</v>
+        <v>4852</v>
       </c>
       <c r="I502" s="97" t="s">
-        <v>4857</v>
+        <v>4853</v>
       </c>
       <c r="J502" s="116" t="s">
-        <v>5332</v>
+        <v>5331</v>
       </c>
       <c r="K502" s="98" t="s">
-        <v>5097</v>
+        <v>5096</v>
       </c>
       <c r="L502" s="110" t="s">
-        <v>5100</v>
+        <v>5099</v>
       </c>
       <c r="M502" s="99">
         <v>1</v>
@@ -74160,13 +74508,13 @@
         <v>13</v>
       </c>
       <c r="P502" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q502">
         <v>1060</v>
       </c>
       <c r="R502" s="100">
-        <v>94505</v>
+        <v>94504</v>
       </c>
       <c r="T502" s="85">
         <v>0</v>
@@ -74177,42 +74525,42 @@
       <c r="Z502" s="101"/>
       <c r="AA502" s="101"/>
     </row>
-    <row r="503" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="503" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B503" s="85">
-        <v>800036</v>
+        <v>800035</v>
       </c>
       <c r="C503" s="95" t="s">
-        <v>4858</v>
+        <v>4854</v>
       </c>
       <c r="D503" s="95" t="s">
-        <v>4859</v>
+        <v>4855</v>
       </c>
       <c r="E503" s="117" t="s">
-        <v>5330</v>
+        <v>5328</v>
       </c>
       <c r="F503" s="108" t="s">
-        <v>5090</v>
+        <v>5087</v>
       </c>
       <c r="G503" s="109" t="s">
-        <v>5091</v>
+        <v>5088</v>
       </c>
       <c r="H503" s="97" t="s">
-        <v>4860</v>
+        <v>4856</v>
       </c>
       <c r="I503" s="97" t="s">
-        <v>4861</v>
+        <v>4857</v>
       </c>
       <c r="J503" s="116" t="s">
-        <v>5333</v>
+        <v>5332</v>
       </c>
       <c r="K503" s="98" t="s">
-        <v>5098</v>
+        <v>5097</v>
       </c>
       <c r="L503" s="110" t="s">
-        <v>5101</v>
-      </c>
-      <c r="M503" s="103">
-        <v>2</v>
+        <v>5100</v>
+      </c>
+      <c r="M503" s="99">
+        <v>1</v>
       </c>
       <c r="N503" s="85">
         <v>0</v>
@@ -74221,13 +74569,13 @@
         <v>13</v>
       </c>
       <c r="P503" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q503">
         <v>1060</v>
       </c>
       <c r="R503" s="100">
-        <v>94506</v>
+        <v>94505</v>
       </c>
       <c r="T503" s="85">
         <v>0</v>
@@ -74238,42 +74586,42 @@
       <c r="Z503" s="101"/>
       <c r="AA503" s="101"/>
     </row>
-    <row r="504" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="504" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B504" s="85">
-        <v>800037</v>
+        <v>800036</v>
       </c>
       <c r="C504" s="95" t="s">
-        <v>4862</v>
+        <v>4858</v>
       </c>
       <c r="D504" s="95" t="s">
-        <v>4863</v>
+        <v>4859</v>
       </c>
       <c r="E504" s="117" t="s">
-        <v>5334</v>
-      </c>
-      <c r="F504" s="96" t="s">
-        <v>5102</v>
-      </c>
-      <c r="G504" s="111" t="s">
-        <v>5103</v>
+        <v>5330</v>
+      </c>
+      <c r="F504" s="108" t="s">
+        <v>5090</v>
+      </c>
+      <c r="G504" s="109" t="s">
+        <v>5091</v>
       </c>
       <c r="H504" s="97" t="s">
-        <v>4864</v>
+        <v>4860</v>
       </c>
       <c r="I504" s="97" t="s">
-        <v>4865</v>
+        <v>4861</v>
       </c>
       <c r="J504" s="116" t="s">
-        <v>5340</v>
+        <v>5333</v>
       </c>
       <c r="K504" s="98" t="s">
-        <v>5213</v>
-      </c>
-      <c r="L504" s="109" t="s">
-        <v>5216</v>
-      </c>
-      <c r="M504" s="99">
-        <v>1</v>
+        <v>5098</v>
+      </c>
+      <c r="L504" s="110" t="s">
+        <v>5101</v>
+      </c>
+      <c r="M504" s="103">
+        <v>2</v>
       </c>
       <c r="N504" s="85">
         <v>0</v>
@@ -74282,13 +74630,13 @@
         <v>13</v>
       </c>
       <c r="P504" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q504">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R504" s="100">
-        <v>94507</v>
+        <v>94506</v>
       </c>
       <c r="T504" s="85">
         <v>0</v>
@@ -74301,37 +74649,37 @@
     </row>
     <row r="505" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B505" s="85">
-        <v>800038</v>
+        <v>800037</v>
       </c>
       <c r="C505" s="95" t="s">
-        <v>4866</v>
+        <v>4862</v>
       </c>
       <c r="D505" s="95" t="s">
-        <v>4867</v>
+        <v>4863</v>
       </c>
       <c r="E505" s="117" t="s">
-        <v>5336</v>
+        <v>5334</v>
       </c>
       <c r="F505" s="96" t="s">
-        <v>5105</v>
+        <v>5102</v>
       </c>
       <c r="G505" s="111" t="s">
-        <v>5106</v>
+        <v>5103</v>
       </c>
       <c r="H505" s="97" t="s">
-        <v>4868</v>
+        <v>4864</v>
       </c>
       <c r="I505" s="97" t="s">
-        <v>4869</v>
+        <v>4865</v>
       </c>
       <c r="J505" s="116" t="s">
-        <v>5341</v>
+        <v>5340</v>
       </c>
       <c r="K505" s="98" t="s">
-        <v>5214</v>
+        <v>5213</v>
       </c>
       <c r="L505" s="109" t="s">
-        <v>5217</v>
+        <v>5216</v>
       </c>
       <c r="M505" s="99">
         <v>1</v>
@@ -74343,13 +74691,13 @@
         <v>13</v>
       </c>
       <c r="P505" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q505">
         <v>1061</v>
       </c>
       <c r="R505" s="100">
-        <v>94508</v>
+        <v>94507</v>
       </c>
       <c r="T505" s="85">
         <v>0</v>
@@ -74362,40 +74710,40 @@
     </row>
     <row r="506" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B506" s="85">
-        <v>800039</v>
+        <v>800038</v>
       </c>
       <c r="C506" s="95" t="s">
-        <v>4870</v>
-      </c>
-      <c r="D506" s="114" t="s">
-        <v>5184</v>
+        <v>4866</v>
+      </c>
+      <c r="D506" s="95" t="s">
+        <v>4867</v>
       </c>
       <c r="E506" s="117" t="s">
-        <v>5335</v>
+        <v>5336</v>
       </c>
       <c r="F506" s="96" t="s">
-        <v>5104</v>
+        <v>5105</v>
       </c>
       <c r="G506" s="111" t="s">
-        <v>5107</v>
+        <v>5106</v>
       </c>
       <c r="H506" s="97" t="s">
-        <v>4871</v>
+        <v>4868</v>
       </c>
       <c r="I506" s="97" t="s">
-        <v>4872</v>
+        <v>4869</v>
       </c>
       <c r="J506" s="116" t="s">
-        <v>5342</v>
+        <v>5341</v>
       </c>
       <c r="K506" s="98" t="s">
-        <v>5215</v>
+        <v>5214</v>
       </c>
       <c r="L506" s="109" t="s">
-        <v>5218</v>
+        <v>5217</v>
       </c>
       <c r="M506" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N506" s="85">
         <v>0</v>
@@ -74404,13 +74752,13 @@
         <v>13</v>
       </c>
       <c r="P506" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q506">
         <v>1061</v>
       </c>
       <c r="R506" s="100">
-        <v>94509</v>
+        <v>94508</v>
       </c>
       <c r="T506" s="85">
         <v>0</v>
@@ -74423,40 +74771,40 @@
     </row>
     <row r="507" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B507" s="85">
-        <v>800040</v>
+        <v>800039</v>
       </c>
       <c r="C507" s="95" t="s">
-        <v>4873</v>
-      </c>
-      <c r="D507" s="95" t="s">
-        <v>4874</v>
+        <v>4870</v>
+      </c>
+      <c r="D507" s="114" t="s">
+        <v>5184</v>
       </c>
       <c r="E507" s="117" t="s">
-        <v>5344</v>
-      </c>
-      <c r="F507" s="108" t="s">
-        <v>5108</v>
-      </c>
-      <c r="G507" s="112" t="s">
-        <v>5109</v>
+        <v>5335</v>
+      </c>
+      <c r="F507" s="96" t="s">
+        <v>5104</v>
+      </c>
+      <c r="G507" s="111" t="s">
+        <v>5107</v>
       </c>
       <c r="H507" s="97" t="s">
-        <v>4875</v>
+        <v>4871</v>
       </c>
       <c r="I507" s="97" t="s">
-        <v>4876</v>
-      </c>
-      <c r="J507" s="118" t="s">
-        <v>5346</v>
+        <v>4872</v>
+      </c>
+      <c r="J507" s="116" t="s">
+        <v>5342</v>
       </c>
       <c r="K507" s="98" t="s">
-        <v>5219</v>
-      </c>
-      <c r="L507" s="110" t="s">
-        <v>5220</v>
+        <v>5215</v>
+      </c>
+      <c r="L507" s="109" t="s">
+        <v>5218</v>
       </c>
       <c r="M507" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N507" s="85">
         <v>0</v>
@@ -74465,10 +74813,13 @@
         <v>13</v>
       </c>
       <c r="P507" s="85">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="Q507">
+        <v>1061</v>
       </c>
       <c r="R507" s="100">
-        <v>94510</v>
+        <v>94509</v>
       </c>
       <c r="T507" s="85">
         <v>0</v>
@@ -74481,37 +74832,37 @@
     </row>
     <row r="508" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B508" s="85">
-        <v>800041</v>
+        <v>800040</v>
       </c>
       <c r="C508" s="95" t="s">
-        <v>4877</v>
+        <v>4873</v>
       </c>
       <c r="D508" s="95" t="s">
-        <v>4878</v>
+        <v>4874</v>
       </c>
       <c r="E508" s="117" t="s">
-        <v>5345</v>
+        <v>5344</v>
       </c>
       <c r="F508" s="108" t="s">
-        <v>5110</v>
-      </c>
-      <c r="G508" s="108" t="s">
-        <v>5111</v>
+        <v>5108</v>
+      </c>
+      <c r="G508" s="112" t="s">
+        <v>5109</v>
       </c>
       <c r="H508" s="97" t="s">
-        <v>4879</v>
+        <v>4875</v>
       </c>
       <c r="I508" s="97" t="s">
-        <v>4880</v>
+        <v>4876</v>
       </c>
       <c r="J508" s="118" t="s">
-        <v>5347</v>
+        <v>5346</v>
       </c>
       <c r="K508" s="98" t="s">
-        <v>5221</v>
+        <v>5219</v>
       </c>
       <c r="L508" s="110" t="s">
-        <v>5222</v>
+        <v>5220</v>
       </c>
       <c r="M508" s="99">
         <v>1</v>
@@ -74523,10 +74874,10 @@
         <v>13</v>
       </c>
       <c r="P508" s="85">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R508" s="100">
-        <v>94511</v>
+        <v>94510</v>
       </c>
       <c r="T508" s="85">
         <v>0</v>
@@ -74537,41 +74888,41 @@
       <c r="Z508" s="101"/>
       <c r="AA508" s="101"/>
     </row>
-    <row r="509" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="509" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B509" s="85">
-        <v>800042</v>
-      </c>
-      <c r="C509" s="104" t="s">
-        <v>4881</v>
-      </c>
-      <c r="D509" s="104" t="s">
-        <v>4881</v>
+        <v>800041</v>
+      </c>
+      <c r="C509" s="95" t="s">
+        <v>4877</v>
+      </c>
+      <c r="D509" s="95" t="s">
+        <v>4878</v>
       </c>
       <c r="E509" s="117" t="s">
-        <v>5348</v>
+        <v>5345</v>
       </c>
       <c r="F509" s="108" t="s">
-        <v>5185</v>
+        <v>5110</v>
       </c>
       <c r="G509" s="108" t="s">
-        <v>5112</v>
-      </c>
-      <c r="H509" s="104" t="s">
-        <v>4882</v>
-      </c>
-      <c r="I509" s="104" t="s">
-        <v>4883</v>
-      </c>
-      <c r="J509" s="116" t="s">
-        <v>5351</v>
-      </c>
-      <c r="K509" s="108" t="s">
-        <v>5223</v>
-      </c>
-      <c r="L509" s="109" t="s">
-        <v>5224</v>
-      </c>
-      <c r="M509" s="103">
+        <v>5111</v>
+      </c>
+      <c r="H509" s="97" t="s">
+        <v>4879</v>
+      </c>
+      <c r="I509" s="97" t="s">
+        <v>4880</v>
+      </c>
+      <c r="J509" s="118" t="s">
+        <v>5347</v>
+      </c>
+      <c r="K509" s="98" t="s">
+        <v>5221</v>
+      </c>
+      <c r="L509" s="110" t="s">
+        <v>5222</v>
+      </c>
+      <c r="M509" s="99">
         <v>1</v>
       </c>
       <c r="N509" s="85">
@@ -74581,13 +74932,10 @@
         <v>13</v>
       </c>
       <c r="P509" s="85">
-        <v>12</v>
-      </c>
-      <c r="Q509">
-        <v>1062</v>
+        <v>11</v>
       </c>
       <c r="R509" s="100">
-        <v>94512</v>
+        <v>94511</v>
       </c>
       <c r="T509" s="85">
         <v>0</v>
@@ -74598,41 +74946,41 @@
       <c r="Z509" s="101"/>
       <c r="AA509" s="101"/>
     </row>
-    <row r="510" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="510" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B510" s="85">
-        <v>800043</v>
+        <v>800042</v>
       </c>
       <c r="C510" s="104" t="s">
-        <v>4884</v>
+        <v>4881</v>
       </c>
       <c r="D510" s="104" t="s">
-        <v>4884</v>
+        <v>4881</v>
       </c>
       <c r="E510" s="117" t="s">
-        <v>5349</v>
+        <v>5348</v>
       </c>
       <c r="F510" s="108" t="s">
-        <v>5186</v>
-      </c>
-      <c r="G510" s="109" t="s">
-        <v>5189</v>
+        <v>5185</v>
+      </c>
+      <c r="G510" s="108" t="s">
+        <v>5112</v>
       </c>
       <c r="H510" s="104" t="s">
-        <v>4885</v>
+        <v>4882</v>
       </c>
       <c r="I510" s="104" t="s">
-        <v>4886</v>
+        <v>4883</v>
       </c>
       <c r="J510" s="116" t="s">
-        <v>5352</v>
+        <v>5351</v>
       </c>
       <c r="K510" s="108" t="s">
-        <v>5225</v>
+        <v>5223</v>
       </c>
       <c r="L510" s="109" t="s">
-        <v>5226</v>
-      </c>
-      <c r="M510" s="99">
+        <v>5224</v>
+      </c>
+      <c r="M510" s="103">
         <v>1</v>
       </c>
       <c r="N510" s="85">
@@ -74642,13 +74990,13 @@
         <v>13</v>
       </c>
       <c r="P510" s="85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q510">
         <v>1062</v>
       </c>
       <c r="R510" s="100">
-        <v>94513</v>
+        <v>94512</v>
       </c>
       <c r="T510" s="85">
         <v>0</v>
@@ -74661,40 +75009,40 @@
     </row>
     <row r="511" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B511" s="85">
-        <v>800044</v>
+        <v>800043</v>
       </c>
       <c r="C511" s="104" t="s">
-        <v>4887</v>
+        <v>4884</v>
       </c>
       <c r="D511" s="104" t="s">
-        <v>4887</v>
+        <v>4884</v>
       </c>
       <c r="E511" s="117" t="s">
-        <v>5350</v>
+        <v>5349</v>
       </c>
       <c r="F511" s="108" t="s">
-        <v>5187</v>
+        <v>5186</v>
       </c>
       <c r="G511" s="109" t="s">
-        <v>5188</v>
+        <v>5189</v>
       </c>
       <c r="H511" s="104" t="s">
-        <v>4888</v>
+        <v>4885</v>
       </c>
       <c r="I511" s="104" t="s">
-        <v>4889</v>
+        <v>4886</v>
       </c>
       <c r="J511" s="116" t="s">
-        <v>5353</v>
+        <v>5352</v>
       </c>
       <c r="K511" s="108" t="s">
-        <v>5227</v>
+        <v>5225</v>
       </c>
       <c r="L511" s="109" t="s">
-        <v>5228</v>
+        <v>5226</v>
       </c>
       <c r="M511" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N511" s="85">
         <v>0</v>
@@ -74703,13 +75051,13 @@
         <v>13</v>
       </c>
       <c r="P511" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q511">
         <v>1062</v>
       </c>
       <c r="R511" s="100">
-        <v>94514</v>
+        <v>94513</v>
       </c>
       <c r="T511" s="85">
         <v>0</v>
@@ -74722,40 +75070,40 @@
     </row>
     <row r="512" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B512" s="85">
-        <v>800045</v>
+        <v>800044</v>
       </c>
       <c r="C512" s="104" t="s">
-        <v>4890</v>
+        <v>4887</v>
       </c>
       <c r="D512" s="104" t="s">
-        <v>4891</v>
+        <v>4887</v>
       </c>
       <c r="E512" s="117" t="s">
-        <v>5354</v>
-      </c>
-      <c r="F512" s="112" t="s">
-        <v>5113</v>
-      </c>
-      <c r="G512" s="108" t="s">
-        <v>5114</v>
+        <v>5350</v>
+      </c>
+      <c r="F512" s="108" t="s">
+        <v>5187</v>
+      </c>
+      <c r="G512" s="109" t="s">
+        <v>5188</v>
       </c>
       <c r="H512" s="104" t="s">
-        <v>4892</v>
+        <v>4888</v>
       </c>
       <c r="I512" s="104" t="s">
-        <v>4893</v>
+        <v>4889</v>
       </c>
       <c r="J512" s="116" t="s">
-        <v>5357</v>
+        <v>5353</v>
       </c>
       <c r="K512" s="108" t="s">
-        <v>5229</v>
+        <v>5227</v>
       </c>
       <c r="L512" s="109" t="s">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="M512" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N512" s="85">
         <v>0</v>
@@ -74764,13 +75112,13 @@
         <v>13</v>
       </c>
       <c r="P512" s="85">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q512">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R512" s="100">
-        <v>94515</v>
+        <v>94514</v>
       </c>
       <c r="T512" s="85">
         <v>0</v>
@@ -74781,41 +75129,41 @@
       <c r="Z512" s="101"/>
       <c r="AA512" s="101"/>
     </row>
-    <row r="513" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="513" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B513" s="85">
-        <v>800046</v>
+        <v>800045</v>
       </c>
       <c r="C513" s="104" t="s">
-        <v>4894</v>
+        <v>4890</v>
       </c>
       <c r="D513" s="104" t="s">
-        <v>4895</v>
+        <v>4891</v>
       </c>
       <c r="E513" s="117" t="s">
-        <v>5355</v>
+        <v>5354</v>
       </c>
       <c r="F513" s="112" t="s">
-        <v>5190</v>
-      </c>
-      <c r="G513" s="109" t="s">
-        <v>5191</v>
+        <v>5113</v>
+      </c>
+      <c r="G513" s="108" t="s">
+        <v>5114</v>
       </c>
       <c r="H513" s="104" t="s">
-        <v>4896</v>
+        <v>4892</v>
       </c>
       <c r="I513" s="104" t="s">
-        <v>4897</v>
+        <v>4893</v>
       </c>
       <c r="J513" s="116" t="s">
-        <v>5358</v>
+        <v>5357</v>
       </c>
       <c r="K513" s="108" t="s">
-        <v>5231</v>
+        <v>5229</v>
       </c>
       <c r="L513" s="109" t="s">
-        <v>5232</v>
-      </c>
-      <c r="M513" s="103">
+        <v>5230</v>
+      </c>
+      <c r="M513" s="99">
         <v>1</v>
       </c>
       <c r="N513" s="85">
@@ -74825,13 +75173,13 @@
         <v>13</v>
       </c>
       <c r="P513" s="85">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q513">
         <v>1063</v>
       </c>
       <c r="R513" s="100">
-        <v>94516</v>
+        <v>94515</v>
       </c>
       <c r="T513" s="85">
         <v>0</v>
@@ -74842,42 +75190,42 @@
       <c r="Z513" s="101"/>
       <c r="AA513" s="101"/>
     </row>
-    <row r="514" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="514" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B514" s="85">
-        <v>800047</v>
+        <v>800046</v>
       </c>
       <c r="C514" s="104" t="s">
-        <v>4898</v>
+        <v>4894</v>
       </c>
       <c r="D514" s="104" t="s">
-        <v>4899</v>
+        <v>4895</v>
       </c>
       <c r="E514" s="117" t="s">
-        <v>5356</v>
+        <v>5355</v>
       </c>
       <c r="F514" s="112" t="s">
-        <v>5192</v>
+        <v>5190</v>
       </c>
       <c r="G514" s="109" t="s">
-        <v>5193</v>
+        <v>5191</v>
       </c>
       <c r="H514" s="104" t="s">
-        <v>4900</v>
+        <v>4896</v>
       </c>
       <c r="I514" s="104" t="s">
-        <v>4901</v>
+        <v>4897</v>
       </c>
       <c r="J514" s="116" t="s">
-        <v>5359</v>
+        <v>5358</v>
       </c>
       <c r="K514" s="108" t="s">
-        <v>5233</v>
+        <v>5231</v>
       </c>
       <c r="L514" s="109" t="s">
-        <v>5234</v>
-      </c>
-      <c r="M514" s="99">
-        <v>2</v>
+        <v>5232</v>
+      </c>
+      <c r="M514" s="103">
+        <v>1</v>
       </c>
       <c r="N514" s="85">
         <v>0</v>
@@ -74886,13 +75234,13 @@
         <v>13</v>
       </c>
       <c r="P514" s="85">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q514">
         <v>1063</v>
       </c>
       <c r="R514" s="100">
-        <v>94517</v>
+        <v>94516</v>
       </c>
       <c r="T514" s="85">
         <v>0</v>
@@ -74905,40 +75253,40 @@
     </row>
     <row r="515" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B515" s="85">
-        <v>800048</v>
+        <v>800047</v>
       </c>
       <c r="C515" s="104" t="s">
-        <v>4902</v>
+        <v>4898</v>
       </c>
       <c r="D515" s="104" t="s">
-        <v>4903</v>
+        <v>4899</v>
       </c>
       <c r="E515" s="117" t="s">
-        <v>5360</v>
+        <v>5356</v>
       </c>
       <c r="F515" s="112" t="s">
-        <v>5115</v>
-      </c>
-      <c r="G515" s="108" t="s">
-        <v>5116</v>
+        <v>5192</v>
+      </c>
+      <c r="G515" s="109" t="s">
+        <v>5193</v>
       </c>
       <c r="H515" s="104" t="s">
-        <v>4904</v>
+        <v>4900</v>
       </c>
       <c r="I515" s="104" t="s">
-        <v>4905</v>
+        <v>4901</v>
       </c>
       <c r="J515" s="116" t="s">
-        <v>5363</v>
+        <v>5359</v>
       </c>
       <c r="K515" s="108" t="s">
-        <v>5235</v>
+        <v>5233</v>
       </c>
       <c r="L515" s="109" t="s">
-        <v>5238</v>
+        <v>5234</v>
       </c>
       <c r="M515" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N515" s="85">
         <v>0</v>
@@ -74947,13 +75295,13 @@
         <v>13</v>
       </c>
       <c r="P515" s="85">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q515">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R515" s="100">
-        <v>94518</v>
+        <v>94517</v>
       </c>
       <c r="T515" s="85">
         <v>0</v>
@@ -74966,37 +75314,37 @@
     </row>
     <row r="516" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B516" s="85">
-        <v>800049</v>
+        <v>800048</v>
       </c>
       <c r="C516" s="104" t="s">
-        <v>4906</v>
+        <v>4902</v>
       </c>
       <c r="D516" s="104" t="s">
-        <v>4907</v>
+        <v>4903</v>
       </c>
       <c r="E516" s="117" t="s">
-        <v>5361</v>
+        <v>5360</v>
       </c>
       <c r="F516" s="112" t="s">
-        <v>5194</v>
-      </c>
-      <c r="G516" s="109" t="s">
-        <v>5195</v>
+        <v>5115</v>
+      </c>
+      <c r="G516" s="108" t="s">
+        <v>5116</v>
       </c>
       <c r="H516" s="104" t="s">
-        <v>4908</v>
+        <v>4904</v>
       </c>
       <c r="I516" s="104" t="s">
-        <v>4909</v>
+        <v>4905</v>
       </c>
       <c r="J516" s="116" t="s">
-        <v>5364</v>
+        <v>5363</v>
       </c>
       <c r="K516" s="108" t="s">
-        <v>5236</v>
+        <v>5235</v>
       </c>
       <c r="L516" s="109" t="s">
-        <v>5240</v>
+        <v>5238</v>
       </c>
       <c r="M516" s="99">
         <v>1</v>
@@ -75008,13 +75356,13 @@
         <v>13</v>
       </c>
       <c r="P516" s="85">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q516">
         <v>1064</v>
       </c>
       <c r="R516" s="100">
-        <v>94519</v>
+        <v>94518</v>
       </c>
       <c r="T516" s="85">
         <v>0</v>
@@ -75025,42 +75373,42 @@
       <c r="Z516" s="101"/>
       <c r="AA516" s="101"/>
     </row>
-    <row r="517" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="517" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B517" s="85">
-        <v>800050</v>
+        <v>800049</v>
       </c>
       <c r="C517" s="104" t="s">
-        <v>4910</v>
+        <v>4906</v>
       </c>
       <c r="D517" s="104" t="s">
-        <v>4911</v>
+        <v>4907</v>
       </c>
       <c r="E517" s="117" t="s">
-        <v>5362</v>
+        <v>5361</v>
       </c>
       <c r="F517" s="112" t="s">
-        <v>5196</v>
+        <v>5194</v>
       </c>
       <c r="G517" s="109" t="s">
-        <v>5197</v>
+        <v>5195</v>
       </c>
       <c r="H517" s="104" t="s">
-        <v>4912</v>
+        <v>4908</v>
       </c>
       <c r="I517" s="104" t="s">
-        <v>4913</v>
+        <v>4909</v>
       </c>
       <c r="J517" s="116" t="s">
-        <v>5365</v>
+        <v>5364</v>
       </c>
       <c r="K517" s="108" t="s">
-        <v>5237</v>
+        <v>5236</v>
       </c>
       <c r="L517" s="109" t="s">
-        <v>5239</v>
-      </c>
-      <c r="M517" s="103">
-        <v>2</v>
+        <v>5240</v>
+      </c>
+      <c r="M517" s="99">
+        <v>1</v>
       </c>
       <c r="N517" s="85">
         <v>0</v>
@@ -75069,13 +75417,13 @@
         <v>13</v>
       </c>
       <c r="P517" s="85">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q517">
         <v>1064</v>
       </c>
       <c r="R517" s="100">
-        <v>94520</v>
+        <v>94519</v>
       </c>
       <c r="T517" s="85">
         <v>0</v>
@@ -75086,42 +75434,42 @@
       <c r="Z517" s="101"/>
       <c r="AA517" s="101"/>
     </row>
-    <row r="518" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="518" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B518" s="85">
-        <v>800051</v>
+        <v>800050</v>
       </c>
       <c r="C518" s="104" t="s">
-        <v>4914</v>
-      </c>
-      <c r="D518" s="119" t="s">
-        <v>5448</v>
-      </c>
-      <c r="E518" s="108" t="s">
-        <v>5366</v>
+        <v>4910</v>
+      </c>
+      <c r="D518" s="104" t="s">
+        <v>4911</v>
+      </c>
+      <c r="E518" s="117" t="s">
+        <v>5362</v>
       </c>
       <c r="F518" s="112" t="s">
-        <v>5117</v>
-      </c>
-      <c r="G518" s="108" t="s">
-        <v>5118</v>
+        <v>5196</v>
+      </c>
+      <c r="G518" s="109" t="s">
+        <v>5197</v>
       </c>
       <c r="H518" s="104" t="s">
-        <v>4915</v>
-      </c>
-      <c r="I518" s="119" t="s">
-        <v>5451</v>
-      </c>
-      <c r="J518" s="108" t="s">
-        <v>5380</v>
+        <v>4912</v>
+      </c>
+      <c r="I518" s="104" t="s">
+        <v>4913</v>
+      </c>
+      <c r="J518" s="116" t="s">
+        <v>5365</v>
       </c>
       <c r="K518" s="108" t="s">
-        <v>5241</v>
-      </c>
-      <c r="L518" s="108" t="s">
-        <v>5242</v>
-      </c>
-      <c r="M518" s="99">
-        <v>1</v>
+        <v>5237</v>
+      </c>
+      <c r="L518" s="109" t="s">
+        <v>5239</v>
+      </c>
+      <c r="M518" s="103">
+        <v>2</v>
       </c>
       <c r="N518" s="85">
         <v>0</v>
@@ -75130,10 +75478,13 @@
         <v>13</v>
       </c>
       <c r="P518" s="85">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="Q518">
+        <v>1064</v>
       </c>
       <c r="R518" s="100">
-        <v>94521</v>
+        <v>94520</v>
       </c>
       <c r="T518" s="85">
         <v>0</v>
@@ -75146,37 +75497,37 @@
     </row>
     <row r="519" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B519" s="85">
-        <v>800052</v>
+        <v>800051</v>
       </c>
       <c r="C519" s="104" t="s">
-        <v>4916</v>
+        <v>4914</v>
       </c>
       <c r="D519" s="119" t="s">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="E519" s="108" t="s">
-        <v>5367</v>
+        <v>5366</v>
       </c>
       <c r="F519" s="112" t="s">
-        <v>5119</v>
+        <v>5117</v>
       </c>
       <c r="G519" s="108" t="s">
-        <v>5120</v>
+        <v>5118</v>
       </c>
       <c r="H519" s="104" t="s">
-        <v>4917</v>
+        <v>4915</v>
       </c>
       <c r="I519" s="119" t="s">
-        <v>5452</v>
+        <v>5451</v>
       </c>
       <c r="J519" s="108" t="s">
-        <v>5381</v>
+        <v>5380</v>
       </c>
       <c r="K519" s="108" t="s">
-        <v>5243</v>
+        <v>5241</v>
       </c>
       <c r="L519" s="108" t="s">
-        <v>5244</v>
+        <v>5242</v>
       </c>
       <c r="M519" s="99">
         <v>1</v>
@@ -75188,10 +75539,10 @@
         <v>13</v>
       </c>
       <c r="P519" s="85">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R519" s="100">
-        <v>94522</v>
+        <v>94521</v>
       </c>
       <c r="T519" s="85">
         <v>0</v>
@@ -75204,37 +75555,37 @@
     </row>
     <row r="520" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B520" s="85">
-        <v>800053</v>
+        <v>800052</v>
       </c>
       <c r="C520" s="104" t="s">
-        <v>4918</v>
-      </c>
-      <c r="D520" s="104" t="s">
-        <v>4919</v>
+        <v>4916</v>
+      </c>
+      <c r="D520" s="119" t="s">
+        <v>5449</v>
       </c>
       <c r="E520" s="108" t="s">
-        <v>5368</v>
+        <v>5367</v>
       </c>
       <c r="F520" s="112" t="s">
-        <v>5121</v>
+        <v>5119</v>
       </c>
       <c r="G520" s="108" t="s">
-        <v>5122</v>
+        <v>5120</v>
       </c>
       <c r="H520" s="104" t="s">
-        <v>4920</v>
-      </c>
-      <c r="I520" s="104" t="s">
-        <v>4921</v>
+        <v>4917</v>
+      </c>
+      <c r="I520" s="119" t="s">
+        <v>5452</v>
       </c>
       <c r="J520" s="108" t="s">
-        <v>5382</v>
+        <v>5381</v>
       </c>
       <c r="K520" s="108" t="s">
-        <v>5245</v>
+        <v>5243</v>
       </c>
       <c r="L520" s="108" t="s">
-        <v>5246</v>
+        <v>5244</v>
       </c>
       <c r="M520" s="99">
         <v>1</v>
@@ -75246,10 +75597,10 @@
         <v>13</v>
       </c>
       <c r="P520" s="85">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R520" s="100">
-        <v>94523</v>
+        <v>94522</v>
       </c>
       <c r="T520" s="85">
         <v>0</v>
@@ -75260,41 +75611,41 @@
       <c r="Z520" s="101"/>
       <c r="AA520" s="101"/>
     </row>
-    <row r="521" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="521" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B521" s="85">
-        <v>800054</v>
+        <v>800053</v>
       </c>
       <c r="C521" s="104" t="s">
-        <v>4922</v>
-      </c>
-      <c r="D521" s="119" t="s">
-        <v>5450</v>
+        <v>4918</v>
+      </c>
+      <c r="D521" s="104" t="s">
+        <v>4919</v>
       </c>
       <c r="E521" s="108" t="s">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="F521" s="112" t="s">
-        <v>5123</v>
+        <v>5121</v>
       </c>
       <c r="G521" s="108" t="s">
-        <v>5124</v>
+        <v>5122</v>
       </c>
       <c r="H521" s="104" t="s">
-        <v>4923</v>
-      </c>
-      <c r="I521" s="119" t="s">
-        <v>5453</v>
+        <v>4920</v>
+      </c>
+      <c r="I521" s="104" t="s">
+        <v>4921</v>
       </c>
       <c r="J521" s="108" t="s">
-        <v>5383</v>
+        <v>5382</v>
       </c>
       <c r="K521" s="108" t="s">
-        <v>5247</v>
+        <v>5245</v>
       </c>
       <c r="L521" s="108" t="s">
-        <v>5248</v>
-      </c>
-      <c r="M521" s="103">
+        <v>5246</v>
+      </c>
+      <c r="M521" s="99">
         <v>1</v>
       </c>
       <c r="N521" s="85">
@@ -75304,10 +75655,10 @@
         <v>13</v>
       </c>
       <c r="P521" s="85">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R521" s="100">
-        <v>94524</v>
+        <v>94523</v>
       </c>
       <c r="T521" s="85">
         <v>0</v>
@@ -75318,41 +75669,41 @@
       <c r="Z521" s="101"/>
       <c r="AA521" s="101"/>
     </row>
-    <row r="522" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="522" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B522" s="85">
-        <v>800055</v>
+        <v>800054</v>
       </c>
       <c r="C522" s="104" t="s">
-        <v>4924</v>
+        <v>4922</v>
       </c>
       <c r="D522" s="119" t="s">
-        <v>5455</v>
+        <v>5450</v>
       </c>
       <c r="E522" s="108" t="s">
-        <v>5370</v>
+        <v>5369</v>
       </c>
       <c r="F522" s="112" t="s">
-        <v>5125</v>
+        <v>5123</v>
       </c>
       <c r="G522" s="108" t="s">
-        <v>5126</v>
+        <v>5124</v>
       </c>
       <c r="H522" s="104" t="s">
-        <v>4925</v>
-      </c>
-      <c r="I522" s="104" t="s">
-        <v>4926</v>
+        <v>4923</v>
+      </c>
+      <c r="I522" s="119" t="s">
+        <v>5453</v>
       </c>
       <c r="J522" s="108" t="s">
-        <v>5384</v>
+        <v>5383</v>
       </c>
       <c r="K522" s="108" t="s">
-        <v>5249</v>
+        <v>5247</v>
       </c>
       <c r="L522" s="108" t="s">
-        <v>5250</v>
-      </c>
-      <c r="M522" s="99">
+        <v>5248</v>
+      </c>
+      <c r="M522" s="103">
         <v>1</v>
       </c>
       <c r="N522" s="85">
@@ -75362,10 +75713,10 @@
         <v>13</v>
       </c>
       <c r="P522" s="85">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R522" s="100">
-        <v>94525</v>
+        <v>94524</v>
       </c>
       <c r="T522" s="85">
         <v>0</v>
@@ -75378,40 +75729,40 @@
     </row>
     <row r="523" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B523" s="85">
-        <v>800056</v>
+        <v>800055</v>
       </c>
       <c r="C523" s="104" t="s">
-        <v>4927</v>
-      </c>
-      <c r="D523" s="104" t="s">
-        <v>4928</v>
+        <v>4924</v>
+      </c>
+      <c r="D523" s="119" t="s">
+        <v>5455</v>
       </c>
       <c r="E523" s="108" t="s">
-        <v>5371</v>
+        <v>5370</v>
       </c>
       <c r="F523" s="112" t="s">
-        <v>5127</v>
+        <v>5125</v>
       </c>
       <c r="G523" s="108" t="s">
-        <v>5128</v>
+        <v>5126</v>
       </c>
       <c r="H523" s="104" t="s">
-        <v>4929</v>
+        <v>4925</v>
       </c>
       <c r="I523" s="104" t="s">
-        <v>4930</v>
+        <v>4926</v>
       </c>
       <c r="J523" s="108" t="s">
-        <v>5385</v>
+        <v>5384</v>
       </c>
       <c r="K523" s="108" t="s">
-        <v>5251</v>
+        <v>5249</v>
       </c>
       <c r="L523" s="108" t="s">
-        <v>5252</v>
+        <v>5250</v>
       </c>
       <c r="M523" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N523" s="85">
         <v>0</v>
@@ -75420,10 +75771,10 @@
         <v>13</v>
       </c>
       <c r="P523" s="85">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R523" s="100">
-        <v>94526</v>
+        <v>94525</v>
       </c>
       <c r="T523" s="85">
         <v>0</v>
@@ -75436,40 +75787,40 @@
     </row>
     <row r="524" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B524" s="85">
-        <v>800057</v>
+        <v>800056</v>
       </c>
       <c r="C524" s="104" t="s">
-        <v>4931</v>
+        <v>4927</v>
       </c>
       <c r="D524" s="104" t="s">
-        <v>4932</v>
+        <v>4928</v>
       </c>
       <c r="E524" s="108" t="s">
-        <v>5372</v>
+        <v>5371</v>
       </c>
       <c r="F524" s="112" t="s">
-        <v>5129</v>
+        <v>5127</v>
       </c>
       <c r="G524" s="108" t="s">
-        <v>5130</v>
+        <v>5128</v>
       </c>
       <c r="H524" s="104" t="s">
-        <v>4933</v>
+        <v>4929</v>
       </c>
       <c r="I524" s="104" t="s">
-        <v>4934</v>
+        <v>4930</v>
       </c>
       <c r="J524" s="108" t="s">
-        <v>5386</v>
+        <v>5385</v>
       </c>
       <c r="K524" s="108" t="s">
-        <v>5253</v>
+        <v>5251</v>
       </c>
       <c r="L524" s="108" t="s">
-        <v>5254</v>
+        <v>5252</v>
       </c>
       <c r="M524" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N524" s="85">
         <v>0</v>
@@ -75478,10 +75829,10 @@
         <v>13</v>
       </c>
       <c r="P524" s="85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R524" s="100">
-        <v>94527</v>
+        <v>94526</v>
       </c>
       <c r="T524" s="85">
         <v>0</v>
@@ -75492,41 +75843,41 @@
       <c r="Z524" s="101"/>
       <c r="AA524" s="101"/>
     </row>
-    <row r="525" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="525" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B525" s="85">
-        <v>800058</v>
+        <v>800057</v>
       </c>
       <c r="C525" s="104" t="s">
-        <v>4935</v>
-      </c>
-      <c r="D525" s="119" t="s">
-        <v>5454</v>
+        <v>4931</v>
+      </c>
+      <c r="D525" s="104" t="s">
+        <v>4932</v>
       </c>
       <c r="E525" s="108" t="s">
-        <v>5373</v>
+        <v>5372</v>
       </c>
       <c r="F525" s="112" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="G525" s="108" t="s">
-        <v>5132</v>
+        <v>5130</v>
       </c>
       <c r="H525" s="104" t="s">
-        <v>4936</v>
+        <v>4933</v>
       </c>
       <c r="I525" s="104" t="s">
-        <v>4937</v>
+        <v>4934</v>
       </c>
       <c r="J525" s="108" t="s">
-        <v>5387</v>
+        <v>5386</v>
       </c>
       <c r="K525" s="108" t="s">
-        <v>5255</v>
+        <v>5253</v>
       </c>
       <c r="L525" s="108" t="s">
-        <v>5256</v>
-      </c>
-      <c r="M525" s="103">
+        <v>5254</v>
+      </c>
+      <c r="M525" s="99">
         <v>1</v>
       </c>
       <c r="N525" s="85">
@@ -75536,10 +75887,10 @@
         <v>13</v>
       </c>
       <c r="P525" s="85">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R525" s="100">
-        <v>94528</v>
+        <v>94527</v>
       </c>
       <c r="T525" s="85">
         <v>0</v>
@@ -75550,41 +75901,41 @@
       <c r="Z525" s="101"/>
       <c r="AA525" s="101"/>
     </row>
-    <row r="526" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="526" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B526" s="85">
-        <v>800059</v>
+        <v>800058</v>
       </c>
       <c r="C526" s="104" t="s">
-        <v>4938</v>
+        <v>4935</v>
       </c>
       <c r="D526" s="119" t="s">
-        <v>5456</v>
+        <v>5454</v>
       </c>
       <c r="E526" s="108" t="s">
-        <v>5374</v>
+        <v>5373</v>
       </c>
       <c r="F526" s="112" t="s">
-        <v>5133</v>
+        <v>5131</v>
       </c>
       <c r="G526" s="108" t="s">
-        <v>5134</v>
+        <v>5132</v>
       </c>
       <c r="H526" s="104" t="s">
-        <v>4939</v>
-      </c>
-      <c r="I526" s="119" t="s">
-        <v>5457</v>
+        <v>4936</v>
+      </c>
+      <c r="I526" s="104" t="s">
+        <v>4937</v>
       </c>
       <c r="J526" s="108" t="s">
-        <v>5388</v>
+        <v>5387</v>
       </c>
       <c r="K526" s="108" t="s">
-        <v>5257</v>
+        <v>5255</v>
       </c>
       <c r="L526" s="108" t="s">
-        <v>5258</v>
-      </c>
-      <c r="M526" s="99">
+        <v>5256</v>
+      </c>
+      <c r="M526" s="103">
         <v>1</v>
       </c>
       <c r="N526" s="85">
@@ -75594,10 +75945,10 @@
         <v>13</v>
       </c>
       <c r="P526" s="85">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R526" s="100">
-        <v>94529</v>
+        <v>94528</v>
       </c>
       <c r="T526" s="85">
         <v>0</v>
@@ -75610,40 +75961,40 @@
     </row>
     <row r="527" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B527" s="85">
-        <v>800060</v>
-      </c>
-      <c r="C527" s="105" t="s">
-        <v>4940</v>
-      </c>
-      <c r="D527" s="105" t="s">
-        <v>4941</v>
+        <v>800059</v>
+      </c>
+      <c r="C527" s="104" t="s">
+        <v>4938</v>
+      </c>
+      <c r="D527" s="119" t="s">
+        <v>5456</v>
       </c>
       <c r="E527" s="108" t="s">
-        <v>5375</v>
+        <v>5374</v>
       </c>
       <c r="F527" s="112" t="s">
-        <v>5135</v>
+        <v>5133</v>
       </c>
       <c r="G527" s="108" t="s">
-        <v>5136</v>
+        <v>5134</v>
       </c>
       <c r="H527" s="104" t="s">
-        <v>4942</v>
-      </c>
-      <c r="I527" s="104" t="s">
-        <v>4943</v>
+        <v>4939</v>
+      </c>
+      <c r="I527" s="119" t="s">
+        <v>5457</v>
       </c>
       <c r="J527" s="108" t="s">
-        <v>5389</v>
+        <v>5388</v>
       </c>
       <c r="K527" s="108" t="s">
-        <v>5259</v>
+        <v>5257</v>
       </c>
       <c r="L527" s="108" t="s">
-        <v>5260</v>
+        <v>5258</v>
       </c>
       <c r="M527" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N527" s="85">
         <v>0</v>
@@ -75652,10 +76003,10 @@
         <v>13</v>
       </c>
       <c r="P527" s="85">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R527" s="100">
-        <v>94530</v>
+        <v>94529</v>
       </c>
       <c r="T527" s="85">
         <v>0</v>
@@ -75668,37 +76019,37 @@
     </row>
     <row r="528" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B528" s="85">
-        <v>800061</v>
-      </c>
-      <c r="C528" s="104" t="s">
-        <v>4944</v>
-      </c>
-      <c r="D528" s="104" t="s">
-        <v>4945</v>
+        <v>800060</v>
+      </c>
+      <c r="C528" s="105" t="s">
+        <v>4940</v>
+      </c>
+      <c r="D528" s="105" t="s">
+        <v>4941</v>
       </c>
       <c r="E528" s="108" t="s">
-        <v>5376</v>
+        <v>5375</v>
       </c>
       <c r="F528" s="112" t="s">
-        <v>5137</v>
+        <v>5135</v>
       </c>
       <c r="G528" s="108" t="s">
-        <v>5138</v>
+        <v>5136</v>
       </c>
       <c r="H528" s="104" t="s">
-        <v>4946</v>
+        <v>4942</v>
       </c>
       <c r="I528" s="104" t="s">
-        <v>4947</v>
+        <v>4943</v>
       </c>
       <c r="J528" s="108" t="s">
-        <v>5390</v>
+        <v>5389</v>
       </c>
       <c r="K528" s="108" t="s">
-        <v>5261</v>
+        <v>5259</v>
       </c>
       <c r="L528" s="108" t="s">
-        <v>5262</v>
+        <v>5260</v>
       </c>
       <c r="M528" s="99">
         <v>2</v>
@@ -75710,10 +76061,10 @@
         <v>13</v>
       </c>
       <c r="P528" s="85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R528" s="100">
-        <v>94531</v>
+        <v>94530</v>
       </c>
       <c r="T528" s="85">
         <v>0</v>
@@ -75724,41 +76075,41 @@
       <c r="Z528" s="101"/>
       <c r="AA528" s="101"/>
     </row>
-    <row r="529" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="529" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B529" s="85">
-        <v>800062</v>
+        <v>800061</v>
       </c>
       <c r="C529" s="104" t="s">
-        <v>4948</v>
+        <v>4944</v>
       </c>
       <c r="D529" s="104" t="s">
-        <v>4949</v>
+        <v>4945</v>
       </c>
       <c r="E529" s="108" t="s">
-        <v>5377</v>
+        <v>5376</v>
       </c>
       <c r="F529" s="112" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="G529" s="108" t="s">
-        <v>5140</v>
+        <v>5138</v>
       </c>
       <c r="H529" s="104" t="s">
-        <v>4950</v>
+        <v>4946</v>
       </c>
       <c r="I529" s="104" t="s">
-        <v>4951</v>
+        <v>4947</v>
       </c>
       <c r="J529" s="108" t="s">
-        <v>5391</v>
+        <v>5390</v>
       </c>
       <c r="K529" s="108" t="s">
-        <v>5263</v>
+        <v>5261</v>
       </c>
       <c r="L529" s="108" t="s">
-        <v>5264</v>
-      </c>
-      <c r="M529" s="103">
+        <v>5262</v>
+      </c>
+      <c r="M529" s="99">
         <v>2</v>
       </c>
       <c r="N529" s="85">
@@ -75768,10 +76119,10 @@
         <v>13</v>
       </c>
       <c r="P529" s="85">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R529" s="100">
-        <v>94532</v>
+        <v>94531</v>
       </c>
       <c r="T529" s="85">
         <v>0</v>
@@ -75782,41 +76133,41 @@
       <c r="Z529" s="101"/>
       <c r="AA529" s="101"/>
     </row>
-    <row r="530" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="530" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B530" s="85">
-        <v>800063</v>
+        <v>800062</v>
       </c>
       <c r="C530" s="104" t="s">
-        <v>4952</v>
+        <v>4948</v>
       </c>
       <c r="D530" s="104" t="s">
-        <v>4952</v>
+        <v>4949</v>
       </c>
       <c r="E530" s="108" t="s">
-        <v>5378</v>
+        <v>5377</v>
       </c>
       <c r="F530" s="112" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="G530" s="108" t="s">
-        <v>5142</v>
+        <v>5140</v>
       </c>
       <c r="H530" s="104" t="s">
-        <v>4953</v>
+        <v>4950</v>
       </c>
       <c r="I530" s="104" t="s">
-        <v>4954</v>
+        <v>4951</v>
       </c>
       <c r="J530" s="108" t="s">
-        <v>5392</v>
+        <v>5391</v>
       </c>
       <c r="K530" s="108" t="s">
-        <v>5265</v>
+        <v>5263</v>
       </c>
       <c r="L530" s="108" t="s">
-        <v>5266</v>
-      </c>
-      <c r="M530" s="99">
+        <v>5264</v>
+      </c>
+      <c r="M530" s="103">
         <v>2</v>
       </c>
       <c r="N530" s="85">
@@ -75826,10 +76177,10 @@
         <v>13</v>
       </c>
       <c r="P530" s="85">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R530" s="100">
-        <v>94533</v>
+        <v>94532</v>
       </c>
       <c r="T530" s="85">
         <v>0</v>
@@ -75842,37 +76193,37 @@
     </row>
     <row r="531" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B531" s="85">
-        <v>800064</v>
+        <v>800063</v>
       </c>
       <c r="C531" s="104" t="s">
-        <v>4955</v>
+        <v>4952</v>
       </c>
       <c r="D531" s="104" t="s">
-        <v>4955</v>
+        <v>4952</v>
       </c>
       <c r="E531" s="108" t="s">
-        <v>5379</v>
+        <v>5378</v>
       </c>
       <c r="F531" s="112" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="G531" s="108" t="s">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="H531" s="104" t="s">
-        <v>4956</v>
+        <v>4953</v>
       </c>
       <c r="I531" s="104" t="s">
-        <v>4957</v>
+        <v>4954</v>
       </c>
       <c r="J531" s="108" t="s">
-        <v>5393</v>
+        <v>5392</v>
       </c>
       <c r="K531" s="108" t="s">
-        <v>5267</v>
+        <v>5265</v>
       </c>
       <c r="L531" s="108" t="s">
-        <v>5268</v>
+        <v>5266</v>
       </c>
       <c r="M531" s="99">
         <v>2</v>
@@ -75884,10 +76235,10 @@
         <v>13</v>
       </c>
       <c r="P531" s="85">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R531" s="100">
-        <v>94534</v>
+        <v>94533</v>
       </c>
       <c r="T531" s="85">
         <v>0</v>
@@ -75898,42 +76249,42 @@
       <c r="Z531" s="101"/>
       <c r="AA531" s="101"/>
     </row>
-    <row r="532" spans="2:27" s="85" customFormat="1" ht="16.5">
+    <row r="532" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B532" s="85">
-        <v>800065</v>
+        <v>800064</v>
       </c>
       <c r="C532" s="104" t="s">
-        <v>4958</v>
+        <v>4955</v>
       </c>
       <c r="D532" s="104" t="s">
-        <v>4959</v>
+        <v>4955</v>
       </c>
       <c r="E532" s="108" t="s">
-        <v>5394</v>
-      </c>
-      <c r="F532" s="108" t="s">
-        <v>5145</v>
+        <v>5379</v>
+      </c>
+      <c r="F532" s="112" t="s">
+        <v>5143</v>
       </c>
       <c r="G532" s="108" t="s">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="H532" s="104" t="s">
-        <v>4960</v>
+        <v>4956</v>
       </c>
       <c r="I532" s="104" t="s">
-        <v>4961</v>
+        <v>4957</v>
       </c>
       <c r="J532" s="108" t="s">
-        <v>5398</v>
+        <v>5393</v>
       </c>
       <c r="K532" s="108" t="s">
-        <v>5269</v>
+        <v>5267</v>
       </c>
       <c r="L532" s="108" t="s">
-        <v>5270</v>
+        <v>5268</v>
       </c>
       <c r="M532" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N532" s="85">
         <v>0</v>
@@ -75942,10 +76293,10 @@
         <v>13</v>
       </c>
       <c r="P532" s="85">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R532" s="100">
-        <v>94535</v>
+        <v>94534</v>
       </c>
       <c r="T532" s="85">
         <v>0</v>
@@ -75956,41 +76307,41 @@
       <c r="Z532" s="101"/>
       <c r="AA532" s="101"/>
     </row>
-    <row r="533" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="533" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B533" s="85">
-        <v>800066</v>
+        <v>800065</v>
       </c>
       <c r="C533" s="104" t="s">
-        <v>4962</v>
+        <v>4958</v>
       </c>
       <c r="D533" s="104" t="s">
-        <v>4963</v>
+        <v>4959</v>
       </c>
       <c r="E533" s="108" t="s">
-        <v>5395</v>
+        <v>5394</v>
       </c>
       <c r="F533" s="108" t="s">
-        <v>5147</v>
+        <v>5145</v>
       </c>
       <c r="G533" s="108" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="H533" s="104" t="s">
-        <v>4964</v>
+        <v>4960</v>
       </c>
       <c r="I533" s="104" t="s">
-        <v>4965</v>
+        <v>4961</v>
       </c>
       <c r="J533" s="108" t="s">
-        <v>5399</v>
+        <v>5398</v>
       </c>
       <c r="K533" s="108" t="s">
-        <v>5271</v>
+        <v>5269</v>
       </c>
       <c r="L533" s="108" t="s">
-        <v>5272</v>
-      </c>
-      <c r="M533" s="103">
+        <v>5270</v>
+      </c>
+      <c r="M533" s="99">
         <v>1</v>
       </c>
       <c r="N533" s="85">
@@ -76000,13 +76351,10 @@
         <v>13</v>
       </c>
       <c r="P533" s="85">
-        <v>36</v>
-      </c>
-      <c r="Q533">
-        <v>1065</v>
+        <v>35</v>
       </c>
       <c r="R533" s="100">
-        <v>94536</v>
+        <v>94535</v>
       </c>
       <c r="T533" s="85">
         <v>0</v>
@@ -76017,42 +76365,42 @@
       <c r="Z533" s="101"/>
       <c r="AA533" s="101"/>
     </row>
-    <row r="534" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="534" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B534" s="85">
-        <v>800067</v>
+        <v>800066</v>
       </c>
       <c r="C534" s="104" t="s">
-        <v>4966</v>
+        <v>4962</v>
       </c>
       <c r="D534" s="104" t="s">
-        <v>4967</v>
+        <v>4963</v>
       </c>
       <c r="E534" s="108" t="s">
-        <v>5396</v>
+        <v>5395</v>
       </c>
       <c r="F534" s="108" t="s">
-        <v>5149</v>
+        <v>5147</v>
       </c>
       <c r="G534" s="108" t="s">
-        <v>5150</v>
+        <v>5148</v>
       </c>
       <c r="H534" s="104" t="s">
-        <v>4968</v>
+        <v>4964</v>
       </c>
       <c r="I534" s="104" t="s">
-        <v>4969</v>
+        <v>4965</v>
       </c>
       <c r="J534" s="108" t="s">
-        <v>5400</v>
+        <v>5399</v>
       </c>
       <c r="K534" s="108" t="s">
-        <v>5273</v>
+        <v>5271</v>
       </c>
       <c r="L534" s="108" t="s">
-        <v>5274</v>
-      </c>
-      <c r="M534" s="99">
-        <v>2</v>
+        <v>5272</v>
+      </c>
+      <c r="M534" s="103">
+        <v>1</v>
       </c>
       <c r="N534" s="85">
         <v>0</v>
@@ -76061,13 +76409,13 @@
         <v>13</v>
       </c>
       <c r="P534" s="85">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q534">
         <v>1065</v>
       </c>
       <c r="R534" s="100">
-        <v>94537</v>
+        <v>94536</v>
       </c>
       <c r="T534" s="85">
         <v>0</v>
@@ -76080,40 +76428,40 @@
     </row>
     <row r="535" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B535" s="85">
-        <v>800068</v>
+        <v>800067</v>
       </c>
       <c r="C535" s="104" t="s">
-        <v>4970</v>
+        <v>4966</v>
       </c>
       <c r="D535" s="104" t="s">
-        <v>4971</v>
+        <v>4967</v>
       </c>
       <c r="E535" s="108" t="s">
-        <v>5397</v>
+        <v>5396</v>
       </c>
       <c r="F535" s="108" t="s">
-        <v>5151</v>
+        <v>5149</v>
       </c>
       <c r="G535" s="108" t="s">
-        <v>5152</v>
+        <v>5150</v>
       </c>
       <c r="H535" s="104" t="s">
-        <v>4972</v>
+        <v>4968</v>
       </c>
       <c r="I535" s="104" t="s">
-        <v>4973</v>
+        <v>4969</v>
       </c>
       <c r="J535" s="108" t="s">
-        <v>5401</v>
+        <v>5400</v>
       </c>
       <c r="K535" s="108" t="s">
-        <v>5275</v>
+        <v>5273</v>
       </c>
       <c r="L535" s="108" t="s">
-        <v>5276</v>
+        <v>5274</v>
       </c>
       <c r="M535" s="99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N535" s="85">
         <v>0</v>
@@ -76122,13 +76470,13 @@
         <v>13</v>
       </c>
       <c r="P535" s="85">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q535">
         <v>1065</v>
       </c>
       <c r="R535" s="100">
-        <v>94538</v>
+        <v>94537</v>
       </c>
       <c r="T535" s="85">
         <v>0</v>
@@ -76141,40 +76489,40 @@
     </row>
     <row r="536" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B536" s="85">
-        <v>800069</v>
+        <v>800068</v>
       </c>
       <c r="C536" s="104" t="s">
-        <v>4974</v>
+        <v>4970</v>
       </c>
       <c r="D536" s="104" t="s">
-        <v>4975</v>
-      </c>
-      <c r="E536" s="117" t="s">
-        <v>5402</v>
+        <v>4971</v>
+      </c>
+      <c r="E536" s="108" t="s">
+        <v>5397</v>
       </c>
       <c r="F536" s="108" t="s">
-        <v>5153</v>
+        <v>5151</v>
       </c>
       <c r="G536" s="108" t="s">
-        <v>5154</v>
+        <v>5152</v>
       </c>
       <c r="H536" s="104" t="s">
-        <v>4976</v>
+        <v>4972</v>
       </c>
       <c r="I536" s="104" t="s">
-        <v>4977</v>
-      </c>
-      <c r="J536" s="116" t="s">
-        <v>5437</v>
+        <v>4973</v>
+      </c>
+      <c r="J536" s="108" t="s">
+        <v>5401</v>
       </c>
       <c r="K536" s="108" t="s">
-        <v>5277</v>
-      </c>
-      <c r="L536" s="109" t="s">
-        <v>5280</v>
+        <v>5275</v>
+      </c>
+      <c r="L536" s="108" t="s">
+        <v>5276</v>
       </c>
       <c r="M536" s="99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N536" s="85">
         <v>0</v>
@@ -76183,13 +76531,13 @@
         <v>13</v>
       </c>
       <c r="P536" s="85">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q536">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R536" s="100">
-        <v>94539</v>
+        <v>94538</v>
       </c>
       <c r="T536" s="85">
         <v>0</v>
@@ -76200,41 +76548,41 @@
       <c r="Z536" s="101"/>
       <c r="AA536" s="101"/>
     </row>
-    <row r="537" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="537" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B537" s="85">
-        <v>800070</v>
+        <v>800069</v>
       </c>
       <c r="C537" s="104" t="s">
-        <v>4978</v>
+        <v>4974</v>
       </c>
       <c r="D537" s="104" t="s">
-        <v>4979</v>
+        <v>4975</v>
       </c>
       <c r="E537" s="117" t="s">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="F537" s="108" t="s">
-        <v>5200</v>
-      </c>
-      <c r="G537" s="109" t="s">
-        <v>5201</v>
+        <v>5153</v>
+      </c>
+      <c r="G537" s="108" t="s">
+        <v>5154</v>
       </c>
       <c r="H537" s="104" t="s">
-        <v>4980</v>
+        <v>4976</v>
       </c>
       <c r="I537" s="104" t="s">
-        <v>4981</v>
+        <v>4977</v>
       </c>
       <c r="J537" s="116" t="s">
-        <v>5438</v>
+        <v>5437</v>
       </c>
       <c r="K537" s="108" t="s">
-        <v>5278</v>
+        <v>5277</v>
       </c>
       <c r="L537" s="109" t="s">
-        <v>5281</v>
-      </c>
-      <c r="M537" s="103">
+        <v>5280</v>
+      </c>
+      <c r="M537" s="99">
         <v>1</v>
       </c>
       <c r="N537" s="85">
@@ -76244,13 +76592,13 @@
         <v>13</v>
       </c>
       <c r="P537" s="85">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q537">
         <v>1066</v>
       </c>
       <c r="R537" s="100">
-        <v>94540</v>
+        <v>94539</v>
       </c>
       <c r="T537" s="85">
         <v>0</v>
@@ -76261,42 +76609,42 @@
       <c r="Z537" s="101"/>
       <c r="AA537" s="101"/>
     </row>
-    <row r="538" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="538" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B538" s="85">
-        <v>800071</v>
+        <v>800070</v>
       </c>
       <c r="C538" s="104" t="s">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="D538" s="104" t="s">
-        <v>4983</v>
+        <v>4979</v>
       </c>
       <c r="E538" s="117" t="s">
-        <v>5404</v>
+        <v>5403</v>
       </c>
       <c r="F538" s="108" t="s">
-        <v>5198</v>
+        <v>5200</v>
       </c>
       <c r="G538" s="109" t="s">
-        <v>5199</v>
+        <v>5201</v>
       </c>
       <c r="H538" s="104" t="s">
-        <v>4984</v>
+        <v>4980</v>
       </c>
       <c r="I538" s="104" t="s">
-        <v>4985</v>
+        <v>4981</v>
       </c>
       <c r="J538" s="116" t="s">
-        <v>5439</v>
+        <v>5438</v>
       </c>
       <c r="K538" s="108" t="s">
-        <v>5279</v>
+        <v>5278</v>
       </c>
       <c r="L538" s="109" t="s">
-        <v>5282</v>
-      </c>
-      <c r="M538" s="99">
-        <v>2</v>
+        <v>5281</v>
+      </c>
+      <c r="M538" s="103">
+        <v>1</v>
       </c>
       <c r="N538" s="85">
         <v>0</v>
@@ -76305,13 +76653,13 @@
         <v>13</v>
       </c>
       <c r="P538" s="85">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q538">
         <v>1066</v>
       </c>
       <c r="R538" s="100">
-        <v>94541</v>
+        <v>94540</v>
       </c>
       <c r="T538" s="85">
         <v>0</v>
@@ -76324,40 +76672,40 @@
     </row>
     <row r="539" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B539" s="85">
-        <v>800072</v>
+        <v>800071</v>
       </c>
       <c r="C539" s="104" t="s">
-        <v>4986</v>
+        <v>4982</v>
       </c>
       <c r="D539" s="104" t="s">
-        <v>4987</v>
+        <v>4983</v>
       </c>
       <c r="E539" s="117" t="s">
-        <v>5405</v>
+        <v>5404</v>
       </c>
       <c r="F539" s="108" t="s">
-        <v>5204</v>
-      </c>
-      <c r="G539" s="108" t="s">
-        <v>5155</v>
+        <v>5198</v>
+      </c>
+      <c r="G539" s="109" t="s">
+        <v>5199</v>
       </c>
       <c r="H539" s="104" t="s">
-        <v>4988</v>
+        <v>4984</v>
       </c>
       <c r="I539" s="104" t="s">
-        <v>4989</v>
+        <v>4985</v>
       </c>
       <c r="J539" s="116" t="s">
-        <v>5440</v>
+        <v>5439</v>
       </c>
       <c r="K539" s="108" t="s">
-        <v>5283</v>
+        <v>5279</v>
       </c>
       <c r="L539" s="109" t="s">
-        <v>5284</v>
+        <v>5282</v>
       </c>
       <c r="M539" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N539" s="85">
         <v>0</v>
@@ -76366,13 +76714,13 @@
         <v>13</v>
       </c>
       <c r="P539" s="85">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q539">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R539" s="100">
-        <v>94542</v>
+        <v>94541</v>
       </c>
       <c r="T539" s="85">
         <v>0</v>
@@ -76385,37 +76733,37 @@
     </row>
     <row r="540" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B540" s="85">
-        <v>800073</v>
+        <v>800072</v>
       </c>
       <c r="C540" s="104" t="s">
-        <v>4990</v>
+        <v>4986</v>
       </c>
       <c r="D540" s="104" t="s">
-        <v>4991</v>
+        <v>4987</v>
       </c>
       <c r="E540" s="117" t="s">
-        <v>5406</v>
+        <v>5405</v>
       </c>
       <c r="F540" s="108" t="s">
-        <v>5202</v>
-      </c>
-      <c r="G540" s="109" t="s">
-        <v>5203</v>
+        <v>5204</v>
+      </c>
+      <c r="G540" s="108" t="s">
+        <v>5155</v>
       </c>
       <c r="H540" s="104" t="s">
-        <v>4992</v>
+        <v>4988</v>
       </c>
       <c r="I540" s="104" t="s">
-        <v>4993</v>
+        <v>4989</v>
       </c>
       <c r="J540" s="116" t="s">
-        <v>5441</v>
+        <v>5440</v>
       </c>
       <c r="K540" s="108" t="s">
-        <v>5285</v>
+        <v>5283</v>
       </c>
       <c r="L540" s="109" t="s">
-        <v>5286</v>
+        <v>5284</v>
       </c>
       <c r="M540" s="99">
         <v>1</v>
@@ -76427,13 +76775,13 @@
         <v>13</v>
       </c>
       <c r="P540" s="85">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q540">
         <v>1067</v>
       </c>
       <c r="R540" s="100">
-        <v>94543</v>
+        <v>94542</v>
       </c>
       <c r="T540" s="85">
         <v>0</v>
@@ -76444,42 +76792,42 @@
       <c r="Z540" s="101"/>
       <c r="AA540" s="101"/>
     </row>
-    <row r="541" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="541" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B541" s="85">
-        <v>800074</v>
+        <v>800073</v>
       </c>
       <c r="C541" s="104" t="s">
-        <v>4994</v>
+        <v>4990</v>
       </c>
       <c r="D541" s="104" t="s">
-        <v>4995</v>
+        <v>4991</v>
       </c>
       <c r="E541" s="117" t="s">
-        <v>5407</v>
+        <v>5406</v>
       </c>
       <c r="F541" s="108" t="s">
-        <v>5205</v>
+        <v>5202</v>
       </c>
       <c r="G541" s="109" t="s">
-        <v>5206</v>
+        <v>5203</v>
       </c>
       <c r="H541" s="104" t="s">
-        <v>4996</v>
+        <v>4992</v>
       </c>
       <c r="I541" s="104" t="s">
-        <v>4997</v>
+        <v>4993</v>
       </c>
       <c r="J541" s="116" t="s">
-        <v>5442</v>
+        <v>5441</v>
       </c>
       <c r="K541" s="108" t="s">
-        <v>5287</v>
+        <v>5285</v>
       </c>
       <c r="L541" s="109" t="s">
-        <v>5288</v>
-      </c>
-      <c r="M541" s="103">
-        <v>2</v>
+        <v>5286</v>
+      </c>
+      <c r="M541" s="99">
+        <v>1</v>
       </c>
       <c r="N541" s="85">
         <v>0</v>
@@ -76488,13 +76836,13 @@
         <v>13</v>
       </c>
       <c r="P541" s="85">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q541">
         <v>1067</v>
       </c>
       <c r="R541" s="100">
-        <v>94544</v>
+        <v>94543</v>
       </c>
       <c r="T541" s="85">
         <v>0</v>
@@ -76505,42 +76853,42 @@
       <c r="Z541" s="101"/>
       <c r="AA541" s="101"/>
     </row>
-    <row r="542" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="542" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B542" s="85">
-        <v>800075</v>
+        <v>800074</v>
       </c>
       <c r="C542" s="104" t="s">
-        <v>4998</v>
+        <v>4994</v>
       </c>
       <c r="D542" s="104" t="s">
-        <v>4999</v>
+        <v>4995</v>
       </c>
       <c r="E542" s="117" t="s">
-        <v>5408</v>
+        <v>5407</v>
       </c>
       <c r="F542" s="108" t="s">
-        <v>5156</v>
-      </c>
-      <c r="G542" s="108" t="s">
-        <v>5157</v>
+        <v>5205</v>
+      </c>
+      <c r="G542" s="109" t="s">
+        <v>5206</v>
       </c>
       <c r="H542" s="104" t="s">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="I542" s="104" t="s">
-        <v>5001</v>
+        <v>4997</v>
       </c>
       <c r="J542" s="116" t="s">
-        <v>5443</v>
+        <v>5442</v>
       </c>
       <c r="K542" s="108" t="s">
-        <v>5289</v>
+        <v>5287</v>
       </c>
       <c r="L542" s="109" t="s">
-        <v>5292</v>
-      </c>
-      <c r="M542" s="99">
-        <v>1</v>
+        <v>5288</v>
+      </c>
+      <c r="M542" s="103">
+        <v>2</v>
       </c>
       <c r="N542" s="85">
         <v>0</v>
@@ -76549,13 +76897,13 @@
         <v>13</v>
       </c>
       <c r="P542" s="85">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q542">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R542" s="100">
-        <v>94545</v>
+        <v>94544</v>
       </c>
       <c r="T542" s="85">
         <v>0</v>
@@ -76568,37 +76916,37 @@
     </row>
     <row r="543" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B543" s="85">
-        <v>800076</v>
+        <v>800075</v>
       </c>
       <c r="C543" s="104" t="s">
-        <v>5002</v>
+        <v>4998</v>
       </c>
       <c r="D543" s="104" t="s">
-        <v>5003</v>
+        <v>4999</v>
       </c>
       <c r="E543" s="117" t="s">
-        <v>5409</v>
+        <v>5408</v>
       </c>
       <c r="F543" s="108" t="s">
-        <v>5209</v>
-      </c>
-      <c r="G543" s="109" t="s">
-        <v>5210</v>
+        <v>5156</v>
+      </c>
+      <c r="G543" s="108" t="s">
+        <v>5157</v>
       </c>
       <c r="H543" s="104" t="s">
-        <v>5004</v>
+        <v>5000</v>
       </c>
       <c r="I543" s="104" t="s">
-        <v>5005</v>
+        <v>5001</v>
       </c>
       <c r="J543" s="116" t="s">
-        <v>5444</v>
+        <v>5443</v>
       </c>
       <c r="K543" s="108" t="s">
-        <v>5290</v>
+        <v>5289</v>
       </c>
       <c r="L543" s="109" t="s">
-        <v>5294</v>
+        <v>5292</v>
       </c>
       <c r="M543" s="99">
         <v>1</v>
@@ -76610,13 +76958,13 @@
         <v>13</v>
       </c>
       <c r="P543" s="85">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q543">
         <v>1068</v>
       </c>
       <c r="R543" s="100">
-        <v>94546</v>
+        <v>94545</v>
       </c>
       <c r="T543" s="85">
         <v>0</v>
@@ -76629,40 +76977,40 @@
     </row>
     <row r="544" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B544" s="85">
-        <v>800077</v>
+        <v>800076</v>
       </c>
       <c r="C544" s="104" t="s">
-        <v>5006</v>
+        <v>5002</v>
       </c>
       <c r="D544" s="104" t="s">
-        <v>5007</v>
+        <v>5003</v>
       </c>
       <c r="E544" s="117" t="s">
-        <v>5410</v>
+        <v>5409</v>
       </c>
       <c r="F544" s="108" t="s">
-        <v>5207</v>
+        <v>5209</v>
       </c>
       <c r="G544" s="109" t="s">
-        <v>5208</v>
+        <v>5210</v>
       </c>
       <c r="H544" s="104" t="s">
-        <v>5008</v>
+        <v>5004</v>
       </c>
       <c r="I544" s="104" t="s">
-        <v>5009</v>
+        <v>5005</v>
       </c>
       <c r="J544" s="116" t="s">
-        <v>5445</v>
+        <v>5444</v>
       </c>
       <c r="K544" s="108" t="s">
-        <v>5291</v>
+        <v>5290</v>
       </c>
       <c r="L544" s="109" t="s">
-        <v>5293</v>
+        <v>5294</v>
       </c>
       <c r="M544" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N544" s="85">
         <v>0</v>
@@ -76671,13 +77019,13 @@
         <v>13</v>
       </c>
       <c r="P544" s="85">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q544">
         <v>1068</v>
       </c>
       <c r="R544" s="100">
-        <v>94547</v>
+        <v>94546</v>
       </c>
       <c r="T544" s="85">
         <v>0</v>
@@ -76688,42 +77036,42 @@
       <c r="Z544" s="101"/>
       <c r="AA544" s="101"/>
     </row>
-    <row r="545" spans="1:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="545" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B545" s="85">
-        <v>800078</v>
+        <v>800077</v>
       </c>
       <c r="C545" s="104" t="s">
-        <v>5010</v>
+        <v>5006</v>
       </c>
       <c r="D545" s="104" t="s">
-        <v>5011</v>
+        <v>5007</v>
       </c>
       <c r="E545" s="117" t="s">
-        <v>5411</v>
+        <v>5410</v>
       </c>
       <c r="F545" s="108" t="s">
-        <v>5182</v>
-      </c>
-      <c r="G545" s="108" t="s">
-        <v>5158</v>
+        <v>5207</v>
+      </c>
+      <c r="G545" s="109" t="s">
+        <v>5208</v>
       </c>
       <c r="H545" s="104" t="s">
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="I545" s="104" t="s">
-        <v>5013</v>
+        <v>5009</v>
       </c>
       <c r="J545" s="116" t="s">
-        <v>5446</v>
+        <v>5445</v>
       </c>
       <c r="K545" s="108" t="s">
-        <v>5295</v>
+        <v>5291</v>
       </c>
       <c r="L545" s="109" t="s">
-        <v>5297</v>
-      </c>
-      <c r="M545" s="103">
-        <v>1</v>
+        <v>5293</v>
+      </c>
+      <c r="M545" s="99">
+        <v>2</v>
       </c>
       <c r="N545" s="85">
         <v>0</v>
@@ -76732,13 +77080,13 @@
         <v>13</v>
       </c>
       <c r="P545" s="85">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q545">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R545" s="100">
-        <v>94548</v>
+        <v>94547</v>
       </c>
       <c r="T545" s="85">
         <v>0</v>
@@ -76749,42 +77097,42 @@
       <c r="Z545" s="101"/>
       <c r="AA545" s="101"/>
     </row>
-    <row r="546" spans="1:27" s="85" customFormat="1" ht="33">
+    <row r="546" spans="1:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B546" s="85">
-        <v>800079</v>
+        <v>800078</v>
       </c>
       <c r="C546" s="104" t="s">
-        <v>5014</v>
+        <v>5010</v>
       </c>
       <c r="D546" s="104" t="s">
-        <v>5015</v>
+        <v>5011</v>
       </c>
       <c r="E546" s="117" t="s">
-        <v>5412</v>
+        <v>5411</v>
       </c>
       <c r="F546" s="108" t="s">
-        <v>5211</v>
-      </c>
-      <c r="G546" s="109" t="s">
-        <v>5212</v>
+        <v>5182</v>
+      </c>
+      <c r="G546" s="108" t="s">
+        <v>5158</v>
       </c>
       <c r="H546" s="104" t="s">
-        <v>5016</v>
+        <v>5012</v>
       </c>
       <c r="I546" s="104" t="s">
-        <v>5017</v>
+        <v>5013</v>
       </c>
       <c r="J546" s="116" t="s">
-        <v>5447</v>
+        <v>5446</v>
       </c>
       <c r="K546" s="108" t="s">
-        <v>5296</v>
+        <v>5295</v>
       </c>
       <c r="L546" s="109" t="s">
-        <v>5298</v>
-      </c>
-      <c r="M546" s="99">
-        <v>2</v>
+        <v>5297</v>
+      </c>
+      <c r="M546" s="103">
+        <v>1</v>
       </c>
       <c r="N546" s="85">
         <v>0</v>
@@ -76793,13 +77141,13 @@
         <v>13</v>
       </c>
       <c r="P546" s="85">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q546">
         <v>1069</v>
       </c>
       <c r="R546" s="100">
-        <v>94549</v>
+        <v>94548</v>
       </c>
       <c r="T546" s="85">
         <v>0</v>
@@ -76812,40 +77160,40 @@
     </row>
     <row r="547" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B547" s="85">
-        <v>800080</v>
+        <v>800079</v>
       </c>
       <c r="C547" s="104" t="s">
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="D547" s="104" t="s">
-        <v>5019</v>
+        <v>5015</v>
       </c>
       <c r="E547" s="117" t="s">
-        <v>5413</v>
+        <v>5412</v>
       </c>
       <c r="F547" s="108" t="s">
-        <v>5159</v>
-      </c>
-      <c r="G547" s="108" t="s">
-        <v>5160</v>
+        <v>5211</v>
+      </c>
+      <c r="G547" s="109" t="s">
+        <v>5212</v>
       </c>
       <c r="H547" s="104" t="s">
-        <v>5020</v>
+        <v>5016</v>
       </c>
       <c r="I547" s="104" t="s">
-        <v>5021</v>
-      </c>
-      <c r="J547" s="98" t="s">
-        <v>5415</v>
+        <v>5017</v>
+      </c>
+      <c r="J547" s="116" t="s">
+        <v>5447</v>
       </c>
       <c r="K547" s="108" t="s">
-        <v>5299</v>
-      </c>
-      <c r="L547" s="108" t="s">
-        <v>5300</v>
+        <v>5296</v>
+      </c>
+      <c r="L547" s="109" t="s">
+        <v>5298</v>
       </c>
       <c r="M547" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N547" s="85">
         <v>0</v>
@@ -76854,13 +77202,13 @@
         <v>13</v>
       </c>
       <c r="P547" s="85">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q547">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="R547" s="100">
-        <v>94550</v>
+        <v>94549</v>
       </c>
       <c r="T547" s="85">
         <v>0</v>
@@ -76873,40 +77221,40 @@
     </row>
     <row r="548" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B548" s="85">
-        <v>800081</v>
+        <v>800080</v>
       </c>
       <c r="C548" s="104" t="s">
-        <v>5022</v>
+        <v>5018</v>
       </c>
       <c r="D548" s="104" t="s">
-        <v>5023</v>
+        <v>5019</v>
       </c>
       <c r="E548" s="117" t="s">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="F548" s="108" t="s">
-        <v>5161</v>
+        <v>5159</v>
       </c>
       <c r="G548" s="108" t="s">
-        <v>5162</v>
+        <v>5160</v>
       </c>
       <c r="H548" s="104" t="s">
-        <v>5024</v>
+        <v>5020</v>
       </c>
       <c r="I548" s="104" t="s">
-        <v>5025</v>
+        <v>5021</v>
       </c>
       <c r="J548" s="98" t="s">
-        <v>5416</v>
+        <v>5415</v>
       </c>
       <c r="K548" s="108" t="s">
-        <v>5301</v>
-      </c>
-      <c r="L548" s="109" t="s">
-        <v>5302</v>
+        <v>5299</v>
+      </c>
+      <c r="L548" s="108" t="s">
+        <v>5300</v>
       </c>
       <c r="M548" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N548" s="85">
         <v>0</v>
@@ -76915,13 +77263,13 @@
         <v>13</v>
       </c>
       <c r="P548" s="85">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q548">
         <v>1070</v>
       </c>
       <c r="R548" s="100">
-        <v>94551</v>
+        <v>94550</v>
       </c>
       <c r="T548" s="85">
         <v>0</v>
@@ -76932,54 +77280,57 @@
       <c r="Z548" s="101"/>
       <c r="AA548" s="101"/>
     </row>
-    <row r="549" spans="1:27" s="85" customFormat="1" ht="18.75">
+    <row r="549" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B549" s="85">
-        <v>800101</v>
+        <v>800081</v>
       </c>
       <c r="C549" s="104" t="s">
-        <v>5026</v>
+        <v>5022</v>
       </c>
       <c r="D549" s="104" t="s">
-        <v>5027</v>
-      </c>
-      <c r="E549" s="108" t="s">
-        <v>5417</v>
+        <v>5023</v>
+      </c>
+      <c r="E549" s="117" t="s">
+        <v>5414</v>
       </c>
       <c r="F549" s="108" t="s">
-        <v>5163</v>
-      </c>
-      <c r="G549" s="113" t="s">
-        <v>5164</v>
+        <v>5161</v>
+      </c>
+      <c r="G549" s="108" t="s">
+        <v>5162</v>
       </c>
       <c r="H549" s="104" t="s">
-        <v>5028</v>
+        <v>5024</v>
       </c>
       <c r="I549" s="104" t="s">
-        <v>5029</v>
-      </c>
-      <c r="J549" s="118" t="s">
-        <v>5427</v>
+        <v>5025</v>
+      </c>
+      <c r="J549" s="98" t="s">
+        <v>5416</v>
       </c>
       <c r="K549" s="108" t="s">
-        <v>5303</v>
-      </c>
-      <c r="L549" s="115" t="s">
-        <v>5322</v>
+        <v>5301</v>
+      </c>
+      <c r="L549" s="109" t="s">
+        <v>5302</v>
       </c>
       <c r="M549" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N549" s="85">
         <v>0</v>
       </c>
       <c r="O549" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P549" s="85">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="Q549">
+        <v>1070</v>
       </c>
       <c r="R549" s="100">
-        <v>95001</v>
+        <v>94551</v>
       </c>
       <c r="T549" s="85">
         <v>0</v>
@@ -76990,41 +77341,41 @@
       <c r="Z549" s="101"/>
       <c r="AA549" s="101"/>
     </row>
-    <row r="550" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="550" spans="1:27" s="85" customFormat="1" ht="18.75">
       <c r="B550" s="85">
-        <v>800102</v>
+        <v>800101</v>
       </c>
       <c r="C550" s="104" t="s">
-        <v>5030</v>
+        <v>5026</v>
       </c>
       <c r="D550" s="104" t="s">
-        <v>5031</v>
+        <v>5027</v>
       </c>
       <c r="E550" s="108" t="s">
-        <v>5418</v>
+        <v>5417</v>
       </c>
       <c r="F550" s="108" t="s">
-        <v>5165</v>
+        <v>5163</v>
       </c>
       <c r="G550" s="113" t="s">
-        <v>5166</v>
+        <v>5164</v>
       </c>
       <c r="H550" s="104" t="s">
-        <v>5032</v>
+        <v>5028</v>
       </c>
       <c r="I550" s="104" t="s">
-        <v>5033</v>
-      </c>
-      <c r="J550" s="98" t="s">
-        <v>5428</v>
+        <v>5029</v>
+      </c>
+      <c r="J550" s="118" t="s">
+        <v>5427</v>
       </c>
       <c r="K550" s="108" t="s">
-        <v>5304</v>
-      </c>
-      <c r="L550" s="109" t="s">
-        <v>5305</v>
-      </c>
-      <c r="M550" s="103">
+        <v>5303</v>
+      </c>
+      <c r="L550" s="115" t="s">
+        <v>5322</v>
+      </c>
+      <c r="M550" s="99">
         <v>1</v>
       </c>
       <c r="N550" s="85">
@@ -77034,10 +77385,10 @@
         <v>14</v>
       </c>
       <c r="P550" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R550" s="100">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="T550" s="85">
         <v>0</v>
@@ -77048,41 +77399,41 @@
       <c r="Z550" s="101"/>
       <c r="AA550" s="101"/>
     </row>
-    <row r="551" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="551" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B551" s="85">
-        <v>800103</v>
+        <v>800102</v>
       </c>
       <c r="C551" s="104" t="s">
-        <v>5034</v>
+        <v>5030</v>
       </c>
       <c r="D551" s="104" t="s">
-        <v>5035</v>
+        <v>5031</v>
       </c>
       <c r="E551" s="108" t="s">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="F551" s="108" t="s">
-        <v>5183</v>
+        <v>5165</v>
       </c>
       <c r="G551" s="113" t="s">
-        <v>5167</v>
+        <v>5166</v>
       </c>
       <c r="H551" s="104" t="s">
-        <v>5036</v>
+        <v>5032</v>
       </c>
       <c r="I551" s="104" t="s">
-        <v>5037</v>
+        <v>5033</v>
       </c>
       <c r="J551" s="98" t="s">
-        <v>5429</v>
-      </c>
-      <c r="K551" s="98" t="s">
-        <v>5306</v>
-      </c>
-      <c r="L551" s="98" t="s">
-        <v>5307</v>
-      </c>
-      <c r="M551" s="99">
+        <v>5428</v>
+      </c>
+      <c r="K551" s="108" t="s">
+        <v>5304</v>
+      </c>
+      <c r="L551" s="109" t="s">
+        <v>5305</v>
+      </c>
+      <c r="M551" s="103">
         <v>1</v>
       </c>
       <c r="N551" s="85">
@@ -77092,10 +77443,10 @@
         <v>14</v>
       </c>
       <c r="P551" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R551" s="100">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="T551" s="85">
         <v>0</v>
@@ -77108,37 +77459,37 @@
     </row>
     <row r="552" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B552" s="85">
-        <v>800104</v>
+        <v>800103</v>
       </c>
       <c r="C552" s="104" t="s">
-        <v>5038</v>
+        <v>5034</v>
       </c>
       <c r="D552" s="104" t="s">
-        <v>5039</v>
+        <v>5035</v>
       </c>
       <c r="E552" s="108" t="s">
-        <v>5420</v>
+        <v>5419</v>
       </c>
       <c r="F552" s="108" t="s">
-        <v>5168</v>
+        <v>5183</v>
       </c>
       <c r="G552" s="113" t="s">
-        <v>5169</v>
+        <v>5167</v>
       </c>
       <c r="H552" s="104" t="s">
-        <v>5040</v>
+        <v>5036</v>
       </c>
       <c r="I552" s="104" t="s">
-        <v>5041</v>
+        <v>5037</v>
       </c>
       <c r="J552" s="98" t="s">
-        <v>5430</v>
+        <v>5429</v>
       </c>
       <c r="K552" s="98" t="s">
-        <v>5308</v>
+        <v>5306</v>
       </c>
       <c r="L552" s="98" t="s">
-        <v>5309</v>
+        <v>5307</v>
       </c>
       <c r="M552" s="99">
         <v>1</v>
@@ -77150,10 +77501,10 @@
         <v>14</v>
       </c>
       <c r="P552" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R552" s="100">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="T552" s="85">
         <v>0</v>
@@ -77166,37 +77517,37 @@
     </row>
     <row r="553" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B553" s="85">
-        <v>800105</v>
+        <v>800104</v>
       </c>
       <c r="C553" s="104" t="s">
-        <v>5042</v>
+        <v>5038</v>
       </c>
       <c r="D553" s="104" t="s">
-        <v>5043</v>
+        <v>5039</v>
       </c>
       <c r="E553" s="108" t="s">
-        <v>5421</v>
+        <v>5420</v>
       </c>
       <c r="F553" s="108" t="s">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="G553" s="113" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
       <c r="H553" s="104" t="s">
-        <v>5044</v>
+        <v>5040</v>
       </c>
       <c r="I553" s="104" t="s">
-        <v>5045</v>
+        <v>5041</v>
       </c>
       <c r="J553" s="98" t="s">
-        <v>5431</v>
+        <v>5430</v>
       </c>
       <c r="K553" s="98" t="s">
-        <v>5310</v>
+        <v>5308</v>
       </c>
       <c r="L553" s="98" t="s">
-        <v>5311</v>
+        <v>5309</v>
       </c>
       <c r="M553" s="99">
         <v>1</v>
@@ -77208,10 +77559,10 @@
         <v>14</v>
       </c>
       <c r="P553" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R553" s="100">
-        <v>95005</v>
+        <v>95004</v>
       </c>
       <c r="T553" s="85">
         <v>0</v>
@@ -77222,41 +77573,41 @@
       <c r="Z553" s="101"/>
       <c r="AA553" s="101"/>
     </row>
-    <row r="554" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="554" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B554" s="85">
-        <v>800106</v>
+        <v>800105</v>
       </c>
       <c r="C554" s="104" t="s">
-        <v>5046</v>
+        <v>5042</v>
       </c>
       <c r="D554" s="104" t="s">
-        <v>5047</v>
+        <v>5043</v>
       </c>
       <c r="E554" s="108" t="s">
-        <v>5422</v>
+        <v>5421</v>
       </c>
       <c r="F554" s="108" t="s">
-        <v>5172</v>
+        <v>5170</v>
       </c>
       <c r="G554" s="113" t="s">
-        <v>5173</v>
+        <v>5171</v>
       </c>
       <c r="H554" s="104" t="s">
-        <v>5048</v>
+        <v>5044</v>
       </c>
       <c r="I554" s="104" t="s">
-        <v>5049</v>
+        <v>5045</v>
       </c>
       <c r="J554" s="98" t="s">
-        <v>5432</v>
+        <v>5431</v>
       </c>
       <c r="K554" s="98" t="s">
-        <v>5312</v>
+        <v>5310</v>
       </c>
       <c r="L554" s="98" t="s">
-        <v>5313</v>
-      </c>
-      <c r="M554" s="103">
+        <v>5311</v>
+      </c>
+      <c r="M554" s="99">
         <v>1</v>
       </c>
       <c r="N554" s="85">
@@ -77266,10 +77617,10 @@
         <v>14</v>
       </c>
       <c r="P554" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R554" s="100">
-        <v>95006</v>
+        <v>95005</v>
       </c>
       <c r="T554" s="85">
         <v>0</v>
@@ -77280,42 +77631,42 @@
       <c r="Z554" s="101"/>
       <c r="AA554" s="101"/>
     </row>
-    <row r="555" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="555" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B555" s="85">
-        <v>800107</v>
+        <v>800106</v>
       </c>
       <c r="C555" s="104" t="s">
-        <v>5050</v>
+        <v>5046</v>
       </c>
       <c r="D555" s="104" t="s">
-        <v>5051</v>
+        <v>5047</v>
       </c>
       <c r="E555" s="108" t="s">
-        <v>5423</v>
+        <v>5422</v>
       </c>
       <c r="F555" s="108" t="s">
-        <v>5174</v>
+        <v>5172</v>
       </c>
       <c r="G555" s="113" t="s">
-        <v>5175</v>
+        <v>5173</v>
       </c>
       <c r="H555" s="104" t="s">
-        <v>5052</v>
+        <v>5048</v>
       </c>
       <c r="I555" s="104" t="s">
-        <v>5053</v>
+        <v>5049</v>
       </c>
       <c r="J555" s="98" t="s">
-        <v>5433</v>
+        <v>5432</v>
       </c>
       <c r="K555" s="98" t="s">
-        <v>5314</v>
+        <v>5312</v>
       </c>
       <c r="L555" s="98" t="s">
-        <v>5315</v>
-      </c>
-      <c r="M555" s="99">
-        <v>2</v>
+        <v>5313</v>
+      </c>
+      <c r="M555" s="103">
+        <v>1</v>
       </c>
       <c r="N555" s="85">
         <v>0</v>
@@ -77324,10 +77675,10 @@
         <v>14</v>
       </c>
       <c r="P555" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R555" s="100">
-        <v>95007</v>
+        <v>95006</v>
       </c>
       <c r="T555" s="85">
         <v>0</v>
@@ -77340,37 +77691,37 @@
     </row>
     <row r="556" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B556" s="85">
-        <v>800108</v>
+        <v>800107</v>
       </c>
       <c r="C556" s="104" t="s">
-        <v>5054</v>
+        <v>5050</v>
       </c>
       <c r="D556" s="104" t="s">
-        <v>5055</v>
+        <v>5051</v>
       </c>
       <c r="E556" s="108" t="s">
-        <v>5424</v>
+        <v>5423</v>
       </c>
       <c r="F556" s="108" t="s">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="G556" s="113" t="s">
-        <v>5177</v>
+        <v>5175</v>
       </c>
       <c r="H556" s="104" t="s">
-        <v>5056</v>
+        <v>5052</v>
       </c>
       <c r="I556" s="104" t="s">
-        <v>5057</v>
+        <v>5053</v>
       </c>
       <c r="J556" s="98" t="s">
-        <v>5434</v>
+        <v>5433</v>
       </c>
       <c r="K556" s="98" t="s">
-        <v>5316</v>
+        <v>5314</v>
       </c>
       <c r="L556" s="98" t="s">
-        <v>5317</v>
+        <v>5315</v>
       </c>
       <c r="M556" s="99">
         <v>2</v>
@@ -77382,10 +77733,10 @@
         <v>14</v>
       </c>
       <c r="P556" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R556" s="100">
-        <v>95008</v>
+        <v>95007</v>
       </c>
       <c r="T556" s="85">
         <v>0</v>
@@ -77398,37 +77749,37 @@
     </row>
     <row r="557" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B557" s="85">
-        <v>800109</v>
+        <v>800108</v>
       </c>
       <c r="C557" s="104" t="s">
-        <v>5058</v>
+        <v>5054</v>
       </c>
       <c r="D557" s="104" t="s">
-        <v>5059</v>
+        <v>5055</v>
       </c>
       <c r="E557" s="108" t="s">
-        <v>5425</v>
+        <v>5424</v>
       </c>
       <c r="F557" s="108" t="s">
-        <v>5178</v>
+        <v>5176</v>
       </c>
       <c r="G557" s="113" t="s">
-        <v>5179</v>
+        <v>5177</v>
       </c>
       <c r="H557" s="104" t="s">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="I557" s="104" t="s">
-        <v>5061</v>
+        <v>5057</v>
       </c>
       <c r="J557" s="98" t="s">
-        <v>5435</v>
+        <v>5434</v>
       </c>
       <c r="K557" s="98" t="s">
-        <v>5318</v>
+        <v>5316</v>
       </c>
       <c r="L557" s="98" t="s">
-        <v>5319</v>
+        <v>5317</v>
       </c>
       <c r="M557" s="99">
         <v>2</v>
@@ -77440,10 +77791,10 @@
         <v>14</v>
       </c>
       <c r="P557" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R557" s="100">
-        <v>95009</v>
+        <v>95008</v>
       </c>
       <c r="T557" s="85">
         <v>0</v>
@@ -77454,42 +77805,42 @@
       <c r="Z557" s="101"/>
       <c r="AA557" s="101"/>
     </row>
-    <row r="558" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="558" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B558" s="85">
-        <v>800110</v>
+        <v>800109</v>
       </c>
       <c r="C558" s="104" t="s">
-        <v>5062</v>
+        <v>5058</v>
       </c>
       <c r="D558" s="104" t="s">
-        <v>5063</v>
+        <v>5059</v>
       </c>
       <c r="E558" s="108" t="s">
-        <v>5426</v>
+        <v>5425</v>
       </c>
       <c r="F558" s="108" t="s">
-        <v>5180</v>
+        <v>5178</v>
       </c>
       <c r="G558" s="113" t="s">
-        <v>5181</v>
+        <v>5179</v>
       </c>
       <c r="H558" s="104" t="s">
-        <v>5064</v>
+        <v>5060</v>
       </c>
       <c r="I558" s="104" t="s">
-        <v>5065</v>
+        <v>5061</v>
       </c>
       <c r="J558" s="98" t="s">
-        <v>5436</v>
+        <v>5435</v>
       </c>
       <c r="K558" s="98" t="s">
-        <v>5320</v>
+        <v>5318</v>
       </c>
       <c r="L558" s="98" t="s">
-        <v>5321</v>
-      </c>
-      <c r="M558" s="103">
-        <v>3</v>
+        <v>5319</v>
+      </c>
+      <c r="M558" s="99">
+        <v>2</v>
       </c>
       <c r="N558" s="85">
         <v>0</v>
@@ -77498,10 +77849,10 @@
         <v>14</v>
       </c>
       <c r="P558" s="85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R558" s="100">
-        <v>95010</v>
+        <v>95009</v>
       </c>
       <c r="T558" s="85">
         <v>0</v>
@@ -77512,37 +77863,95 @@
       <c r="Z558" s="101"/>
       <c r="AA558" s="101"/>
     </row>
-    <row r="559" spans="1:27" s="2" customFormat="1">
-      <c r="A559" s="2" t="s">
+    <row r="559" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+      <c r="B559" s="85">
+        <v>800110</v>
+      </c>
+      <c r="C559" s="104" t="s">
+        <v>5062</v>
+      </c>
+      <c r="D559" s="104" t="s">
+        <v>5063</v>
+      </c>
+      <c r="E559" s="108" t="s">
+        <v>5426</v>
+      </c>
+      <c r="F559" s="108" t="s">
+        <v>5180</v>
+      </c>
+      <c r="G559" s="113" t="s">
+        <v>5181</v>
+      </c>
+      <c r="H559" s="104" t="s">
+        <v>5064</v>
+      </c>
+      <c r="I559" s="104" t="s">
+        <v>5065</v>
+      </c>
+      <c r="J559" s="98" t="s">
+        <v>5436</v>
+      </c>
+      <c r="K559" s="98" t="s">
+        <v>5320</v>
+      </c>
+      <c r="L559" s="98" t="s">
+        <v>5321</v>
+      </c>
+      <c r="M559" s="103">
+        <v>3</v>
+      </c>
+      <c r="N559" s="85">
+        <v>0</v>
+      </c>
+      <c r="O559" s="85">
+        <v>14</v>
+      </c>
+      <c r="P559" s="85">
+        <v>10</v>
+      </c>
+      <c r="R559" s="100">
+        <v>95010</v>
+      </c>
+      <c r="T559" s="85">
+        <v>0</v>
+      </c>
+      <c r="U559" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z559" s="101"/>
+      <c r="AA559" s="101"/>
+    </row>
+    <row r="560" spans="1:27" s="2" customFormat="1">
+      <c r="A560" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="B559" s="2">
+      <c r="B560" s="2">
         <v>900001</v>
       </c>
-      <c r="M559" s="2">
-        <v>0</v>
-      </c>
-      <c r="N559" s="2">
-        <v>0</v>
-      </c>
-      <c r="O559" s="2">
+      <c r="M560" s="2">
+        <v>0</v>
+      </c>
+      <c r="N560" s="2">
+        <v>0</v>
+      </c>
+      <c r="O560" s="2">
         <v>2</v>
       </c>
-      <c r="P559" s="2">
+      <c r="P560" s="2">
         <v>999</v>
       </c>
-      <c r="R559" s="2">
+      <c r="R560" s="2">
         <v>98001</v>
       </c>
-      <c r="T559" s="2">
+      <c r="T560" s="2">
         <v>1</v>
       </c>
-      <c r="U559" s="2">
+      <c r="U560" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U498" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:U499" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="N1:N445 N449:N459 N462:N479 N482:N1048576">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">

--- a/source/bin/excel/achievement.xlsx
+++ b/source/bin/excel/achievement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABC02A0-4414-422B-9F2E-307AFD1F185F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F2219A-7B29-4D82-AE60-15767F7964F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="badge_group" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$503</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6628" uniqueCount="5717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6668" uniqueCount="5749">
   <si>
     <t>sheet</t>
   </si>
@@ -38581,6 +38581,110 @@
   </si>
   <si>
     <t>30740019-1</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>ジェーンとの出会い</t>
+  </si>
+  <si>
+    <t>An Encounter with Jane</t>
+  </si>
+  <si>
+    <t>제인와의 만남</t>
+  </si>
+  <si>
+    <t>ジェーンを入手する</t>
+  </si>
+  <si>
+    <t>Obtain Jyanshi Jane</t>
+  </si>
+  <si>
+    <t>제인 획득하기.</t>
+  </si>
+  <si>
+    <t>サターンとの出会い</t>
+  </si>
+  <si>
+    <t>An Encounter with Saturne</t>
+  </si>
+  <si>
+    <t>새턴와의 만남</t>
+  </si>
+  <si>
+    <t>サターンを入手する</t>
+  </si>
+  <si>
+    <t>Obtain Jyanshi Saturne</t>
+  </si>
+  <si>
+    <t>새턴 획득하기.</t>
+  </si>
+  <si>
+    <t>ジェーンの契約者</t>
+  </si>
+  <si>
+    <t>Bonded with Jane</t>
+  </si>
+  <si>
+    <t>제인의 계약자</t>
+  </si>
+  <si>
+    <t>ジェーンと契約を結ぶ</t>
+  </si>
+  <si>
+    <t>Bond with Jane</t>
+  </si>
+  <si>
+    <t>제인와(과) 계약 맺기.</t>
+  </si>
+  <si>
+    <t>サターンの契約者</t>
+  </si>
+  <si>
+    <t>Bonded with Saturne</t>
+  </si>
+  <si>
+    <t>새턴의 계약자</t>
+  </si>
+  <si>
+    <t>サターンと契約を結ぶ</t>
+  </si>
+  <si>
+    <t>Bond with Saturne</t>
+  </si>
+  <si>
+    <t>새턴와(과) 계약 맺기.</t>
+  </si>
+  <si>
+    <t>与tbd的邂逅</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbd的契约者</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>與tbd的邂逅</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>tbd的契約者</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得雀士tbd</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得雀士tbd</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>与tbd签订契约</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>與tbd簽訂契約</t>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
 </sst>
@@ -39348,7 +39452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -39661,18 +39765,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -40707,7 +40807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM560"/>
+  <dimension ref="A1:AM564"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -72944,236 +73044,236 @@
       <c r="Z479" s="27"/>
       <c r="AA479" s="27"/>
     </row>
-    <row r="480" spans="1:31" s="144" customFormat="1" ht="16.5">
-      <c r="B480" s="144">
+    <row r="480" spans="1:31" ht="16.5">
+      <c r="B480">
         <v>100482</v>
       </c>
-      <c r="C480" s="144" t="s">
+      <c r="C480" t="s">
         <v>5684</v>
       </c>
-      <c r="D480" s="145" t="s">
+      <c r="D480" s="29" t="s">
         <v>5507</v>
       </c>
-      <c r="E480" s="146" t="s">
+      <c r="E480" s="62" t="s">
         <v>5686</v>
       </c>
-      <c r="F480" s="147" t="s">
+      <c r="F480" s="63" t="s">
         <v>5688</v>
       </c>
-      <c r="G480" s="148" t="s">
+      <c r="G480" s="73" t="s">
         <v>5690</v>
       </c>
-      <c r="H480" s="145" t="s">
+      <c r="H480" s="29" t="s">
         <v>5509</v>
       </c>
-      <c r="I480" s="145" t="s">
+      <c r="I480" s="29" t="s">
         <v>5510</v>
       </c>
-      <c r="J480" s="147" t="s">
+      <c r="J480" s="63" t="s">
         <v>5692</v>
       </c>
-      <c r="K480" s="149" t="s">
+      <c r="K480" s="60" t="s">
         <v>5694</v>
       </c>
-      <c r="L480" s="150" t="s">
+      <c r="L480" s="79" t="s">
         <v>5696</v>
       </c>
-      <c r="M480" s="144">
+      <c r="M480">
         <v>2</v>
       </c>
-      <c r="N480" s="144">
-        <v>0</v>
-      </c>
-      <c r="O480" s="144">
+      <c r="N480">
+        <v>0</v>
+      </c>
+      <c r="O480">
         <v>10</v>
       </c>
-      <c r="P480" s="144">
+      <c r="P480" s="85">
         <v>169</v>
       </c>
-      <c r="R480" s="144">
+      <c r="R480">
         <v>99170</v>
       </c>
-      <c r="T480" s="144">
-        <v>0</v>
-      </c>
-      <c r="U480" s="144">
-        <v>0</v>
-      </c>
-      <c r="X480" s="151"/>
-      <c r="Y480" s="151"/>
-      <c r="Z480" s="151"/>
-      <c r="AA480" s="151"/>
+      <c r="T480">
+        <v>0</v>
+      </c>
+      <c r="U480">
+        <v>0</v>
+      </c>
+      <c r="X480" s="27"/>
+      <c r="Y480" s="27"/>
+      <c r="Z480" s="27"/>
+      <c r="AA480" s="27"/>
     </row>
-    <row r="481" spans="1:39" s="144" customFormat="1" ht="16.5">
-      <c r="B481" s="144">
+    <row r="481" spans="1:39" ht="16.5">
+      <c r="B481">
         <v>100483</v>
       </c>
-      <c r="C481" s="144" t="s">
+      <c r="C481" t="s">
         <v>5685</v>
       </c>
-      <c r="D481" s="145" t="s">
+      <c r="D481" s="29" t="s">
         <v>5508</v>
       </c>
-      <c r="E481" s="146" t="s">
+      <c r="E481" s="62" t="s">
         <v>5687</v>
       </c>
-      <c r="F481" s="147" t="s">
+      <c r="F481" s="63" t="s">
         <v>5689</v>
       </c>
-      <c r="G481" s="148" t="s">
+      <c r="G481" s="73" t="s">
         <v>5691</v>
       </c>
-      <c r="H481" s="145" t="s">
+      <c r="H481" s="29" t="s">
         <v>5511</v>
       </c>
-      <c r="I481" s="145" t="s">
+      <c r="I481" s="29" t="s">
         <v>5512</v>
       </c>
-      <c r="J481" s="147" t="s">
+      <c r="J481" s="63" t="s">
         <v>5693</v>
       </c>
-      <c r="K481" s="145" t="s">
+      <c r="K481" s="29" t="s">
         <v>5695</v>
       </c>
-      <c r="L481" s="152" t="s">
+      <c r="L481" s="78" t="s">
         <v>5697</v>
       </c>
-      <c r="M481" s="144">
+      <c r="M481">
         <v>2</v>
       </c>
-      <c r="N481" s="144">
-        <v>0</v>
-      </c>
-      <c r="O481" s="144">
+      <c r="N481">
+        <v>0</v>
+      </c>
+      <c r="O481">
         <v>10</v>
       </c>
-      <c r="P481" s="144">
+      <c r="P481" s="86">
         <v>371</v>
       </c>
-      <c r="R481" s="144">
+      <c r="R481">
         <v>99171</v>
       </c>
-      <c r="T481" s="144">
-        <v>0</v>
-      </c>
-      <c r="U481" s="144">
-        <v>0</v>
-      </c>
-      <c r="X481" s="151"/>
-      <c r="Y481" s="151"/>
-      <c r="Z481" s="151"/>
-      <c r="AA481" s="151"/>
+      <c r="T481">
+        <v>0</v>
+      </c>
+      <c r="U481">
+        <v>0</v>
+      </c>
+      <c r="X481" s="27"/>
+      <c r="Y481" s="27"/>
+      <c r="Z481" s="27"/>
+      <c r="AA481" s="27"/>
     </row>
-    <row r="482" spans="1:39" s="144" customFormat="1" ht="16.5">
-      <c r="A482" s="144">
+    <row r="482" spans="1:39" ht="16.5">
+      <c r="A482">
         <v>18</v>
       </c>
-      <c r="B482" s="144">
+      <c r="B482">
         <v>100484</v>
       </c>
-      <c r="C482" s="145" t="s">
+      <c r="C482" s="29" t="s">
         <v>5513</v>
       </c>
-      <c r="D482" s="145" t="s">
+      <c r="D482" s="29" t="s">
         <v>5514</v>
       </c>
-      <c r="E482" s="146" t="s">
+      <c r="E482" s="62" t="s">
         <v>5515</v>
       </c>
-      <c r="F482" s="147" t="s">
+      <c r="F482" s="63" t="s">
         <v>5516</v>
       </c>
-      <c r="G482" s="152" t="s">
+      <c r="G482" s="78" t="s">
         <v>5517</v>
       </c>
-      <c r="H482" s="149" t="s">
+      <c r="H482" s="60" t="s">
         <v>5518</v>
       </c>
-      <c r="I482" s="145" t="s">
+      <c r="I482" s="29" t="s">
         <v>5519</v>
       </c>
-      <c r="J482" s="147" t="s">
+      <c r="J482" s="63" t="s">
         <v>5520</v>
       </c>
-      <c r="K482" s="145" t="s">
+      <c r="K482" s="29" t="s">
         <v>5521</v>
       </c>
-      <c r="L482" s="152" t="s">
+      <c r="L482" s="78" t="s">
         <v>5522</v>
       </c>
-      <c r="M482" s="153">
+      <c r="M482" s="66">
         <v>1</v>
       </c>
-      <c r="N482" s="144">
-        <v>0</v>
-      </c>
-      <c r="O482" s="144">
+      <c r="N482">
+        <v>0</v>
+      </c>
+      <c r="O482">
         <v>10</v>
       </c>
       <c r="P482" s="142">
         <v>518</v>
       </c>
-      <c r="R482" s="144">
+      <c r="R482">
         <v>99172</v>
       </c>
-      <c r="S482" s="151" t="s">
+      <c r="S482" s="27" t="s">
         <v>5523</v>
       </c>
-      <c r="T482" s="144">
-        <v>0</v>
-      </c>
-      <c r="U482" s="144">
-        <v>0</v>
-      </c>
-      <c r="X482" s="151"/>
-      <c r="Y482" s="151"/>
-      <c r="Z482" s="151"/>
-      <c r="AA482" s="151"/>
+      <c r="T482">
+        <v>0</v>
+      </c>
+      <c r="U482">
+        <v>0</v>
+      </c>
+      <c r="X482" s="27"/>
+      <c r="Y482" s="27"/>
+      <c r="Z482" s="27"/>
+      <c r="AA482" s="27"/>
     </row>
-    <row r="483" spans="1:39" s="59" customFormat="1">
-      <c r="A483" s="59">
+    <row r="483" spans="1:39" s="144" customFormat="1">
+      <c r="A483" s="144">
         <v>19</v>
       </c>
       <c r="B483" s="144">
         <v>100485</v>
       </c>
-      <c r="C483" s="87" t="s">
+      <c r="C483" s="145" t="s">
         <v>5706</v>
       </c>
-      <c r="D483" s="87" t="s">
+      <c r="D483" s="145" t="s">
         <v>5707</v>
       </c>
-      <c r="E483" s="88" t="s">
+      <c r="E483" s="146" t="s">
         <v>5708</v>
       </c>
-      <c r="F483" s="89" t="s">
+      <c r="F483" s="147" t="s">
         <v>5709</v>
       </c>
-      <c r="G483" s="93" t="s">
+      <c r="G483" s="148" t="s">
         <v>5710</v>
       </c>
-      <c r="H483" s="90" t="s">
+      <c r="H483" s="149" t="s">
         <v>5711</v>
       </c>
-      <c r="I483" s="87" t="s">
+      <c r="I483" s="145" t="s">
         <v>5712</v>
       </c>
-      <c r="J483" s="89" t="s">
+      <c r="J483" s="147" t="s">
         <v>5713</v>
       </c>
-      <c r="K483" s="87" t="s">
+      <c r="K483" s="145" t="s">
         <v>5714</v>
       </c>
-      <c r="L483" s="93" t="s">
+      <c r="L483" s="148" t="s">
         <v>5715</v>
       </c>
-      <c r="M483" s="91">
+      <c r="M483" s="150">
         <v>1</v>
       </c>
-      <c r="N483" s="59">
-        <v>0</v>
-      </c>
-      <c r="O483" s="59">
+      <c r="N483" s="144">
+        <v>0</v>
+      </c>
+      <c r="O483" s="144">
         <v>10</v>
       </c>
       <c r="P483" s="142">
@@ -73182,350 +73282,303 @@
       <c r="R483" s="130">
         <v>99173</v>
       </c>
-      <c r="S483" s="92" t="s">
+      <c r="S483" s="151" t="s">
         <v>5716</v>
       </c>
-      <c r="T483" s="59">
-        <v>0</v>
-      </c>
-      <c r="U483" s="59">
-        <v>0</v>
-      </c>
-      <c r="X483" s="27"/>
-      <c r="Y483" s="27"/>
-      <c r="Z483" s="27"/>
-      <c r="AA483" s="27"/>
+      <c r="T483" s="144">
+        <v>0</v>
+      </c>
+      <c r="U483" s="144">
+        <v>0</v>
+      </c>
+      <c r="X483" s="151"/>
+      <c r="Y483" s="151"/>
+      <c r="Z483" s="151"/>
+      <c r="AA483" s="151"/>
     </row>
-    <row r="484" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="A484" s="1" t="s">
-        <v>4234</v>
-      </c>
-      <c r="B484" s="1">
-        <v>800011</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E484" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F484" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G484" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H484" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I484" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J484" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="K484" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="L484" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="M484" s="47">
+    <row r="484" spans="1:39" s="59" customFormat="1">
+      <c r="B484">
+        <v>100486</v>
+      </c>
+      <c r="C484" s="87" t="s">
+        <v>5741</v>
+      </c>
+      <c r="D484" s="87" t="s">
+        <v>5743</v>
+      </c>
+      <c r="E484" s="88" t="s">
+        <v>5717</v>
+      </c>
+      <c r="F484" s="89" t="s">
+        <v>5718</v>
+      </c>
+      <c r="G484" s="93" t="s">
+        <v>5719</v>
+      </c>
+      <c r="H484" s="90" t="s">
+        <v>5745</v>
+      </c>
+      <c r="I484" s="87" t="s">
+        <v>5746</v>
+      </c>
+      <c r="J484" s="89" t="s">
+        <v>5720</v>
+      </c>
+      <c r="K484" s="87" t="s">
+        <v>5721</v>
+      </c>
+      <c r="L484" s="93" t="s">
+        <v>5722</v>
+      </c>
+      <c r="M484" s="91">
         <v>1</v>
       </c>
-      <c r="N484" s="1">
-        <v>0</v>
-      </c>
-      <c r="O484" s="1">
-        <v>12</v>
-      </c>
-      <c r="P484" s="1">
+      <c r="N484" s="59">
+        <v>0</v>
+      </c>
+      <c r="O484" s="59">
+        <v>10</v>
+      </c>
+      <c r="P484" s="85">
+        <v>170</v>
+      </c>
+      <c r="R484">
+        <v>99174</v>
+      </c>
+      <c r="S484" s="92"/>
+      <c r="T484" s="59">
+        <v>0</v>
+      </c>
+      <c r="U484" s="59">
+        <v>0</v>
+      </c>
+      <c r="X484" s="27"/>
+      <c r="Y484" s="27"/>
+      <c r="Z484" s="27"/>
+      <c r="AA484" s="27"/>
+    </row>
+    <row r="485" spans="1:39" s="59" customFormat="1">
+      <c r="B485">
+        <v>100487</v>
+      </c>
+      <c r="C485" s="87" t="s">
+        <v>5741</v>
+      </c>
+      <c r="D485" s="87" t="s">
+        <v>5743</v>
+      </c>
+      <c r="E485" s="88" t="s">
+        <v>5723</v>
+      </c>
+      <c r="F485" s="89" t="s">
+        <v>5724</v>
+      </c>
+      <c r="G485" s="93" t="s">
+        <v>5725</v>
+      </c>
+      <c r="H485" s="90" t="s">
+        <v>5745</v>
+      </c>
+      <c r="I485" s="87" t="s">
+        <v>5746</v>
+      </c>
+      <c r="J485" s="89" t="s">
+        <v>5726</v>
+      </c>
+      <c r="K485" s="87" t="s">
+        <v>5727</v>
+      </c>
+      <c r="L485" s="93" t="s">
+        <v>5728</v>
+      </c>
+      <c r="M485" s="91">
         <v>1</v>
       </c>
-      <c r="R484" s="1">
-        <v>90501</v>
-      </c>
-      <c r="T484" s="1">
-        <v>0</v>
-      </c>
-      <c r="U484" s="1">
-        <v>0</v>
-      </c>
-      <c r="X484" s="1">
-        <v>90501</v>
-      </c>
-      <c r="Y484" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z484" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA484" s="42">
+      <c r="N485" s="59">
+        <v>0</v>
+      </c>
+      <c r="O485" s="59">
+        <v>10</v>
+      </c>
+      <c r="P485" s="85">
+        <v>171</v>
+      </c>
+      <c r="R485">
+        <v>99175</v>
+      </c>
+      <c r="S485" s="92"/>
+      <c r="T485" s="59">
+        <v>0</v>
+      </c>
+      <c r="U485" s="59">
+        <v>0</v>
+      </c>
+      <c r="X485" s="27"/>
+      <c r="Y485" s="27"/>
+      <c r="Z485" s="27"/>
+      <c r="AA485" s="27"/>
+    </row>
+    <row r="486" spans="1:39" s="59" customFormat="1">
+      <c r="B486" s="144">
+        <v>100488</v>
+      </c>
+      <c r="C486" s="87" t="s">
+        <v>5742</v>
+      </c>
+      <c r="D486" s="87" t="s">
+        <v>5744</v>
+      </c>
+      <c r="E486" s="88" t="s">
+        <v>5729</v>
+      </c>
+      <c r="F486" s="89" t="s">
+        <v>5730</v>
+      </c>
+      <c r="G486" s="93" t="s">
+        <v>5731</v>
+      </c>
+      <c r="H486" s="90" t="s">
+        <v>5747</v>
+      </c>
+      <c r="I486" s="87" t="s">
+        <v>5748</v>
+      </c>
+      <c r="J486" s="89" t="s">
+        <v>5732</v>
+      </c>
+      <c r="K486" s="87" t="s">
+        <v>5733</v>
+      </c>
+      <c r="L486" s="93" t="s">
+        <v>5734</v>
+      </c>
+      <c r="M486" s="91">
         <v>1</v>
       </c>
-      <c r="AB484" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE484" s="51"/>
-      <c r="AF484" s="51"/>
-      <c r="AG484" s="51"/>
-      <c r="AH484" s="51"/>
-      <c r="AI484" s="51"/>
-      <c r="AL484" s="51"/>
-      <c r="AM484" s="51"/>
+      <c r="N486" s="59">
+        <v>0</v>
+      </c>
+      <c r="O486" s="59">
+        <v>10</v>
+      </c>
+      <c r="P486" s="86">
+        <v>372</v>
+      </c>
+      <c r="R486">
+        <v>99176</v>
+      </c>
+      <c r="S486" s="92"/>
+      <c r="T486" s="59">
+        <v>0</v>
+      </c>
+      <c r="U486" s="59">
+        <v>0</v>
+      </c>
+      <c r="X486" s="27"/>
+      <c r="Y486" s="27"/>
+      <c r="Z486" s="27"/>
+      <c r="AA486" s="27"/>
     </row>
-    <row r="485" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B485" s="1">
-        <v>800012</v>
-      </c>
-      <c r="C485" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D485" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E485" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="F485" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G485" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H485" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="I485" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="J485" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="K485" s="42" t="s">
-        <v>4235</v>
-      </c>
-      <c r="L485" s="42" t="s">
-        <v>249</v>
-      </c>
-      <c r="M485" s="47">
-        <v>2</v>
-      </c>
-      <c r="N485" s="1">
-        <v>0</v>
-      </c>
-      <c r="O485" s="1">
-        <v>12</v>
-      </c>
-      <c r="P485" s="1">
-        <v>2</v>
-      </c>
-      <c r="R485" s="1">
-        <v>90502</v>
-      </c>
-      <c r="T485" s="1">
-        <v>0</v>
-      </c>
-      <c r="U485" s="1">
-        <v>0</v>
-      </c>
-      <c r="X485" s="1">
-        <v>90502</v>
-      </c>
-      <c r="Y485" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z485" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA485" s="42">
-        <v>3</v>
-      </c>
-      <c r="AB485" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="486" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B486" s="1">
-        <v>800013</v>
-      </c>
-      <c r="C486" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D486" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E486" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="F486" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G486" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="H486" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="I486" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="J486" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="K486" s="42" t="s">
-        <v>4236</v>
-      </c>
-      <c r="L486" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="M486" s="48">
-        <v>3</v>
-      </c>
-      <c r="N486" s="1">
-        <v>0</v>
-      </c>
-      <c r="O486" s="1">
-        <v>12</v>
-      </c>
-      <c r="P486" s="1">
-        <v>3</v>
-      </c>
-      <c r="R486" s="1">
-        <v>90503</v>
-      </c>
-      <c r="T486" s="1">
-        <v>0</v>
-      </c>
-      <c r="U486" s="1">
-        <v>0</v>
-      </c>
-      <c r="X486" s="1">
-        <v>90503</v>
-      </c>
-      <c r="Y486" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z486" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA486" s="42">
-        <v>5</v>
-      </c>
-      <c r="AB486" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="487" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B487" s="1">
-        <v>800014</v>
-      </c>
-      <c r="C487" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E487" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="F487" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G487" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="H487" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="I487" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="J487" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="K487" s="42" t="s">
-        <v>269</v>
-      </c>
-      <c r="L487" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M487" s="47">
+    <row r="487" spans="1:39" s="59" customFormat="1">
+      <c r="B487">
+        <v>100489</v>
+      </c>
+      <c r="C487" s="87" t="s">
+        <v>5742</v>
+      </c>
+      <c r="D487" s="87" t="s">
+        <v>5744</v>
+      </c>
+      <c r="E487" s="88" t="s">
+        <v>5735</v>
+      </c>
+      <c r="F487" s="89" t="s">
+        <v>5736</v>
+      </c>
+      <c r="G487" s="93" t="s">
+        <v>5737</v>
+      </c>
+      <c r="H487" s="90" t="s">
+        <v>5747</v>
+      </c>
+      <c r="I487" s="87" t="s">
+        <v>5748</v>
+      </c>
+      <c r="J487" s="89" t="s">
+        <v>5738</v>
+      </c>
+      <c r="K487" s="87" t="s">
+        <v>5739</v>
+      </c>
+      <c r="L487" s="93" t="s">
+        <v>5740</v>
+      </c>
+      <c r="M487" s="91">
         <v>1</v>
       </c>
-      <c r="N487" s="1">
-        <v>0</v>
-      </c>
-      <c r="O487" s="1">
-        <v>12</v>
-      </c>
-      <c r="P487" s="1">
-        <v>4</v>
-      </c>
-      <c r="R487" s="1">
-        <v>90504</v>
-      </c>
-      <c r="T487" s="1">
-        <v>0</v>
-      </c>
-      <c r="U487" s="1">
-        <v>0</v>
-      </c>
-      <c r="X487" s="1">
-        <v>90504</v>
-      </c>
-      <c r="Y487" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z487" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA487" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB487" s="1" t="s">
-        <v>271</v>
-      </c>
+      <c r="N487" s="59">
+        <v>0</v>
+      </c>
+      <c r="O487" s="59">
+        <v>10</v>
+      </c>
+      <c r="P487" s="86">
+        <v>373</v>
+      </c>
+      <c r="R487" s="130">
+        <v>99177</v>
+      </c>
+      <c r="S487" s="92"/>
+      <c r="T487" s="59">
+        <v>0</v>
+      </c>
+      <c r="U487" s="59">
+        <v>0</v>
+      </c>
+      <c r="X487" s="27"/>
+      <c r="Y487" s="27"/>
+      <c r="Z487" s="27"/>
+      <c r="AA487" s="27"/>
     </row>
     <row r="488" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="A488" s="1" t="s">
+        <v>4234</v>
+      </c>
       <c r="B488" s="1">
-        <v>800015</v>
+        <v>800011</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E488" s="41" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="H488" s="42" t="s">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="I488" s="42" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="J488" s="46" t="s">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="K488" s="42" t="s">
-        <v>4237</v>
+        <v>235</v>
       </c>
       <c r="L488" s="42" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="M488" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N488" s="1">
         <v>0</v>
@@ -73534,10 +73587,10 @@
         <v>12</v>
       </c>
       <c r="P488" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R488" s="1">
-        <v>90505</v>
+        <v>90501</v>
       </c>
       <c r="T488" s="1">
         <v>0</v>
@@ -73546,57 +73599,64 @@
         <v>0</v>
       </c>
       <c r="X488" s="1">
-        <v>90505</v>
+        <v>90501</v>
       </c>
       <c r="Y488" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z488" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA488" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB488" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="AE488" s="51"/>
+      <c r="AF488" s="51"/>
+      <c r="AG488" s="51"/>
+      <c r="AH488" s="51"/>
+      <c r="AI488" s="51"/>
+      <c r="AL488" s="51"/>
+      <c r="AM488" s="51"/>
     </row>
     <row r="489" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B489" s="1">
-        <v>800016</v>
+        <v>800012</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E489" s="43" t="s">
-        <v>284</v>
+        <v>241</v>
+      </c>
+      <c r="E489" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="H489" s="42" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="I489" s="42" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="J489" s="46" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="K489" s="42" t="s">
-        <v>4238</v>
+        <v>4235</v>
       </c>
       <c r="L489" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="M489" s="48">
-        <v>3</v>
+        <v>249</v>
+      </c>
+      <c r="M489" s="47">
+        <v>2</v>
       </c>
       <c r="N489" s="1">
         <v>0</v>
@@ -73605,10 +73665,10 @@
         <v>12</v>
       </c>
       <c r="P489" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R489" s="1">
-        <v>90506</v>
+        <v>90502</v>
       </c>
       <c r="T489" s="1">
         <v>0</v>
@@ -73617,7 +73677,7 @@
         <v>0</v>
       </c>
       <c r="X489" s="1">
-        <v>90506</v>
+        <v>90502</v>
       </c>
       <c r="Y489" s="1" t="s">
         <v>237</v>
@@ -73626,48 +73686,48 @@
         <v>250</v>
       </c>
       <c r="AA489" s="42">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB489" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="490" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B490" s="1">
-        <v>800017</v>
+        <v>800013</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E490" s="43" t="s">
-        <v>294</v>
+        <v>252</v>
+      </c>
+      <c r="E490" s="41" t="s">
+        <v>253</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="H490" s="42" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="I490" s="42" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J490" s="46" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="K490" s="42" t="s">
-        <v>300</v>
+        <v>4236</v>
       </c>
       <c r="L490" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="M490" s="47">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="M490" s="48">
+        <v>3</v>
       </c>
       <c r="N490" s="1">
         <v>0</v>
@@ -73676,10 +73736,10 @@
         <v>12</v>
       </c>
       <c r="P490" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R490" s="1">
-        <v>90507</v>
+        <v>90503</v>
       </c>
       <c r="T490" s="1">
         <v>0</v>
@@ -73688,54 +73748,54 @@
         <v>0</v>
       </c>
       <c r="X490" s="1">
-        <v>90507</v>
+        <v>90503</v>
       </c>
       <c r="Y490" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z490" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA490" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB490" s="1" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
     </row>
     <row r="491" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B491" s="1">
-        <v>800018</v>
+        <v>800014</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="E491" s="41" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="F491" s="1" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="H491" s="42" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="I491" s="42" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="J491" s="46" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="K491" s="42" t="s">
-        <v>4239</v>
+        <v>269</v>
       </c>
       <c r="L491" s="42" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="M491" s="47">
         <v>1</v>
@@ -73747,10 +73807,10 @@
         <v>12</v>
       </c>
       <c r="P491" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R491" s="1">
-        <v>90508</v>
+        <v>90504</v>
       </c>
       <c r="T491" s="1">
         <v>0</v>
@@ -73759,54 +73819,54 @@
         <v>0</v>
       </c>
       <c r="X491" s="1">
-        <v>90508</v>
+        <v>90504</v>
       </c>
       <c r="Y491" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z491" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA491" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB491" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="492" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B492" s="1">
-        <v>800019</v>
+        <v>800015</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="E492" s="41" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="G492" s="1" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="H492" s="42" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="I492" s="42" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="J492" s="46" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="K492" s="42" t="s">
-        <v>4240</v>
+        <v>4237</v>
       </c>
       <c r="L492" s="42" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="M492" s="47">
         <v>2</v>
@@ -73818,10 +73878,10 @@
         <v>12</v>
       </c>
       <c r="P492" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R492" s="1">
-        <v>90509</v>
+        <v>90505</v>
       </c>
       <c r="T492" s="1">
         <v>0</v>
@@ -73830,7 +73890,7 @@
         <v>0</v>
       </c>
       <c r="X492" s="1">
-        <v>90509</v>
+        <v>90505</v>
       </c>
       <c r="Y492" s="1" t="s">
         <v>237</v>
@@ -73839,48 +73899,48 @@
         <v>250</v>
       </c>
       <c r="AA492" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB492" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="493" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B493" s="1">
-        <v>800020</v>
+        <v>800016</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E493" s="41" t="s">
-        <v>325</v>
+        <v>283</v>
+      </c>
+      <c r="E493" s="43" t="s">
+        <v>284</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="G493" s="1" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="H493" s="42" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="I493" s="42" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="J493" s="46" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="K493" s="42" t="s">
-        <v>331</v>
+        <v>4238</v>
       </c>
       <c r="L493" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="M493" s="47">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="M493" s="48">
+        <v>3</v>
       </c>
       <c r="N493" s="1">
         <v>0</v>
@@ -73889,10 +73949,10 @@
         <v>12</v>
       </c>
       <c r="P493" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R493" s="1">
-        <v>90510</v>
+        <v>90506</v>
       </c>
       <c r="T493" s="1">
         <v>0</v>
@@ -73901,57 +73961,57 @@
         <v>0</v>
       </c>
       <c r="X493" s="1">
-        <v>90510</v>
+        <v>90506</v>
       </c>
       <c r="Y493" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z493" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA493" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB493" s="1" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="494" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B494" s="1">
-        <v>800021</v>
+        <v>800017</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E494" s="41" t="s">
-        <v>336</v>
+        <v>293</v>
+      </c>
+      <c r="E494" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>337</v>
+        <v>295</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="H494" s="42" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="I494" s="42" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="J494" s="46" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="K494" s="42" t="s">
-        <v>4241</v>
+        <v>300</v>
       </c>
       <c r="L494" s="42" t="s">
-        <v>343</v>
+        <v>301</v>
       </c>
       <c r="M494" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N494" s="1">
         <v>0</v>
@@ -73960,10 +74020,10 @@
         <v>12</v>
       </c>
       <c r="P494" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R494" s="1">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="T494" s="1">
         <v>0</v>
@@ -73972,57 +74032,57 @@
         <v>0</v>
       </c>
       <c r="X494" s="1">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="Y494" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z494" s="42" t="s">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="AA494" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB494" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="495" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B495" s="1">
-        <v>800022</v>
+        <v>800018</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="E495" s="41" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="H495" s="42" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="I495" s="42" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="J495" s="46" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="K495" s="42" t="s">
-        <v>4242</v>
+        <v>4239</v>
       </c>
       <c r="L495" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="M495" s="48">
-        <v>3</v>
+        <v>312</v>
+      </c>
+      <c r="M495" s="47">
+        <v>1</v>
       </c>
       <c r="N495" s="1">
         <v>0</v>
@@ -74031,10 +74091,10 @@
         <v>12</v>
       </c>
       <c r="P495" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R495" s="1">
-        <v>90512</v>
+        <v>90508</v>
       </c>
       <c r="T495" s="1">
         <v>0</v>
@@ -74043,57 +74103,57 @@
         <v>0</v>
       </c>
       <c r="X495" s="1">
-        <v>90512</v>
+        <v>90508</v>
       </c>
       <c r="Y495" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z495" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA495" s="42">
         <v>5</v>
       </c>
       <c r="AB495" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="496" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B496" s="1">
-        <v>800023</v>
+        <v>800019</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="E496" s="41" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="H496" s="42" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="I496" s="42" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="J496" s="46" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="K496" s="42" t="s">
-        <v>362</v>
+        <v>4240</v>
       </c>
       <c r="L496" s="42" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="M496" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N496" s="1">
         <v>0</v>
@@ -74102,10 +74162,10 @@
         <v>12</v>
       </c>
       <c r="P496" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R496" s="1">
-        <v>90513</v>
+        <v>90509</v>
       </c>
       <c r="T496" s="1">
         <v>0</v>
@@ -74114,54 +74174,54 @@
         <v>0</v>
       </c>
       <c r="X496" s="1">
-        <v>90513</v>
+        <v>90509</v>
       </c>
       <c r="Y496" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z496" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA496" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB496" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="497" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B497" s="1">
-        <v>800024</v>
+        <v>800020</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="E497" s="41" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="H497" s="42" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="I497" s="42" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="J497" s="46" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="K497" s="42" t="s">
-        <v>4243</v>
+        <v>331</v>
       </c>
       <c r="L497" s="42" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="M497" s="47">
         <v>1</v>
@@ -74173,10 +74233,10 @@
         <v>12</v>
       </c>
       <c r="P497" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R497" s="1">
-        <v>90514</v>
+        <v>90510</v>
       </c>
       <c r="T497" s="1">
         <v>0</v>
@@ -74185,7 +74245,7 @@
         <v>0</v>
       </c>
       <c r="X497" s="1">
-        <v>90514</v>
+        <v>90510</v>
       </c>
       <c r="Y497" s="1" t="s">
         <v>237</v>
@@ -74194,45 +74254,45 @@
         <v>333</v>
       </c>
       <c r="AA497" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB497" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="498" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B498" s="1">
-        <v>800025</v>
+        <v>800021</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="E498" s="41" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="H498" s="42" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="I498" s="42" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="J498" s="46" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="K498" s="42" t="s">
-        <v>4244</v>
+        <v>4241</v>
       </c>
       <c r="L498" s="42" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="M498" s="47">
         <v>2</v>
@@ -74244,10 +74304,10 @@
         <v>12</v>
       </c>
       <c r="P498" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R498" s="1">
-        <v>90515</v>
+        <v>90511</v>
       </c>
       <c r="T498" s="1">
         <v>0</v>
@@ -74256,7 +74316,7 @@
         <v>0</v>
       </c>
       <c r="X498" s="1">
-        <v>90515</v>
+        <v>90511</v>
       </c>
       <c r="Y498" s="1" t="s">
         <v>237</v>
@@ -74265,299 +74325,332 @@
         <v>333</v>
       </c>
       <c r="AA498" s="42">
+        <v>3</v>
+      </c>
+      <c r="AB498" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="499" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B499" s="1">
+        <v>800022</v>
+      </c>
+      <c r="C499" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E499" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="F499" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G499" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H499" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="I499" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="J499" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="K499" s="42" t="s">
+        <v>4242</v>
+      </c>
+      <c r="L499" s="42" t="s">
+        <v>353</v>
+      </c>
+      <c r="M499" s="48">
+        <v>3</v>
+      </c>
+      <c r="N499" s="1">
+        <v>0</v>
+      </c>
+      <c r="O499" s="1">
+        <v>12</v>
+      </c>
+      <c r="P499" s="1">
+        <v>12</v>
+      </c>
+      <c r="R499" s="1">
+        <v>90512</v>
+      </c>
+      <c r="T499" s="1">
+        <v>0</v>
+      </c>
+      <c r="U499" s="1">
+        <v>0</v>
+      </c>
+      <c r="X499" s="1">
+        <v>90512</v>
+      </c>
+      <c r="Y499" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z499" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA499" s="42">
+        <v>5</v>
+      </c>
+      <c r="AB499" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="500" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B500" s="1">
+        <v>800023</v>
+      </c>
+      <c r="C500" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E500" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="F500" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G500" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H500" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="I500" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="J500" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="K500" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="L500" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="M500" s="47">
+        <v>1</v>
+      </c>
+      <c r="N500" s="1">
+        <v>0</v>
+      </c>
+      <c r="O500" s="1">
+        <v>12</v>
+      </c>
+      <c r="P500" s="1">
+        <v>13</v>
+      </c>
+      <c r="R500" s="1">
+        <v>90513</v>
+      </c>
+      <c r="T500" s="1">
+        <v>0</v>
+      </c>
+      <c r="U500" s="1">
+        <v>0</v>
+      </c>
+      <c r="X500" s="1">
+        <v>90513</v>
+      </c>
+      <c r="Y500" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z500" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA500" s="42">
+        <v>1</v>
+      </c>
+      <c r="AB500" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="501" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B501" s="1">
+        <v>800024</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E501" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="F501" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G501" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H501" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="I501" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="J501" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="K501" s="42" t="s">
+        <v>4243</v>
+      </c>
+      <c r="L501" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="M501" s="47">
+        <v>1</v>
+      </c>
+      <c r="N501" s="1">
+        <v>0</v>
+      </c>
+      <c r="O501" s="1">
+        <v>12</v>
+      </c>
+      <c r="P501" s="1">
+        <v>14</v>
+      </c>
+      <c r="R501" s="1">
+        <v>90514</v>
+      </c>
+      <c r="T501" s="1">
+        <v>0</v>
+      </c>
+      <c r="U501" s="1">
+        <v>0</v>
+      </c>
+      <c r="X501" s="1">
+        <v>90514</v>
+      </c>
+      <c r="Y501" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z501" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA501" s="42">
+        <v>5</v>
+      </c>
+      <c r="AB501" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="502" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B502" s="1">
+        <v>800025</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E502" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F502" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G502" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H502" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="I502" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="J502" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="K502" s="42" t="s">
+        <v>4244</v>
+      </c>
+      <c r="L502" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="M502" s="47">
+        <v>2</v>
+      </c>
+      <c r="N502" s="1">
+        <v>0</v>
+      </c>
+      <c r="O502" s="1">
+        <v>12</v>
+      </c>
+      <c r="P502" s="1">
+        <v>15</v>
+      </c>
+      <c r="R502" s="1">
+        <v>90515</v>
+      </c>
+      <c r="T502" s="1">
+        <v>0</v>
+      </c>
+      <c r="U502" s="1">
+        <v>0</v>
+      </c>
+      <c r="X502" s="1">
+        <v>90515</v>
+      </c>
+      <c r="Y502" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z502" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA502" s="42">
         <v>10</v>
       </c>
-      <c r="AB498" s="1" t="s">
+      <c r="AB502" s="1" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="499" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="A499" s="94" t="s">
-        <v>4838</v>
-      </c>
-      <c r="B499" s="85">
-        <v>800031</v>
-      </c>
-      <c r="C499" s="95" t="s">
-        <v>4839</v>
-      </c>
-      <c r="D499" s="95" t="s">
-        <v>4840</v>
-      </c>
-      <c r="E499" s="108" t="s">
-        <v>5325</v>
-      </c>
-      <c r="F499" s="108" t="s">
-        <v>5078</v>
-      </c>
-      <c r="G499" s="108" t="s">
-        <v>5079</v>
-      </c>
-      <c r="H499" s="97" t="s">
-        <v>4841</v>
-      </c>
-      <c r="I499" s="114" t="s">
-        <v>5343</v>
-      </c>
-      <c r="J499" s="116" t="s">
-        <v>5337</v>
-      </c>
-      <c r="K499" s="108" t="s">
-        <v>5082</v>
-      </c>
-      <c r="L499" s="109" t="s">
-        <v>5083</v>
-      </c>
-      <c r="M499" s="99">
-        <v>1</v>
-      </c>
-      <c r="N499" s="85">
-        <v>0</v>
-      </c>
-      <c r="O499" s="85">
-        <v>13</v>
-      </c>
-      <c r="P499" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q499">
-        <v>1059</v>
-      </c>
-      <c r="R499" s="100">
-        <v>94501</v>
-      </c>
-      <c r="T499" s="85">
-        <v>0</v>
-      </c>
-      <c r="U499" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z499" s="101"/>
-      <c r="AA499" s="101"/>
-      <c r="AE499" s="102"/>
-      <c r="AF499" s="102"/>
-      <c r="AG499" s="102"/>
-      <c r="AH499" s="102"/>
-      <c r="AI499" s="102"/>
-      <c r="AL499" s="102"/>
-      <c r="AM499" s="102"/>
-    </row>
-    <row r="500" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="B500" s="85">
-        <v>800032</v>
-      </c>
-      <c r="C500" s="95" t="s">
-        <v>4842</v>
-      </c>
-      <c r="D500" s="95" t="s">
-        <v>4843</v>
-      </c>
-      <c r="E500" s="108" t="s">
-        <v>5327</v>
-      </c>
-      <c r="F500" s="108" t="s">
-        <v>5086</v>
-      </c>
-      <c r="G500" s="108" t="s">
-        <v>5080</v>
-      </c>
-      <c r="H500" s="97" t="s">
-        <v>4844</v>
-      </c>
-      <c r="I500" s="97" t="s">
-        <v>4845</v>
-      </c>
-      <c r="J500" s="116" t="s">
-        <v>5338</v>
-      </c>
-      <c r="K500" s="108" t="s">
-        <v>5092</v>
-      </c>
-      <c r="L500" s="109" t="s">
-        <v>5094</v>
-      </c>
-      <c r="M500" s="99">
-        <v>1</v>
-      </c>
-      <c r="N500" s="85">
-        <v>0</v>
-      </c>
-      <c r="O500" s="85">
-        <v>13</v>
-      </c>
-      <c r="P500" s="85">
-        <v>2</v>
-      </c>
-      <c r="Q500">
-        <v>1059</v>
-      </c>
-      <c r="R500" s="100">
-        <v>94502</v>
-      </c>
-      <c r="T500" s="85">
-        <v>0</v>
-      </c>
-      <c r="U500" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z500" s="101"/>
-      <c r="AA500" s="101"/>
-    </row>
-    <row r="501" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
-      <c r="B501" s="85">
-        <v>800033</v>
-      </c>
-      <c r="C501" s="95" t="s">
-        <v>4846</v>
-      </c>
-      <c r="D501" s="95" t="s">
-        <v>4847</v>
-      </c>
-      <c r="E501" s="108" t="s">
-        <v>5329</v>
-      </c>
-      <c r="F501" s="108" t="s">
-        <v>5089</v>
-      </c>
-      <c r="G501" s="108" t="s">
-        <v>5081</v>
-      </c>
-      <c r="H501" s="97" t="s">
-        <v>4848</v>
-      </c>
-      <c r="I501" s="97" t="s">
-        <v>4849</v>
-      </c>
-      <c r="J501" s="116" t="s">
-        <v>5339</v>
-      </c>
-      <c r="K501" s="108" t="s">
-        <v>5093</v>
-      </c>
-      <c r="L501" s="109" t="s">
-        <v>5095</v>
-      </c>
-      <c r="M501" s="103">
-        <v>2</v>
-      </c>
-      <c r="N501" s="85">
-        <v>0</v>
-      </c>
-      <c r="O501" s="85">
-        <v>13</v>
-      </c>
-      <c r="P501" s="85">
-        <v>3</v>
-      </c>
-      <c r="Q501">
-        <v>1059</v>
-      </c>
-      <c r="R501" s="100">
-        <v>94503</v>
-      </c>
-      <c r="T501" s="85">
-        <v>0</v>
-      </c>
-      <c r="U501" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z501" s="101"/>
-      <c r="AA501" s="101"/>
-    </row>
-    <row r="502" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="B502" s="85">
-        <v>800034</v>
-      </c>
-      <c r="C502" s="95" t="s">
-        <v>4850</v>
-      </c>
-      <c r="D502" s="95" t="s">
-        <v>4851</v>
-      </c>
-      <c r="E502" s="117" t="s">
-        <v>5326</v>
-      </c>
-      <c r="F502" s="108" t="s">
-        <v>5084</v>
-      </c>
-      <c r="G502" s="108" t="s">
-        <v>5085</v>
-      </c>
-      <c r="H502" s="97" t="s">
-        <v>4852</v>
-      </c>
-      <c r="I502" s="97" t="s">
-        <v>4853</v>
-      </c>
-      <c r="J502" s="116" t="s">
-        <v>5331</v>
-      </c>
-      <c r="K502" s="98" t="s">
-        <v>5096</v>
-      </c>
-      <c r="L502" s="110" t="s">
-        <v>5099</v>
-      </c>
-      <c r="M502" s="99">
-        <v>1</v>
-      </c>
-      <c r="N502" s="85">
-        <v>0</v>
-      </c>
-      <c r="O502" s="85">
-        <v>13</v>
-      </c>
-      <c r="P502" s="85">
-        <v>4</v>
-      </c>
-      <c r="Q502">
-        <v>1060</v>
-      </c>
-      <c r="R502" s="100">
-        <v>94504</v>
-      </c>
-      <c r="T502" s="85">
-        <v>0</v>
-      </c>
-      <c r="U502" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z502" s="101"/>
-      <c r="AA502" s="101"/>
     </row>
     <row r="503" spans="1:39" s="85" customFormat="1" ht="33">
+      <c r="A503" s="94" t="s">
+        <v>4838</v>
+      </c>
       <c r="B503" s="85">
-        <v>800035</v>
+        <v>800031</v>
       </c>
       <c r="C503" s="95" t="s">
-        <v>4854</v>
+        <v>4839</v>
       </c>
       <c r="D503" s="95" t="s">
-        <v>4855</v>
-      </c>
-      <c r="E503" s="117" t="s">
-        <v>5328</v>
+        <v>4840</v>
+      </c>
+      <c r="E503" s="108" t="s">
+        <v>5325</v>
       </c>
       <c r="F503" s="108" t="s">
-        <v>5087</v>
-      </c>
-      <c r="G503" s="109" t="s">
-        <v>5088</v>
+        <v>5078</v>
+      </c>
+      <c r="G503" s="108" t="s">
+        <v>5079</v>
       </c>
       <c r="H503" s="97" t="s">
-        <v>4856</v>
-      </c>
-      <c r="I503" s="97" t="s">
-        <v>4857</v>
+        <v>4841</v>
+      </c>
+      <c r="I503" s="114" t="s">
+        <v>5343</v>
       </c>
       <c r="J503" s="116" t="s">
-        <v>5332</v>
-      </c>
-      <c r="K503" s="98" t="s">
-        <v>5097</v>
-      </c>
-      <c r="L503" s="110" t="s">
-        <v>5100</v>
+        <v>5337</v>
+      </c>
+      <c r="K503" s="108" t="s">
+        <v>5082</v>
+      </c>
+      <c r="L503" s="109" t="s">
+        <v>5083</v>
       </c>
       <c r="M503" s="99">
         <v>1</v>
@@ -74569,13 +74662,13 @@
         <v>13</v>
       </c>
       <c r="P503" s="85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q503">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R503" s="100">
-        <v>94505</v>
+        <v>94501</v>
       </c>
       <c r="T503" s="85">
         <v>0</v>
@@ -74585,43 +74678,50 @@
       </c>
       <c r="Z503" s="101"/>
       <c r="AA503" s="101"/>
+      <c r="AE503" s="102"/>
+      <c r="AF503" s="102"/>
+      <c r="AG503" s="102"/>
+      <c r="AH503" s="102"/>
+      <c r="AI503" s="102"/>
+      <c r="AL503" s="102"/>
+      <c r="AM503" s="102"/>
     </row>
-    <row r="504" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="504" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B504" s="85">
-        <v>800036</v>
+        <v>800032</v>
       </c>
       <c r="C504" s="95" t="s">
-        <v>4858</v>
+        <v>4842</v>
       </c>
       <c r="D504" s="95" t="s">
-        <v>4859</v>
-      </c>
-      <c r="E504" s="117" t="s">
-        <v>5330</v>
+        <v>4843</v>
+      </c>
+      <c r="E504" s="108" t="s">
+        <v>5327</v>
       </c>
       <c r="F504" s="108" t="s">
-        <v>5090</v>
-      </c>
-      <c r="G504" s="109" t="s">
-        <v>5091</v>
+        <v>5086</v>
+      </c>
+      <c r="G504" s="108" t="s">
+        <v>5080</v>
       </c>
       <c r="H504" s="97" t="s">
-        <v>4860</v>
+        <v>4844</v>
       </c>
       <c r="I504" s="97" t="s">
-        <v>4861</v>
+        <v>4845</v>
       </c>
       <c r="J504" s="116" t="s">
-        <v>5333</v>
-      </c>
-      <c r="K504" s="98" t="s">
-        <v>5098</v>
-      </c>
-      <c r="L504" s="110" t="s">
-        <v>5101</v>
-      </c>
-      <c r="M504" s="103">
-        <v>2</v>
+        <v>5338</v>
+      </c>
+      <c r="K504" s="108" t="s">
+        <v>5092</v>
+      </c>
+      <c r="L504" s="109" t="s">
+        <v>5094</v>
+      </c>
+      <c r="M504" s="99">
+        <v>1</v>
       </c>
       <c r="N504" s="85">
         <v>0</v>
@@ -74630,13 +74730,13 @@
         <v>13</v>
       </c>
       <c r="P504" s="85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q504">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R504" s="100">
-        <v>94506</v>
+        <v>94502</v>
       </c>
       <c r="T504" s="85">
         <v>0</v>
@@ -74647,42 +74747,42 @@
       <c r="Z504" s="101"/>
       <c r="AA504" s="101"/>
     </row>
-    <row r="505" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="505" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B505" s="85">
-        <v>800037</v>
+        <v>800033</v>
       </c>
       <c r="C505" s="95" t="s">
-        <v>4862</v>
+        <v>4846</v>
       </c>
       <c r="D505" s="95" t="s">
-        <v>4863</v>
-      </c>
-      <c r="E505" s="117" t="s">
-        <v>5334</v>
-      </c>
-      <c r="F505" s="96" t="s">
-        <v>5102</v>
-      </c>
-      <c r="G505" s="111" t="s">
-        <v>5103</v>
+        <v>4847</v>
+      </c>
+      <c r="E505" s="108" t="s">
+        <v>5329</v>
+      </c>
+      <c r="F505" s="108" t="s">
+        <v>5089</v>
+      </c>
+      <c r="G505" s="108" t="s">
+        <v>5081</v>
       </c>
       <c r="H505" s="97" t="s">
-        <v>4864</v>
+        <v>4848</v>
       </c>
       <c r="I505" s="97" t="s">
-        <v>4865</v>
+        <v>4849</v>
       </c>
       <c r="J505" s="116" t="s">
-        <v>5340</v>
-      </c>
-      <c r="K505" s="98" t="s">
-        <v>5213</v>
+        <v>5339</v>
+      </c>
+      <c r="K505" s="108" t="s">
+        <v>5093</v>
       </c>
       <c r="L505" s="109" t="s">
-        <v>5216</v>
-      </c>
-      <c r="M505" s="99">
-        <v>1</v>
+        <v>5095</v>
+      </c>
+      <c r="M505" s="103">
+        <v>2</v>
       </c>
       <c r="N505" s="85">
         <v>0</v>
@@ -74691,13 +74791,13 @@
         <v>13</v>
       </c>
       <c r="P505" s="85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q505">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="R505" s="100">
-        <v>94507</v>
+        <v>94503</v>
       </c>
       <c r="T505" s="85">
         <v>0</v>
@@ -74710,37 +74810,37 @@
     </row>
     <row r="506" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B506" s="85">
-        <v>800038</v>
+        <v>800034</v>
       </c>
       <c r="C506" s="95" t="s">
-        <v>4866</v>
+        <v>4850</v>
       </c>
       <c r="D506" s="95" t="s">
-        <v>4867</v>
+        <v>4851</v>
       </c>
       <c r="E506" s="117" t="s">
-        <v>5336</v>
-      </c>
-      <c r="F506" s="96" t="s">
-        <v>5105</v>
-      </c>
-      <c r="G506" s="111" t="s">
-        <v>5106</v>
+        <v>5326</v>
+      </c>
+      <c r="F506" s="108" t="s">
+        <v>5084</v>
+      </c>
+      <c r="G506" s="108" t="s">
+        <v>5085</v>
       </c>
       <c r="H506" s="97" t="s">
-        <v>4868</v>
+        <v>4852</v>
       </c>
       <c r="I506" s="97" t="s">
-        <v>4869</v>
+        <v>4853</v>
       </c>
       <c r="J506" s="116" t="s">
-        <v>5341</v>
+        <v>5331</v>
       </c>
       <c r="K506" s="98" t="s">
-        <v>5214</v>
-      </c>
-      <c r="L506" s="109" t="s">
-        <v>5217</v>
+        <v>5096</v>
+      </c>
+      <c r="L506" s="110" t="s">
+        <v>5099</v>
       </c>
       <c r="M506" s="99">
         <v>1</v>
@@ -74752,13 +74852,13 @@
         <v>13</v>
       </c>
       <c r="P506" s="85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q506">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R506" s="100">
-        <v>94508</v>
+        <v>94504</v>
       </c>
       <c r="T506" s="85">
         <v>0</v>
@@ -74771,40 +74871,40 @@
     </row>
     <row r="507" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B507" s="85">
-        <v>800039</v>
+        <v>800035</v>
       </c>
       <c r="C507" s="95" t="s">
-        <v>4870</v>
-      </c>
-      <c r="D507" s="114" t="s">
-        <v>5184</v>
+        <v>4854</v>
+      </c>
+      <c r="D507" s="95" t="s">
+        <v>4855</v>
       </c>
       <c r="E507" s="117" t="s">
-        <v>5335</v>
-      </c>
-      <c r="F507" s="96" t="s">
-        <v>5104</v>
-      </c>
-      <c r="G507" s="111" t="s">
-        <v>5107</v>
+        <v>5328</v>
+      </c>
+      <c r="F507" s="108" t="s">
+        <v>5087</v>
+      </c>
+      <c r="G507" s="109" t="s">
+        <v>5088</v>
       </c>
       <c r="H507" s="97" t="s">
-        <v>4871</v>
+        <v>4856</v>
       </c>
       <c r="I507" s="97" t="s">
-        <v>4872</v>
+        <v>4857</v>
       </c>
       <c r="J507" s="116" t="s">
-        <v>5342</v>
+        <v>5332</v>
       </c>
       <c r="K507" s="98" t="s">
-        <v>5215</v>
-      </c>
-      <c r="L507" s="109" t="s">
-        <v>5218</v>
+        <v>5097</v>
+      </c>
+      <c r="L507" s="110" t="s">
+        <v>5100</v>
       </c>
       <c r="M507" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N507" s="85">
         <v>0</v>
@@ -74813,13 +74913,13 @@
         <v>13</v>
       </c>
       <c r="P507" s="85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q507">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R507" s="100">
-        <v>94509</v>
+        <v>94505</v>
       </c>
       <c r="T507" s="85">
         <v>0</v>
@@ -74830,42 +74930,42 @@
       <c r="Z507" s="101"/>
       <c r="AA507" s="101"/>
     </row>
-    <row r="508" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="508" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B508" s="85">
-        <v>800040</v>
+        <v>800036</v>
       </c>
       <c r="C508" s="95" t="s">
-        <v>4873</v>
+        <v>4858</v>
       </c>
       <c r="D508" s="95" t="s">
-        <v>4874</v>
+        <v>4859</v>
       </c>
       <c r="E508" s="117" t="s">
-        <v>5344</v>
+        <v>5330</v>
       </c>
       <c r="F508" s="108" t="s">
-        <v>5108</v>
-      </c>
-      <c r="G508" s="112" t="s">
-        <v>5109</v>
+        <v>5090</v>
+      </c>
+      <c r="G508" s="109" t="s">
+        <v>5091</v>
       </c>
       <c r="H508" s="97" t="s">
-        <v>4875</v>
+        <v>4860</v>
       </c>
       <c r="I508" s="97" t="s">
-        <v>4876</v>
-      </c>
-      <c r="J508" s="118" t="s">
-        <v>5346</v>
+        <v>4861</v>
+      </c>
+      <c r="J508" s="116" t="s">
+        <v>5333</v>
       </c>
       <c r="K508" s="98" t="s">
-        <v>5219</v>
+        <v>5098</v>
       </c>
       <c r="L508" s="110" t="s">
-        <v>5220</v>
-      </c>
-      <c r="M508" s="99">
-        <v>1</v>
+        <v>5101</v>
+      </c>
+      <c r="M508" s="103">
+        <v>2</v>
       </c>
       <c r="N508" s="85">
         <v>0</v>
@@ -74874,10 +74974,13 @@
         <v>13</v>
       </c>
       <c r="P508" s="85">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="Q508">
+        <v>1060</v>
       </c>
       <c r="R508" s="100">
-        <v>94510</v>
+        <v>94506</v>
       </c>
       <c r="T508" s="85">
         <v>0</v>
@@ -74890,37 +74993,37 @@
     </row>
     <row r="509" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B509" s="85">
-        <v>800041</v>
+        <v>800037</v>
       </c>
       <c r="C509" s="95" t="s">
-        <v>4877</v>
+        <v>4862</v>
       </c>
       <c r="D509" s="95" t="s">
-        <v>4878</v>
+        <v>4863</v>
       </c>
       <c r="E509" s="117" t="s">
-        <v>5345</v>
-      </c>
-      <c r="F509" s="108" t="s">
-        <v>5110</v>
-      </c>
-      <c r="G509" s="108" t="s">
-        <v>5111</v>
+        <v>5334</v>
+      </c>
+      <c r="F509" s="96" t="s">
+        <v>5102</v>
+      </c>
+      <c r="G509" s="111" t="s">
+        <v>5103</v>
       </c>
       <c r="H509" s="97" t="s">
-        <v>4879</v>
+        <v>4864</v>
       </c>
       <c r="I509" s="97" t="s">
-        <v>4880</v>
-      </c>
-      <c r="J509" s="118" t="s">
-        <v>5347</v>
+        <v>4865</v>
+      </c>
+      <c r="J509" s="116" t="s">
+        <v>5340</v>
       </c>
       <c r="K509" s="98" t="s">
-        <v>5221</v>
-      </c>
-      <c r="L509" s="110" t="s">
-        <v>5222</v>
+        <v>5213</v>
+      </c>
+      <c r="L509" s="109" t="s">
+        <v>5216</v>
       </c>
       <c r="M509" s="99">
         <v>1</v>
@@ -74932,10 +75035,13 @@
         <v>13</v>
       </c>
       <c r="P509" s="85">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="Q509">
+        <v>1061</v>
       </c>
       <c r="R509" s="100">
-        <v>94511</v>
+        <v>94507</v>
       </c>
       <c r="T509" s="85">
         <v>0</v>
@@ -74946,41 +75052,41 @@
       <c r="Z509" s="101"/>
       <c r="AA509" s="101"/>
     </row>
-    <row r="510" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="510" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B510" s="85">
-        <v>800042</v>
-      </c>
-      <c r="C510" s="104" t="s">
-        <v>4881</v>
-      </c>
-      <c r="D510" s="104" t="s">
-        <v>4881</v>
+        <v>800038</v>
+      </c>
+      <c r="C510" s="95" t="s">
+        <v>4866</v>
+      </c>
+      <c r="D510" s="95" t="s">
+        <v>4867</v>
       </c>
       <c r="E510" s="117" t="s">
-        <v>5348</v>
-      </c>
-      <c r="F510" s="108" t="s">
-        <v>5185</v>
-      </c>
-      <c r="G510" s="108" t="s">
-        <v>5112</v>
-      </c>
-      <c r="H510" s="104" t="s">
-        <v>4882</v>
-      </c>
-      <c r="I510" s="104" t="s">
-        <v>4883</v>
+        <v>5336</v>
+      </c>
+      <c r="F510" s="96" t="s">
+        <v>5105</v>
+      </c>
+      <c r="G510" s="111" t="s">
+        <v>5106</v>
+      </c>
+      <c r="H510" s="97" t="s">
+        <v>4868</v>
+      </c>
+      <c r="I510" s="97" t="s">
+        <v>4869</v>
       </c>
       <c r="J510" s="116" t="s">
-        <v>5351</v>
-      </c>
-      <c r="K510" s="108" t="s">
-        <v>5223</v>
+        <v>5341</v>
+      </c>
+      <c r="K510" s="98" t="s">
+        <v>5214</v>
       </c>
       <c r="L510" s="109" t="s">
-        <v>5224</v>
-      </c>
-      <c r="M510" s="103">
+        <v>5217</v>
+      </c>
+      <c r="M510" s="99">
         <v>1</v>
       </c>
       <c r="N510" s="85">
@@ -74990,13 +75096,13 @@
         <v>13</v>
       </c>
       <c r="P510" s="85">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q510">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="R510" s="100">
-        <v>94512</v>
+        <v>94508</v>
       </c>
       <c r="T510" s="85">
         <v>0</v>
@@ -75009,40 +75115,40 @@
     </row>
     <row r="511" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B511" s="85">
-        <v>800043</v>
-      </c>
-      <c r="C511" s="104" t="s">
-        <v>4884</v>
-      </c>
-      <c r="D511" s="104" t="s">
-        <v>4884</v>
+        <v>800039</v>
+      </c>
+      <c r="C511" s="95" t="s">
+        <v>4870</v>
+      </c>
+      <c r="D511" s="114" t="s">
+        <v>5184</v>
       </c>
       <c r="E511" s="117" t="s">
-        <v>5349</v>
-      </c>
-      <c r="F511" s="108" t="s">
-        <v>5186</v>
-      </c>
-      <c r="G511" s="109" t="s">
-        <v>5189</v>
-      </c>
-      <c r="H511" s="104" t="s">
-        <v>4885</v>
-      </c>
-      <c r="I511" s="104" t="s">
-        <v>4886</v>
+        <v>5335</v>
+      </c>
+      <c r="F511" s="96" t="s">
+        <v>5104</v>
+      </c>
+      <c r="G511" s="111" t="s">
+        <v>5107</v>
+      </c>
+      <c r="H511" s="97" t="s">
+        <v>4871</v>
+      </c>
+      <c r="I511" s="97" t="s">
+        <v>4872</v>
       </c>
       <c r="J511" s="116" t="s">
-        <v>5352</v>
-      </c>
-      <c r="K511" s="108" t="s">
-        <v>5225</v>
+        <v>5342</v>
+      </c>
+      <c r="K511" s="98" t="s">
+        <v>5215</v>
       </c>
       <c r="L511" s="109" t="s">
-        <v>5226</v>
+        <v>5218</v>
       </c>
       <c r="M511" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N511" s="85">
         <v>0</v>
@@ -75051,13 +75157,13 @@
         <v>13</v>
       </c>
       <c r="P511" s="85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q511">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="R511" s="100">
-        <v>94513</v>
+        <v>94509</v>
       </c>
       <c r="T511" s="85">
         <v>0</v>
@@ -75070,40 +75176,40 @@
     </row>
     <row r="512" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B512" s="85">
-        <v>800044</v>
-      </c>
-      <c r="C512" s="104" t="s">
-        <v>4887</v>
-      </c>
-      <c r="D512" s="104" t="s">
-        <v>4887</v>
+        <v>800040</v>
+      </c>
+      <c r="C512" s="95" t="s">
+        <v>4873</v>
+      </c>
+      <c r="D512" s="95" t="s">
+        <v>4874</v>
       </c>
       <c r="E512" s="117" t="s">
-        <v>5350</v>
+        <v>5344</v>
       </c>
       <c r="F512" s="108" t="s">
-        <v>5187</v>
-      </c>
-      <c r="G512" s="109" t="s">
-        <v>5188</v>
-      </c>
-      <c r="H512" s="104" t="s">
-        <v>4888</v>
-      </c>
-      <c r="I512" s="104" t="s">
-        <v>4889</v>
-      </c>
-      <c r="J512" s="116" t="s">
-        <v>5353</v>
-      </c>
-      <c r="K512" s="108" t="s">
-        <v>5227</v>
-      </c>
-      <c r="L512" s="109" t="s">
-        <v>5228</v>
+        <v>5108</v>
+      </c>
+      <c r="G512" s="112" t="s">
+        <v>5109</v>
+      </c>
+      <c r="H512" s="97" t="s">
+        <v>4875</v>
+      </c>
+      <c r="I512" s="97" t="s">
+        <v>4876</v>
+      </c>
+      <c r="J512" s="118" t="s">
+        <v>5346</v>
+      </c>
+      <c r="K512" s="98" t="s">
+        <v>5219</v>
+      </c>
+      <c r="L512" s="110" t="s">
+        <v>5220</v>
       </c>
       <c r="M512" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N512" s="85">
         <v>0</v>
@@ -75112,13 +75218,10 @@
         <v>13</v>
       </c>
       <c r="P512" s="85">
-        <v>14</v>
-      </c>
-      <c r="Q512">
-        <v>1062</v>
+        <v>10</v>
       </c>
       <c r="R512" s="100">
-        <v>94514</v>
+        <v>94510</v>
       </c>
       <c r="T512" s="85">
         <v>0</v>
@@ -75131,37 +75234,37 @@
     </row>
     <row r="513" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B513" s="85">
-        <v>800045</v>
-      </c>
-      <c r="C513" s="104" t="s">
-        <v>4890</v>
-      </c>
-      <c r="D513" s="104" t="s">
-        <v>4891</v>
+        <v>800041</v>
+      </c>
+      <c r="C513" s="95" t="s">
+        <v>4877</v>
+      </c>
+      <c r="D513" s="95" t="s">
+        <v>4878</v>
       </c>
       <c r="E513" s="117" t="s">
-        <v>5354</v>
-      </c>
-      <c r="F513" s="112" t="s">
-        <v>5113</v>
+        <v>5345</v>
+      </c>
+      <c r="F513" s="108" t="s">
+        <v>5110</v>
       </c>
       <c r="G513" s="108" t="s">
-        <v>5114</v>
-      </c>
-      <c r="H513" s="104" t="s">
-        <v>4892</v>
-      </c>
-      <c r="I513" s="104" t="s">
-        <v>4893</v>
-      </c>
-      <c r="J513" s="116" t="s">
-        <v>5357</v>
-      </c>
-      <c r="K513" s="108" t="s">
-        <v>5229</v>
-      </c>
-      <c r="L513" s="109" t="s">
-        <v>5230</v>
+        <v>5111</v>
+      </c>
+      <c r="H513" s="97" t="s">
+        <v>4879</v>
+      </c>
+      <c r="I513" s="97" t="s">
+        <v>4880</v>
+      </c>
+      <c r="J513" s="118" t="s">
+        <v>5347</v>
+      </c>
+      <c r="K513" s="98" t="s">
+        <v>5221</v>
+      </c>
+      <c r="L513" s="110" t="s">
+        <v>5222</v>
       </c>
       <c r="M513" s="99">
         <v>1</v>
@@ -75173,13 +75276,10 @@
         <v>13</v>
       </c>
       <c r="P513" s="85">
-        <v>15</v>
-      </c>
-      <c r="Q513">
-        <v>1063</v>
+        <v>11</v>
       </c>
       <c r="R513" s="100">
-        <v>94515</v>
+        <v>94511</v>
       </c>
       <c r="T513" s="85">
         <v>0</v>
@@ -75192,37 +75292,37 @@
     </row>
     <row r="514" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B514" s="85">
-        <v>800046</v>
+        <v>800042</v>
       </c>
       <c r="C514" s="104" t="s">
-        <v>4894</v>
+        <v>4881</v>
       </c>
       <c r="D514" s="104" t="s">
-        <v>4895</v>
+        <v>4881</v>
       </c>
       <c r="E514" s="117" t="s">
-        <v>5355</v>
-      </c>
-      <c r="F514" s="112" t="s">
-        <v>5190</v>
-      </c>
-      <c r="G514" s="109" t="s">
-        <v>5191</v>
+        <v>5348</v>
+      </c>
+      <c r="F514" s="108" t="s">
+        <v>5185</v>
+      </c>
+      <c r="G514" s="108" t="s">
+        <v>5112</v>
       </c>
       <c r="H514" s="104" t="s">
-        <v>4896</v>
+        <v>4882</v>
       </c>
       <c r="I514" s="104" t="s">
-        <v>4897</v>
+        <v>4883</v>
       </c>
       <c r="J514" s="116" t="s">
-        <v>5358</v>
+        <v>5351</v>
       </c>
       <c r="K514" s="108" t="s">
-        <v>5231</v>
+        <v>5223</v>
       </c>
       <c r="L514" s="109" t="s">
-        <v>5232</v>
+        <v>5224</v>
       </c>
       <c r="M514" s="103">
         <v>1</v>
@@ -75234,13 +75334,13 @@
         <v>13</v>
       </c>
       <c r="P514" s="85">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q514">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R514" s="100">
-        <v>94516</v>
+        <v>94512</v>
       </c>
       <c r="T514" s="85">
         <v>0</v>
@@ -75253,40 +75353,40 @@
     </row>
     <row r="515" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B515" s="85">
-        <v>800047</v>
+        <v>800043</v>
       </c>
       <c r="C515" s="104" t="s">
-        <v>4898</v>
+        <v>4884</v>
       </c>
       <c r="D515" s="104" t="s">
-        <v>4899</v>
+        <v>4884</v>
       </c>
       <c r="E515" s="117" t="s">
-        <v>5356</v>
-      </c>
-      <c r="F515" s="112" t="s">
-        <v>5192</v>
+        <v>5349</v>
+      </c>
+      <c r="F515" s="108" t="s">
+        <v>5186</v>
       </c>
       <c r="G515" s="109" t="s">
-        <v>5193</v>
+        <v>5189</v>
       </c>
       <c r="H515" s="104" t="s">
-        <v>4900</v>
+        <v>4885</v>
       </c>
       <c r="I515" s="104" t="s">
-        <v>4901</v>
+        <v>4886</v>
       </c>
       <c r="J515" s="116" t="s">
-        <v>5359</v>
+        <v>5352</v>
       </c>
       <c r="K515" s="108" t="s">
-        <v>5233</v>
+        <v>5225</v>
       </c>
       <c r="L515" s="109" t="s">
-        <v>5234</v>
+        <v>5226</v>
       </c>
       <c r="M515" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N515" s="85">
         <v>0</v>
@@ -75295,13 +75395,13 @@
         <v>13</v>
       </c>
       <c r="P515" s="85">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q515">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R515" s="100">
-        <v>94517</v>
+        <v>94513</v>
       </c>
       <c r="T515" s="85">
         <v>0</v>
@@ -75314,40 +75414,40 @@
     </row>
     <row r="516" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B516" s="85">
-        <v>800048</v>
+        <v>800044</v>
       </c>
       <c r="C516" s="104" t="s">
-        <v>4902</v>
+        <v>4887</v>
       </c>
       <c r="D516" s="104" t="s">
-        <v>4903</v>
+        <v>4887</v>
       </c>
       <c r="E516" s="117" t="s">
-        <v>5360</v>
-      </c>
-      <c r="F516" s="112" t="s">
-        <v>5115</v>
-      </c>
-      <c r="G516" s="108" t="s">
-        <v>5116</v>
+        <v>5350</v>
+      </c>
+      <c r="F516" s="108" t="s">
+        <v>5187</v>
+      </c>
+      <c r="G516" s="109" t="s">
+        <v>5188</v>
       </c>
       <c r="H516" s="104" t="s">
-        <v>4904</v>
+        <v>4888</v>
       </c>
       <c r="I516" s="104" t="s">
-        <v>4905</v>
+        <v>4889</v>
       </c>
       <c r="J516" s="116" t="s">
-        <v>5363</v>
+        <v>5353</v>
       </c>
       <c r="K516" s="108" t="s">
-        <v>5235</v>
+        <v>5227</v>
       </c>
       <c r="L516" s="109" t="s">
-        <v>5238</v>
+        <v>5228</v>
       </c>
       <c r="M516" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N516" s="85">
         <v>0</v>
@@ -75356,13 +75456,13 @@
         <v>13</v>
       </c>
       <c r="P516" s="85">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Q516">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="R516" s="100">
-        <v>94518</v>
+        <v>94514</v>
       </c>
       <c r="T516" s="85">
         <v>0</v>
@@ -75375,37 +75475,37 @@
     </row>
     <row r="517" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B517" s="85">
-        <v>800049</v>
+        <v>800045</v>
       </c>
       <c r="C517" s="104" t="s">
-        <v>4906</v>
+        <v>4890</v>
       </c>
       <c r="D517" s="104" t="s">
-        <v>4907</v>
+        <v>4891</v>
       </c>
       <c r="E517" s="117" t="s">
-        <v>5361</v>
+        <v>5354</v>
       </c>
       <c r="F517" s="112" t="s">
-        <v>5194</v>
-      </c>
-      <c r="G517" s="109" t="s">
-        <v>5195</v>
+        <v>5113</v>
+      </c>
+      <c r="G517" s="108" t="s">
+        <v>5114</v>
       </c>
       <c r="H517" s="104" t="s">
-        <v>4908</v>
+        <v>4892</v>
       </c>
       <c r="I517" s="104" t="s">
-        <v>4909</v>
+        <v>4893</v>
       </c>
       <c r="J517" s="116" t="s">
-        <v>5364</v>
+        <v>5357</v>
       </c>
       <c r="K517" s="108" t="s">
-        <v>5236</v>
+        <v>5229</v>
       </c>
       <c r="L517" s="109" t="s">
-        <v>5240</v>
+        <v>5230</v>
       </c>
       <c r="M517" s="99">
         <v>1</v>
@@ -75417,13 +75517,13 @@
         <v>13</v>
       </c>
       <c r="P517" s="85">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q517">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R517" s="100">
-        <v>94519</v>
+        <v>94515</v>
       </c>
       <c r="T517" s="85">
         <v>0</v>
@@ -75436,40 +75536,40 @@
     </row>
     <row r="518" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B518" s="85">
-        <v>800050</v>
+        <v>800046</v>
       </c>
       <c r="C518" s="104" t="s">
-        <v>4910</v>
+        <v>4894</v>
       </c>
       <c r="D518" s="104" t="s">
-        <v>4911</v>
+        <v>4895</v>
       </c>
       <c r="E518" s="117" t="s">
-        <v>5362</v>
+        <v>5355</v>
       </c>
       <c r="F518" s="112" t="s">
-        <v>5196</v>
+        <v>5190</v>
       </c>
       <c r="G518" s="109" t="s">
-        <v>5197</v>
+        <v>5191</v>
       </c>
       <c r="H518" s="104" t="s">
-        <v>4912</v>
+        <v>4896</v>
       </c>
       <c r="I518" s="104" t="s">
-        <v>4913</v>
+        <v>4897</v>
       </c>
       <c r="J518" s="116" t="s">
-        <v>5365</v>
+        <v>5358</v>
       </c>
       <c r="K518" s="108" t="s">
-        <v>5237</v>
+        <v>5231</v>
       </c>
       <c r="L518" s="109" t="s">
-        <v>5239</v>
+        <v>5232</v>
       </c>
       <c r="M518" s="103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N518" s="85">
         <v>0</v>
@@ -75478,13 +75578,13 @@
         <v>13</v>
       </c>
       <c r="P518" s="85">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q518">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R518" s="100">
-        <v>94520</v>
+        <v>94516</v>
       </c>
       <c r="T518" s="85">
         <v>0</v>
@@ -75497,40 +75597,40 @@
     </row>
     <row r="519" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B519" s="85">
-        <v>800051</v>
+        <v>800047</v>
       </c>
       <c r="C519" s="104" t="s">
-        <v>4914</v>
-      </c>
-      <c r="D519" s="119" t="s">
-        <v>5448</v>
-      </c>
-      <c r="E519" s="108" t="s">
-        <v>5366</v>
+        <v>4898</v>
+      </c>
+      <c r="D519" s="104" t="s">
+        <v>4899</v>
+      </c>
+      <c r="E519" s="117" t="s">
+        <v>5356</v>
       </c>
       <c r="F519" s="112" t="s">
-        <v>5117</v>
-      </c>
-      <c r="G519" s="108" t="s">
-        <v>5118</v>
+        <v>5192</v>
+      </c>
+      <c r="G519" s="109" t="s">
+        <v>5193</v>
       </c>
       <c r="H519" s="104" t="s">
-        <v>4915</v>
-      </c>
-      <c r="I519" s="119" t="s">
-        <v>5451</v>
-      </c>
-      <c r="J519" s="108" t="s">
-        <v>5380</v>
+        <v>4900</v>
+      </c>
+      <c r="I519" s="104" t="s">
+        <v>4901</v>
+      </c>
+      <c r="J519" s="116" t="s">
+        <v>5359</v>
       </c>
       <c r="K519" s="108" t="s">
-        <v>5241</v>
-      </c>
-      <c r="L519" s="108" t="s">
-        <v>5242</v>
+        <v>5233</v>
+      </c>
+      <c r="L519" s="109" t="s">
+        <v>5234</v>
       </c>
       <c r="M519" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N519" s="85">
         <v>0</v>
@@ -75539,10 +75639,13 @@
         <v>13</v>
       </c>
       <c r="P519" s="85">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="Q519">
+        <v>1063</v>
       </c>
       <c r="R519" s="100">
-        <v>94521</v>
+        <v>94517</v>
       </c>
       <c r="T519" s="85">
         <v>0</v>
@@ -75555,37 +75658,37 @@
     </row>
     <row r="520" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B520" s="85">
-        <v>800052</v>
+        <v>800048</v>
       </c>
       <c r="C520" s="104" t="s">
-        <v>4916</v>
-      </c>
-      <c r="D520" s="119" t="s">
-        <v>5449</v>
-      </c>
-      <c r="E520" s="108" t="s">
-        <v>5367</v>
+        <v>4902</v>
+      </c>
+      <c r="D520" s="104" t="s">
+        <v>4903</v>
+      </c>
+      <c r="E520" s="117" t="s">
+        <v>5360</v>
       </c>
       <c r="F520" s="112" t="s">
-        <v>5119</v>
+        <v>5115</v>
       </c>
       <c r="G520" s="108" t="s">
-        <v>5120</v>
+        <v>5116</v>
       </c>
       <c r="H520" s="104" t="s">
-        <v>4917</v>
-      </c>
-      <c r="I520" s="119" t="s">
-        <v>5452</v>
-      </c>
-      <c r="J520" s="108" t="s">
-        <v>5381</v>
+        <v>4904</v>
+      </c>
+      <c r="I520" s="104" t="s">
+        <v>4905</v>
+      </c>
+      <c r="J520" s="116" t="s">
+        <v>5363</v>
       </c>
       <c r="K520" s="108" t="s">
-        <v>5243</v>
-      </c>
-      <c r="L520" s="108" t="s">
-        <v>5244</v>
+        <v>5235</v>
+      </c>
+      <c r="L520" s="109" t="s">
+        <v>5238</v>
       </c>
       <c r="M520" s="99">
         <v>1</v>
@@ -75597,10 +75700,13 @@
         <v>13</v>
       </c>
       <c r="P520" s="85">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="Q520">
+        <v>1064</v>
       </c>
       <c r="R520" s="100">
-        <v>94522</v>
+        <v>94518</v>
       </c>
       <c r="T520" s="85">
         <v>0</v>
@@ -75613,37 +75719,37 @@
     </row>
     <row r="521" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B521" s="85">
-        <v>800053</v>
+        <v>800049</v>
       </c>
       <c r="C521" s="104" t="s">
-        <v>4918</v>
+        <v>4906</v>
       </c>
       <c r="D521" s="104" t="s">
-        <v>4919</v>
-      </c>
-      <c r="E521" s="108" t="s">
-        <v>5368</v>
+        <v>4907</v>
+      </c>
+      <c r="E521" s="117" t="s">
+        <v>5361</v>
       </c>
       <c r="F521" s="112" t="s">
-        <v>5121</v>
-      </c>
-      <c r="G521" s="108" t="s">
-        <v>5122</v>
+        <v>5194</v>
+      </c>
+      <c r="G521" s="109" t="s">
+        <v>5195</v>
       </c>
       <c r="H521" s="104" t="s">
-        <v>4920</v>
+        <v>4908</v>
       </c>
       <c r="I521" s="104" t="s">
-        <v>4921</v>
-      </c>
-      <c r="J521" s="108" t="s">
-        <v>5382</v>
+        <v>4909</v>
+      </c>
+      <c r="J521" s="116" t="s">
+        <v>5364</v>
       </c>
       <c r="K521" s="108" t="s">
-        <v>5245</v>
-      </c>
-      <c r="L521" s="108" t="s">
-        <v>5246</v>
+        <v>5236</v>
+      </c>
+      <c r="L521" s="109" t="s">
+        <v>5240</v>
       </c>
       <c r="M521" s="99">
         <v>1</v>
@@ -75655,10 +75761,13 @@
         <v>13</v>
       </c>
       <c r="P521" s="85">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="Q521">
+        <v>1064</v>
       </c>
       <c r="R521" s="100">
-        <v>94523</v>
+        <v>94519</v>
       </c>
       <c r="T521" s="85">
         <v>0</v>
@@ -75671,40 +75780,40 @@
     </row>
     <row r="522" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B522" s="85">
-        <v>800054</v>
+        <v>800050</v>
       </c>
       <c r="C522" s="104" t="s">
-        <v>4922</v>
-      </c>
-      <c r="D522" s="119" t="s">
-        <v>5450</v>
-      </c>
-      <c r="E522" s="108" t="s">
-        <v>5369</v>
+        <v>4910</v>
+      </c>
+      <c r="D522" s="104" t="s">
+        <v>4911</v>
+      </c>
+      <c r="E522" s="117" t="s">
+        <v>5362</v>
       </c>
       <c r="F522" s="112" t="s">
-        <v>5123</v>
-      </c>
-      <c r="G522" s="108" t="s">
-        <v>5124</v>
+        <v>5196</v>
+      </c>
+      <c r="G522" s="109" t="s">
+        <v>5197</v>
       </c>
       <c r="H522" s="104" t="s">
-        <v>4923</v>
-      </c>
-      <c r="I522" s="119" t="s">
-        <v>5453</v>
-      </c>
-      <c r="J522" s="108" t="s">
-        <v>5383</v>
+        <v>4912</v>
+      </c>
+      <c r="I522" s="104" t="s">
+        <v>4913</v>
+      </c>
+      <c r="J522" s="116" t="s">
+        <v>5365</v>
       </c>
       <c r="K522" s="108" t="s">
-        <v>5247</v>
-      </c>
-      <c r="L522" s="108" t="s">
-        <v>5248</v>
+        <v>5237</v>
+      </c>
+      <c r="L522" s="109" t="s">
+        <v>5239</v>
       </c>
       <c r="M522" s="103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N522" s="85">
         <v>0</v>
@@ -75713,10 +75822,13 @@
         <v>13</v>
       </c>
       <c r="P522" s="85">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="Q522">
+        <v>1064</v>
       </c>
       <c r="R522" s="100">
-        <v>94524</v>
+        <v>94520</v>
       </c>
       <c r="T522" s="85">
         <v>0</v>
@@ -75729,37 +75841,37 @@
     </row>
     <row r="523" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B523" s="85">
-        <v>800055</v>
+        <v>800051</v>
       </c>
       <c r="C523" s="104" t="s">
-        <v>4924</v>
+        <v>4914</v>
       </c>
       <c r="D523" s="119" t="s">
-        <v>5455</v>
+        <v>5448</v>
       </c>
       <c r="E523" s="108" t="s">
-        <v>5370</v>
+        <v>5366</v>
       </c>
       <c r="F523" s="112" t="s">
-        <v>5125</v>
+        <v>5117</v>
       </c>
       <c r="G523" s="108" t="s">
-        <v>5126</v>
+        <v>5118</v>
       </c>
       <c r="H523" s="104" t="s">
-        <v>4925</v>
-      </c>
-      <c r="I523" s="104" t="s">
-        <v>4926</v>
+        <v>4915</v>
+      </c>
+      <c r="I523" s="119" t="s">
+        <v>5451</v>
       </c>
       <c r="J523" s="108" t="s">
-        <v>5384</v>
+        <v>5380</v>
       </c>
       <c r="K523" s="108" t="s">
-        <v>5249</v>
+        <v>5241</v>
       </c>
       <c r="L523" s="108" t="s">
-        <v>5250</v>
+        <v>5242</v>
       </c>
       <c r="M523" s="99">
         <v>1</v>
@@ -75771,10 +75883,10 @@
         <v>13</v>
       </c>
       <c r="P523" s="85">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R523" s="100">
-        <v>94525</v>
+        <v>94521</v>
       </c>
       <c r="T523" s="85">
         <v>0</v>
@@ -75787,40 +75899,40 @@
     </row>
     <row r="524" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B524" s="85">
-        <v>800056</v>
+        <v>800052</v>
       </c>
       <c r="C524" s="104" t="s">
-        <v>4927</v>
-      </c>
-      <c r="D524" s="104" t="s">
-        <v>4928</v>
+        <v>4916</v>
+      </c>
+      <c r="D524" s="119" t="s">
+        <v>5449</v>
       </c>
       <c r="E524" s="108" t="s">
-        <v>5371</v>
+        <v>5367</v>
       </c>
       <c r="F524" s="112" t="s">
-        <v>5127</v>
+        <v>5119</v>
       </c>
       <c r="G524" s="108" t="s">
-        <v>5128</v>
+        <v>5120</v>
       </c>
       <c r="H524" s="104" t="s">
-        <v>4929</v>
-      </c>
-      <c r="I524" s="104" t="s">
-        <v>4930</v>
+        <v>4917</v>
+      </c>
+      <c r="I524" s="119" t="s">
+        <v>5452</v>
       </c>
       <c r="J524" s="108" t="s">
-        <v>5385</v>
+        <v>5381</v>
       </c>
       <c r="K524" s="108" t="s">
-        <v>5251</v>
+        <v>5243</v>
       </c>
       <c r="L524" s="108" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
       <c r="M524" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N524" s="85">
         <v>0</v>
@@ -75829,10 +75941,10 @@
         <v>13</v>
       </c>
       <c r="P524" s="85">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="R524" s="100">
-        <v>94526</v>
+        <v>94522</v>
       </c>
       <c r="T524" s="85">
         <v>0</v>
@@ -75845,37 +75957,37 @@
     </row>
     <row r="525" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B525" s="85">
-        <v>800057</v>
+        <v>800053</v>
       </c>
       <c r="C525" s="104" t="s">
-        <v>4931</v>
+        <v>4918</v>
       </c>
       <c r="D525" s="104" t="s">
-        <v>4932</v>
+        <v>4919</v>
       </c>
       <c r="E525" s="108" t="s">
-        <v>5372</v>
+        <v>5368</v>
       </c>
       <c r="F525" s="112" t="s">
-        <v>5129</v>
+        <v>5121</v>
       </c>
       <c r="G525" s="108" t="s">
-        <v>5130</v>
+        <v>5122</v>
       </c>
       <c r="H525" s="104" t="s">
-        <v>4933</v>
+        <v>4920</v>
       </c>
       <c r="I525" s="104" t="s">
-        <v>4934</v>
+        <v>4921</v>
       </c>
       <c r="J525" s="108" t="s">
-        <v>5386</v>
+        <v>5382</v>
       </c>
       <c r="K525" s="108" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="L525" s="108" t="s">
-        <v>5254</v>
+        <v>5246</v>
       </c>
       <c r="M525" s="99">
         <v>1</v>
@@ -75887,10 +75999,10 @@
         <v>13</v>
       </c>
       <c r="P525" s="85">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R525" s="100">
-        <v>94527</v>
+        <v>94523</v>
       </c>
       <c r="T525" s="85">
         <v>0</v>
@@ -75903,37 +76015,37 @@
     </row>
     <row r="526" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B526" s="85">
-        <v>800058</v>
+        <v>800054</v>
       </c>
       <c r="C526" s="104" t="s">
-        <v>4935</v>
+        <v>4922</v>
       </c>
       <c r="D526" s="119" t="s">
-        <v>5454</v>
+        <v>5450</v>
       </c>
       <c r="E526" s="108" t="s">
-        <v>5373</v>
+        <v>5369</v>
       </c>
       <c r="F526" s="112" t="s">
-        <v>5131</v>
+        <v>5123</v>
       </c>
       <c r="G526" s="108" t="s">
-        <v>5132</v>
+        <v>5124</v>
       </c>
       <c r="H526" s="104" t="s">
-        <v>4936</v>
-      </c>
-      <c r="I526" s="104" t="s">
-        <v>4937</v>
+        <v>4923</v>
+      </c>
+      <c r="I526" s="119" t="s">
+        <v>5453</v>
       </c>
       <c r="J526" s="108" t="s">
-        <v>5387</v>
+        <v>5383</v>
       </c>
       <c r="K526" s="108" t="s">
-        <v>5255</v>
+        <v>5247</v>
       </c>
       <c r="L526" s="108" t="s">
-        <v>5256</v>
+        <v>5248</v>
       </c>
       <c r="M526" s="103">
         <v>1</v>
@@ -75945,10 +76057,10 @@
         <v>13</v>
       </c>
       <c r="P526" s="85">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R526" s="100">
-        <v>94528</v>
+        <v>94524</v>
       </c>
       <c r="T526" s="85">
         <v>0</v>
@@ -75961,37 +76073,37 @@
     </row>
     <row r="527" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B527" s="85">
-        <v>800059</v>
+        <v>800055</v>
       </c>
       <c r="C527" s="104" t="s">
-        <v>4938</v>
+        <v>4924</v>
       </c>
       <c r="D527" s="119" t="s">
-        <v>5456</v>
+        <v>5455</v>
       </c>
       <c r="E527" s="108" t="s">
-        <v>5374</v>
+        <v>5370</v>
       </c>
       <c r="F527" s="112" t="s">
-        <v>5133</v>
+        <v>5125</v>
       </c>
       <c r="G527" s="108" t="s">
-        <v>5134</v>
+        <v>5126</v>
       </c>
       <c r="H527" s="104" t="s">
-        <v>4939</v>
-      </c>
-      <c r="I527" s="119" t="s">
-        <v>5457</v>
+        <v>4925</v>
+      </c>
+      <c r="I527" s="104" t="s">
+        <v>4926</v>
       </c>
       <c r="J527" s="108" t="s">
-        <v>5388</v>
+        <v>5384</v>
       </c>
       <c r="K527" s="108" t="s">
-        <v>5257</v>
+        <v>5249</v>
       </c>
       <c r="L527" s="108" t="s">
-        <v>5258</v>
+        <v>5250</v>
       </c>
       <c r="M527" s="99">
         <v>1</v>
@@ -76003,10 +76115,10 @@
         <v>13</v>
       </c>
       <c r="P527" s="85">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R527" s="100">
-        <v>94529</v>
+        <v>94525</v>
       </c>
       <c r="T527" s="85">
         <v>0</v>
@@ -76019,37 +76131,37 @@
     </row>
     <row r="528" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B528" s="85">
-        <v>800060</v>
-      </c>
-      <c r="C528" s="105" t="s">
-        <v>4940</v>
-      </c>
-      <c r="D528" s="105" t="s">
-        <v>4941</v>
+        <v>800056</v>
+      </c>
+      <c r="C528" s="104" t="s">
+        <v>4927</v>
+      </c>
+      <c r="D528" s="104" t="s">
+        <v>4928</v>
       </c>
       <c r="E528" s="108" t="s">
-        <v>5375</v>
+        <v>5371</v>
       </c>
       <c r="F528" s="112" t="s">
-        <v>5135</v>
+        <v>5127</v>
       </c>
       <c r="G528" s="108" t="s">
-        <v>5136</v>
+        <v>5128</v>
       </c>
       <c r="H528" s="104" t="s">
-        <v>4942</v>
+        <v>4929</v>
       </c>
       <c r="I528" s="104" t="s">
-        <v>4943</v>
+        <v>4930</v>
       </c>
       <c r="J528" s="108" t="s">
-        <v>5389</v>
+        <v>5385</v>
       </c>
       <c r="K528" s="108" t="s">
-        <v>5259</v>
+        <v>5251</v>
       </c>
       <c r="L528" s="108" t="s">
-        <v>5260</v>
+        <v>5252</v>
       </c>
       <c r="M528" s="99">
         <v>2</v>
@@ -76061,10 +76173,10 @@
         <v>13</v>
       </c>
       <c r="P528" s="85">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R528" s="100">
-        <v>94530</v>
+        <v>94526</v>
       </c>
       <c r="T528" s="85">
         <v>0</v>
@@ -76077,40 +76189,40 @@
     </row>
     <row r="529" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B529" s="85">
-        <v>800061</v>
+        <v>800057</v>
       </c>
       <c r="C529" s="104" t="s">
-        <v>4944</v>
+        <v>4931</v>
       </c>
       <c r="D529" s="104" t="s">
-        <v>4945</v>
+        <v>4932</v>
       </c>
       <c r="E529" s="108" t="s">
-        <v>5376</v>
+        <v>5372</v>
       </c>
       <c r="F529" s="112" t="s">
-        <v>5137</v>
+        <v>5129</v>
       </c>
       <c r="G529" s="108" t="s">
-        <v>5138</v>
+        <v>5130</v>
       </c>
       <c r="H529" s="104" t="s">
-        <v>4946</v>
+        <v>4933</v>
       </c>
       <c r="I529" s="104" t="s">
-        <v>4947</v>
+        <v>4934</v>
       </c>
       <c r="J529" s="108" t="s">
-        <v>5390</v>
+        <v>5386</v>
       </c>
       <c r="K529" s="108" t="s">
-        <v>5261</v>
+        <v>5253</v>
       </c>
       <c r="L529" s="108" t="s">
-        <v>5262</v>
+        <v>5254</v>
       </c>
       <c r="M529" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N529" s="85">
         <v>0</v>
@@ -76119,10 +76231,10 @@
         <v>13</v>
       </c>
       <c r="P529" s="85">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R529" s="100">
-        <v>94531</v>
+        <v>94527</v>
       </c>
       <c r="T529" s="85">
         <v>0</v>
@@ -76135,40 +76247,40 @@
     </row>
     <row r="530" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B530" s="85">
-        <v>800062</v>
+        <v>800058</v>
       </c>
       <c r="C530" s="104" t="s">
-        <v>4948</v>
-      </c>
-      <c r="D530" s="104" t="s">
-        <v>4949</v>
+        <v>4935</v>
+      </c>
+      <c r="D530" s="119" t="s">
+        <v>5454</v>
       </c>
       <c r="E530" s="108" t="s">
-        <v>5377</v>
+        <v>5373</v>
       </c>
       <c r="F530" s="112" t="s">
-        <v>5139</v>
+        <v>5131</v>
       </c>
       <c r="G530" s="108" t="s">
-        <v>5140</v>
+        <v>5132</v>
       </c>
       <c r="H530" s="104" t="s">
-        <v>4950</v>
+        <v>4936</v>
       </c>
       <c r="I530" s="104" t="s">
-        <v>4951</v>
+        <v>4937</v>
       </c>
       <c r="J530" s="108" t="s">
-        <v>5391</v>
+        <v>5387</v>
       </c>
       <c r="K530" s="108" t="s">
-        <v>5263</v>
+        <v>5255</v>
       </c>
       <c r="L530" s="108" t="s">
-        <v>5264</v>
+        <v>5256</v>
       </c>
       <c r="M530" s="103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N530" s="85">
         <v>0</v>
@@ -76177,10 +76289,10 @@
         <v>13</v>
       </c>
       <c r="P530" s="85">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R530" s="100">
-        <v>94532</v>
+        <v>94528</v>
       </c>
       <c r="T530" s="85">
         <v>0</v>
@@ -76193,40 +76305,40 @@
     </row>
     <row r="531" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B531" s="85">
-        <v>800063</v>
+        <v>800059</v>
       </c>
       <c r="C531" s="104" t="s">
-        <v>4952</v>
-      </c>
-      <c r="D531" s="104" t="s">
-        <v>4952</v>
+        <v>4938</v>
+      </c>
+      <c r="D531" s="119" t="s">
+        <v>5456</v>
       </c>
       <c r="E531" s="108" t="s">
-        <v>5378</v>
+        <v>5374</v>
       </c>
       <c r="F531" s="112" t="s">
-        <v>5141</v>
+        <v>5133</v>
       </c>
       <c r="G531" s="108" t="s">
-        <v>5142</v>
+        <v>5134</v>
       </c>
       <c r="H531" s="104" t="s">
-        <v>4953</v>
-      </c>
-      <c r="I531" s="104" t="s">
-        <v>4954</v>
+        <v>4939</v>
+      </c>
+      <c r="I531" s="119" t="s">
+        <v>5457</v>
       </c>
       <c r="J531" s="108" t="s">
-        <v>5392</v>
+        <v>5388</v>
       </c>
       <c r="K531" s="108" t="s">
-        <v>5265</v>
+        <v>5257</v>
       </c>
       <c r="L531" s="108" t="s">
-        <v>5266</v>
+        <v>5258</v>
       </c>
       <c r="M531" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N531" s="85">
         <v>0</v>
@@ -76235,10 +76347,10 @@
         <v>13</v>
       </c>
       <c r="P531" s="85">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R531" s="100">
-        <v>94533</v>
+        <v>94529</v>
       </c>
       <c r="T531" s="85">
         <v>0</v>
@@ -76251,37 +76363,37 @@
     </row>
     <row r="532" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B532" s="85">
-        <v>800064</v>
-      </c>
-      <c r="C532" s="104" t="s">
-        <v>4955</v>
-      </c>
-      <c r="D532" s="104" t="s">
-        <v>4955</v>
+        <v>800060</v>
+      </c>
+      <c r="C532" s="105" t="s">
+        <v>4940</v>
+      </c>
+      <c r="D532" s="105" t="s">
+        <v>4941</v>
       </c>
       <c r="E532" s="108" t="s">
-        <v>5379</v>
+        <v>5375</v>
       </c>
       <c r="F532" s="112" t="s">
-        <v>5143</v>
+        <v>5135</v>
       </c>
       <c r="G532" s="108" t="s">
-        <v>5144</v>
+        <v>5136</v>
       </c>
       <c r="H532" s="104" t="s">
-        <v>4956</v>
+        <v>4942</v>
       </c>
       <c r="I532" s="104" t="s">
-        <v>4957</v>
+        <v>4943</v>
       </c>
       <c r="J532" s="108" t="s">
-        <v>5393</v>
+        <v>5389</v>
       </c>
       <c r="K532" s="108" t="s">
-        <v>5267</v>
+        <v>5259</v>
       </c>
       <c r="L532" s="108" t="s">
-        <v>5268</v>
+        <v>5260</v>
       </c>
       <c r="M532" s="99">
         <v>2</v>
@@ -76293,10 +76405,10 @@
         <v>13</v>
       </c>
       <c r="P532" s="85">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R532" s="100">
-        <v>94534</v>
+        <v>94530</v>
       </c>
       <c r="T532" s="85">
         <v>0</v>
@@ -76307,42 +76419,42 @@
       <c r="Z532" s="101"/>
       <c r="AA532" s="101"/>
     </row>
-    <row r="533" spans="2:27" s="85" customFormat="1" ht="16.5">
+    <row r="533" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B533" s="85">
-        <v>800065</v>
+        <v>800061</v>
       </c>
       <c r="C533" s="104" t="s">
-        <v>4958</v>
+        <v>4944</v>
       </c>
       <c r="D533" s="104" t="s">
-        <v>4959</v>
+        <v>4945</v>
       </c>
       <c r="E533" s="108" t="s">
-        <v>5394</v>
-      </c>
-      <c r="F533" s="108" t="s">
-        <v>5145</v>
+        <v>5376</v>
+      </c>
+      <c r="F533" s="112" t="s">
+        <v>5137</v>
       </c>
       <c r="G533" s="108" t="s">
-        <v>5146</v>
+        <v>5138</v>
       </c>
       <c r="H533" s="104" t="s">
-        <v>4960</v>
+        <v>4946</v>
       </c>
       <c r="I533" s="104" t="s">
-        <v>4961</v>
+        <v>4947</v>
       </c>
       <c r="J533" s="108" t="s">
-        <v>5398</v>
+        <v>5390</v>
       </c>
       <c r="K533" s="108" t="s">
-        <v>5269</v>
+        <v>5261</v>
       </c>
       <c r="L533" s="108" t="s">
-        <v>5270</v>
+        <v>5262</v>
       </c>
       <c r="M533" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N533" s="85">
         <v>0</v>
@@ -76351,10 +76463,10 @@
         <v>13</v>
       </c>
       <c r="P533" s="85">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R533" s="100">
-        <v>94535</v>
+        <v>94531</v>
       </c>
       <c r="T533" s="85">
         <v>0</v>
@@ -76367,40 +76479,40 @@
     </row>
     <row r="534" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B534" s="85">
-        <v>800066</v>
+        <v>800062</v>
       </c>
       <c r="C534" s="104" t="s">
-        <v>4962</v>
+        <v>4948</v>
       </c>
       <c r="D534" s="104" t="s">
-        <v>4963</v>
+        <v>4949</v>
       </c>
       <c r="E534" s="108" t="s">
-        <v>5395</v>
-      </c>
-      <c r="F534" s="108" t="s">
-        <v>5147</v>
+        <v>5377</v>
+      </c>
+      <c r="F534" s="112" t="s">
+        <v>5139</v>
       </c>
       <c r="G534" s="108" t="s">
-        <v>5148</v>
+        <v>5140</v>
       </c>
       <c r="H534" s="104" t="s">
-        <v>4964</v>
+        <v>4950</v>
       </c>
       <c r="I534" s="104" t="s">
-        <v>4965</v>
+        <v>4951</v>
       </c>
       <c r="J534" s="108" t="s">
-        <v>5399</v>
+        <v>5391</v>
       </c>
       <c r="K534" s="108" t="s">
-        <v>5271</v>
+        <v>5263</v>
       </c>
       <c r="L534" s="108" t="s">
-        <v>5272</v>
+        <v>5264</v>
       </c>
       <c r="M534" s="103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N534" s="85">
         <v>0</v>
@@ -76409,13 +76521,10 @@
         <v>13</v>
       </c>
       <c r="P534" s="85">
-        <v>36</v>
-      </c>
-      <c r="Q534">
-        <v>1065</v>
+        <v>32</v>
       </c>
       <c r="R534" s="100">
-        <v>94536</v>
+        <v>94532</v>
       </c>
       <c r="T534" s="85">
         <v>0</v>
@@ -76428,37 +76537,37 @@
     </row>
     <row r="535" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B535" s="85">
-        <v>800067</v>
+        <v>800063</v>
       </c>
       <c r="C535" s="104" t="s">
-        <v>4966</v>
+        <v>4952</v>
       </c>
       <c r="D535" s="104" t="s">
-        <v>4967</v>
+        <v>4952</v>
       </c>
       <c r="E535" s="108" t="s">
-        <v>5396</v>
-      </c>
-      <c r="F535" s="108" t="s">
-        <v>5149</v>
+        <v>5378</v>
+      </c>
+      <c r="F535" s="112" t="s">
+        <v>5141</v>
       </c>
       <c r="G535" s="108" t="s">
-        <v>5150</v>
+        <v>5142</v>
       </c>
       <c r="H535" s="104" t="s">
-        <v>4968</v>
+        <v>4953</v>
       </c>
       <c r="I535" s="104" t="s">
-        <v>4969</v>
+        <v>4954</v>
       </c>
       <c r="J535" s="108" t="s">
-        <v>5400</v>
+        <v>5392</v>
       </c>
       <c r="K535" s="108" t="s">
-        <v>5273</v>
+        <v>5265</v>
       </c>
       <c r="L535" s="108" t="s">
-        <v>5274</v>
+        <v>5266</v>
       </c>
       <c r="M535" s="99">
         <v>2</v>
@@ -76470,13 +76579,10 @@
         <v>13</v>
       </c>
       <c r="P535" s="85">
-        <v>37</v>
-      </c>
-      <c r="Q535">
-        <v>1065</v>
+        <v>33</v>
       </c>
       <c r="R535" s="100">
-        <v>94537</v>
+        <v>94533</v>
       </c>
       <c r="T535" s="85">
         <v>0</v>
@@ -76489,40 +76595,40 @@
     </row>
     <row r="536" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B536" s="85">
-        <v>800068</v>
+        <v>800064</v>
       </c>
       <c r="C536" s="104" t="s">
-        <v>4970</v>
+        <v>4955</v>
       </c>
       <c r="D536" s="104" t="s">
-        <v>4971</v>
+        <v>4955</v>
       </c>
       <c r="E536" s="108" t="s">
-        <v>5397</v>
-      </c>
-      <c r="F536" s="108" t="s">
-        <v>5151</v>
+        <v>5379</v>
+      </c>
+      <c r="F536" s="112" t="s">
+        <v>5143</v>
       </c>
       <c r="G536" s="108" t="s">
-        <v>5152</v>
+        <v>5144</v>
       </c>
       <c r="H536" s="104" t="s">
-        <v>4972</v>
+        <v>4956</v>
       </c>
       <c r="I536" s="104" t="s">
-        <v>4973</v>
+        <v>4957</v>
       </c>
       <c r="J536" s="108" t="s">
-        <v>5401</v>
+        <v>5393</v>
       </c>
       <c r="K536" s="108" t="s">
-        <v>5275</v>
+        <v>5267</v>
       </c>
       <c r="L536" s="108" t="s">
-        <v>5276</v>
+        <v>5268</v>
       </c>
       <c r="M536" s="99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N536" s="85">
         <v>0</v>
@@ -76531,13 +76637,10 @@
         <v>13</v>
       </c>
       <c r="P536" s="85">
-        <v>38</v>
-      </c>
-      <c r="Q536">
-        <v>1065</v>
+        <v>34</v>
       </c>
       <c r="R536" s="100">
-        <v>94538</v>
+        <v>94534</v>
       </c>
       <c r="T536" s="85">
         <v>0</v>
@@ -76548,39 +76651,39 @@
       <c r="Z536" s="101"/>
       <c r="AA536" s="101"/>
     </row>
-    <row r="537" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="537" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B537" s="85">
-        <v>800069</v>
+        <v>800065</v>
       </c>
       <c r="C537" s="104" t="s">
-        <v>4974</v>
+        <v>4958</v>
       </c>
       <c r="D537" s="104" t="s">
-        <v>4975</v>
-      </c>
-      <c r="E537" s="117" t="s">
-        <v>5402</v>
+        <v>4959</v>
+      </c>
+      <c r="E537" s="108" t="s">
+        <v>5394</v>
       </c>
       <c r="F537" s="108" t="s">
-        <v>5153</v>
+        <v>5145</v>
       </c>
       <c r="G537" s="108" t="s">
-        <v>5154</v>
+        <v>5146</v>
       </c>
       <c r="H537" s="104" t="s">
-        <v>4976</v>
+        <v>4960</v>
       </c>
       <c r="I537" s="104" t="s">
-        <v>4977</v>
-      </c>
-      <c r="J537" s="116" t="s">
-        <v>5437</v>
+        <v>4961</v>
+      </c>
+      <c r="J537" s="108" t="s">
+        <v>5398</v>
       </c>
       <c r="K537" s="108" t="s">
-        <v>5277</v>
-      </c>
-      <c r="L537" s="109" t="s">
-        <v>5280</v>
+        <v>5269</v>
+      </c>
+      <c r="L537" s="108" t="s">
+        <v>5270</v>
       </c>
       <c r="M537" s="99">
         <v>1</v>
@@ -76592,13 +76695,10 @@
         <v>13</v>
       </c>
       <c r="P537" s="85">
-        <v>39</v>
-      </c>
-      <c r="Q537">
-        <v>1066</v>
+        <v>35</v>
       </c>
       <c r="R537" s="100">
-        <v>94539</v>
+        <v>94535</v>
       </c>
       <c r="T537" s="85">
         <v>0</v>
@@ -76611,37 +76711,37 @@
     </row>
     <row r="538" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B538" s="85">
-        <v>800070</v>
+        <v>800066</v>
       </c>
       <c r="C538" s="104" t="s">
-        <v>4978</v>
+        <v>4962</v>
       </c>
       <c r="D538" s="104" t="s">
-        <v>4979</v>
-      </c>
-      <c r="E538" s="117" t="s">
-        <v>5403</v>
+        <v>4963</v>
+      </c>
+      <c r="E538" s="108" t="s">
+        <v>5395</v>
       </c>
       <c r="F538" s="108" t="s">
-        <v>5200</v>
-      </c>
-      <c r="G538" s="109" t="s">
-        <v>5201</v>
+        <v>5147</v>
+      </c>
+      <c r="G538" s="108" t="s">
+        <v>5148</v>
       </c>
       <c r="H538" s="104" t="s">
-        <v>4980</v>
+        <v>4964</v>
       </c>
       <c r="I538" s="104" t="s">
-        <v>4981</v>
-      </c>
-      <c r="J538" s="116" t="s">
-        <v>5438</v>
+        <v>4965</v>
+      </c>
+      <c r="J538" s="108" t="s">
+        <v>5399</v>
       </c>
       <c r="K538" s="108" t="s">
-        <v>5278</v>
-      </c>
-      <c r="L538" s="109" t="s">
-        <v>5281</v>
+        <v>5271</v>
+      </c>
+      <c r="L538" s="108" t="s">
+        <v>5272</v>
       </c>
       <c r="M538" s="103">
         <v>1</v>
@@ -76653,13 +76753,13 @@
         <v>13</v>
       </c>
       <c r="P538" s="85">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q538">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R538" s="100">
-        <v>94540</v>
+        <v>94536</v>
       </c>
       <c r="T538" s="85">
         <v>0</v>
@@ -76672,37 +76772,37 @@
     </row>
     <row r="539" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B539" s="85">
-        <v>800071</v>
+        <v>800067</v>
       </c>
       <c r="C539" s="104" t="s">
-        <v>4982</v>
+        <v>4966</v>
       </c>
       <c r="D539" s="104" t="s">
-        <v>4983</v>
-      </c>
-      <c r="E539" s="117" t="s">
-        <v>5404</v>
+        <v>4967</v>
+      </c>
+      <c r="E539" s="108" t="s">
+        <v>5396</v>
       </c>
       <c r="F539" s="108" t="s">
-        <v>5198</v>
-      </c>
-      <c r="G539" s="109" t="s">
-        <v>5199</v>
+        <v>5149</v>
+      </c>
+      <c r="G539" s="108" t="s">
+        <v>5150</v>
       </c>
       <c r="H539" s="104" t="s">
-        <v>4984</v>
+        <v>4968</v>
       </c>
       <c r="I539" s="104" t="s">
-        <v>4985</v>
-      </c>
-      <c r="J539" s="116" t="s">
-        <v>5439</v>
+        <v>4969</v>
+      </c>
+      <c r="J539" s="108" t="s">
+        <v>5400</v>
       </c>
       <c r="K539" s="108" t="s">
-        <v>5279</v>
-      </c>
-      <c r="L539" s="109" t="s">
-        <v>5282</v>
+        <v>5273</v>
+      </c>
+      <c r="L539" s="108" t="s">
+        <v>5274</v>
       </c>
       <c r="M539" s="99">
         <v>2</v>
@@ -76714,13 +76814,13 @@
         <v>13</v>
       </c>
       <c r="P539" s="85">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q539">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R539" s="100">
-        <v>94541</v>
+        <v>94537</v>
       </c>
       <c r="T539" s="85">
         <v>0</v>
@@ -76733,40 +76833,40 @@
     </row>
     <row r="540" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B540" s="85">
-        <v>800072</v>
+        <v>800068</v>
       </c>
       <c r="C540" s="104" t="s">
-        <v>4986</v>
+        <v>4970</v>
       </c>
       <c r="D540" s="104" t="s">
-        <v>4987</v>
-      </c>
-      <c r="E540" s="117" t="s">
-        <v>5405</v>
+        <v>4971</v>
+      </c>
+      <c r="E540" s="108" t="s">
+        <v>5397</v>
       </c>
       <c r="F540" s="108" t="s">
-        <v>5204</v>
+        <v>5151</v>
       </c>
       <c r="G540" s="108" t="s">
-        <v>5155</v>
+        <v>5152</v>
       </c>
       <c r="H540" s="104" t="s">
-        <v>4988</v>
+        <v>4972</v>
       </c>
       <c r="I540" s="104" t="s">
-        <v>4989</v>
-      </c>
-      <c r="J540" s="116" t="s">
-        <v>5440</v>
+        <v>4973</v>
+      </c>
+      <c r="J540" s="108" t="s">
+        <v>5401</v>
       </c>
       <c r="K540" s="108" t="s">
-        <v>5283</v>
-      </c>
-      <c r="L540" s="109" t="s">
-        <v>5284</v>
+        <v>5275</v>
+      </c>
+      <c r="L540" s="108" t="s">
+        <v>5276</v>
       </c>
       <c r="M540" s="99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N540" s="85">
         <v>0</v>
@@ -76775,13 +76875,13 @@
         <v>13</v>
       </c>
       <c r="P540" s="85">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q540">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="R540" s="100">
-        <v>94542</v>
+        <v>94538</v>
       </c>
       <c r="T540" s="85">
         <v>0</v>
@@ -76794,37 +76894,37 @@
     </row>
     <row r="541" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B541" s="85">
-        <v>800073</v>
+        <v>800069</v>
       </c>
       <c r="C541" s="104" t="s">
-        <v>4990</v>
+        <v>4974</v>
       </c>
       <c r="D541" s="104" t="s">
-        <v>4991</v>
+        <v>4975</v>
       </c>
       <c r="E541" s="117" t="s">
-        <v>5406</v>
+        <v>5402</v>
       </c>
       <c r="F541" s="108" t="s">
-        <v>5202</v>
-      </c>
-      <c r="G541" s="109" t="s">
-        <v>5203</v>
+        <v>5153</v>
+      </c>
+      <c r="G541" s="108" t="s">
+        <v>5154</v>
       </c>
       <c r="H541" s="104" t="s">
-        <v>4992</v>
+        <v>4976</v>
       </c>
       <c r="I541" s="104" t="s">
-        <v>4993</v>
+        <v>4977</v>
       </c>
       <c r="J541" s="116" t="s">
-        <v>5441</v>
+        <v>5437</v>
       </c>
       <c r="K541" s="108" t="s">
-        <v>5285</v>
+        <v>5277</v>
       </c>
       <c r="L541" s="109" t="s">
-        <v>5286</v>
+        <v>5280</v>
       </c>
       <c r="M541" s="99">
         <v>1</v>
@@ -76836,13 +76936,13 @@
         <v>13</v>
       </c>
       <c r="P541" s="85">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q541">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R541" s="100">
-        <v>94543</v>
+        <v>94539</v>
       </c>
       <c r="T541" s="85">
         <v>0</v>
@@ -76855,40 +76955,40 @@
     </row>
     <row r="542" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B542" s="85">
-        <v>800074</v>
+        <v>800070</v>
       </c>
       <c r="C542" s="104" t="s">
-        <v>4994</v>
+        <v>4978</v>
       </c>
       <c r="D542" s="104" t="s">
-        <v>4995</v>
+        <v>4979</v>
       </c>
       <c r="E542" s="117" t="s">
-        <v>5407</v>
+        <v>5403</v>
       </c>
       <c r="F542" s="108" t="s">
-        <v>5205</v>
+        <v>5200</v>
       </c>
       <c r="G542" s="109" t="s">
-        <v>5206</v>
+        <v>5201</v>
       </c>
       <c r="H542" s="104" t="s">
-        <v>4996</v>
+        <v>4980</v>
       </c>
       <c r="I542" s="104" t="s">
-        <v>4997</v>
+        <v>4981</v>
       </c>
       <c r="J542" s="116" t="s">
-        <v>5442</v>
+        <v>5438</v>
       </c>
       <c r="K542" s="108" t="s">
-        <v>5287</v>
+        <v>5278</v>
       </c>
       <c r="L542" s="109" t="s">
-        <v>5288</v>
+        <v>5281</v>
       </c>
       <c r="M542" s="103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N542" s="85">
         <v>0</v>
@@ -76897,13 +76997,13 @@
         <v>13</v>
       </c>
       <c r="P542" s="85">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q542">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R542" s="100">
-        <v>94544</v>
+        <v>94540</v>
       </c>
       <c r="T542" s="85">
         <v>0</v>
@@ -76916,40 +77016,40 @@
     </row>
     <row r="543" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B543" s="85">
-        <v>800075</v>
+        <v>800071</v>
       </c>
       <c r="C543" s="104" t="s">
-        <v>4998</v>
+        <v>4982</v>
       </c>
       <c r="D543" s="104" t="s">
-        <v>4999</v>
+        <v>4983</v>
       </c>
       <c r="E543" s="117" t="s">
-        <v>5408</v>
+        <v>5404</v>
       </c>
       <c r="F543" s="108" t="s">
-        <v>5156</v>
-      </c>
-      <c r="G543" s="108" t="s">
-        <v>5157</v>
+        <v>5198</v>
+      </c>
+      <c r="G543" s="109" t="s">
+        <v>5199</v>
       </c>
       <c r="H543" s="104" t="s">
-        <v>5000</v>
+        <v>4984</v>
       </c>
       <c r="I543" s="104" t="s">
-        <v>5001</v>
+        <v>4985</v>
       </c>
       <c r="J543" s="116" t="s">
-        <v>5443</v>
+        <v>5439</v>
       </c>
       <c r="K543" s="108" t="s">
-        <v>5289</v>
+        <v>5279</v>
       </c>
       <c r="L543" s="109" t="s">
-        <v>5292</v>
+        <v>5282</v>
       </c>
       <c r="M543" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N543" s="85">
         <v>0</v>
@@ -76958,13 +77058,13 @@
         <v>13</v>
       </c>
       <c r="P543" s="85">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q543">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="R543" s="100">
-        <v>94545</v>
+        <v>94541</v>
       </c>
       <c r="T543" s="85">
         <v>0</v>
@@ -76977,37 +77077,37 @@
     </row>
     <row r="544" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B544" s="85">
-        <v>800076</v>
+        <v>800072</v>
       </c>
       <c r="C544" s="104" t="s">
-        <v>5002</v>
+        <v>4986</v>
       </c>
       <c r="D544" s="104" t="s">
-        <v>5003</v>
+        <v>4987</v>
       </c>
       <c r="E544" s="117" t="s">
-        <v>5409</v>
+        <v>5405</v>
       </c>
       <c r="F544" s="108" t="s">
-        <v>5209</v>
-      </c>
-      <c r="G544" s="109" t="s">
-        <v>5210</v>
+        <v>5204</v>
+      </c>
+      <c r="G544" s="108" t="s">
+        <v>5155</v>
       </c>
       <c r="H544" s="104" t="s">
-        <v>5004</v>
+        <v>4988</v>
       </c>
       <c r="I544" s="104" t="s">
-        <v>5005</v>
+        <v>4989</v>
       </c>
       <c r="J544" s="116" t="s">
-        <v>5444</v>
+        <v>5440</v>
       </c>
       <c r="K544" s="108" t="s">
-        <v>5290</v>
+        <v>5283</v>
       </c>
       <c r="L544" s="109" t="s">
-        <v>5294</v>
+        <v>5284</v>
       </c>
       <c r="M544" s="99">
         <v>1</v>
@@ -77019,13 +77119,13 @@
         <v>13</v>
       </c>
       <c r="P544" s="85">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q544">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R544" s="100">
-        <v>94546</v>
+        <v>94542</v>
       </c>
       <c r="T544" s="85">
         <v>0</v>
@@ -77036,42 +77136,42 @@
       <c r="Z544" s="101"/>
       <c r="AA544" s="101"/>
     </row>
-    <row r="545" spans="1:27" s="85" customFormat="1" ht="33">
+    <row r="545" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B545" s="85">
-        <v>800077</v>
+        <v>800073</v>
       </c>
       <c r="C545" s="104" t="s">
-        <v>5006</v>
+        <v>4990</v>
       </c>
       <c r="D545" s="104" t="s">
-        <v>5007</v>
+        <v>4991</v>
       </c>
       <c r="E545" s="117" t="s">
-        <v>5410</v>
+        <v>5406</v>
       </c>
       <c r="F545" s="108" t="s">
-        <v>5207</v>
+        <v>5202</v>
       </c>
       <c r="G545" s="109" t="s">
-        <v>5208</v>
+        <v>5203</v>
       </c>
       <c r="H545" s="104" t="s">
-        <v>5008</v>
+        <v>4992</v>
       </c>
       <c r="I545" s="104" t="s">
-        <v>5009</v>
+        <v>4993</v>
       </c>
       <c r="J545" s="116" t="s">
-        <v>5445</v>
+        <v>5441</v>
       </c>
       <c r="K545" s="108" t="s">
-        <v>5291</v>
+        <v>5285</v>
       </c>
       <c r="L545" s="109" t="s">
-        <v>5293</v>
+        <v>5286</v>
       </c>
       <c r="M545" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N545" s="85">
         <v>0</v>
@@ -77080,13 +77180,13 @@
         <v>13</v>
       </c>
       <c r="P545" s="85">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q545">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R545" s="100">
-        <v>94547</v>
+        <v>94543</v>
       </c>
       <c r="T545" s="85">
         <v>0</v>
@@ -77097,42 +77197,42 @@
       <c r="Z545" s="101"/>
       <c r="AA545" s="101"/>
     </row>
-    <row r="546" spans="1:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="546" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B546" s="85">
-        <v>800078</v>
+        <v>800074</v>
       </c>
       <c r="C546" s="104" t="s">
-        <v>5010</v>
+        <v>4994</v>
       </c>
       <c r="D546" s="104" t="s">
-        <v>5011</v>
+        <v>4995</v>
       </c>
       <c r="E546" s="117" t="s">
-        <v>5411</v>
+        <v>5407</v>
       </c>
       <c r="F546" s="108" t="s">
-        <v>5182</v>
-      </c>
-      <c r="G546" s="108" t="s">
-        <v>5158</v>
+        <v>5205</v>
+      </c>
+      <c r="G546" s="109" t="s">
+        <v>5206</v>
       </c>
       <c r="H546" s="104" t="s">
-        <v>5012</v>
+        <v>4996</v>
       </c>
       <c r="I546" s="104" t="s">
-        <v>5013</v>
+        <v>4997</v>
       </c>
       <c r="J546" s="116" t="s">
-        <v>5446</v>
+        <v>5442</v>
       </c>
       <c r="K546" s="108" t="s">
-        <v>5295</v>
+        <v>5287</v>
       </c>
       <c r="L546" s="109" t="s">
-        <v>5297</v>
+        <v>5288</v>
       </c>
       <c r="M546" s="103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N546" s="85">
         <v>0</v>
@@ -77141,13 +77241,13 @@
         <v>13</v>
       </c>
       <c r="P546" s="85">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q546">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="R546" s="100">
-        <v>94548</v>
+        <v>94544</v>
       </c>
       <c r="T546" s="85">
         <v>0</v>
@@ -77158,42 +77258,42 @@
       <c r="Z546" s="101"/>
       <c r="AA546" s="101"/>
     </row>
-    <row r="547" spans="1:27" s="85" customFormat="1" ht="33">
+    <row r="547" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B547" s="85">
-        <v>800079</v>
+        <v>800075</v>
       </c>
       <c r="C547" s="104" t="s">
-        <v>5014</v>
+        <v>4998</v>
       </c>
       <c r="D547" s="104" t="s">
-        <v>5015</v>
+        <v>4999</v>
       </c>
       <c r="E547" s="117" t="s">
-        <v>5412</v>
+        <v>5408</v>
       </c>
       <c r="F547" s="108" t="s">
-        <v>5211</v>
-      </c>
-      <c r="G547" s="109" t="s">
-        <v>5212</v>
+        <v>5156</v>
+      </c>
+      <c r="G547" s="108" t="s">
+        <v>5157</v>
       </c>
       <c r="H547" s="104" t="s">
-        <v>5016</v>
+        <v>5000</v>
       </c>
       <c r="I547" s="104" t="s">
-        <v>5017</v>
+        <v>5001</v>
       </c>
       <c r="J547" s="116" t="s">
-        <v>5447</v>
+        <v>5443</v>
       </c>
       <c r="K547" s="108" t="s">
-        <v>5296</v>
+        <v>5289</v>
       </c>
       <c r="L547" s="109" t="s">
-        <v>5298</v>
+        <v>5292</v>
       </c>
       <c r="M547" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N547" s="85">
         <v>0</v>
@@ -77202,13 +77302,13 @@
         <v>13</v>
       </c>
       <c r="P547" s="85">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q547">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R547" s="100">
-        <v>94549</v>
+        <v>94545</v>
       </c>
       <c r="T547" s="85">
         <v>0</v>
@@ -77219,39 +77319,39 @@
       <c r="Z547" s="101"/>
       <c r="AA547" s="101"/>
     </row>
-    <row r="548" spans="1:27" s="85" customFormat="1" ht="33">
+    <row r="548" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B548" s="85">
-        <v>800080</v>
+        <v>800076</v>
       </c>
       <c r="C548" s="104" t="s">
-        <v>5018</v>
+        <v>5002</v>
       </c>
       <c r="D548" s="104" t="s">
-        <v>5019</v>
+        <v>5003</v>
       </c>
       <c r="E548" s="117" t="s">
-        <v>5413</v>
+        <v>5409</v>
       </c>
       <c r="F548" s="108" t="s">
-        <v>5159</v>
-      </c>
-      <c r="G548" s="108" t="s">
-        <v>5160</v>
+        <v>5209</v>
+      </c>
+      <c r="G548" s="109" t="s">
+        <v>5210</v>
       </c>
       <c r="H548" s="104" t="s">
-        <v>5020</v>
+        <v>5004</v>
       </c>
       <c r="I548" s="104" t="s">
-        <v>5021</v>
-      </c>
-      <c r="J548" s="98" t="s">
-        <v>5415</v>
+        <v>5005</v>
+      </c>
+      <c r="J548" s="116" t="s">
+        <v>5444</v>
       </c>
       <c r="K548" s="108" t="s">
-        <v>5299</v>
-      </c>
-      <c r="L548" s="108" t="s">
-        <v>5300</v>
+        <v>5290</v>
+      </c>
+      <c r="L548" s="109" t="s">
+        <v>5294</v>
       </c>
       <c r="M548" s="99">
         <v>1</v>
@@ -77263,13 +77363,13 @@
         <v>13</v>
       </c>
       <c r="P548" s="85">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q548">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="R548" s="100">
-        <v>94550</v>
+        <v>94546</v>
       </c>
       <c r="T548" s="85">
         <v>0</v>
@@ -77280,39 +77380,39 @@
       <c r="Z548" s="101"/>
       <c r="AA548" s="101"/>
     </row>
-    <row r="549" spans="1:27" s="85" customFormat="1" ht="33">
+    <row r="549" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B549" s="85">
-        <v>800081</v>
+        <v>800077</v>
       </c>
       <c r="C549" s="104" t="s">
-        <v>5022</v>
+        <v>5006</v>
       </c>
       <c r="D549" s="104" t="s">
-        <v>5023</v>
+        <v>5007</v>
       </c>
       <c r="E549" s="117" t="s">
-        <v>5414</v>
+        <v>5410</v>
       </c>
       <c r="F549" s="108" t="s">
-        <v>5161</v>
-      </c>
-      <c r="G549" s="108" t="s">
-        <v>5162</v>
+        <v>5207</v>
+      </c>
+      <c r="G549" s="109" t="s">
+        <v>5208</v>
       </c>
       <c r="H549" s="104" t="s">
-        <v>5024</v>
+        <v>5008</v>
       </c>
       <c r="I549" s="104" t="s">
-        <v>5025</v>
-      </c>
-      <c r="J549" s="98" t="s">
-        <v>5416</v>
+        <v>5009</v>
+      </c>
+      <c r="J549" s="116" t="s">
+        <v>5445</v>
       </c>
       <c r="K549" s="108" t="s">
-        <v>5301</v>
+        <v>5291</v>
       </c>
       <c r="L549" s="109" t="s">
-        <v>5302</v>
+        <v>5293</v>
       </c>
       <c r="M549" s="99">
         <v>2</v>
@@ -77324,13 +77424,13 @@
         <v>13</v>
       </c>
       <c r="P549" s="85">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q549">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="R549" s="100">
-        <v>94551</v>
+        <v>94547</v>
       </c>
       <c r="T549" s="85">
         <v>0</v>
@@ -77341,54 +77441,57 @@
       <c r="Z549" s="101"/>
       <c r="AA549" s="101"/>
     </row>
-    <row r="550" spans="1:27" s="85" customFormat="1" ht="18.75">
+    <row r="550" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B550" s="85">
-        <v>800101</v>
+        <v>800078</v>
       </c>
       <c r="C550" s="104" t="s">
-        <v>5026</v>
+        <v>5010</v>
       </c>
       <c r="D550" s="104" t="s">
-        <v>5027</v>
-      </c>
-      <c r="E550" s="108" t="s">
-        <v>5417</v>
+        <v>5011</v>
+      </c>
+      <c r="E550" s="117" t="s">
+        <v>5411</v>
       </c>
       <c r="F550" s="108" t="s">
-        <v>5163</v>
-      </c>
-      <c r="G550" s="113" t="s">
-        <v>5164</v>
+        <v>5182</v>
+      </c>
+      <c r="G550" s="108" t="s">
+        <v>5158</v>
       </c>
       <c r="H550" s="104" t="s">
-        <v>5028</v>
+        <v>5012</v>
       </c>
       <c r="I550" s="104" t="s">
-        <v>5029</v>
-      </c>
-      <c r="J550" s="118" t="s">
-        <v>5427</v>
+        <v>5013</v>
+      </c>
+      <c r="J550" s="116" t="s">
+        <v>5446</v>
       </c>
       <c r="K550" s="108" t="s">
-        <v>5303</v>
-      </c>
-      <c r="L550" s="115" t="s">
-        <v>5322</v>
-      </c>
-      <c r="M550" s="99">
+        <v>5295</v>
+      </c>
+      <c r="L550" s="109" t="s">
+        <v>5297</v>
+      </c>
+      <c r="M550" s="103">
         <v>1</v>
       </c>
       <c r="N550" s="85">
         <v>0</v>
       </c>
       <c r="O550" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P550" s="85">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="Q550">
+        <v>1069</v>
       </c>
       <c r="R550" s="100">
-        <v>95001</v>
+        <v>94548</v>
       </c>
       <c r="T550" s="85">
         <v>0</v>
@@ -77399,54 +77502,57 @@
       <c r="Z550" s="101"/>
       <c r="AA550" s="101"/>
     </row>
-    <row r="551" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="551" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B551" s="85">
-        <v>800102</v>
+        <v>800079</v>
       </c>
       <c r="C551" s="104" t="s">
-        <v>5030</v>
+        <v>5014</v>
       </c>
       <c r="D551" s="104" t="s">
-        <v>5031</v>
-      </c>
-      <c r="E551" s="108" t="s">
-        <v>5418</v>
+        <v>5015</v>
+      </c>
+      <c r="E551" s="117" t="s">
+        <v>5412</v>
       </c>
       <c r="F551" s="108" t="s">
-        <v>5165</v>
-      </c>
-      <c r="G551" s="113" t="s">
-        <v>5166</v>
+        <v>5211</v>
+      </c>
+      <c r="G551" s="109" t="s">
+        <v>5212</v>
       </c>
       <c r="H551" s="104" t="s">
-        <v>5032</v>
+        <v>5016</v>
       </c>
       <c r="I551" s="104" t="s">
-        <v>5033</v>
-      </c>
-      <c r="J551" s="98" t="s">
-        <v>5428</v>
+        <v>5017</v>
+      </c>
+      <c r="J551" s="116" t="s">
+        <v>5447</v>
       </c>
       <c r="K551" s="108" t="s">
-        <v>5304</v>
+        <v>5296</v>
       </c>
       <c r="L551" s="109" t="s">
-        <v>5305</v>
-      </c>
-      <c r="M551" s="103">
-        <v>1</v>
+        <v>5298</v>
+      </c>
+      <c r="M551" s="99">
+        <v>2</v>
       </c>
       <c r="N551" s="85">
         <v>0</v>
       </c>
       <c r="O551" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P551" s="85">
-        <v>2</v>
+        <v>49</v>
+      </c>
+      <c r="Q551">
+        <v>1069</v>
       </c>
       <c r="R551" s="100">
-        <v>95002</v>
+        <v>94549</v>
       </c>
       <c r="T551" s="85">
         <v>0</v>
@@ -77457,39 +77563,39 @@
       <c r="Z551" s="101"/>
       <c r="AA551" s="101"/>
     </row>
-    <row r="552" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="552" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B552" s="85">
-        <v>800103</v>
+        <v>800080</v>
       </c>
       <c r="C552" s="104" t="s">
-        <v>5034</v>
+        <v>5018</v>
       </c>
       <c r="D552" s="104" t="s">
-        <v>5035</v>
-      </c>
-      <c r="E552" s="108" t="s">
-        <v>5419</v>
+        <v>5019</v>
+      </c>
+      <c r="E552" s="117" t="s">
+        <v>5413</v>
       </c>
       <c r="F552" s="108" t="s">
-        <v>5183</v>
-      </c>
-      <c r="G552" s="113" t="s">
-        <v>5167</v>
+        <v>5159</v>
+      </c>
+      <c r="G552" s="108" t="s">
+        <v>5160</v>
       </c>
       <c r="H552" s="104" t="s">
-        <v>5036</v>
+        <v>5020</v>
       </c>
       <c r="I552" s="104" t="s">
-        <v>5037</v>
+        <v>5021</v>
       </c>
       <c r="J552" s="98" t="s">
-        <v>5429</v>
-      </c>
-      <c r="K552" s="98" t="s">
-        <v>5306</v>
-      </c>
-      <c r="L552" s="98" t="s">
-        <v>5307</v>
+        <v>5415</v>
+      </c>
+      <c r="K552" s="108" t="s">
+        <v>5299</v>
+      </c>
+      <c r="L552" s="108" t="s">
+        <v>5300</v>
       </c>
       <c r="M552" s="99">
         <v>1</v>
@@ -77498,13 +77604,16 @@
         <v>0</v>
       </c>
       <c r="O552" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P552" s="85">
-        <v>3</v>
+        <v>50</v>
+      </c>
+      <c r="Q552">
+        <v>1070</v>
       </c>
       <c r="R552" s="100">
-        <v>95003</v>
+        <v>94550</v>
       </c>
       <c r="T552" s="85">
         <v>0</v>
@@ -77515,54 +77624,57 @@
       <c r="Z552" s="101"/>
       <c r="AA552" s="101"/>
     </row>
-    <row r="553" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="553" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B553" s="85">
-        <v>800104</v>
+        <v>800081</v>
       </c>
       <c r="C553" s="104" t="s">
-        <v>5038</v>
+        <v>5022</v>
       </c>
       <c r="D553" s="104" t="s">
-        <v>5039</v>
-      </c>
-      <c r="E553" s="108" t="s">
-        <v>5420</v>
+        <v>5023</v>
+      </c>
+      <c r="E553" s="117" t="s">
+        <v>5414</v>
       </c>
       <c r="F553" s="108" t="s">
-        <v>5168</v>
-      </c>
-      <c r="G553" s="113" t="s">
-        <v>5169</v>
+        <v>5161</v>
+      </c>
+      <c r="G553" s="108" t="s">
+        <v>5162</v>
       </c>
       <c r="H553" s="104" t="s">
-        <v>5040</v>
+        <v>5024</v>
       </c>
       <c r="I553" s="104" t="s">
-        <v>5041</v>
+        <v>5025</v>
       </c>
       <c r="J553" s="98" t="s">
-        <v>5430</v>
-      </c>
-      <c r="K553" s="98" t="s">
-        <v>5308</v>
-      </c>
-      <c r="L553" s="98" t="s">
-        <v>5309</v>
+        <v>5416</v>
+      </c>
+      <c r="K553" s="108" t="s">
+        <v>5301</v>
+      </c>
+      <c r="L553" s="109" t="s">
+        <v>5302</v>
       </c>
       <c r="M553" s="99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N553" s="85">
         <v>0</v>
       </c>
       <c r="O553" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P553" s="85">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="Q553">
+        <v>1070</v>
       </c>
       <c r="R553" s="100">
-        <v>95004</v>
+        <v>94551</v>
       </c>
       <c r="T553" s="85">
         <v>0</v>
@@ -77573,39 +77685,39 @@
       <c r="Z553" s="101"/>
       <c r="AA553" s="101"/>
     </row>
-    <row r="554" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="554" spans="2:27" s="85" customFormat="1" ht="18.75">
       <c r="B554" s="85">
-        <v>800105</v>
+        <v>800101</v>
       </c>
       <c r="C554" s="104" t="s">
-        <v>5042</v>
+        <v>5026</v>
       </c>
       <c r="D554" s="104" t="s">
-        <v>5043</v>
+        <v>5027</v>
       </c>
       <c r="E554" s="108" t="s">
-        <v>5421</v>
+        <v>5417</v>
       </c>
       <c r="F554" s="108" t="s">
-        <v>5170</v>
+        <v>5163</v>
       </c>
       <c r="G554" s="113" t="s">
-        <v>5171</v>
+        <v>5164</v>
       </c>
       <c r="H554" s="104" t="s">
-        <v>5044</v>
+        <v>5028</v>
       </c>
       <c r="I554" s="104" t="s">
-        <v>5045</v>
-      </c>
-      <c r="J554" s="98" t="s">
-        <v>5431</v>
-      </c>
-      <c r="K554" s="98" t="s">
-        <v>5310</v>
-      </c>
-      <c r="L554" s="98" t="s">
-        <v>5311</v>
+        <v>5029</v>
+      </c>
+      <c r="J554" s="118" t="s">
+        <v>5427</v>
+      </c>
+      <c r="K554" s="108" t="s">
+        <v>5303</v>
+      </c>
+      <c r="L554" s="115" t="s">
+        <v>5322</v>
       </c>
       <c r="M554" s="99">
         <v>1</v>
@@ -77617,10 +77729,10 @@
         <v>14</v>
       </c>
       <c r="P554" s="85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R554" s="100">
-        <v>95005</v>
+        <v>95001</v>
       </c>
       <c r="T554" s="85">
         <v>0</v>
@@ -77631,39 +77743,39 @@
       <c r="Z554" s="101"/>
       <c r="AA554" s="101"/>
     </row>
-    <row r="555" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="555" spans="2:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B555" s="85">
-        <v>800106</v>
+        <v>800102</v>
       </c>
       <c r="C555" s="104" t="s">
-        <v>5046</v>
+        <v>5030</v>
       </c>
       <c r="D555" s="104" t="s">
-        <v>5047</v>
+        <v>5031</v>
       </c>
       <c r="E555" s="108" t="s">
-        <v>5422</v>
+        <v>5418</v>
       </c>
       <c r="F555" s="108" t="s">
-        <v>5172</v>
+        <v>5165</v>
       </c>
       <c r="G555" s="113" t="s">
-        <v>5173</v>
+        <v>5166</v>
       </c>
       <c r="H555" s="104" t="s">
-        <v>5048</v>
+        <v>5032</v>
       </c>
       <c r="I555" s="104" t="s">
-        <v>5049</v>
+        <v>5033</v>
       </c>
       <c r="J555" s="98" t="s">
-        <v>5432</v>
-      </c>
-      <c r="K555" s="98" t="s">
-        <v>5312</v>
-      </c>
-      <c r="L555" s="98" t="s">
-        <v>5313</v>
+        <v>5428</v>
+      </c>
+      <c r="K555" s="108" t="s">
+        <v>5304</v>
+      </c>
+      <c r="L555" s="109" t="s">
+        <v>5305</v>
       </c>
       <c r="M555" s="103">
         <v>1</v>
@@ -77675,10 +77787,10 @@
         <v>14</v>
       </c>
       <c r="P555" s="85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R555" s="100">
-        <v>95006</v>
+        <v>95002</v>
       </c>
       <c r="T555" s="85">
         <v>0</v>
@@ -77689,42 +77801,42 @@
       <c r="Z555" s="101"/>
       <c r="AA555" s="101"/>
     </row>
-    <row r="556" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="556" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B556" s="85">
-        <v>800107</v>
+        <v>800103</v>
       </c>
       <c r="C556" s="104" t="s">
-        <v>5050</v>
+        <v>5034</v>
       </c>
       <c r="D556" s="104" t="s">
-        <v>5051</v>
+        <v>5035</v>
       </c>
       <c r="E556" s="108" t="s">
-        <v>5423</v>
+        <v>5419</v>
       </c>
       <c r="F556" s="108" t="s">
-        <v>5174</v>
+        <v>5183</v>
       </c>
       <c r="G556" s="113" t="s">
-        <v>5175</v>
+        <v>5167</v>
       </c>
       <c r="H556" s="104" t="s">
-        <v>5052</v>
+        <v>5036</v>
       </c>
       <c r="I556" s="104" t="s">
-        <v>5053</v>
+        <v>5037</v>
       </c>
       <c r="J556" s="98" t="s">
-        <v>5433</v>
+        <v>5429</v>
       </c>
       <c r="K556" s="98" t="s">
-        <v>5314</v>
+        <v>5306</v>
       </c>
       <c r="L556" s="98" t="s">
-        <v>5315</v>
+        <v>5307</v>
       </c>
       <c r="M556" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N556" s="85">
         <v>0</v>
@@ -77733,10 +77845,10 @@
         <v>14</v>
       </c>
       <c r="P556" s="85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R556" s="100">
-        <v>95007</v>
+        <v>95003</v>
       </c>
       <c r="T556" s="85">
         <v>0</v>
@@ -77747,42 +77859,42 @@
       <c r="Z556" s="101"/>
       <c r="AA556" s="101"/>
     </row>
-    <row r="557" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="557" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B557" s="85">
-        <v>800108</v>
+        <v>800104</v>
       </c>
       <c r="C557" s="104" t="s">
-        <v>5054</v>
+        <v>5038</v>
       </c>
       <c r="D557" s="104" t="s">
-        <v>5055</v>
+        <v>5039</v>
       </c>
       <c r="E557" s="108" t="s">
-        <v>5424</v>
+        <v>5420</v>
       </c>
       <c r="F557" s="108" t="s">
-        <v>5176</v>
+        <v>5168</v>
       </c>
       <c r="G557" s="113" t="s">
-        <v>5177</v>
+        <v>5169</v>
       </c>
       <c r="H557" s="104" t="s">
-        <v>5056</v>
+        <v>5040</v>
       </c>
       <c r="I557" s="104" t="s">
-        <v>5057</v>
+        <v>5041</v>
       </c>
       <c r="J557" s="98" t="s">
-        <v>5434</v>
+        <v>5430</v>
       </c>
       <c r="K557" s="98" t="s">
-        <v>5316</v>
+        <v>5308</v>
       </c>
       <c r="L557" s="98" t="s">
-        <v>5317</v>
+        <v>5309</v>
       </c>
       <c r="M557" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N557" s="85">
         <v>0</v>
@@ -77791,10 +77903,10 @@
         <v>14</v>
       </c>
       <c r="P557" s="85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R557" s="100">
-        <v>95008</v>
+        <v>95004</v>
       </c>
       <c r="T557" s="85">
         <v>0</v>
@@ -77805,42 +77917,42 @@
       <c r="Z557" s="101"/>
       <c r="AA557" s="101"/>
     </row>
-    <row r="558" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="558" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B558" s="85">
-        <v>800109</v>
+        <v>800105</v>
       </c>
       <c r="C558" s="104" t="s">
-        <v>5058</v>
+        <v>5042</v>
       </c>
       <c r="D558" s="104" t="s">
-        <v>5059</v>
+        <v>5043</v>
       </c>
       <c r="E558" s="108" t="s">
-        <v>5425</v>
+        <v>5421</v>
       </c>
       <c r="F558" s="108" t="s">
-        <v>5178</v>
+        <v>5170</v>
       </c>
       <c r="G558" s="113" t="s">
-        <v>5179</v>
+        <v>5171</v>
       </c>
       <c r="H558" s="104" t="s">
-        <v>5060</v>
+        <v>5044</v>
       </c>
       <c r="I558" s="104" t="s">
-        <v>5061</v>
+        <v>5045</v>
       </c>
       <c r="J558" s="98" t="s">
-        <v>5435</v>
+        <v>5431</v>
       </c>
       <c r="K558" s="98" t="s">
-        <v>5318</v>
+        <v>5310</v>
       </c>
       <c r="L558" s="98" t="s">
-        <v>5319</v>
+        <v>5311</v>
       </c>
       <c r="M558" s="99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N558" s="85">
         <v>0</v>
@@ -77849,10 +77961,10 @@
         <v>14</v>
       </c>
       <c r="P558" s="85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R558" s="100">
-        <v>95009</v>
+        <v>95005</v>
       </c>
       <c r="T558" s="85">
         <v>0</v>
@@ -77863,42 +77975,42 @@
       <c r="Z558" s="101"/>
       <c r="AA558" s="101"/>
     </row>
-    <row r="559" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="559" spans="2:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B559" s="85">
-        <v>800110</v>
+        <v>800106</v>
       </c>
       <c r="C559" s="104" t="s">
-        <v>5062</v>
+        <v>5046</v>
       </c>
       <c r="D559" s="104" t="s">
-        <v>5063</v>
+        <v>5047</v>
       </c>
       <c r="E559" s="108" t="s">
-        <v>5426</v>
+        <v>5422</v>
       </c>
       <c r="F559" s="108" t="s">
-        <v>5180</v>
+        <v>5172</v>
       </c>
       <c r="G559" s="113" t="s">
-        <v>5181</v>
+        <v>5173</v>
       </c>
       <c r="H559" s="104" t="s">
-        <v>5064</v>
+        <v>5048</v>
       </c>
       <c r="I559" s="104" t="s">
-        <v>5065</v>
+        <v>5049</v>
       </c>
       <c r="J559" s="98" t="s">
-        <v>5436</v>
+        <v>5432</v>
       </c>
       <c r="K559" s="98" t="s">
-        <v>5320</v>
+        <v>5312</v>
       </c>
       <c r="L559" s="98" t="s">
-        <v>5321</v>
+        <v>5313</v>
       </c>
       <c r="M559" s="103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N559" s="85">
         <v>0</v>
@@ -77907,10 +78019,10 @@
         <v>14</v>
       </c>
       <c r="P559" s="85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R559" s="100">
-        <v>95010</v>
+        <v>95006</v>
       </c>
       <c r="T559" s="85">
         <v>0</v>
@@ -77921,37 +78033,269 @@
       <c r="Z559" s="101"/>
       <c r="AA559" s="101"/>
     </row>
-    <row r="560" spans="1:27" s="2" customFormat="1">
-      <c r="A560" s="2" t="s">
+    <row r="560" spans="2:27" s="85" customFormat="1" ht="16.5">
+      <c r="B560" s="85">
+        <v>800107</v>
+      </c>
+      <c r="C560" s="104" t="s">
+        <v>5050</v>
+      </c>
+      <c r="D560" s="104" t="s">
+        <v>5051</v>
+      </c>
+      <c r="E560" s="108" t="s">
+        <v>5423</v>
+      </c>
+      <c r="F560" s="108" t="s">
+        <v>5174</v>
+      </c>
+      <c r="G560" s="113" t="s">
+        <v>5175</v>
+      </c>
+      <c r="H560" s="104" t="s">
+        <v>5052</v>
+      </c>
+      <c r="I560" s="104" t="s">
+        <v>5053</v>
+      </c>
+      <c r="J560" s="98" t="s">
+        <v>5433</v>
+      </c>
+      <c r="K560" s="98" t="s">
+        <v>5314</v>
+      </c>
+      <c r="L560" s="98" t="s">
+        <v>5315</v>
+      </c>
+      <c r="M560" s="99">
+        <v>2</v>
+      </c>
+      <c r="N560" s="85">
+        <v>0</v>
+      </c>
+      <c r="O560" s="85">
+        <v>14</v>
+      </c>
+      <c r="P560" s="85">
+        <v>7</v>
+      </c>
+      <c r="R560" s="100">
+        <v>95007</v>
+      </c>
+      <c r="T560" s="85">
+        <v>0</v>
+      </c>
+      <c r="U560" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z560" s="101"/>
+      <c r="AA560" s="101"/>
+    </row>
+    <row r="561" spans="1:27" s="85" customFormat="1" ht="16.5">
+      <c r="B561" s="85">
+        <v>800108</v>
+      </c>
+      <c r="C561" s="104" t="s">
+        <v>5054</v>
+      </c>
+      <c r="D561" s="104" t="s">
+        <v>5055</v>
+      </c>
+      <c r="E561" s="108" t="s">
+        <v>5424</v>
+      </c>
+      <c r="F561" s="108" t="s">
+        <v>5176</v>
+      </c>
+      <c r="G561" s="113" t="s">
+        <v>5177</v>
+      </c>
+      <c r="H561" s="104" t="s">
+        <v>5056</v>
+      </c>
+      <c r="I561" s="104" t="s">
+        <v>5057</v>
+      </c>
+      <c r="J561" s="98" t="s">
+        <v>5434</v>
+      </c>
+      <c r="K561" s="98" t="s">
+        <v>5316</v>
+      </c>
+      <c r="L561" s="98" t="s">
+        <v>5317</v>
+      </c>
+      <c r="M561" s="99">
+        <v>2</v>
+      </c>
+      <c r="N561" s="85">
+        <v>0</v>
+      </c>
+      <c r="O561" s="85">
+        <v>14</v>
+      </c>
+      <c r="P561" s="85">
+        <v>8</v>
+      </c>
+      <c r="R561" s="100">
+        <v>95008</v>
+      </c>
+      <c r="T561" s="85">
+        <v>0</v>
+      </c>
+      <c r="U561" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z561" s="101"/>
+      <c r="AA561" s="101"/>
+    </row>
+    <row r="562" spans="1:27" s="85" customFormat="1" ht="16.5">
+      <c r="B562" s="85">
+        <v>800109</v>
+      </c>
+      <c r="C562" s="104" t="s">
+        <v>5058</v>
+      </c>
+      <c r="D562" s="104" t="s">
+        <v>5059</v>
+      </c>
+      <c r="E562" s="108" t="s">
+        <v>5425</v>
+      </c>
+      <c r="F562" s="108" t="s">
+        <v>5178</v>
+      </c>
+      <c r="G562" s="113" t="s">
+        <v>5179</v>
+      </c>
+      <c r="H562" s="104" t="s">
+        <v>5060</v>
+      </c>
+      <c r="I562" s="104" t="s">
+        <v>5061</v>
+      </c>
+      <c r="J562" s="98" t="s">
+        <v>5435</v>
+      </c>
+      <c r="K562" s="98" t="s">
+        <v>5318</v>
+      </c>
+      <c r="L562" s="98" t="s">
+        <v>5319</v>
+      </c>
+      <c r="M562" s="99">
+        <v>2</v>
+      </c>
+      <c r="N562" s="85">
+        <v>0</v>
+      </c>
+      <c r="O562" s="85">
+        <v>14</v>
+      </c>
+      <c r="P562" s="85">
+        <v>9</v>
+      </c>
+      <c r="R562" s="100">
+        <v>95009</v>
+      </c>
+      <c r="T562" s="85">
+        <v>0</v>
+      </c>
+      <c r="U562" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z562" s="101"/>
+      <c r="AA562" s="101"/>
+    </row>
+    <row r="563" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+      <c r="B563" s="85">
+        <v>800110</v>
+      </c>
+      <c r="C563" s="104" t="s">
+        <v>5062</v>
+      </c>
+      <c r="D563" s="104" t="s">
+        <v>5063</v>
+      </c>
+      <c r="E563" s="108" t="s">
+        <v>5426</v>
+      </c>
+      <c r="F563" s="108" t="s">
+        <v>5180</v>
+      </c>
+      <c r="G563" s="113" t="s">
+        <v>5181</v>
+      </c>
+      <c r="H563" s="104" t="s">
+        <v>5064</v>
+      </c>
+      <c r="I563" s="104" t="s">
+        <v>5065</v>
+      </c>
+      <c r="J563" s="98" t="s">
+        <v>5436</v>
+      </c>
+      <c r="K563" s="98" t="s">
+        <v>5320</v>
+      </c>
+      <c r="L563" s="98" t="s">
+        <v>5321</v>
+      </c>
+      <c r="M563" s="103">
+        <v>3</v>
+      </c>
+      <c r="N563" s="85">
+        <v>0</v>
+      </c>
+      <c r="O563" s="85">
+        <v>14</v>
+      </c>
+      <c r="P563" s="85">
+        <v>10</v>
+      </c>
+      <c r="R563" s="100">
+        <v>95010</v>
+      </c>
+      <c r="T563" s="85">
+        <v>0</v>
+      </c>
+      <c r="U563" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z563" s="101"/>
+      <c r="AA563" s="101"/>
+    </row>
+    <row r="564" spans="1:27" s="2" customFormat="1">
+      <c r="A564" s="2" t="s">
         <v>4245</v>
       </c>
-      <c r="B560" s="2">
+      <c r="B564" s="2">
         <v>900001</v>
       </c>
-      <c r="M560" s="2">
-        <v>0</v>
-      </c>
-      <c r="N560" s="2">
-        <v>0</v>
-      </c>
-      <c r="O560" s="2">
+      <c r="M564" s="2">
+        <v>0</v>
+      </c>
+      <c r="N564" s="2">
+        <v>0</v>
+      </c>
+      <c r="O564" s="2">
         <v>2</v>
       </c>
-      <c r="P560" s="2">
+      <c r="P564" s="2">
         <v>999</v>
       </c>
-      <c r="R560" s="2">
+      <c r="R564" s="2">
         <v>98001</v>
       </c>
-      <c r="T560" s="2">
+      <c r="T564" s="2">
         <v>1</v>
       </c>
-      <c r="U560" s="2">
+      <c r="U564" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U499" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:U503" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="N1:N445 N449:N459 N462:N479 N482:N1048576">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">

--- a/source/bin/excel/achievement.xlsx
+++ b/source/bin/excel/achievement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7936D0-A676-4BEB-A25F-940FB2B60C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A840FC4D-B829-4397-86E8-01CECC1D109C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -20,14 +20,25 @@
     <sheet name="badge_group" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$509</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6719" uniqueCount="5808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6730" uniqueCount="5819">
   <si>
     <t>sheet</t>
   </si>
@@ -41017,6 +41028,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41038,6 +41050,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41059,6 +41072,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41080,6 +41094,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41101,6 +41116,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41122,6 +41138,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41143,6 +41160,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41164,6 +41182,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -41185,11 +41204,401 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
     </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>小鸟游雏田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守护者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>小鳥遊雛田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小鳥遊雛田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Protector of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Hinata Takanashi</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타카나시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>히나타</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수호자</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解锁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>小鸟游雏田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传记中的所有结局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解鎖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>小鳥遊雛田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>傳記中的所有結局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小鳥遊雛田</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の物語のエンディングをすべて解放する</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unlock all endings in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hinata Takanashi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'s Story</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>타카나시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>히나타</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스토리의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엔딩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오픈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>30740021-1</t>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
 </sst>
@@ -43338,7 +43747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM569"/>
+  <dimension ref="A1:AM570"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -76393,123 +76802,111 @@
       <c r="Z492" s="27"/>
       <c r="AA492" s="27"/>
     </row>
-    <row r="493" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="A493" s="1" t="s">
-        <v>4230</v>
-      </c>
-      <c r="B493" s="1">
-        <v>800011</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D493" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E493" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F493" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G493" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H493" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I493" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J493" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="K493" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="L493" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="M493" s="47">
+    <row r="493" spans="1:39" ht="16.5">
+      <c r="A493">
+        <v>21</v>
+      </c>
+      <c r="B493">
+        <v>100495</v>
+      </c>
+      <c r="C493" s="29" t="s">
+        <v>5808</v>
+      </c>
+      <c r="D493" s="29" t="s">
+        <v>5809</v>
+      </c>
+      <c r="E493" s="62" t="s">
+        <v>5810</v>
+      </c>
+      <c r="F493" s="63" t="s">
+        <v>5811</v>
+      </c>
+      <c r="G493" s="78" t="s">
+        <v>5812</v>
+      </c>
+      <c r="H493" s="60" t="s">
+        <v>5813</v>
+      </c>
+      <c r="I493" s="29" t="s">
+        <v>5814</v>
+      </c>
+      <c r="J493" s="63" t="s">
+        <v>5815</v>
+      </c>
+      <c r="K493" s="29" t="s">
+        <v>5816</v>
+      </c>
+      <c r="L493" s="78" t="s">
+        <v>5817</v>
+      </c>
+      <c r="M493" s="66">
         <v>1</v>
       </c>
-      <c r="N493" s="1">
-        <v>0</v>
-      </c>
-      <c r="O493" s="1">
-        <v>12</v>
-      </c>
-      <c r="P493" s="1">
-        <v>1</v>
-      </c>
-      <c r="R493" s="1">
-        <v>90501</v>
-      </c>
-      <c r="T493" s="1">
-        <v>0</v>
-      </c>
-      <c r="U493" s="1">
-        <v>0</v>
-      </c>
-      <c r="X493" s="1">
-        <v>90501</v>
-      </c>
-      <c r="Y493" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z493" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA493" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB493" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE493" s="51"/>
-      <c r="AF493" s="51"/>
-      <c r="AG493" s="51"/>
-      <c r="AH493" s="51"/>
-      <c r="AI493" s="51"/>
-      <c r="AL493" s="51"/>
-      <c r="AM493" s="51"/>
+      <c r="N493">
+        <v>0</v>
+      </c>
+      <c r="O493">
+        <v>10</v>
+      </c>
+      <c r="P493" s="135">
+        <v>521</v>
+      </c>
+      <c r="R493">
+        <v>99183</v>
+      </c>
+      <c r="S493" s="27" t="s">
+        <v>5818</v>
+      </c>
+      <c r="T493">
+        <v>0</v>
+      </c>
+      <c r="U493">
+        <v>0</v>
+      </c>
+      <c r="X493" s="27"/>
+      <c r="Y493" s="27"/>
+      <c r="Z493" s="27"/>
+      <c r="AA493" s="27"/>
     </row>
     <row r="494" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="A494" s="1" t="s">
+        <v>4230</v>
+      </c>
       <c r="B494" s="1">
-        <v>800012</v>
+        <v>800011</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E494" s="41" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="G494" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="H494" s="42" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="I494" s="42" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J494" s="46" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="K494" s="42" t="s">
-        <v>4231</v>
+        <v>235</v>
       </c>
       <c r="L494" s="42" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="M494" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N494" s="1">
         <v>0</v>
@@ -76518,10 +76915,10 @@
         <v>12</v>
       </c>
       <c r="P494" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R494" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="T494" s="1">
         <v>0</v>
@@ -76530,57 +76927,64 @@
         <v>0</v>
       </c>
       <c r="X494" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="Y494" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z494" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA494" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB494" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="AE494" s="51"/>
+      <c r="AF494" s="51"/>
+      <c r="AG494" s="51"/>
+      <c r="AH494" s="51"/>
+      <c r="AI494" s="51"/>
+      <c r="AL494" s="51"/>
+      <c r="AM494" s="51"/>
     </row>
     <row r="495" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B495" s="1">
-        <v>800013</v>
+        <v>800012</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E495" s="41" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H495" s="42" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I495" s="42" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="J495" s="46" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="K495" s="42" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
       <c r="L495" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="M495" s="48">
-        <v>3</v>
+        <v>249</v>
+      </c>
+      <c r="M495" s="47">
+        <v>2</v>
       </c>
       <c r="N495" s="1">
         <v>0</v>
@@ -76589,10 +76993,10 @@
         <v>12</v>
       </c>
       <c r="P495" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R495" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="T495" s="1">
         <v>0</v>
@@ -76601,7 +77005,7 @@
         <v>0</v>
       </c>
       <c r="X495" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="Y495" s="1" t="s">
         <v>237</v>
@@ -76610,7 +77014,7 @@
         <v>250</v>
       </c>
       <c r="AA495" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB495" s="1" t="s">
         <v>239</v>
@@ -76618,40 +77022,40 @@
     </row>
     <row r="496" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B496" s="1">
-        <v>800014</v>
+        <v>800013</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E496" s="41" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H496" s="42" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I496" s="42" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="J496" s="46" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="K496" s="42" t="s">
-        <v>269</v>
+        <v>4232</v>
       </c>
       <c r="L496" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M496" s="47">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="M496" s="48">
+        <v>3</v>
       </c>
       <c r="N496" s="1">
         <v>0</v>
@@ -76660,10 +77064,10 @@
         <v>12</v>
       </c>
       <c r="P496" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R496" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="T496" s="1">
         <v>0</v>
@@ -76672,57 +77076,57 @@
         <v>0</v>
       </c>
       <c r="X496" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="Y496" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z496" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA496" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB496" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="497" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B497" s="1">
-        <v>800015</v>
+        <v>800014</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="E497" s="41" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="H497" s="42" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I497" s="42" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="J497" s="46" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="K497" s="42" t="s">
-        <v>4233</v>
+        <v>269</v>
       </c>
       <c r="L497" s="42" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="M497" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N497" s="1">
         <v>0</v>
@@ -76731,10 +77135,10 @@
         <v>12</v>
       </c>
       <c r="P497" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R497" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="T497" s="1">
         <v>0</v>
@@ -76743,16 +77147,16 @@
         <v>0</v>
       </c>
       <c r="X497" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="Y497" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z497" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA497" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB497" s="1" t="s">
         <v>271</v>
@@ -76760,40 +77164,40 @@
     </row>
     <row r="498" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B498" s="1">
-        <v>800016</v>
+        <v>800015</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E498" s="43" t="s">
-        <v>284</v>
+        <v>273</v>
+      </c>
+      <c r="E498" s="41" t="s">
+        <v>274</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H498" s="42" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I498" s="42" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J498" s="46" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K498" s="42" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
       <c r="L498" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="M498" s="48">
-        <v>3</v>
+        <v>281</v>
+      </c>
+      <c r="M498" s="47">
+        <v>2</v>
       </c>
       <c r="N498" s="1">
         <v>0</v>
@@ -76802,10 +77206,10 @@
         <v>12</v>
       </c>
       <c r="P498" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R498" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="T498" s="1">
         <v>0</v>
@@ -76814,7 +77218,7 @@
         <v>0</v>
       </c>
       <c r="X498" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="Y498" s="1" t="s">
         <v>237</v>
@@ -76823,7 +77227,7 @@
         <v>250</v>
       </c>
       <c r="AA498" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB498" s="1" t="s">
         <v>271</v>
@@ -76831,40 +77235,40 @@
     </row>
     <row r="499" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B499" s="1">
-        <v>800017</v>
+        <v>800016</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E499" s="43" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="H499" s="42" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I499" s="42" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J499" s="46" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="K499" s="42" t="s">
-        <v>300</v>
+        <v>4234</v>
       </c>
       <c r="L499" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="M499" s="47">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="M499" s="48">
+        <v>3</v>
       </c>
       <c r="N499" s="1">
         <v>0</v>
@@ -76873,10 +77277,10 @@
         <v>12</v>
       </c>
       <c r="P499" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R499" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="T499" s="1">
         <v>0</v>
@@ -76885,54 +77289,54 @@
         <v>0</v>
       </c>
       <c r="X499" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="Y499" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z499" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA499" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB499" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="500" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B500" s="1">
-        <v>800018</v>
+        <v>800017</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E500" s="41" t="s">
-        <v>305</v>
+        <v>293</v>
+      </c>
+      <c r="E500" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="H500" s="42" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="I500" s="42" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="J500" s="46" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="K500" s="42" t="s">
-        <v>4235</v>
+        <v>300</v>
       </c>
       <c r="L500" s="42" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="M500" s="47">
         <v>1</v>
@@ -76944,10 +77348,10 @@
         <v>12</v>
       </c>
       <c r="P500" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R500" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="T500" s="1">
         <v>0</v>
@@ -76956,16 +77360,16 @@
         <v>0</v>
       </c>
       <c r="X500" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="Y500" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z500" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA500" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB500" s="1" t="s">
         <v>302</v>
@@ -76973,40 +77377,40 @@
     </row>
     <row r="501" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B501" s="1">
-        <v>800019</v>
+        <v>800018</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E501" s="41" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H501" s="42" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I501" s="42" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J501" s="46" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="K501" s="42" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
       <c r="L501" s="42" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M501" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N501" s="1">
         <v>0</v>
@@ -77015,10 +77419,10 @@
         <v>12</v>
       </c>
       <c r="P501" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R501" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="T501" s="1">
         <v>0</v>
@@ -77027,7 +77431,7 @@
         <v>0</v>
       </c>
       <c r="X501" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="Y501" s="1" t="s">
         <v>237</v>
@@ -77036,7 +77440,7 @@
         <v>250</v>
       </c>
       <c r="AA501" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB501" s="1" t="s">
         <v>302</v>
@@ -77044,40 +77448,40 @@
     </row>
     <row r="502" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B502" s="1">
-        <v>800020</v>
+        <v>800019</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E502" s="41" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="H502" s="42" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="I502" s="42" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="J502" s="46" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="K502" s="42" t="s">
-        <v>331</v>
+        <v>4236</v>
       </c>
       <c r="L502" s="42" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="M502" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N502" s="1">
         <v>0</v>
@@ -77086,10 +77490,10 @@
         <v>12</v>
       </c>
       <c r="P502" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R502" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="T502" s="1">
         <v>0</v>
@@ -77098,57 +77502,57 @@
         <v>0</v>
       </c>
       <c r="X502" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="Y502" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z502" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA502" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB502" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="503" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B503" s="1">
-        <v>800021</v>
+        <v>800020</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E503" s="41" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="H503" s="42" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I503" s="42" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="J503" s="46" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="K503" s="42" t="s">
-        <v>4237</v>
+        <v>331</v>
       </c>
       <c r="L503" s="42" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="M503" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N503" s="1">
         <v>0</v>
@@ -77157,10 +77561,10 @@
         <v>12</v>
       </c>
       <c r="P503" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R503" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="T503" s="1">
         <v>0</v>
@@ -77169,7 +77573,7 @@
         <v>0</v>
       </c>
       <c r="X503" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="Y503" s="1" t="s">
         <v>237</v>
@@ -77178,7 +77582,7 @@
         <v>333</v>
       </c>
       <c r="AA503" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB503" s="1" t="s">
         <v>239</v>
@@ -77186,40 +77590,40 @@
     </row>
     <row r="504" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B504" s="1">
-        <v>800022</v>
+        <v>800021</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E504" s="41" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="H504" s="42" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I504" s="42" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J504" s="46" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="K504" s="42" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
       <c r="L504" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="M504" s="48">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="M504" s="47">
+        <v>2</v>
       </c>
       <c r="N504" s="1">
         <v>0</v>
@@ -77228,10 +77632,10 @@
         <v>12</v>
       </c>
       <c r="P504" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R504" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="T504" s="1">
         <v>0</v>
@@ -77240,7 +77644,7 @@
         <v>0</v>
       </c>
       <c r="X504" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="Y504" s="1" t="s">
         <v>237</v>
@@ -77249,7 +77653,7 @@
         <v>333</v>
       </c>
       <c r="AA504" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB504" s="1" t="s">
         <v>239</v>
@@ -77257,40 +77661,40 @@
     </row>
     <row r="505" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B505" s="1">
-        <v>800023</v>
+        <v>800022</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E505" s="41" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H505" s="42" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I505" s="42" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="J505" s="46" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="K505" s="42" t="s">
-        <v>362</v>
+        <v>4238</v>
       </c>
       <c r="L505" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="M505" s="47">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="M505" s="48">
+        <v>3</v>
       </c>
       <c r="N505" s="1">
         <v>0</v>
@@ -77299,10 +77703,10 @@
         <v>12</v>
       </c>
       <c r="P505" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R505" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="T505" s="1">
         <v>0</v>
@@ -77311,7 +77715,7 @@
         <v>0</v>
       </c>
       <c r="X505" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="Y505" s="1" t="s">
         <v>237</v>
@@ -77320,45 +77724,45 @@
         <v>333</v>
       </c>
       <c r="AA505" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB505" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="506" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B506" s="1">
-        <v>800024</v>
+        <v>800023</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E506" s="41" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="H506" s="42" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I506" s="42" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J506" s="46" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="K506" s="42" t="s">
-        <v>4239</v>
+        <v>362</v>
       </c>
       <c r="L506" s="42" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M506" s="47">
         <v>1</v>
@@ -77370,10 +77774,10 @@
         <v>12</v>
       </c>
       <c r="P506" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R506" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="T506" s="1">
         <v>0</v>
@@ -77382,7 +77786,7 @@
         <v>0</v>
       </c>
       <c r="X506" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="Y506" s="1" t="s">
         <v>237</v>
@@ -77391,7 +77795,7 @@
         <v>333</v>
       </c>
       <c r="AA506" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB506" s="1" t="s">
         <v>271</v>
@@ -77399,40 +77803,40 @@
     </row>
     <row r="507" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B507" s="1">
-        <v>800025</v>
+        <v>800024</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E507" s="41" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="H507" s="42" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I507" s="42" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="J507" s="46" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K507" s="42" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
       <c r="L507" s="42" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="M507" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N507" s="1">
         <v>0</v>
@@ -77441,10 +77845,10 @@
         <v>12</v>
       </c>
       <c r="P507" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R507" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="T507" s="1">
         <v>0</v>
@@ -77453,7 +77857,7 @@
         <v>0</v>
       </c>
       <c r="X507" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="Y507" s="1" t="s">
         <v>237</v>
@@ -77462,116 +77866,119 @@
         <v>333</v>
       </c>
       <c r="AA507" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB507" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="508" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="A508" s="87" t="s">
-        <v>4833</v>
-      </c>
-      <c r="B508" s="85">
-        <v>800031</v>
-      </c>
-      <c r="C508" s="88" t="s">
-        <v>4834</v>
-      </c>
-      <c r="D508" s="88" t="s">
-        <v>4835</v>
-      </c>
-      <c r="E508" s="101" t="s">
-        <v>5320</v>
-      </c>
-      <c r="F508" s="101" t="s">
-        <v>5073</v>
-      </c>
-      <c r="G508" s="101" t="s">
-        <v>5074</v>
-      </c>
-      <c r="H508" s="90" t="s">
-        <v>4836</v>
-      </c>
-      <c r="I508" s="107" t="s">
-        <v>5338</v>
-      </c>
-      <c r="J508" s="109" t="s">
-        <v>5332</v>
-      </c>
-      <c r="K508" s="101" t="s">
-        <v>5077</v>
-      </c>
-      <c r="L508" s="102" t="s">
-        <v>5078</v>
-      </c>
-      <c r="M508" s="92">
-        <v>1</v>
-      </c>
-      <c r="N508" s="85">
-        <v>0</v>
-      </c>
-      <c r="O508" s="85">
-        <v>13</v>
-      </c>
-      <c r="P508" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q508">
-        <v>1059</v>
-      </c>
-      <c r="R508" s="93">
-        <v>94501</v>
-      </c>
-      <c r="T508" s="85">
-        <v>0</v>
-      </c>
-      <c r="U508" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z508" s="94"/>
-      <c r="AA508" s="94"/>
-      <c r="AE508" s="95"/>
-      <c r="AF508" s="95"/>
-      <c r="AG508" s="95"/>
-      <c r="AH508" s="95"/>
-      <c r="AI508" s="95"/>
-      <c r="AL508" s="95"/>
-      <c r="AM508" s="95"/>
+    <row r="508" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B508" s="1">
+        <v>800025</v>
+      </c>
+      <c r="C508" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D508" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E508" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F508" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G508" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H508" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="I508" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="J508" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="K508" s="42" t="s">
+        <v>4240</v>
+      </c>
+      <c r="L508" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="M508" s="47">
+        <v>2</v>
+      </c>
+      <c r="N508" s="1">
+        <v>0</v>
+      </c>
+      <c r="O508" s="1">
+        <v>12</v>
+      </c>
+      <c r="P508" s="1">
+        <v>15</v>
+      </c>
+      <c r="R508" s="1">
+        <v>90515</v>
+      </c>
+      <c r="T508" s="1">
+        <v>0</v>
+      </c>
+      <c r="U508" s="1">
+        <v>0</v>
+      </c>
+      <c r="X508" s="1">
+        <v>90515</v>
+      </c>
+      <c r="Y508" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z508" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA508" s="42">
+        <v>10</v>
+      </c>
+      <c r="AB508" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="509" spans="1:39" s="85" customFormat="1" ht="33">
+      <c r="A509" s="87" t="s">
+        <v>4833</v>
+      </c>
       <c r="B509" s="85">
-        <v>800032</v>
+        <v>800031</v>
       </c>
       <c r="C509" s="88" t="s">
-        <v>4837</v>
+        <v>4834</v>
       </c>
       <c r="D509" s="88" t="s">
-        <v>4838</v>
+        <v>4835</v>
       </c>
       <c r="E509" s="101" t="s">
-        <v>5322</v>
+        <v>5320</v>
       </c>
       <c r="F509" s="101" t="s">
-        <v>5081</v>
+        <v>5073</v>
       </c>
       <c r="G509" s="101" t="s">
-        <v>5075</v>
+        <v>5074</v>
       </c>
       <c r="H509" s="90" t="s">
-        <v>4839</v>
-      </c>
-      <c r="I509" s="90" t="s">
-        <v>4840</v>
+        <v>4836</v>
+      </c>
+      <c r="I509" s="107" t="s">
+        <v>5338</v>
       </c>
       <c r="J509" s="109" t="s">
-        <v>5333</v>
+        <v>5332</v>
       </c>
       <c r="K509" s="101" t="s">
-        <v>5087</v>
+        <v>5077</v>
       </c>
       <c r="L509" s="102" t="s">
-        <v>5089</v>
+        <v>5078</v>
       </c>
       <c r="M509" s="92">
         <v>1</v>
@@ -77583,13 +77990,13 @@
         <v>13</v>
       </c>
       <c r="P509" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q509">
         <v>1059</v>
       </c>
       <c r="R509" s="93">
-        <v>94502</v>
+        <v>94501</v>
       </c>
       <c r="T509" s="85">
         <v>0</v>
@@ -77599,43 +78006,50 @@
       </c>
       <c r="Z509" s="94"/>
       <c r="AA509" s="94"/>
+      <c r="AE509" s="95"/>
+      <c r="AF509" s="95"/>
+      <c r="AG509" s="95"/>
+      <c r="AH509" s="95"/>
+      <c r="AI509" s="95"/>
+      <c r="AL509" s="95"/>
+      <c r="AM509" s="95"/>
     </row>
-    <row r="510" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="510" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B510" s="85">
-        <v>800033</v>
+        <v>800032</v>
       </c>
       <c r="C510" s="88" t="s">
-        <v>4841</v>
+        <v>4837</v>
       </c>
       <c r="D510" s="88" t="s">
-        <v>4842</v>
+        <v>4838</v>
       </c>
       <c r="E510" s="101" t="s">
-        <v>5324</v>
+        <v>5322</v>
       </c>
       <c r="F510" s="101" t="s">
-        <v>5084</v>
+        <v>5081</v>
       </c>
       <c r="G510" s="101" t="s">
-        <v>5076</v>
+        <v>5075</v>
       </c>
       <c r="H510" s="90" t="s">
-        <v>4843</v>
+        <v>4839</v>
       </c>
       <c r="I510" s="90" t="s">
-        <v>4844</v>
+        <v>4840</v>
       </c>
       <c r="J510" s="109" t="s">
-        <v>5334</v>
+        <v>5333</v>
       </c>
       <c r="K510" s="101" t="s">
-        <v>5088</v>
+        <v>5087</v>
       </c>
       <c r="L510" s="102" t="s">
-        <v>5090</v>
-      </c>
-      <c r="M510" s="96">
-        <v>2</v>
+        <v>5089</v>
+      </c>
+      <c r="M510" s="92">
+        <v>1</v>
       </c>
       <c r="N510" s="85">
         <v>0</v>
@@ -77644,13 +78058,13 @@
         <v>13</v>
       </c>
       <c r="P510" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q510">
         <v>1059</v>
       </c>
       <c r="R510" s="93">
-        <v>94503</v>
+        <v>94502</v>
       </c>
       <c r="T510" s="85">
         <v>0</v>
@@ -77661,42 +78075,42 @@
       <c r="Z510" s="94"/>
       <c r="AA510" s="94"/>
     </row>
-    <row r="511" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="511" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B511" s="85">
-        <v>800034</v>
+        <v>800033</v>
       </c>
       <c r="C511" s="88" t="s">
-        <v>4845</v>
+        <v>4841</v>
       </c>
       <c r="D511" s="88" t="s">
-        <v>4846</v>
-      </c>
-      <c r="E511" s="110" t="s">
-        <v>5321</v>
+        <v>4842</v>
+      </c>
+      <c r="E511" s="101" t="s">
+        <v>5324</v>
       </c>
       <c r="F511" s="101" t="s">
-        <v>5079</v>
+        <v>5084</v>
       </c>
       <c r="G511" s="101" t="s">
-        <v>5080</v>
+        <v>5076</v>
       </c>
       <c r="H511" s="90" t="s">
-        <v>4847</v>
+        <v>4843</v>
       </c>
       <c r="I511" s="90" t="s">
-        <v>4848</v>
+        <v>4844</v>
       </c>
       <c r="J511" s="109" t="s">
-        <v>5326</v>
-      </c>
-      <c r="K511" s="91" t="s">
-        <v>5091</v>
-      </c>
-      <c r="L511" s="103" t="s">
-        <v>5094</v>
-      </c>
-      <c r="M511" s="92">
-        <v>1</v>
+        <v>5334</v>
+      </c>
+      <c r="K511" s="101" t="s">
+        <v>5088</v>
+      </c>
+      <c r="L511" s="102" t="s">
+        <v>5090</v>
+      </c>
+      <c r="M511" s="96">
+        <v>2</v>
       </c>
       <c r="N511" s="85">
         <v>0</v>
@@ -77705,13 +78119,13 @@
         <v>13</v>
       </c>
       <c r="P511" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q511">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R511" s="93">
-        <v>94504</v>
+        <v>94503</v>
       </c>
       <c r="T511" s="85">
         <v>0</v>
@@ -77724,37 +78138,37 @@
     </row>
     <row r="512" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B512" s="85">
-        <v>800035</v>
+        <v>800034</v>
       </c>
       <c r="C512" s="88" t="s">
-        <v>4849</v>
+        <v>4845</v>
       </c>
       <c r="D512" s="88" t="s">
-        <v>4850</v>
+        <v>4846</v>
       </c>
       <c r="E512" s="110" t="s">
-        <v>5323</v>
+        <v>5321</v>
       </c>
       <c r="F512" s="101" t="s">
-        <v>5082</v>
-      </c>
-      <c r="G512" s="102" t="s">
-        <v>5083</v>
+        <v>5079</v>
+      </c>
+      <c r="G512" s="101" t="s">
+        <v>5080</v>
       </c>
       <c r="H512" s="90" t="s">
-        <v>4851</v>
+        <v>4847</v>
       </c>
       <c r="I512" s="90" t="s">
-        <v>4852</v>
+        <v>4848</v>
       </c>
       <c r="J512" s="109" t="s">
-        <v>5327</v>
+        <v>5326</v>
       </c>
       <c r="K512" s="91" t="s">
-        <v>5092</v>
+        <v>5091</v>
       </c>
       <c r="L512" s="103" t="s">
-        <v>5095</v>
+        <v>5094</v>
       </c>
       <c r="M512" s="92">
         <v>1</v>
@@ -77766,13 +78180,13 @@
         <v>13</v>
       </c>
       <c r="P512" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q512">
         <v>1060</v>
       </c>
       <c r="R512" s="93">
-        <v>94505</v>
+        <v>94504</v>
       </c>
       <c r="T512" s="85">
         <v>0</v>
@@ -77783,42 +78197,42 @@
       <c r="Z512" s="94"/>
       <c r="AA512" s="94"/>
     </row>
-    <row r="513" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="513" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B513" s="85">
-        <v>800036</v>
+        <v>800035</v>
       </c>
       <c r="C513" s="88" t="s">
-        <v>4853</v>
+        <v>4849</v>
       </c>
       <c r="D513" s="88" t="s">
-        <v>4854</v>
+        <v>4850</v>
       </c>
       <c r="E513" s="110" t="s">
-        <v>5325</v>
+        <v>5323</v>
       </c>
       <c r="F513" s="101" t="s">
-        <v>5085</v>
+        <v>5082</v>
       </c>
       <c r="G513" s="102" t="s">
-        <v>5086</v>
+        <v>5083</v>
       </c>
       <c r="H513" s="90" t="s">
-        <v>4855</v>
+        <v>4851</v>
       </c>
       <c r="I513" s="90" t="s">
-        <v>4856</v>
+        <v>4852</v>
       </c>
       <c r="J513" s="109" t="s">
-        <v>5328</v>
+        <v>5327</v>
       </c>
       <c r="K513" s="91" t="s">
-        <v>5093</v>
+        <v>5092</v>
       </c>
       <c r="L513" s="103" t="s">
-        <v>5096</v>
-      </c>
-      <c r="M513" s="96">
-        <v>2</v>
+        <v>5095</v>
+      </c>
+      <c r="M513" s="92">
+        <v>1</v>
       </c>
       <c r="N513" s="85">
         <v>0</v>
@@ -77827,13 +78241,13 @@
         <v>13</v>
       </c>
       <c r="P513" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q513">
         <v>1060</v>
       </c>
       <c r="R513" s="93">
-        <v>94506</v>
+        <v>94505</v>
       </c>
       <c r="T513" s="85">
         <v>0</v>
@@ -77844,42 +78258,42 @@
       <c r="Z513" s="94"/>
       <c r="AA513" s="94"/>
     </row>
-    <row r="514" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="514" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B514" s="85">
-        <v>800037</v>
+        <v>800036</v>
       </c>
       <c r="C514" s="88" t="s">
-        <v>4857</v>
+        <v>4853</v>
       </c>
       <c r="D514" s="88" t="s">
-        <v>4858</v>
+        <v>4854</v>
       </c>
       <c r="E514" s="110" t="s">
-        <v>5329</v>
-      </c>
-      <c r="F514" s="89" t="s">
-        <v>5097</v>
-      </c>
-      <c r="G514" s="104" t="s">
-        <v>5098</v>
+        <v>5325</v>
+      </c>
+      <c r="F514" s="101" t="s">
+        <v>5085</v>
+      </c>
+      <c r="G514" s="102" t="s">
+        <v>5086</v>
       </c>
       <c r="H514" s="90" t="s">
-        <v>4859</v>
+        <v>4855</v>
       </c>
       <c r="I514" s="90" t="s">
-        <v>4860</v>
+        <v>4856</v>
       </c>
       <c r="J514" s="109" t="s">
-        <v>5335</v>
+        <v>5328</v>
       </c>
       <c r="K514" s="91" t="s">
-        <v>5208</v>
-      </c>
-      <c r="L514" s="102" t="s">
-        <v>5211</v>
-      </c>
-      <c r="M514" s="92">
-        <v>1</v>
+        <v>5093</v>
+      </c>
+      <c r="L514" s="103" t="s">
+        <v>5096</v>
+      </c>
+      <c r="M514" s="96">
+        <v>2</v>
       </c>
       <c r="N514" s="85">
         <v>0</v>
@@ -77888,13 +78302,13 @@
         <v>13</v>
       </c>
       <c r="P514" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q514">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R514" s="93">
-        <v>94507</v>
+        <v>94506</v>
       </c>
       <c r="T514" s="85">
         <v>0</v>
@@ -77907,37 +78321,37 @@
     </row>
     <row r="515" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B515" s="85">
-        <v>800038</v>
+        <v>800037</v>
       </c>
       <c r="C515" s="88" t="s">
-        <v>4861</v>
+        <v>4857</v>
       </c>
       <c r="D515" s="88" t="s">
-        <v>4862</v>
+        <v>4858</v>
       </c>
       <c r="E515" s="110" t="s">
-        <v>5331</v>
+        <v>5329</v>
       </c>
       <c r="F515" s="89" t="s">
-        <v>5100</v>
+        <v>5097</v>
       </c>
       <c r="G515" s="104" t="s">
-        <v>5101</v>
+        <v>5098</v>
       </c>
       <c r="H515" s="90" t="s">
-        <v>4863</v>
+        <v>4859</v>
       </c>
       <c r="I515" s="90" t="s">
-        <v>4864</v>
+        <v>4860</v>
       </c>
       <c r="J515" s="109" t="s">
-        <v>5336</v>
+        <v>5335</v>
       </c>
       <c r="K515" s="91" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="L515" s="102" t="s">
-        <v>5212</v>
+        <v>5211</v>
       </c>
       <c r="M515" s="92">
         <v>1</v>
@@ -77949,13 +78363,13 @@
         <v>13</v>
       </c>
       <c r="P515" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q515">
         <v>1061</v>
       </c>
       <c r="R515" s="93">
-        <v>94508</v>
+        <v>94507</v>
       </c>
       <c r="T515" s="85">
         <v>0</v>
@@ -77968,40 +78382,40 @@
     </row>
     <row r="516" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B516" s="85">
-        <v>800039</v>
+        <v>800038</v>
       </c>
       <c r="C516" s="88" t="s">
-        <v>4865</v>
-      </c>
-      <c r="D516" s="107" t="s">
-        <v>5179</v>
+        <v>4861</v>
+      </c>
+      <c r="D516" s="88" t="s">
+        <v>4862</v>
       </c>
       <c r="E516" s="110" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="F516" s="89" t="s">
-        <v>5099</v>
+        <v>5100</v>
       </c>
       <c r="G516" s="104" t="s">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="H516" s="90" t="s">
-        <v>4866</v>
+        <v>4863</v>
       </c>
       <c r="I516" s="90" t="s">
-        <v>4867</v>
+        <v>4864</v>
       </c>
       <c r="J516" s="109" t="s">
-        <v>5337</v>
+        <v>5336</v>
       </c>
       <c r="K516" s="91" t="s">
-        <v>5210</v>
+        <v>5209</v>
       </c>
       <c r="L516" s="102" t="s">
-        <v>5213</v>
+        <v>5212</v>
       </c>
       <c r="M516" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N516" s="85">
         <v>0</v>
@@ -78010,13 +78424,13 @@
         <v>13</v>
       </c>
       <c r="P516" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q516">
         <v>1061</v>
       </c>
       <c r="R516" s="93">
-        <v>94509</v>
+        <v>94508</v>
       </c>
       <c r="T516" s="85">
         <v>0</v>
@@ -78029,40 +78443,40 @@
     </row>
     <row r="517" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B517" s="85">
-        <v>800040</v>
+        <v>800039</v>
       </c>
       <c r="C517" s="88" t="s">
-        <v>4868</v>
-      </c>
-      <c r="D517" s="88" t="s">
-        <v>4869</v>
+        <v>4865</v>
+      </c>
+      <c r="D517" s="107" t="s">
+        <v>5179</v>
       </c>
       <c r="E517" s="110" t="s">
-        <v>5339</v>
-      </c>
-      <c r="F517" s="101" t="s">
-        <v>5103</v>
-      </c>
-      <c r="G517" s="105" t="s">
-        <v>5104</v>
+        <v>5330</v>
+      </c>
+      <c r="F517" s="89" t="s">
+        <v>5099</v>
+      </c>
+      <c r="G517" s="104" t="s">
+        <v>5102</v>
       </c>
       <c r="H517" s="90" t="s">
-        <v>4870</v>
+        <v>4866</v>
       </c>
       <c r="I517" s="90" t="s">
-        <v>4871</v>
-      </c>
-      <c r="J517" s="111" t="s">
-        <v>5341</v>
+        <v>4867</v>
+      </c>
+      <c r="J517" s="109" t="s">
+        <v>5337</v>
       </c>
       <c r="K517" s="91" t="s">
-        <v>5214</v>
-      </c>
-      <c r="L517" s="103" t="s">
-        <v>5215</v>
+        <v>5210</v>
+      </c>
+      <c r="L517" s="102" t="s">
+        <v>5213</v>
       </c>
       <c r="M517" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N517" s="85">
         <v>0</v>
@@ -78071,10 +78485,13 @@
         <v>13</v>
       </c>
       <c r="P517" s="85">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="Q517">
+        <v>1061</v>
       </c>
       <c r="R517" s="93">
-        <v>94510</v>
+        <v>94509</v>
       </c>
       <c r="T517" s="85">
         <v>0</v>
@@ -78087,37 +78504,37 @@
     </row>
     <row r="518" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B518" s="85">
-        <v>800041</v>
+        <v>800040</v>
       </c>
       <c r="C518" s="88" t="s">
-        <v>4872</v>
+        <v>4868</v>
       </c>
       <c r="D518" s="88" t="s">
-        <v>4873</v>
+        <v>4869</v>
       </c>
       <c r="E518" s="110" t="s">
-        <v>5340</v>
+        <v>5339</v>
       </c>
       <c r="F518" s="101" t="s">
-        <v>5105</v>
-      </c>
-      <c r="G518" s="101" t="s">
-        <v>5106</v>
+        <v>5103</v>
+      </c>
+      <c r="G518" s="105" t="s">
+        <v>5104</v>
       </c>
       <c r="H518" s="90" t="s">
-        <v>4874</v>
+        <v>4870</v>
       </c>
       <c r="I518" s="90" t="s">
-        <v>4875</v>
+        <v>4871</v>
       </c>
       <c r="J518" s="111" t="s">
-        <v>5342</v>
+        <v>5341</v>
       </c>
       <c r="K518" s="91" t="s">
-        <v>5216</v>
+        <v>5214</v>
       </c>
       <c r="L518" s="103" t="s">
-        <v>5217</v>
+        <v>5215</v>
       </c>
       <c r="M518" s="92">
         <v>1</v>
@@ -78129,10 +78546,10 @@
         <v>13</v>
       </c>
       <c r="P518" s="85">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R518" s="93">
-        <v>94511</v>
+        <v>94510</v>
       </c>
       <c r="T518" s="85">
         <v>0</v>
@@ -78143,41 +78560,41 @@
       <c r="Z518" s="94"/>
       <c r="AA518" s="94"/>
     </row>
-    <row r="519" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="519" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B519" s="85">
-        <v>800042</v>
-      </c>
-      <c r="C519" s="97" t="s">
-        <v>4876</v>
-      </c>
-      <c r="D519" s="97" t="s">
-        <v>4876</v>
+        <v>800041</v>
+      </c>
+      <c r="C519" s="88" t="s">
+        <v>4872</v>
+      </c>
+      <c r="D519" s="88" t="s">
+        <v>4873</v>
       </c>
       <c r="E519" s="110" t="s">
-        <v>5343</v>
+        <v>5340</v>
       </c>
       <c r="F519" s="101" t="s">
-        <v>5180</v>
+        <v>5105</v>
       </c>
       <c r="G519" s="101" t="s">
-        <v>5107</v>
-      </c>
-      <c r="H519" s="97" t="s">
-        <v>4877</v>
-      </c>
-      <c r="I519" s="97" t="s">
-        <v>4878</v>
-      </c>
-      <c r="J519" s="109" t="s">
-        <v>5346</v>
-      </c>
-      <c r="K519" s="101" t="s">
-        <v>5218</v>
-      </c>
-      <c r="L519" s="102" t="s">
-        <v>5219</v>
-      </c>
-      <c r="M519" s="96">
+        <v>5106</v>
+      </c>
+      <c r="H519" s="90" t="s">
+        <v>4874</v>
+      </c>
+      <c r="I519" s="90" t="s">
+        <v>4875</v>
+      </c>
+      <c r="J519" s="111" t="s">
+        <v>5342</v>
+      </c>
+      <c r="K519" s="91" t="s">
+        <v>5216</v>
+      </c>
+      <c r="L519" s="103" t="s">
+        <v>5217</v>
+      </c>
+      <c r="M519" s="92">
         <v>1</v>
       </c>
       <c r="N519" s="85">
@@ -78187,13 +78604,10 @@
         <v>13</v>
       </c>
       <c r="P519" s="85">
-        <v>12</v>
-      </c>
-      <c r="Q519">
-        <v>1062</v>
+        <v>11</v>
       </c>
       <c r="R519" s="93">
-        <v>94512</v>
+        <v>94511</v>
       </c>
       <c r="T519" s="85">
         <v>0</v>
@@ -78204,41 +78618,41 @@
       <c r="Z519" s="94"/>
       <c r="AA519" s="94"/>
     </row>
-    <row r="520" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="520" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B520" s="85">
-        <v>800043</v>
+        <v>800042</v>
       </c>
       <c r="C520" s="97" t="s">
-        <v>4879</v>
+        <v>4876</v>
       </c>
       <c r="D520" s="97" t="s">
-        <v>4879</v>
+        <v>4876</v>
       </c>
       <c r="E520" s="110" t="s">
-        <v>5344</v>
+        <v>5343</v>
       </c>
       <c r="F520" s="101" t="s">
-        <v>5181</v>
-      </c>
-      <c r="G520" s="102" t="s">
-        <v>5184</v>
+        <v>5180</v>
+      </c>
+      <c r="G520" s="101" t="s">
+        <v>5107</v>
       </c>
       <c r="H520" s="97" t="s">
-        <v>4880</v>
+        <v>4877</v>
       </c>
       <c r="I520" s="97" t="s">
-        <v>4881</v>
+        <v>4878</v>
       </c>
       <c r="J520" s="109" t="s">
-        <v>5347</v>
+        <v>5346</v>
       </c>
       <c r="K520" s="101" t="s">
-        <v>5220</v>
+        <v>5218</v>
       </c>
       <c r="L520" s="102" t="s">
-        <v>5221</v>
-      </c>
-      <c r="M520" s="92">
+        <v>5219</v>
+      </c>
+      <c r="M520" s="96">
         <v>1</v>
       </c>
       <c r="N520" s="85">
@@ -78248,13 +78662,13 @@
         <v>13</v>
       </c>
       <c r="P520" s="85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q520">
         <v>1062</v>
       </c>
       <c r="R520" s="93">
-        <v>94513</v>
+        <v>94512</v>
       </c>
       <c r="T520" s="85">
         <v>0</v>
@@ -78267,40 +78681,40 @@
     </row>
     <row r="521" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B521" s="85">
-        <v>800044</v>
+        <v>800043</v>
       </c>
       <c r="C521" s="97" t="s">
-        <v>4882</v>
+        <v>4879</v>
       </c>
       <c r="D521" s="97" t="s">
-        <v>4882</v>
+        <v>4879</v>
       </c>
       <c r="E521" s="110" t="s">
-        <v>5345</v>
+        <v>5344</v>
       </c>
       <c r="F521" s="101" t="s">
-        <v>5182</v>
+        <v>5181</v>
       </c>
       <c r="G521" s="102" t="s">
-        <v>5183</v>
+        <v>5184</v>
       </c>
       <c r="H521" s="97" t="s">
-        <v>4883</v>
+        <v>4880</v>
       </c>
       <c r="I521" s="97" t="s">
-        <v>4884</v>
+        <v>4881</v>
       </c>
       <c r="J521" s="109" t="s">
-        <v>5348</v>
+        <v>5347</v>
       </c>
       <c r="K521" s="101" t="s">
-        <v>5222</v>
+        <v>5220</v>
       </c>
       <c r="L521" s="102" t="s">
-        <v>5223</v>
+        <v>5221</v>
       </c>
       <c r="M521" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N521" s="85">
         <v>0</v>
@@ -78309,13 +78723,13 @@
         <v>13</v>
       </c>
       <c r="P521" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q521">
         <v>1062</v>
       </c>
       <c r="R521" s="93">
-        <v>94514</v>
+        <v>94513</v>
       </c>
       <c r="T521" s="85">
         <v>0</v>
@@ -78328,40 +78742,40 @@
     </row>
     <row r="522" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B522" s="85">
-        <v>800045</v>
+        <v>800044</v>
       </c>
       <c r="C522" s="97" t="s">
-        <v>4885</v>
+        <v>4882</v>
       </c>
       <c r="D522" s="97" t="s">
-        <v>4886</v>
+        <v>4882</v>
       </c>
       <c r="E522" s="110" t="s">
-        <v>5349</v>
-      </c>
-      <c r="F522" s="105" t="s">
-        <v>5108</v>
-      </c>
-      <c r="G522" s="101" t="s">
-        <v>5109</v>
+        <v>5345</v>
+      </c>
+      <c r="F522" s="101" t="s">
+        <v>5182</v>
+      </c>
+      <c r="G522" s="102" t="s">
+        <v>5183</v>
       </c>
       <c r="H522" s="97" t="s">
-        <v>4887</v>
+        <v>4883</v>
       </c>
       <c r="I522" s="97" t="s">
-        <v>4888</v>
+        <v>4884</v>
       </c>
       <c r="J522" s="109" t="s">
-        <v>5352</v>
+        <v>5348</v>
       </c>
       <c r="K522" s="101" t="s">
-        <v>5224</v>
+        <v>5222</v>
       </c>
       <c r="L522" s="102" t="s">
-        <v>5225</v>
+        <v>5223</v>
       </c>
       <c r="M522" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N522" s="85">
         <v>0</v>
@@ -78370,13 +78784,13 @@
         <v>13</v>
       </c>
       <c r="P522" s="85">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q522">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R522" s="93">
-        <v>94515</v>
+        <v>94514</v>
       </c>
       <c r="T522" s="85">
         <v>0</v>
@@ -78387,41 +78801,41 @@
       <c r="Z522" s="94"/>
       <c r="AA522" s="94"/>
     </row>
-    <row r="523" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="523" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B523" s="85">
-        <v>800046</v>
+        <v>800045</v>
       </c>
       <c r="C523" s="97" t="s">
-        <v>4889</v>
+        <v>4885</v>
       </c>
       <c r="D523" s="97" t="s">
-        <v>4890</v>
+        <v>4886</v>
       </c>
       <c r="E523" s="110" t="s">
-        <v>5350</v>
+        <v>5349</v>
       </c>
       <c r="F523" s="105" t="s">
-        <v>5185</v>
-      </c>
-      <c r="G523" s="102" t="s">
-        <v>5186</v>
+        <v>5108</v>
+      </c>
+      <c r="G523" s="101" t="s">
+        <v>5109</v>
       </c>
       <c r="H523" s="97" t="s">
-        <v>4891</v>
+        <v>4887</v>
       </c>
       <c r="I523" s="97" t="s">
-        <v>4892</v>
+        <v>4888</v>
       </c>
       <c r="J523" s="109" t="s">
-        <v>5353</v>
+        <v>5352</v>
       </c>
       <c r="K523" s="101" t="s">
-        <v>5226</v>
+        <v>5224</v>
       </c>
       <c r="L523" s="102" t="s">
-        <v>5227</v>
-      </c>
-      <c r="M523" s="96">
+        <v>5225</v>
+      </c>
+      <c r="M523" s="92">
         <v>1</v>
       </c>
       <c r="N523" s="85">
@@ -78431,13 +78845,13 @@
         <v>13</v>
       </c>
       <c r="P523" s="85">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q523">
         <v>1063</v>
       </c>
       <c r="R523" s="93">
-        <v>94516</v>
+        <v>94515</v>
       </c>
       <c r="T523" s="85">
         <v>0</v>
@@ -78448,42 +78862,42 @@
       <c r="Z523" s="94"/>
       <c r="AA523" s="94"/>
     </row>
-    <row r="524" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="524" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B524" s="85">
-        <v>800047</v>
+        <v>800046</v>
       </c>
       <c r="C524" s="97" t="s">
-        <v>4893</v>
+        <v>4889</v>
       </c>
       <c r="D524" s="97" t="s">
-        <v>4894</v>
+        <v>4890</v>
       </c>
       <c r="E524" s="110" t="s">
-        <v>5351</v>
+        <v>5350</v>
       </c>
       <c r="F524" s="105" t="s">
-        <v>5187</v>
+        <v>5185</v>
       </c>
       <c r="G524" s="102" t="s">
-        <v>5188</v>
+        <v>5186</v>
       </c>
       <c r="H524" s="97" t="s">
-        <v>4895</v>
+        <v>4891</v>
       </c>
       <c r="I524" s="97" t="s">
-        <v>4896</v>
+        <v>4892</v>
       </c>
       <c r="J524" s="109" t="s">
-        <v>5354</v>
+        <v>5353</v>
       </c>
       <c r="K524" s="101" t="s">
-        <v>5228</v>
+        <v>5226</v>
       </c>
       <c r="L524" s="102" t="s">
-        <v>5229</v>
-      </c>
-      <c r="M524" s="92">
-        <v>2</v>
+        <v>5227</v>
+      </c>
+      <c r="M524" s="96">
+        <v>1</v>
       </c>
       <c r="N524" s="85">
         <v>0</v>
@@ -78492,13 +78906,13 @@
         <v>13</v>
       </c>
       <c r="P524" s="85">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q524">
         <v>1063</v>
       </c>
       <c r="R524" s="93">
-        <v>94517</v>
+        <v>94516</v>
       </c>
       <c r="T524" s="85">
         <v>0</v>
@@ -78511,40 +78925,40 @@
     </row>
     <row r="525" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B525" s="85">
-        <v>800048</v>
+        <v>800047</v>
       </c>
       <c r="C525" s="97" t="s">
-        <v>4897</v>
+        <v>4893</v>
       </c>
       <c r="D525" s="97" t="s">
-        <v>4898</v>
+        <v>4894</v>
       </c>
       <c r="E525" s="110" t="s">
-        <v>5355</v>
+        <v>5351</v>
       </c>
       <c r="F525" s="105" t="s">
-        <v>5110</v>
-      </c>
-      <c r="G525" s="101" t="s">
-        <v>5111</v>
+        <v>5187</v>
+      </c>
+      <c r="G525" s="102" t="s">
+        <v>5188</v>
       </c>
       <c r="H525" s="97" t="s">
-        <v>4899</v>
+        <v>4895</v>
       </c>
       <c r="I525" s="97" t="s">
-        <v>4900</v>
+        <v>4896</v>
       </c>
       <c r="J525" s="109" t="s">
-        <v>5358</v>
+        <v>5354</v>
       </c>
       <c r="K525" s="101" t="s">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="L525" s="102" t="s">
-        <v>5233</v>
+        <v>5229</v>
       </c>
       <c r="M525" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N525" s="85">
         <v>0</v>
@@ -78553,13 +78967,13 @@
         <v>13</v>
       </c>
       <c r="P525" s="85">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q525">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R525" s="93">
-        <v>94518</v>
+        <v>94517</v>
       </c>
       <c r="T525" s="85">
         <v>0</v>
@@ -78572,37 +78986,37 @@
     </row>
     <row r="526" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B526" s="85">
-        <v>800049</v>
+        <v>800048</v>
       </c>
       <c r="C526" s="97" t="s">
-        <v>4901</v>
+        <v>4897</v>
       </c>
       <c r="D526" s="97" t="s">
-        <v>4902</v>
+        <v>4898</v>
       </c>
       <c r="E526" s="110" t="s">
-        <v>5356</v>
+        <v>5355</v>
       </c>
       <c r="F526" s="105" t="s">
-        <v>5189</v>
-      </c>
-      <c r="G526" s="102" t="s">
-        <v>5190</v>
+        <v>5110</v>
+      </c>
+      <c r="G526" s="101" t="s">
+        <v>5111</v>
       </c>
       <c r="H526" s="97" t="s">
-        <v>4903</v>
+        <v>4899</v>
       </c>
       <c r="I526" s="97" t="s">
-        <v>4904</v>
+        <v>4900</v>
       </c>
       <c r="J526" s="109" t="s">
-        <v>5359</v>
+        <v>5358</v>
       </c>
       <c r="K526" s="101" t="s">
-        <v>5231</v>
+        <v>5230</v>
       </c>
       <c r="L526" s="102" t="s">
-        <v>5235</v>
+        <v>5233</v>
       </c>
       <c r="M526" s="92">
         <v>1</v>
@@ -78614,13 +79028,13 @@
         <v>13</v>
       </c>
       <c r="P526" s="85">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q526">
         <v>1064</v>
       </c>
       <c r="R526" s="93">
-        <v>94519</v>
+        <v>94518</v>
       </c>
       <c r="T526" s="85">
         <v>0</v>
@@ -78631,42 +79045,42 @@
       <c r="Z526" s="94"/>
       <c r="AA526" s="94"/>
     </row>
-    <row r="527" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="527" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B527" s="85">
-        <v>800050</v>
+        <v>800049</v>
       </c>
       <c r="C527" s="97" t="s">
-        <v>4905</v>
+        <v>4901</v>
       </c>
       <c r="D527" s="97" t="s">
-        <v>4906</v>
+        <v>4902</v>
       </c>
       <c r="E527" s="110" t="s">
-        <v>5357</v>
+        <v>5356</v>
       </c>
       <c r="F527" s="105" t="s">
-        <v>5191</v>
+        <v>5189</v>
       </c>
       <c r="G527" s="102" t="s">
-        <v>5192</v>
+        <v>5190</v>
       </c>
       <c r="H527" s="97" t="s">
-        <v>4907</v>
+        <v>4903</v>
       </c>
       <c r="I527" s="97" t="s">
-        <v>4908</v>
+        <v>4904</v>
       </c>
       <c r="J527" s="109" t="s">
-        <v>5360</v>
+        <v>5359</v>
       </c>
       <c r="K527" s="101" t="s">
-        <v>5232</v>
+        <v>5231</v>
       </c>
       <c r="L527" s="102" t="s">
-        <v>5234</v>
-      </c>
-      <c r="M527" s="96">
-        <v>2</v>
+        <v>5235</v>
+      </c>
+      <c r="M527" s="92">
+        <v>1</v>
       </c>
       <c r="N527" s="85">
         <v>0</v>
@@ -78675,13 +79089,13 @@
         <v>13</v>
       </c>
       <c r="P527" s="85">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q527">
         <v>1064</v>
       </c>
       <c r="R527" s="93">
-        <v>94520</v>
+        <v>94519</v>
       </c>
       <c r="T527" s="85">
         <v>0</v>
@@ -78692,42 +79106,42 @@
       <c r="Z527" s="94"/>
       <c r="AA527" s="94"/>
     </row>
-    <row r="528" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="528" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B528" s="85">
-        <v>800051</v>
+        <v>800050</v>
       </c>
       <c r="C528" s="97" t="s">
-        <v>4909</v>
-      </c>
-      <c r="D528" s="112" t="s">
-        <v>5443</v>
-      </c>
-      <c r="E528" s="101" t="s">
-        <v>5361</v>
+        <v>4905</v>
+      </c>
+      <c r="D528" s="97" t="s">
+        <v>4906</v>
+      </c>
+      <c r="E528" s="110" t="s">
+        <v>5357</v>
       </c>
       <c r="F528" s="105" t="s">
-        <v>5112</v>
-      </c>
-      <c r="G528" s="101" t="s">
-        <v>5113</v>
+        <v>5191</v>
+      </c>
+      <c r="G528" s="102" t="s">
+        <v>5192</v>
       </c>
       <c r="H528" s="97" t="s">
-        <v>4910</v>
-      </c>
-      <c r="I528" s="112" t="s">
-        <v>5446</v>
-      </c>
-      <c r="J528" s="101" t="s">
-        <v>5375</v>
+        <v>4907</v>
+      </c>
+      <c r="I528" s="97" t="s">
+        <v>4908</v>
+      </c>
+      <c r="J528" s="109" t="s">
+        <v>5360</v>
       </c>
       <c r="K528" s="101" t="s">
-        <v>5236</v>
-      </c>
-      <c r="L528" s="101" t="s">
-        <v>5237</v>
-      </c>
-      <c r="M528" s="92">
-        <v>1</v>
+        <v>5232</v>
+      </c>
+      <c r="L528" s="102" t="s">
+        <v>5234</v>
+      </c>
+      <c r="M528" s="96">
+        <v>2</v>
       </c>
       <c r="N528" s="85">
         <v>0</v>
@@ -78736,10 +79150,13 @@
         <v>13</v>
       </c>
       <c r="P528" s="85">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="Q528">
+        <v>1064</v>
       </c>
       <c r="R528" s="93">
-        <v>94521</v>
+        <v>94520</v>
       </c>
       <c r="T528" s="85">
         <v>0</v>
@@ -78752,37 +79169,37 @@
     </row>
     <row r="529" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B529" s="85">
-        <v>800052</v>
+        <v>800051</v>
       </c>
       <c r="C529" s="97" t="s">
-        <v>4911</v>
+        <v>4909</v>
       </c>
       <c r="D529" s="112" t="s">
-        <v>5444</v>
+        <v>5443</v>
       </c>
       <c r="E529" s="101" t="s">
-        <v>5362</v>
+        <v>5361</v>
       </c>
       <c r="F529" s="105" t="s">
-        <v>5114</v>
+        <v>5112</v>
       </c>
       <c r="G529" s="101" t="s">
-        <v>5115</v>
+        <v>5113</v>
       </c>
       <c r="H529" s="97" t="s">
-        <v>4912</v>
+        <v>4910</v>
       </c>
       <c r="I529" s="112" t="s">
-        <v>5447</v>
+        <v>5446</v>
       </c>
       <c r="J529" s="101" t="s">
-        <v>5376</v>
+        <v>5375</v>
       </c>
       <c r="K529" s="101" t="s">
-        <v>5238</v>
+        <v>5236</v>
       </c>
       <c r="L529" s="101" t="s">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="M529" s="92">
         <v>1</v>
@@ -78794,10 +79211,10 @@
         <v>13</v>
       </c>
       <c r="P529" s="85">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R529" s="93">
-        <v>94522</v>
+        <v>94521</v>
       </c>
       <c r="T529" s="85">
         <v>0</v>
@@ -78810,37 +79227,37 @@
     </row>
     <row r="530" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B530" s="85">
-        <v>800053</v>
+        <v>800052</v>
       </c>
       <c r="C530" s="97" t="s">
-        <v>4913</v>
-      </c>
-      <c r="D530" s="97" t="s">
-        <v>4914</v>
+        <v>4911</v>
+      </c>
+      <c r="D530" s="112" t="s">
+        <v>5444</v>
       </c>
       <c r="E530" s="101" t="s">
-        <v>5363</v>
+        <v>5362</v>
       </c>
       <c r="F530" s="105" t="s">
-        <v>5116</v>
+        <v>5114</v>
       </c>
       <c r="G530" s="101" t="s">
-        <v>5117</v>
+        <v>5115</v>
       </c>
       <c r="H530" s="97" t="s">
-        <v>4915</v>
-      </c>
-      <c r="I530" s="97" t="s">
-        <v>4916</v>
+        <v>4912</v>
+      </c>
+      <c r="I530" s="112" t="s">
+        <v>5447</v>
       </c>
       <c r="J530" s="101" t="s">
-        <v>5377</v>
+        <v>5376</v>
       </c>
       <c r="K530" s="101" t="s">
-        <v>5240</v>
+        <v>5238</v>
       </c>
       <c r="L530" s="101" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="M530" s="92">
         <v>1</v>
@@ -78852,10 +79269,10 @@
         <v>13</v>
       </c>
       <c r="P530" s="85">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R530" s="93">
-        <v>94523</v>
+        <v>94522</v>
       </c>
       <c r="T530" s="85">
         <v>0</v>
@@ -78866,41 +79283,41 @@
       <c r="Z530" s="94"/>
       <c r="AA530" s="94"/>
     </row>
-    <row r="531" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="531" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B531" s="85">
-        <v>800054</v>
+        <v>800053</v>
       </c>
       <c r="C531" s="97" t="s">
-        <v>4917</v>
-      </c>
-      <c r="D531" s="112" t="s">
-        <v>5445</v>
+        <v>4913</v>
+      </c>
+      <c r="D531" s="97" t="s">
+        <v>4914</v>
       </c>
       <c r="E531" s="101" t="s">
-        <v>5364</v>
+        <v>5363</v>
       </c>
       <c r="F531" s="105" t="s">
-        <v>5118</v>
+        <v>5116</v>
       </c>
       <c r="G531" s="101" t="s">
-        <v>5119</v>
+        <v>5117</v>
       </c>
       <c r="H531" s="97" t="s">
-        <v>4918</v>
-      </c>
-      <c r="I531" s="112" t="s">
-        <v>5448</v>
+        <v>4915</v>
+      </c>
+      <c r="I531" s="97" t="s">
+        <v>4916</v>
       </c>
       <c r="J531" s="101" t="s">
-        <v>5378</v>
+        <v>5377</v>
       </c>
       <c r="K531" s="101" t="s">
-        <v>5242</v>
+        <v>5240</v>
       </c>
       <c r="L531" s="101" t="s">
-        <v>5243</v>
-      </c>
-      <c r="M531" s="96">
+        <v>5241</v>
+      </c>
+      <c r="M531" s="92">
         <v>1</v>
       </c>
       <c r="N531" s="85">
@@ -78910,10 +79327,10 @@
         <v>13</v>
       </c>
       <c r="P531" s="85">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R531" s="93">
-        <v>94524</v>
+        <v>94523</v>
       </c>
       <c r="T531" s="85">
         <v>0</v>
@@ -78924,41 +79341,41 @@
       <c r="Z531" s="94"/>
       <c r="AA531" s="94"/>
     </row>
-    <row r="532" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="532" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B532" s="85">
-        <v>800055</v>
+        <v>800054</v>
       </c>
       <c r="C532" s="97" t="s">
-        <v>4919</v>
+        <v>4917</v>
       </c>
       <c r="D532" s="112" t="s">
-        <v>5450</v>
+        <v>5445</v>
       </c>
       <c r="E532" s="101" t="s">
-        <v>5365</v>
+        <v>5364</v>
       </c>
       <c r="F532" s="105" t="s">
-        <v>5120</v>
+        <v>5118</v>
       </c>
       <c r="G532" s="101" t="s">
-        <v>5121</v>
+        <v>5119</v>
       </c>
       <c r="H532" s="97" t="s">
-        <v>4920</v>
-      </c>
-      <c r="I532" s="97" t="s">
-        <v>4921</v>
+        <v>4918</v>
+      </c>
+      <c r="I532" s="112" t="s">
+        <v>5448</v>
       </c>
       <c r="J532" s="101" t="s">
-        <v>5379</v>
+        <v>5378</v>
       </c>
       <c r="K532" s="101" t="s">
-        <v>5244</v>
+        <v>5242</v>
       </c>
       <c r="L532" s="101" t="s">
-        <v>5245</v>
-      </c>
-      <c r="M532" s="92">
+        <v>5243</v>
+      </c>
+      <c r="M532" s="96">
         <v>1</v>
       </c>
       <c r="N532" s="85">
@@ -78968,10 +79385,10 @@
         <v>13</v>
       </c>
       <c r="P532" s="85">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R532" s="93">
-        <v>94525</v>
+        <v>94524</v>
       </c>
       <c r="T532" s="85">
         <v>0</v>
@@ -78984,40 +79401,40 @@
     </row>
     <row r="533" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B533" s="85">
-        <v>800056</v>
+        <v>800055</v>
       </c>
       <c r="C533" s="97" t="s">
-        <v>4922</v>
-      </c>
-      <c r="D533" s="97" t="s">
-        <v>4923</v>
+        <v>4919</v>
+      </c>
+      <c r="D533" s="112" t="s">
+        <v>5450</v>
       </c>
       <c r="E533" s="101" t="s">
-        <v>5366</v>
+        <v>5365</v>
       </c>
       <c r="F533" s="105" t="s">
-        <v>5122</v>
+        <v>5120</v>
       </c>
       <c r="G533" s="101" t="s">
-        <v>5123</v>
+        <v>5121</v>
       </c>
       <c r="H533" s="97" t="s">
-        <v>4924</v>
+        <v>4920</v>
       </c>
       <c r="I533" s="97" t="s">
-        <v>4925</v>
+        <v>4921</v>
       </c>
       <c r="J533" s="101" t="s">
-        <v>5380</v>
+        <v>5379</v>
       </c>
       <c r="K533" s="101" t="s">
-        <v>5246</v>
+        <v>5244</v>
       </c>
       <c r="L533" s="101" t="s">
-        <v>5247</v>
+        <v>5245</v>
       </c>
       <c r="M533" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N533" s="85">
         <v>0</v>
@@ -79026,10 +79443,10 @@
         <v>13</v>
       </c>
       <c r="P533" s="85">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R533" s="93">
-        <v>94526</v>
+        <v>94525</v>
       </c>
       <c r="T533" s="85">
         <v>0</v>
@@ -79042,40 +79459,40 @@
     </row>
     <row r="534" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B534" s="85">
-        <v>800057</v>
+        <v>800056</v>
       </c>
       <c r="C534" s="97" t="s">
-        <v>4926</v>
+        <v>4922</v>
       </c>
       <c r="D534" s="97" t="s">
-        <v>4927</v>
+        <v>4923</v>
       </c>
       <c r="E534" s="101" t="s">
-        <v>5367</v>
+        <v>5366</v>
       </c>
       <c r="F534" s="105" t="s">
-        <v>5124</v>
+        <v>5122</v>
       </c>
       <c r="G534" s="101" t="s">
-        <v>5125</v>
+        <v>5123</v>
       </c>
       <c r="H534" s="97" t="s">
-        <v>4928</v>
+        <v>4924</v>
       </c>
       <c r="I534" s="97" t="s">
-        <v>4929</v>
+        <v>4925</v>
       </c>
       <c r="J534" s="101" t="s">
-        <v>5381</v>
+        <v>5380</v>
       </c>
       <c r="K534" s="101" t="s">
-        <v>5248</v>
+        <v>5246</v>
       </c>
       <c r="L534" s="101" t="s">
-        <v>5249</v>
+        <v>5247</v>
       </c>
       <c r="M534" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N534" s="85">
         <v>0</v>
@@ -79084,10 +79501,10 @@
         <v>13</v>
       </c>
       <c r="P534" s="85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R534" s="93">
-        <v>94527</v>
+        <v>94526</v>
       </c>
       <c r="T534" s="85">
         <v>0</v>
@@ -79098,41 +79515,41 @@
       <c r="Z534" s="94"/>
       <c r="AA534" s="94"/>
     </row>
-    <row r="535" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="535" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B535" s="85">
-        <v>800058</v>
+        <v>800057</v>
       </c>
       <c r="C535" s="97" t="s">
-        <v>4930</v>
-      </c>
-      <c r="D535" s="112" t="s">
-        <v>5449</v>
+        <v>4926</v>
+      </c>
+      <c r="D535" s="97" t="s">
+        <v>4927</v>
       </c>
       <c r="E535" s="101" t="s">
-        <v>5368</v>
+        <v>5367</v>
       </c>
       <c r="F535" s="105" t="s">
-        <v>5126</v>
+        <v>5124</v>
       </c>
       <c r="G535" s="101" t="s">
-        <v>5127</v>
+        <v>5125</v>
       </c>
       <c r="H535" s="97" t="s">
-        <v>4931</v>
+        <v>4928</v>
       </c>
       <c r="I535" s="97" t="s">
-        <v>4932</v>
+        <v>4929</v>
       </c>
       <c r="J535" s="101" t="s">
-        <v>5382</v>
+        <v>5381</v>
       </c>
       <c r="K535" s="101" t="s">
-        <v>5250</v>
+        <v>5248</v>
       </c>
       <c r="L535" s="101" t="s">
-        <v>5251</v>
-      </c>
-      <c r="M535" s="96">
+        <v>5249</v>
+      </c>
+      <c r="M535" s="92">
         <v>1</v>
       </c>
       <c r="N535" s="85">
@@ -79142,10 +79559,10 @@
         <v>13</v>
       </c>
       <c r="P535" s="85">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R535" s="93">
-        <v>94528</v>
+        <v>94527</v>
       </c>
       <c r="T535" s="85">
         <v>0</v>
@@ -79156,41 +79573,41 @@
       <c r="Z535" s="94"/>
       <c r="AA535" s="94"/>
     </row>
-    <row r="536" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="536" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B536" s="85">
-        <v>800059</v>
+        <v>800058</v>
       </c>
       <c r="C536" s="97" t="s">
-        <v>4933</v>
+        <v>4930</v>
       </c>
       <c r="D536" s="112" t="s">
-        <v>5451</v>
+        <v>5449</v>
       </c>
       <c r="E536" s="101" t="s">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="F536" s="105" t="s">
-        <v>5128</v>
+        <v>5126</v>
       </c>
       <c r="G536" s="101" t="s">
-        <v>5129</v>
+        <v>5127</v>
       </c>
       <c r="H536" s="97" t="s">
-        <v>4934</v>
-      </c>
-      <c r="I536" s="112" t="s">
-        <v>5452</v>
+        <v>4931</v>
+      </c>
+      <c r="I536" s="97" t="s">
+        <v>4932</v>
       </c>
       <c r="J536" s="101" t="s">
-        <v>5383</v>
+        <v>5382</v>
       </c>
       <c r="K536" s="101" t="s">
-        <v>5252</v>
+        <v>5250</v>
       </c>
       <c r="L536" s="101" t="s">
-        <v>5253</v>
-      </c>
-      <c r="M536" s="92">
+        <v>5251</v>
+      </c>
+      <c r="M536" s="96">
         <v>1</v>
       </c>
       <c r="N536" s="85">
@@ -79200,10 +79617,10 @@
         <v>13</v>
       </c>
       <c r="P536" s="85">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R536" s="93">
-        <v>94529</v>
+        <v>94528</v>
       </c>
       <c r="T536" s="85">
         <v>0</v>
@@ -79216,40 +79633,40 @@
     </row>
     <row r="537" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B537" s="85">
-        <v>800060</v>
-      </c>
-      <c r="C537" s="98" t="s">
-        <v>4935</v>
-      </c>
-      <c r="D537" s="98" t="s">
-        <v>4936</v>
+        <v>800059</v>
+      </c>
+      <c r="C537" s="97" t="s">
+        <v>4933</v>
+      </c>
+      <c r="D537" s="112" t="s">
+        <v>5451</v>
       </c>
       <c r="E537" s="101" t="s">
-        <v>5370</v>
+        <v>5369</v>
       </c>
       <c r="F537" s="105" t="s">
-        <v>5130</v>
+        <v>5128</v>
       </c>
       <c r="G537" s="101" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="H537" s="97" t="s">
-        <v>4937</v>
-      </c>
-      <c r="I537" s="97" t="s">
-        <v>4938</v>
+        <v>4934</v>
+      </c>
+      <c r="I537" s="112" t="s">
+        <v>5452</v>
       </c>
       <c r="J537" s="101" t="s">
-        <v>5384</v>
+        <v>5383</v>
       </c>
       <c r="K537" s="101" t="s">
-        <v>5254</v>
+        <v>5252</v>
       </c>
       <c r="L537" s="101" t="s">
-        <v>5255</v>
+        <v>5253</v>
       </c>
       <c r="M537" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N537" s="85">
         <v>0</v>
@@ -79258,10 +79675,10 @@
         <v>13</v>
       </c>
       <c r="P537" s="85">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R537" s="93">
-        <v>94530</v>
+        <v>94529</v>
       </c>
       <c r="T537" s="85">
         <v>0</v>
@@ -79274,37 +79691,37 @@
     </row>
     <row r="538" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B538" s="85">
-        <v>800061</v>
-      </c>
-      <c r="C538" s="97" t="s">
-        <v>4939</v>
-      </c>
-      <c r="D538" s="97" t="s">
-        <v>4940</v>
+        <v>800060</v>
+      </c>
+      <c r="C538" s="98" t="s">
+        <v>4935</v>
+      </c>
+      <c r="D538" s="98" t="s">
+        <v>4936</v>
       </c>
       <c r="E538" s="101" t="s">
-        <v>5371</v>
+        <v>5370</v>
       </c>
       <c r="F538" s="105" t="s">
-        <v>5132</v>
+        <v>5130</v>
       </c>
       <c r="G538" s="101" t="s">
-        <v>5133</v>
+        <v>5131</v>
       </c>
       <c r="H538" s="97" t="s">
-        <v>4941</v>
+        <v>4937</v>
       </c>
       <c r="I538" s="97" t="s">
-        <v>4942</v>
+        <v>4938</v>
       </c>
       <c r="J538" s="101" t="s">
-        <v>5385</v>
+        <v>5384</v>
       </c>
       <c r="K538" s="101" t="s">
-        <v>5256</v>
+        <v>5254</v>
       </c>
       <c r="L538" s="101" t="s">
-        <v>5257</v>
+        <v>5255</v>
       </c>
       <c r="M538" s="92">
         <v>2</v>
@@ -79316,10 +79733,10 @@
         <v>13</v>
       </c>
       <c r="P538" s="85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R538" s="93">
-        <v>94531</v>
+        <v>94530</v>
       </c>
       <c r="T538" s="85">
         <v>0</v>
@@ -79330,41 +79747,41 @@
       <c r="Z538" s="94"/>
       <c r="AA538" s="94"/>
     </row>
-    <row r="539" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="539" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B539" s="85">
-        <v>800062</v>
+        <v>800061</v>
       </c>
       <c r="C539" s="97" t="s">
-        <v>4943</v>
+        <v>4939</v>
       </c>
       <c r="D539" s="97" t="s">
-        <v>4944</v>
+        <v>4940</v>
       </c>
       <c r="E539" s="101" t="s">
-        <v>5372</v>
+        <v>5371</v>
       </c>
       <c r="F539" s="105" t="s">
-        <v>5134</v>
+        <v>5132</v>
       </c>
       <c r="G539" s="101" t="s">
-        <v>5135</v>
+        <v>5133</v>
       </c>
       <c r="H539" s="97" t="s">
-        <v>4945</v>
+        <v>4941</v>
       </c>
       <c r="I539" s="97" t="s">
-        <v>4946</v>
+        <v>4942</v>
       </c>
       <c r="J539" s="101" t="s">
-        <v>5386</v>
+        <v>5385</v>
       </c>
       <c r="K539" s="101" t="s">
-        <v>5258</v>
+        <v>5256</v>
       </c>
       <c r="L539" s="101" t="s">
-        <v>5259</v>
-      </c>
-      <c r="M539" s="96">
+        <v>5257</v>
+      </c>
+      <c r="M539" s="92">
         <v>2</v>
       </c>
       <c r="N539" s="85">
@@ -79374,10 +79791,10 @@
         <v>13</v>
       </c>
       <c r="P539" s="85">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R539" s="93">
-        <v>94532</v>
+        <v>94531</v>
       </c>
       <c r="T539" s="85">
         <v>0</v>
@@ -79388,41 +79805,41 @@
       <c r="Z539" s="94"/>
       <c r="AA539" s="94"/>
     </row>
-    <row r="540" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="540" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B540" s="85">
-        <v>800063</v>
+        <v>800062</v>
       </c>
       <c r="C540" s="97" t="s">
-        <v>4947</v>
+        <v>4943</v>
       </c>
       <c r="D540" s="97" t="s">
-        <v>4947</v>
+        <v>4944</v>
       </c>
       <c r="E540" s="101" t="s">
-        <v>5373</v>
+        <v>5372</v>
       </c>
       <c r="F540" s="105" t="s">
-        <v>5136</v>
+        <v>5134</v>
       </c>
       <c r="G540" s="101" t="s">
-        <v>5137</v>
+        <v>5135</v>
       </c>
       <c r="H540" s="97" t="s">
-        <v>4948</v>
+        <v>4945</v>
       </c>
       <c r="I540" s="97" t="s">
-        <v>4949</v>
+        <v>4946</v>
       </c>
       <c r="J540" s="101" t="s">
-        <v>5387</v>
+        <v>5386</v>
       </c>
       <c r="K540" s="101" t="s">
-        <v>5260</v>
+        <v>5258</v>
       </c>
       <c r="L540" s="101" t="s">
-        <v>5261</v>
-      </c>
-      <c r="M540" s="92">
+        <v>5259</v>
+      </c>
+      <c r="M540" s="96">
         <v>2</v>
       </c>
       <c r="N540" s="85">
@@ -79432,10 +79849,10 @@
         <v>13</v>
       </c>
       <c r="P540" s="85">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R540" s="93">
-        <v>94533</v>
+        <v>94532</v>
       </c>
       <c r="T540" s="85">
         <v>0</v>
@@ -79448,37 +79865,37 @@
     </row>
     <row r="541" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B541" s="85">
-        <v>800064</v>
+        <v>800063</v>
       </c>
       <c r="C541" s="97" t="s">
-        <v>4950</v>
+        <v>4947</v>
       </c>
       <c r="D541" s="97" t="s">
-        <v>4950</v>
+        <v>4947</v>
       </c>
       <c r="E541" s="101" t="s">
-        <v>5374</v>
+        <v>5373</v>
       </c>
       <c r="F541" s="105" t="s">
-        <v>5138</v>
+        <v>5136</v>
       </c>
       <c r="G541" s="101" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="H541" s="97" t="s">
-        <v>4951</v>
+        <v>4948</v>
       </c>
       <c r="I541" s="97" t="s">
-        <v>4952</v>
+        <v>4949</v>
       </c>
       <c r="J541" s="101" t="s">
-        <v>5388</v>
+        <v>5387</v>
       </c>
       <c r="K541" s="101" t="s">
-        <v>5262</v>
+        <v>5260</v>
       </c>
       <c r="L541" s="101" t="s">
-        <v>5263</v>
+        <v>5261</v>
       </c>
       <c r="M541" s="92">
         <v>2</v>
@@ -79490,10 +79907,10 @@
         <v>13</v>
       </c>
       <c r="P541" s="85">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R541" s="93">
-        <v>94534</v>
+        <v>94533</v>
       </c>
       <c r="T541" s="85">
         <v>0</v>
@@ -79504,42 +79921,42 @@
       <c r="Z541" s="94"/>
       <c r="AA541" s="94"/>
     </row>
-    <row r="542" spans="2:27" s="85" customFormat="1" ht="16.5">
+    <row r="542" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B542" s="85">
-        <v>800065</v>
+        <v>800064</v>
       </c>
       <c r="C542" s="97" t="s">
-        <v>4953</v>
+        <v>4950</v>
       </c>
       <c r="D542" s="97" t="s">
-        <v>4954</v>
+        <v>4950</v>
       </c>
       <c r="E542" s="101" t="s">
-        <v>5389</v>
-      </c>
-      <c r="F542" s="101" t="s">
-        <v>5140</v>
+        <v>5374</v>
+      </c>
+      <c r="F542" s="105" t="s">
+        <v>5138</v>
       </c>
       <c r="G542" s="101" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="H542" s="97" t="s">
-        <v>4955</v>
+        <v>4951</v>
       </c>
       <c r="I542" s="97" t="s">
-        <v>4956</v>
+        <v>4952</v>
       </c>
       <c r="J542" s="101" t="s">
-        <v>5393</v>
+        <v>5388</v>
       </c>
       <c r="K542" s="101" t="s">
-        <v>5264</v>
+        <v>5262</v>
       </c>
       <c r="L542" s="101" t="s">
-        <v>5265</v>
+        <v>5263</v>
       </c>
       <c r="M542" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N542" s="85">
         <v>0</v>
@@ -79548,10 +79965,10 @@
         <v>13</v>
       </c>
       <c r="P542" s="85">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R542" s="93">
-        <v>94535</v>
+        <v>94534</v>
       </c>
       <c r="T542" s="85">
         <v>0</v>
@@ -79562,41 +79979,41 @@
       <c r="Z542" s="94"/>
       <c r="AA542" s="94"/>
     </row>
-    <row r="543" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="543" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B543" s="85">
-        <v>800066</v>
+        <v>800065</v>
       </c>
       <c r="C543" s="97" t="s">
-        <v>4957</v>
+        <v>4953</v>
       </c>
       <c r="D543" s="97" t="s">
-        <v>4958</v>
+        <v>4954</v>
       </c>
       <c r="E543" s="101" t="s">
-        <v>5390</v>
+        <v>5389</v>
       </c>
       <c r="F543" s="101" t="s">
-        <v>5142</v>
+        <v>5140</v>
       </c>
       <c r="G543" s="101" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="H543" s="97" t="s">
-        <v>4959</v>
+        <v>4955</v>
       </c>
       <c r="I543" s="97" t="s">
-        <v>4960</v>
+        <v>4956</v>
       </c>
       <c r="J543" s="101" t="s">
-        <v>5394</v>
+        <v>5393</v>
       </c>
       <c r="K543" s="101" t="s">
-        <v>5266</v>
+        <v>5264</v>
       </c>
       <c r="L543" s="101" t="s">
-        <v>5267</v>
-      </c>
-      <c r="M543" s="96">
+        <v>5265</v>
+      </c>
+      <c r="M543" s="92">
         <v>1</v>
       </c>
       <c r="N543" s="85">
@@ -79606,13 +80023,10 @@
         <v>13</v>
       </c>
       <c r="P543" s="85">
-        <v>36</v>
-      </c>
-      <c r="Q543">
-        <v>1065</v>
+        <v>35</v>
       </c>
       <c r="R543" s="93">
-        <v>94536</v>
+        <v>94535</v>
       </c>
       <c r="T543" s="85">
         <v>0</v>
@@ -79623,42 +80037,42 @@
       <c r="Z543" s="94"/>
       <c r="AA543" s="94"/>
     </row>
-    <row r="544" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="544" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B544" s="85">
-        <v>800067</v>
+        <v>800066</v>
       </c>
       <c r="C544" s="97" t="s">
-        <v>4961</v>
+        <v>4957</v>
       </c>
       <c r="D544" s="97" t="s">
-        <v>4962</v>
+        <v>4958</v>
       </c>
       <c r="E544" s="101" t="s">
-        <v>5391</v>
+        <v>5390</v>
       </c>
       <c r="F544" s="101" t="s">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="G544" s="101" t="s">
-        <v>5145</v>
+        <v>5143</v>
       </c>
       <c r="H544" s="97" t="s">
-        <v>4963</v>
+        <v>4959</v>
       </c>
       <c r="I544" s="97" t="s">
-        <v>4964</v>
+        <v>4960</v>
       </c>
       <c r="J544" s="101" t="s">
-        <v>5395</v>
+        <v>5394</v>
       </c>
       <c r="K544" s="101" t="s">
-        <v>5268</v>
+        <v>5266</v>
       </c>
       <c r="L544" s="101" t="s">
-        <v>5269</v>
-      </c>
-      <c r="M544" s="92">
-        <v>2</v>
+        <v>5267</v>
+      </c>
+      <c r="M544" s="96">
+        <v>1</v>
       </c>
       <c r="N544" s="85">
         <v>0</v>
@@ -79667,13 +80081,13 @@
         <v>13</v>
       </c>
       <c r="P544" s="85">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q544">
         <v>1065</v>
       </c>
       <c r="R544" s="93">
-        <v>94537</v>
+        <v>94536</v>
       </c>
       <c r="T544" s="85">
         <v>0</v>
@@ -79686,40 +80100,40 @@
     </row>
     <row r="545" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B545" s="85">
-        <v>800068</v>
+        <v>800067</v>
       </c>
       <c r="C545" s="97" t="s">
-        <v>4965</v>
+        <v>4961</v>
       </c>
       <c r="D545" s="97" t="s">
-        <v>4966</v>
+        <v>4962</v>
       </c>
       <c r="E545" s="101" t="s">
-        <v>5392</v>
+        <v>5391</v>
       </c>
       <c r="F545" s="101" t="s">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="G545" s="101" t="s">
-        <v>5147</v>
+        <v>5145</v>
       </c>
       <c r="H545" s="97" t="s">
-        <v>4967</v>
+        <v>4963</v>
       </c>
       <c r="I545" s="97" t="s">
-        <v>4968</v>
+        <v>4964</v>
       </c>
       <c r="J545" s="101" t="s">
-        <v>5396</v>
+        <v>5395</v>
       </c>
       <c r="K545" s="101" t="s">
-        <v>5270</v>
+        <v>5268</v>
       </c>
       <c r="L545" s="101" t="s">
-        <v>5271</v>
+        <v>5269</v>
       </c>
       <c r="M545" s="92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N545" s="85">
         <v>0</v>
@@ -79728,13 +80142,13 @@
         <v>13</v>
       </c>
       <c r="P545" s="85">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q545">
         <v>1065</v>
       </c>
       <c r="R545" s="93">
-        <v>94538</v>
+        <v>94537</v>
       </c>
       <c r="T545" s="85">
         <v>0</v>
@@ -79747,40 +80161,40 @@
     </row>
     <row r="546" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B546" s="85">
-        <v>800069</v>
+        <v>800068</v>
       </c>
       <c r="C546" s="97" t="s">
-        <v>4969</v>
+        <v>4965</v>
       </c>
       <c r="D546" s="97" t="s">
-        <v>4970</v>
-      </c>
-      <c r="E546" s="110" t="s">
-        <v>5397</v>
+        <v>4966</v>
+      </c>
+      <c r="E546" s="101" t="s">
+        <v>5392</v>
       </c>
       <c r="F546" s="101" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="G546" s="101" t="s">
-        <v>5149</v>
+        <v>5147</v>
       </c>
       <c r="H546" s="97" t="s">
-        <v>4971</v>
+        <v>4967</v>
       </c>
       <c r="I546" s="97" t="s">
-        <v>4972</v>
-      </c>
-      <c r="J546" s="109" t="s">
-        <v>5432</v>
+        <v>4968</v>
+      </c>
+      <c r="J546" s="101" t="s">
+        <v>5396</v>
       </c>
       <c r="K546" s="101" t="s">
-        <v>5272</v>
-      </c>
-      <c r="L546" s="102" t="s">
-        <v>5275</v>
+        <v>5270</v>
+      </c>
+      <c r="L546" s="101" t="s">
+        <v>5271</v>
       </c>
       <c r="M546" s="92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N546" s="85">
         <v>0</v>
@@ -79789,13 +80203,13 @@
         <v>13</v>
       </c>
       <c r="P546" s="85">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q546">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R546" s="93">
-        <v>94539</v>
+        <v>94538</v>
       </c>
       <c r="T546" s="85">
         <v>0</v>
@@ -79806,41 +80220,41 @@
       <c r="Z546" s="94"/>
       <c r="AA546" s="94"/>
     </row>
-    <row r="547" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="547" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B547" s="85">
-        <v>800070</v>
+        <v>800069</v>
       </c>
       <c r="C547" s="97" t="s">
-        <v>4973</v>
+        <v>4969</v>
       </c>
       <c r="D547" s="97" t="s">
-        <v>4974</v>
+        <v>4970</v>
       </c>
       <c r="E547" s="110" t="s">
-        <v>5398</v>
+        <v>5397</v>
       </c>
       <c r="F547" s="101" t="s">
-        <v>5195</v>
-      </c>
-      <c r="G547" s="102" t="s">
-        <v>5196</v>
+        <v>5148</v>
+      </c>
+      <c r="G547" s="101" t="s">
+        <v>5149</v>
       </c>
       <c r="H547" s="97" t="s">
-        <v>4975</v>
+        <v>4971</v>
       </c>
       <c r="I547" s="97" t="s">
-        <v>4976</v>
+        <v>4972</v>
       </c>
       <c r="J547" s="109" t="s">
-        <v>5433</v>
+        <v>5432</v>
       </c>
       <c r="K547" s="101" t="s">
-        <v>5273</v>
+        <v>5272</v>
       </c>
       <c r="L547" s="102" t="s">
-        <v>5276</v>
-      </c>
-      <c r="M547" s="96">
+        <v>5275</v>
+      </c>
+      <c r="M547" s="92">
         <v>1</v>
       </c>
       <c r="N547" s="85">
@@ -79850,13 +80264,13 @@
         <v>13</v>
       </c>
       <c r="P547" s="85">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q547">
         <v>1066</v>
       </c>
       <c r="R547" s="93">
-        <v>94540</v>
+        <v>94539</v>
       </c>
       <c r="T547" s="85">
         <v>0</v>
@@ -79867,42 +80281,42 @@
       <c r="Z547" s="94"/>
       <c r="AA547" s="94"/>
     </row>
-    <row r="548" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="548" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B548" s="85">
-        <v>800071</v>
+        <v>800070</v>
       </c>
       <c r="C548" s="97" t="s">
-        <v>4977</v>
+        <v>4973</v>
       </c>
       <c r="D548" s="97" t="s">
-        <v>4978</v>
+        <v>4974</v>
       </c>
       <c r="E548" s="110" t="s">
-        <v>5399</v>
+        <v>5398</v>
       </c>
       <c r="F548" s="101" t="s">
-        <v>5193</v>
+        <v>5195</v>
       </c>
       <c r="G548" s="102" t="s">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="H548" s="97" t="s">
-        <v>4979</v>
+        <v>4975</v>
       </c>
       <c r="I548" s="97" t="s">
-        <v>4980</v>
+        <v>4976</v>
       </c>
       <c r="J548" s="109" t="s">
-        <v>5434</v>
+        <v>5433</v>
       </c>
       <c r="K548" s="101" t="s">
-        <v>5274</v>
+        <v>5273</v>
       </c>
       <c r="L548" s="102" t="s">
-        <v>5277</v>
-      </c>
-      <c r="M548" s="92">
-        <v>2</v>
+        <v>5276</v>
+      </c>
+      <c r="M548" s="96">
+        <v>1</v>
       </c>
       <c r="N548" s="85">
         <v>0</v>
@@ -79911,13 +80325,13 @@
         <v>13</v>
       </c>
       <c r="P548" s="85">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q548">
         <v>1066</v>
       </c>
       <c r="R548" s="93">
-        <v>94541</v>
+        <v>94540</v>
       </c>
       <c r="T548" s="85">
         <v>0</v>
@@ -79930,40 +80344,40 @@
     </row>
     <row r="549" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B549" s="85">
-        <v>800072</v>
+        <v>800071</v>
       </c>
       <c r="C549" s="97" t="s">
-        <v>4981</v>
+        <v>4977</v>
       </c>
       <c r="D549" s="97" t="s">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="E549" s="110" t="s">
-        <v>5400</v>
+        <v>5399</v>
       </c>
       <c r="F549" s="101" t="s">
-        <v>5199</v>
-      </c>
-      <c r="G549" s="101" t="s">
-        <v>5150</v>
+        <v>5193</v>
+      </c>
+      <c r="G549" s="102" t="s">
+        <v>5194</v>
       </c>
       <c r="H549" s="97" t="s">
-        <v>4983</v>
+        <v>4979</v>
       </c>
       <c r="I549" s="97" t="s">
-        <v>4984</v>
+        <v>4980</v>
       </c>
       <c r="J549" s="109" t="s">
-        <v>5435</v>
+        <v>5434</v>
       </c>
       <c r="K549" s="101" t="s">
-        <v>5278</v>
+        <v>5274</v>
       </c>
       <c r="L549" s="102" t="s">
-        <v>5279</v>
+        <v>5277</v>
       </c>
       <c r="M549" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N549" s="85">
         <v>0</v>
@@ -79972,13 +80386,13 @@
         <v>13</v>
       </c>
       <c r="P549" s="85">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q549">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R549" s="93">
-        <v>94542</v>
+        <v>94541</v>
       </c>
       <c r="T549" s="85">
         <v>0</v>
@@ -79991,37 +80405,37 @@
     </row>
     <row r="550" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B550" s="85">
-        <v>800073</v>
+        <v>800072</v>
       </c>
       <c r="C550" s="97" t="s">
-        <v>4985</v>
+        <v>4981</v>
       </c>
       <c r="D550" s="97" t="s">
-        <v>4986</v>
+        <v>4982</v>
       </c>
       <c r="E550" s="110" t="s">
-        <v>5401</v>
+        <v>5400</v>
       </c>
       <c r="F550" s="101" t="s">
-        <v>5197</v>
-      </c>
-      <c r="G550" s="102" t="s">
-        <v>5198</v>
+        <v>5199</v>
+      </c>
+      <c r="G550" s="101" t="s">
+        <v>5150</v>
       </c>
       <c r="H550" s="97" t="s">
-        <v>4987</v>
+        <v>4983</v>
       </c>
       <c r="I550" s="97" t="s">
-        <v>4988</v>
+        <v>4984</v>
       </c>
       <c r="J550" s="109" t="s">
-        <v>5436</v>
+        <v>5435</v>
       </c>
       <c r="K550" s="101" t="s">
-        <v>5280</v>
+        <v>5278</v>
       </c>
       <c r="L550" s="102" t="s">
-        <v>5281</v>
+        <v>5279</v>
       </c>
       <c r="M550" s="92">
         <v>1</v>
@@ -80033,13 +80447,13 @@
         <v>13</v>
       </c>
       <c r="P550" s="85">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q550">
         <v>1067</v>
       </c>
       <c r="R550" s="93">
-        <v>94543</v>
+        <v>94542</v>
       </c>
       <c r="T550" s="85">
         <v>0</v>
@@ -80050,42 +80464,42 @@
       <c r="Z550" s="94"/>
       <c r="AA550" s="94"/>
     </row>
-    <row r="551" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="551" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B551" s="85">
-        <v>800074</v>
+        <v>800073</v>
       </c>
       <c r="C551" s="97" t="s">
-        <v>4989</v>
+        <v>4985</v>
       </c>
       <c r="D551" s="97" t="s">
-        <v>4990</v>
+        <v>4986</v>
       </c>
       <c r="E551" s="110" t="s">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="F551" s="101" t="s">
-        <v>5200</v>
+        <v>5197</v>
       </c>
       <c r="G551" s="102" t="s">
-        <v>5201</v>
+        <v>5198</v>
       </c>
       <c r="H551" s="97" t="s">
-        <v>4991</v>
+        <v>4987</v>
       </c>
       <c r="I551" s="97" t="s">
-        <v>4992</v>
+        <v>4988</v>
       </c>
       <c r="J551" s="109" t="s">
-        <v>5437</v>
+        <v>5436</v>
       </c>
       <c r="K551" s="101" t="s">
-        <v>5282</v>
+        <v>5280</v>
       </c>
       <c r="L551" s="102" t="s">
-        <v>5283</v>
-      </c>
-      <c r="M551" s="96">
-        <v>2</v>
+        <v>5281</v>
+      </c>
+      <c r="M551" s="92">
+        <v>1</v>
       </c>
       <c r="N551" s="85">
         <v>0</v>
@@ -80094,13 +80508,13 @@
         <v>13</v>
       </c>
       <c r="P551" s="85">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q551">
         <v>1067</v>
       </c>
       <c r="R551" s="93">
-        <v>94544</v>
+        <v>94543</v>
       </c>
       <c r="T551" s="85">
         <v>0</v>
@@ -80111,42 +80525,42 @@
       <c r="Z551" s="94"/>
       <c r="AA551" s="94"/>
     </row>
-    <row r="552" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="552" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B552" s="85">
-        <v>800075</v>
+        <v>800074</v>
       </c>
       <c r="C552" s="97" t="s">
-        <v>4993</v>
+        <v>4989</v>
       </c>
       <c r="D552" s="97" t="s">
-        <v>4994</v>
+        <v>4990</v>
       </c>
       <c r="E552" s="110" t="s">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="F552" s="101" t="s">
-        <v>5151</v>
-      </c>
-      <c r="G552" s="101" t="s">
-        <v>5152</v>
+        <v>5200</v>
+      </c>
+      <c r="G552" s="102" t="s">
+        <v>5201</v>
       </c>
       <c r="H552" s="97" t="s">
-        <v>4995</v>
+        <v>4991</v>
       </c>
       <c r="I552" s="97" t="s">
-        <v>4996</v>
+        <v>4992</v>
       </c>
       <c r="J552" s="109" t="s">
-        <v>5438</v>
+        <v>5437</v>
       </c>
       <c r="K552" s="101" t="s">
-        <v>5284</v>
+        <v>5282</v>
       </c>
       <c r="L552" s="102" t="s">
-        <v>5287</v>
-      </c>
-      <c r="M552" s="92">
-        <v>1</v>
+        <v>5283</v>
+      </c>
+      <c r="M552" s="96">
+        <v>2</v>
       </c>
       <c r="N552" s="85">
         <v>0</v>
@@ -80155,13 +80569,13 @@
         <v>13</v>
       </c>
       <c r="P552" s="85">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q552">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R552" s="93">
-        <v>94545</v>
+        <v>94544</v>
       </c>
       <c r="T552" s="85">
         <v>0</v>
@@ -80174,37 +80588,37 @@
     </row>
     <row r="553" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B553" s="85">
-        <v>800076</v>
+        <v>800075</v>
       </c>
       <c r="C553" s="97" t="s">
-        <v>4997</v>
+        <v>4993</v>
       </c>
       <c r="D553" s="97" t="s">
-        <v>4998</v>
+        <v>4994</v>
       </c>
       <c r="E553" s="110" t="s">
-        <v>5404</v>
+        <v>5403</v>
       </c>
       <c r="F553" s="101" t="s">
-        <v>5204</v>
-      </c>
-      <c r="G553" s="102" t="s">
-        <v>5205</v>
+        <v>5151</v>
+      </c>
+      <c r="G553" s="101" t="s">
+        <v>5152</v>
       </c>
       <c r="H553" s="97" t="s">
-        <v>4999</v>
+        <v>4995</v>
       </c>
       <c r="I553" s="97" t="s">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="J553" s="109" t="s">
-        <v>5439</v>
+        <v>5438</v>
       </c>
       <c r="K553" s="101" t="s">
-        <v>5285</v>
+        <v>5284</v>
       </c>
       <c r="L553" s="102" t="s">
-        <v>5289</v>
+        <v>5287</v>
       </c>
       <c r="M553" s="92">
         <v>1</v>
@@ -80216,13 +80630,13 @@
         <v>13</v>
       </c>
       <c r="P553" s="85">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q553">
         <v>1068</v>
       </c>
       <c r="R553" s="93">
-        <v>94546</v>
+        <v>94545</v>
       </c>
       <c r="T553" s="85">
         <v>0</v>
@@ -80235,40 +80649,40 @@
     </row>
     <row r="554" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B554" s="85">
-        <v>800077</v>
+        <v>800076</v>
       </c>
       <c r="C554" s="97" t="s">
-        <v>5001</v>
+        <v>4997</v>
       </c>
       <c r="D554" s="97" t="s">
-        <v>5002</v>
+        <v>4998</v>
       </c>
       <c r="E554" s="110" t="s">
-        <v>5405</v>
+        <v>5404</v>
       </c>
       <c r="F554" s="101" t="s">
-        <v>5202</v>
+        <v>5204</v>
       </c>
       <c r="G554" s="102" t="s">
-        <v>5203</v>
+        <v>5205</v>
       </c>
       <c r="H554" s="97" t="s">
-        <v>5003</v>
+        <v>4999</v>
       </c>
       <c r="I554" s="97" t="s">
-        <v>5004</v>
+        <v>5000</v>
       </c>
       <c r="J554" s="109" t="s">
-        <v>5440</v>
+        <v>5439</v>
       </c>
       <c r="K554" s="101" t="s">
-        <v>5286</v>
+        <v>5285</v>
       </c>
       <c r="L554" s="102" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="M554" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N554" s="85">
         <v>0</v>
@@ -80277,13 +80691,13 @@
         <v>13</v>
       </c>
       <c r="P554" s="85">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q554">
         <v>1068</v>
       </c>
       <c r="R554" s="93">
-        <v>94547</v>
+        <v>94546</v>
       </c>
       <c r="T554" s="85">
         <v>0</v>
@@ -80294,42 +80708,42 @@
       <c r="Z554" s="94"/>
       <c r="AA554" s="94"/>
     </row>
-    <row r="555" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="555" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B555" s="85">
-        <v>800078</v>
+        <v>800077</v>
       </c>
       <c r="C555" s="97" t="s">
-        <v>5005</v>
+        <v>5001</v>
       </c>
       <c r="D555" s="97" t="s">
-        <v>5006</v>
+        <v>5002</v>
       </c>
       <c r="E555" s="110" t="s">
-        <v>5406</v>
+        <v>5405</v>
       </c>
       <c r="F555" s="101" t="s">
-        <v>5177</v>
-      </c>
-      <c r="G555" s="101" t="s">
-        <v>5153</v>
+        <v>5202</v>
+      </c>
+      <c r="G555" s="102" t="s">
+        <v>5203</v>
       </c>
       <c r="H555" s="97" t="s">
-        <v>5007</v>
+        <v>5003</v>
       </c>
       <c r="I555" s="97" t="s">
-        <v>5008</v>
+        <v>5004</v>
       </c>
       <c r="J555" s="109" t="s">
-        <v>5441</v>
+        <v>5440</v>
       </c>
       <c r="K555" s="101" t="s">
-        <v>5290</v>
+        <v>5286</v>
       </c>
       <c r="L555" s="102" t="s">
-        <v>5292</v>
-      </c>
-      <c r="M555" s="96">
-        <v>1</v>
+        <v>5288</v>
+      </c>
+      <c r="M555" s="92">
+        <v>2</v>
       </c>
       <c r="N555" s="85">
         <v>0</v>
@@ -80338,13 +80752,13 @@
         <v>13</v>
       </c>
       <c r="P555" s="85">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q555">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R555" s="93">
-        <v>94548</v>
+        <v>94547</v>
       </c>
       <c r="T555" s="85">
         <v>0</v>
@@ -80355,42 +80769,42 @@
       <c r="Z555" s="94"/>
       <c r="AA555" s="94"/>
     </row>
-    <row r="556" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="556" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B556" s="85">
-        <v>800079</v>
+        <v>800078</v>
       </c>
       <c r="C556" s="97" t="s">
-        <v>5009</v>
+        <v>5005</v>
       </c>
       <c r="D556" s="97" t="s">
-        <v>5010</v>
+        <v>5006</v>
       </c>
       <c r="E556" s="110" t="s">
-        <v>5407</v>
+        <v>5406</v>
       </c>
       <c r="F556" s="101" t="s">
-        <v>5206</v>
-      </c>
-      <c r="G556" s="102" t="s">
-        <v>5207</v>
+        <v>5177</v>
+      </c>
+      <c r="G556" s="101" t="s">
+        <v>5153</v>
       </c>
       <c r="H556" s="97" t="s">
-        <v>5011</v>
+        <v>5007</v>
       </c>
       <c r="I556" s="97" t="s">
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="J556" s="109" t="s">
-        <v>5442</v>
+        <v>5441</v>
       </c>
       <c r="K556" s="101" t="s">
-        <v>5291</v>
+        <v>5290</v>
       </c>
       <c r="L556" s="102" t="s">
-        <v>5293</v>
-      </c>
-      <c r="M556" s="92">
-        <v>2</v>
+        <v>5292</v>
+      </c>
+      <c r="M556" s="96">
+        <v>1</v>
       </c>
       <c r="N556" s="85">
         <v>0</v>
@@ -80399,13 +80813,13 @@
         <v>13</v>
       </c>
       <c r="P556" s="85">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q556">
         <v>1069</v>
       </c>
       <c r="R556" s="93">
-        <v>94549</v>
+        <v>94548</v>
       </c>
       <c r="T556" s="85">
         <v>0</v>
@@ -80418,40 +80832,40 @@
     </row>
     <row r="557" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B557" s="85">
-        <v>800080</v>
+        <v>800079</v>
       </c>
       <c r="C557" s="97" t="s">
-        <v>5013</v>
+        <v>5009</v>
       </c>
       <c r="D557" s="97" t="s">
-        <v>5014</v>
+        <v>5010</v>
       </c>
       <c r="E557" s="110" t="s">
-        <v>5408</v>
+        <v>5407</v>
       </c>
       <c r="F557" s="101" t="s">
-        <v>5154</v>
-      </c>
-      <c r="G557" s="101" t="s">
-        <v>5155</v>
+        <v>5206</v>
+      </c>
+      <c r="G557" s="102" t="s">
+        <v>5207</v>
       </c>
       <c r="H557" s="97" t="s">
-        <v>5015</v>
+        <v>5011</v>
       </c>
       <c r="I557" s="97" t="s">
-        <v>5016</v>
-      </c>
-      <c r="J557" s="91" t="s">
-        <v>5410</v>
+        <v>5012</v>
+      </c>
+      <c r="J557" s="109" t="s">
+        <v>5442</v>
       </c>
       <c r="K557" s="101" t="s">
-        <v>5294</v>
-      </c>
-      <c r="L557" s="101" t="s">
-        <v>5295</v>
+        <v>5291</v>
+      </c>
+      <c r="L557" s="102" t="s">
+        <v>5293</v>
       </c>
       <c r="M557" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N557" s="85">
         <v>0</v>
@@ -80460,13 +80874,13 @@
         <v>13</v>
       </c>
       <c r="P557" s="85">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q557">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="R557" s="93">
-        <v>94550</v>
+        <v>94549</v>
       </c>
       <c r="T557" s="85">
         <v>0</v>
@@ -80479,40 +80893,40 @@
     </row>
     <row r="558" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B558" s="85">
-        <v>800081</v>
+        <v>800080</v>
       </c>
       <c r="C558" s="97" t="s">
-        <v>5017</v>
+        <v>5013</v>
       </c>
       <c r="D558" s="97" t="s">
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="E558" s="110" t="s">
-        <v>5409</v>
+        <v>5408</v>
       </c>
       <c r="F558" s="101" t="s">
-        <v>5156</v>
+        <v>5154</v>
       </c>
       <c r="G558" s="101" t="s">
-        <v>5157</v>
+        <v>5155</v>
       </c>
       <c r="H558" s="97" t="s">
-        <v>5019</v>
+        <v>5015</v>
       </c>
       <c r="I558" s="97" t="s">
-        <v>5020</v>
+        <v>5016</v>
       </c>
       <c r="J558" s="91" t="s">
-        <v>5411</v>
+        <v>5410</v>
       </c>
       <c r="K558" s="101" t="s">
-        <v>5296</v>
-      </c>
-      <c r="L558" s="102" t="s">
-        <v>5297</v>
+        <v>5294</v>
+      </c>
+      <c r="L558" s="101" t="s">
+        <v>5295</v>
       </c>
       <c r="M558" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N558" s="85">
         <v>0</v>
@@ -80521,13 +80935,13 @@
         <v>13</v>
       </c>
       <c r="P558" s="85">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q558">
         <v>1070</v>
       </c>
       <c r="R558" s="93">
-        <v>94551</v>
+        <v>94550</v>
       </c>
       <c r="T558" s="85">
         <v>0</v>
@@ -80538,54 +80952,57 @@
       <c r="Z558" s="94"/>
       <c r="AA558" s="94"/>
     </row>
-    <row r="559" spans="2:27" s="85" customFormat="1" ht="18.75">
+    <row r="559" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B559" s="85">
-        <v>800101</v>
+        <v>800081</v>
       </c>
       <c r="C559" s="97" t="s">
-        <v>5021</v>
+        <v>5017</v>
       </c>
       <c r="D559" s="97" t="s">
-        <v>5022</v>
-      </c>
-      <c r="E559" s="101" t="s">
-        <v>5412</v>
+        <v>5018</v>
+      </c>
+      <c r="E559" s="110" t="s">
+        <v>5409</v>
       </c>
       <c r="F559" s="101" t="s">
-        <v>5158</v>
-      </c>
-      <c r="G559" s="106" t="s">
-        <v>5159</v>
+        <v>5156</v>
+      </c>
+      <c r="G559" s="101" t="s">
+        <v>5157</v>
       </c>
       <c r="H559" s="97" t="s">
-        <v>5023</v>
+        <v>5019</v>
       </c>
       <c r="I559" s="97" t="s">
-        <v>5024</v>
-      </c>
-      <c r="J559" s="111" t="s">
-        <v>5422</v>
+        <v>5020</v>
+      </c>
+      <c r="J559" s="91" t="s">
+        <v>5411</v>
       </c>
       <c r="K559" s="101" t="s">
-        <v>5298</v>
-      </c>
-      <c r="L559" s="108" t="s">
-        <v>5317</v>
+        <v>5296</v>
+      </c>
+      <c r="L559" s="102" t="s">
+        <v>5297</v>
       </c>
       <c r="M559" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N559" s="85">
         <v>0</v>
       </c>
       <c r="O559" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P559" s="85">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="Q559">
+        <v>1070</v>
       </c>
       <c r="R559" s="93">
-        <v>95001</v>
+        <v>94551</v>
       </c>
       <c r="T559" s="85">
         <v>0</v>
@@ -80596,41 +81013,41 @@
       <c r="Z559" s="94"/>
       <c r="AA559" s="94"/>
     </row>
-    <row r="560" spans="2:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="560" spans="2:27" s="85" customFormat="1" ht="18.75">
       <c r="B560" s="85">
-        <v>800102</v>
+        <v>800101</v>
       </c>
       <c r="C560" s="97" t="s">
-        <v>5025</v>
+        <v>5021</v>
       </c>
       <c r="D560" s="97" t="s">
-        <v>5026</v>
+        <v>5022</v>
       </c>
       <c r="E560" s="101" t="s">
-        <v>5413</v>
+        <v>5412</v>
       </c>
       <c r="F560" s="101" t="s">
-        <v>5160</v>
+        <v>5158</v>
       </c>
       <c r="G560" s="106" t="s">
-        <v>5161</v>
+        <v>5159</v>
       </c>
       <c r="H560" s="97" t="s">
-        <v>5027</v>
+        <v>5023</v>
       </c>
       <c r="I560" s="97" t="s">
-        <v>5028</v>
-      </c>
-      <c r="J560" s="91" t="s">
-        <v>5423</v>
+        <v>5024</v>
+      </c>
+      <c r="J560" s="111" t="s">
+        <v>5422</v>
       </c>
       <c r="K560" s="101" t="s">
-        <v>5299</v>
-      </c>
-      <c r="L560" s="102" t="s">
-        <v>5300</v>
-      </c>
-      <c r="M560" s="96">
+        <v>5298</v>
+      </c>
+      <c r="L560" s="108" t="s">
+        <v>5317</v>
+      </c>
+      <c r="M560" s="92">
         <v>1</v>
       </c>
       <c r="N560" s="85">
@@ -80640,10 +81057,10 @@
         <v>14</v>
       </c>
       <c r="P560" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R560" s="93">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="T560" s="85">
         <v>0</v>
@@ -80654,41 +81071,41 @@
       <c r="Z560" s="94"/>
       <c r="AA560" s="94"/>
     </row>
-    <row r="561" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="561" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B561" s="85">
-        <v>800103</v>
+        <v>800102</v>
       </c>
       <c r="C561" s="97" t="s">
-        <v>5029</v>
+        <v>5025</v>
       </c>
       <c r="D561" s="97" t="s">
-        <v>5030</v>
+        <v>5026</v>
       </c>
       <c r="E561" s="101" t="s">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="F561" s="101" t="s">
-        <v>5178</v>
+        <v>5160</v>
       </c>
       <c r="G561" s="106" t="s">
-        <v>5162</v>
+        <v>5161</v>
       </c>
       <c r="H561" s="97" t="s">
-        <v>5031</v>
+        <v>5027</v>
       </c>
       <c r="I561" s="97" t="s">
-        <v>5032</v>
+        <v>5028</v>
       </c>
       <c r="J561" s="91" t="s">
-        <v>5424</v>
-      </c>
-      <c r="K561" s="91" t="s">
-        <v>5301</v>
-      </c>
-      <c r="L561" s="91" t="s">
-        <v>5302</v>
-      </c>
-      <c r="M561" s="92">
+        <v>5423</v>
+      </c>
+      <c r="K561" s="101" t="s">
+        <v>5299</v>
+      </c>
+      <c r="L561" s="102" t="s">
+        <v>5300</v>
+      </c>
+      <c r="M561" s="96">
         <v>1</v>
       </c>
       <c r="N561" s="85">
@@ -80698,10 +81115,10 @@
         <v>14</v>
       </c>
       <c r="P561" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R561" s="93">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="T561" s="85">
         <v>0</v>
@@ -80714,37 +81131,37 @@
     </row>
     <row r="562" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B562" s="85">
-        <v>800104</v>
+        <v>800103</v>
       </c>
       <c r="C562" s="97" t="s">
-        <v>5033</v>
+        <v>5029</v>
       </c>
       <c r="D562" s="97" t="s">
-        <v>5034</v>
+        <v>5030</v>
       </c>
       <c r="E562" s="101" t="s">
-        <v>5415</v>
+        <v>5414</v>
       </c>
       <c r="F562" s="101" t="s">
-        <v>5163</v>
+        <v>5178</v>
       </c>
       <c r="G562" s="106" t="s">
-        <v>5164</v>
+        <v>5162</v>
       </c>
       <c r="H562" s="97" t="s">
-        <v>5035</v>
+        <v>5031</v>
       </c>
       <c r="I562" s="97" t="s">
-        <v>5036</v>
+        <v>5032</v>
       </c>
       <c r="J562" s="91" t="s">
-        <v>5425</v>
+        <v>5424</v>
       </c>
       <c r="K562" s="91" t="s">
-        <v>5303</v>
+        <v>5301</v>
       </c>
       <c r="L562" s="91" t="s">
-        <v>5304</v>
+        <v>5302</v>
       </c>
       <c r="M562" s="92">
         <v>1</v>
@@ -80756,10 +81173,10 @@
         <v>14</v>
       </c>
       <c r="P562" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R562" s="93">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="T562" s="85">
         <v>0</v>
@@ -80772,37 +81189,37 @@
     </row>
     <row r="563" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B563" s="85">
-        <v>800105</v>
+        <v>800104</v>
       </c>
       <c r="C563" s="97" t="s">
-        <v>5037</v>
+        <v>5033</v>
       </c>
       <c r="D563" s="97" t="s">
-        <v>5038</v>
+        <v>5034</v>
       </c>
       <c r="E563" s="101" t="s">
-        <v>5416</v>
+        <v>5415</v>
       </c>
       <c r="F563" s="101" t="s">
-        <v>5165</v>
+        <v>5163</v>
       </c>
       <c r="G563" s="106" t="s">
-        <v>5166</v>
+        <v>5164</v>
       </c>
       <c r="H563" s="97" t="s">
-        <v>5039</v>
+        <v>5035</v>
       </c>
       <c r="I563" s="97" t="s">
-        <v>5040</v>
+        <v>5036</v>
       </c>
       <c r="J563" s="91" t="s">
-        <v>5426</v>
+        <v>5425</v>
       </c>
       <c r="K563" s="91" t="s">
-        <v>5305</v>
+        <v>5303</v>
       </c>
       <c r="L563" s="91" t="s">
-        <v>5306</v>
+        <v>5304</v>
       </c>
       <c r="M563" s="92">
         <v>1</v>
@@ -80814,10 +81231,10 @@
         <v>14</v>
       </c>
       <c r="P563" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R563" s="93">
-        <v>95005</v>
+        <v>95004</v>
       </c>
       <c r="T563" s="85">
         <v>0</v>
@@ -80828,41 +81245,41 @@
       <c r="Z563" s="94"/>
       <c r="AA563" s="94"/>
     </row>
-    <row r="564" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="564" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B564" s="85">
-        <v>800106</v>
+        <v>800105</v>
       </c>
       <c r="C564" s="97" t="s">
-        <v>5041</v>
+        <v>5037</v>
       </c>
       <c r="D564" s="97" t="s">
-        <v>5042</v>
+        <v>5038</v>
       </c>
       <c r="E564" s="101" t="s">
-        <v>5417</v>
+        <v>5416</v>
       </c>
       <c r="F564" s="101" t="s">
-        <v>5167</v>
+        <v>5165</v>
       </c>
       <c r="G564" s="106" t="s">
-        <v>5168</v>
+        <v>5166</v>
       </c>
       <c r="H564" s="97" t="s">
-        <v>5043</v>
+        <v>5039</v>
       </c>
       <c r="I564" s="97" t="s">
-        <v>5044</v>
+        <v>5040</v>
       </c>
       <c r="J564" s="91" t="s">
-        <v>5427</v>
+        <v>5426</v>
       </c>
       <c r="K564" s="91" t="s">
-        <v>5307</v>
+        <v>5305</v>
       </c>
       <c r="L564" s="91" t="s">
-        <v>5308</v>
-      </c>
-      <c r="M564" s="96">
+        <v>5306</v>
+      </c>
+      <c r="M564" s="92">
         <v>1</v>
       </c>
       <c r="N564" s="85">
@@ -80872,10 +81289,10 @@
         <v>14</v>
       </c>
       <c r="P564" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R564" s="93">
-        <v>95006</v>
+        <v>95005</v>
       </c>
       <c r="T564" s="85">
         <v>0</v>
@@ -80886,42 +81303,42 @@
       <c r="Z564" s="94"/>
       <c r="AA564" s="94"/>
     </row>
-    <row r="565" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="565" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B565" s="85">
-        <v>800107</v>
+        <v>800106</v>
       </c>
       <c r="C565" s="97" t="s">
-        <v>5045</v>
+        <v>5041</v>
       </c>
       <c r="D565" s="97" t="s">
-        <v>5046</v>
+        <v>5042</v>
       </c>
       <c r="E565" s="101" t="s">
-        <v>5418</v>
+        <v>5417</v>
       </c>
       <c r="F565" s="101" t="s">
-        <v>5169</v>
+        <v>5167</v>
       </c>
       <c r="G565" s="106" t="s">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="H565" s="97" t="s">
-        <v>5047</v>
+        <v>5043</v>
       </c>
       <c r="I565" s="97" t="s">
-        <v>5048</v>
+        <v>5044</v>
       </c>
       <c r="J565" s="91" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K565" s="91" t="s">
-        <v>5309</v>
+        <v>5307</v>
       </c>
       <c r="L565" s="91" t="s">
-        <v>5310</v>
-      </c>
-      <c r="M565" s="92">
-        <v>2</v>
+        <v>5308</v>
+      </c>
+      <c r="M565" s="96">
+        <v>1</v>
       </c>
       <c r="N565" s="85">
         <v>0</v>
@@ -80930,10 +81347,10 @@
         <v>14</v>
       </c>
       <c r="P565" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R565" s="93">
-        <v>95007</v>
+        <v>95006</v>
       </c>
       <c r="T565" s="85">
         <v>0</v>
@@ -80946,37 +81363,37 @@
     </row>
     <row r="566" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B566" s="85">
-        <v>800108</v>
+        <v>800107</v>
       </c>
       <c r="C566" s="97" t="s">
-        <v>5049</v>
+        <v>5045</v>
       </c>
       <c r="D566" s="97" t="s">
-        <v>5050</v>
+        <v>5046</v>
       </c>
       <c r="E566" s="101" t="s">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="F566" s="101" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
       <c r="G566" s="106" t="s">
-        <v>5172</v>
+        <v>5170</v>
       </c>
       <c r="H566" s="97" t="s">
-        <v>5051</v>
+        <v>5047</v>
       </c>
       <c r="I566" s="97" t="s">
-        <v>5052</v>
+        <v>5048</v>
       </c>
       <c r="J566" s="91" t="s">
-        <v>5429</v>
+        <v>5428</v>
       </c>
       <c r="K566" s="91" t="s">
-        <v>5311</v>
+        <v>5309</v>
       </c>
       <c r="L566" s="91" t="s">
-        <v>5312</v>
+        <v>5310</v>
       </c>
       <c r="M566" s="92">
         <v>2</v>
@@ -80988,10 +81405,10 @@
         <v>14</v>
       </c>
       <c r="P566" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R566" s="93">
-        <v>95008</v>
+        <v>95007</v>
       </c>
       <c r="T566" s="85">
         <v>0</v>
@@ -81004,37 +81421,37 @@
     </row>
     <row r="567" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B567" s="85">
-        <v>800109</v>
+        <v>800108</v>
       </c>
       <c r="C567" s="97" t="s">
-        <v>5053</v>
+        <v>5049</v>
       </c>
       <c r="D567" s="97" t="s">
-        <v>5054</v>
+        <v>5050</v>
       </c>
       <c r="E567" s="101" t="s">
-        <v>5420</v>
+        <v>5419</v>
       </c>
       <c r="F567" s="101" t="s">
-        <v>5173</v>
+        <v>5171</v>
       </c>
       <c r="G567" s="106" t="s">
-        <v>5174</v>
+        <v>5172</v>
       </c>
       <c r="H567" s="97" t="s">
-        <v>5055</v>
+        <v>5051</v>
       </c>
       <c r="I567" s="97" t="s">
-        <v>5056</v>
+        <v>5052</v>
       </c>
       <c r="J567" s="91" t="s">
-        <v>5430</v>
+        <v>5429</v>
       </c>
       <c r="K567" s="91" t="s">
-        <v>5313</v>
+        <v>5311</v>
       </c>
       <c r="L567" s="91" t="s">
-        <v>5314</v>
+        <v>5312</v>
       </c>
       <c r="M567" s="92">
         <v>2</v>
@@ -81046,10 +81463,10 @@
         <v>14</v>
       </c>
       <c r="P567" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R567" s="93">
-        <v>95009</v>
+        <v>95008</v>
       </c>
       <c r="T567" s="85">
         <v>0</v>
@@ -81060,42 +81477,42 @@
       <c r="Z567" s="94"/>
       <c r="AA567" s="94"/>
     </row>
-    <row r="568" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="568" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B568" s="85">
-        <v>800110</v>
+        <v>800109</v>
       </c>
       <c r="C568" s="97" t="s">
-        <v>5057</v>
+        <v>5053</v>
       </c>
       <c r="D568" s="97" t="s">
-        <v>5058</v>
+        <v>5054</v>
       </c>
       <c r="E568" s="101" t="s">
-        <v>5421</v>
+        <v>5420</v>
       </c>
       <c r="F568" s="101" t="s">
-        <v>5175</v>
+        <v>5173</v>
       </c>
       <c r="G568" s="106" t="s">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="H568" s="97" t="s">
-        <v>5059</v>
+        <v>5055</v>
       </c>
       <c r="I568" s="97" t="s">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="J568" s="91" t="s">
-        <v>5431</v>
+        <v>5430</v>
       </c>
       <c r="K568" s="91" t="s">
-        <v>5315</v>
+        <v>5313</v>
       </c>
       <c r="L568" s="91" t="s">
-        <v>5316</v>
-      </c>
-      <c r="M568" s="96">
-        <v>3</v>
+        <v>5314</v>
+      </c>
+      <c r="M568" s="92">
+        <v>2</v>
       </c>
       <c r="N568" s="85">
         <v>0</v>
@@ -81104,10 +81521,10 @@
         <v>14</v>
       </c>
       <c r="P568" s="85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R568" s="93">
-        <v>95010</v>
+        <v>95009</v>
       </c>
       <c r="T568" s="85">
         <v>0</v>
@@ -81118,37 +81535,95 @@
       <c r="Z568" s="94"/>
       <c r="AA568" s="94"/>
     </row>
-    <row r="569" spans="1:27" s="2" customFormat="1">
-      <c r="A569" s="2" t="s">
+    <row r="569" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+      <c r="B569" s="85">
+        <v>800110</v>
+      </c>
+      <c r="C569" s="97" t="s">
+        <v>5057</v>
+      </c>
+      <c r="D569" s="97" t="s">
+        <v>5058</v>
+      </c>
+      <c r="E569" s="101" t="s">
+        <v>5421</v>
+      </c>
+      <c r="F569" s="101" t="s">
+        <v>5175</v>
+      </c>
+      <c r="G569" s="106" t="s">
+        <v>5176</v>
+      </c>
+      <c r="H569" s="97" t="s">
+        <v>5059</v>
+      </c>
+      <c r="I569" s="97" t="s">
+        <v>5060</v>
+      </c>
+      <c r="J569" s="91" t="s">
+        <v>5431</v>
+      </c>
+      <c r="K569" s="91" t="s">
+        <v>5315</v>
+      </c>
+      <c r="L569" s="91" t="s">
+        <v>5316</v>
+      </c>
+      <c r="M569" s="96">
+        <v>3</v>
+      </c>
+      <c r="N569" s="85">
+        <v>0</v>
+      </c>
+      <c r="O569" s="85">
+        <v>14</v>
+      </c>
+      <c r="P569" s="85">
+        <v>10</v>
+      </c>
+      <c r="R569" s="93">
+        <v>95010</v>
+      </c>
+      <c r="T569" s="85">
+        <v>0</v>
+      </c>
+      <c r="U569" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z569" s="94"/>
+      <c r="AA569" s="94"/>
+    </row>
+    <row r="570" spans="1:27" s="2" customFormat="1">
+      <c r="A570" s="2" t="s">
         <v>4241</v>
       </c>
-      <c r="B569" s="2">
+      <c r="B570" s="2">
         <v>900001</v>
       </c>
-      <c r="M569" s="2">
-        <v>0</v>
-      </c>
-      <c r="N569" s="2">
-        <v>0</v>
-      </c>
-      <c r="O569" s="2">
+      <c r="M570" s="2">
+        <v>0</v>
+      </c>
+      <c r="N570" s="2">
+        <v>0</v>
+      </c>
+      <c r="O570" s="2">
         <v>2</v>
       </c>
-      <c r="P569" s="2">
+      <c r="P570" s="2">
         <v>999</v>
       </c>
-      <c r="R569" s="2">
+      <c r="R570" s="2">
         <v>98001</v>
       </c>
-      <c r="T569" s="2">
+      <c r="T570" s="2">
         <v>1</v>
       </c>
-      <c r="U569" s="2">
+      <c r="U570" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U508" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:U509" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="N1:N445 N449:N459 N462:N479 N482:N1048576">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">

--- a/source/bin/excel/achievement.xlsx
+++ b/source/bin/excel/achievement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Git\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A840FC4D-B829-4397-86E8-01CECC1D109C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA2C3E0-1A4F-4B1C-8B74-7FA84B66A205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="885" yWindow="-120" windowWidth="28035" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -20,25 +20,14 @@
     <sheet name="badge_group" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$510</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6730" uniqueCount="5819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6741" uniqueCount="5830">
   <si>
     <t>sheet</t>
   </si>
@@ -41599,6 +41588,357 @@
   </si>
   <si>
     <t>30740021-1</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>简</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守护者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>簡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ジェーン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の守護者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Protector of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Jane</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수호자</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解锁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>简</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>传记中的所有结局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>解鎖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>簡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>傳記中的所有結局</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ジェーン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の物語のエンディングをすべて解放する</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unlock all endings in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jane</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'s Story</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>스토리의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>엔딩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>오픈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>30740022-1</t>
     <phoneticPr fontId="38" type="noConversion"/>
   </si>
 </sst>
@@ -43747,7 +44087,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM570"/>
+  <dimension ref="A1:AM571"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -76868,123 +77208,111 @@
       <c r="Z493" s="27"/>
       <c r="AA493" s="27"/>
     </row>
-    <row r="494" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="A494" s="1" t="s">
-        <v>4230</v>
-      </c>
-      <c r="B494" s="1">
-        <v>800011</v>
-      </c>
-      <c r="C494" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D494" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E494" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F494" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G494" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H494" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I494" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J494" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="K494" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="L494" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="M494" s="47">
+    <row r="494" spans="1:39">
+      <c r="A494">
+        <v>22</v>
+      </c>
+      <c r="B494">
+        <v>100496</v>
+      </c>
+      <c r="C494" s="29" t="s">
+        <v>5819</v>
+      </c>
+      <c r="D494" s="29" t="s">
+        <v>5820</v>
+      </c>
+      <c r="E494" s="62" t="s">
+        <v>5821</v>
+      </c>
+      <c r="F494" s="63" t="s">
+        <v>5822</v>
+      </c>
+      <c r="G494" s="78" t="s">
+        <v>5823</v>
+      </c>
+      <c r="H494" s="60" t="s">
+        <v>5824</v>
+      </c>
+      <c r="I494" s="29" t="s">
+        <v>5825</v>
+      </c>
+      <c r="J494" s="63" t="s">
+        <v>5826</v>
+      </c>
+      <c r="K494" s="29" t="s">
+        <v>5827</v>
+      </c>
+      <c r="L494" s="78" t="s">
+        <v>5828</v>
+      </c>
+      <c r="M494" s="66">
         <v>1</v>
       </c>
-      <c r="N494" s="1">
-        <v>0</v>
-      </c>
-      <c r="O494" s="1">
-        <v>12</v>
-      </c>
-      <c r="P494" s="1">
-        <v>1</v>
-      </c>
-      <c r="R494" s="1">
-        <v>90501</v>
-      </c>
-      <c r="T494" s="1">
-        <v>0</v>
-      </c>
-      <c r="U494" s="1">
-        <v>0</v>
-      </c>
-      <c r="X494" s="1">
-        <v>90501</v>
-      </c>
-      <c r="Y494" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z494" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA494" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB494" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE494" s="51"/>
-      <c r="AF494" s="51"/>
-      <c r="AG494" s="51"/>
-      <c r="AH494" s="51"/>
-      <c r="AI494" s="51"/>
-      <c r="AL494" s="51"/>
-      <c r="AM494" s="51"/>
+      <c r="N494">
+        <v>0</v>
+      </c>
+      <c r="O494">
+        <v>10</v>
+      </c>
+      <c r="P494" s="135">
+        <v>522</v>
+      </c>
+      <c r="R494">
+        <v>99184</v>
+      </c>
+      <c r="S494" s="27" t="s">
+        <v>5829</v>
+      </c>
+      <c r="T494">
+        <v>0</v>
+      </c>
+      <c r="U494">
+        <v>0</v>
+      </c>
+      <c r="X494" s="27"/>
+      <c r="Y494" s="27"/>
+      <c r="Z494" s="27"/>
+      <c r="AA494" s="27"/>
     </row>
     <row r="495" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="A495" s="1" t="s">
+        <v>4230</v>
+      </c>
       <c r="B495" s="1">
-        <v>800012</v>
+        <v>800011</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="E495" s="41" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="G495" s="1" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="H495" s="42" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="I495" s="42" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="J495" s="46" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="K495" s="42" t="s">
-        <v>4231</v>
+        <v>235</v>
       </c>
       <c r="L495" s="42" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="M495" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N495" s="1">
         <v>0</v>
@@ -76993,10 +77321,10 @@
         <v>12</v>
       </c>
       <c r="P495" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R495" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="T495" s="1">
         <v>0</v>
@@ -77005,57 +77333,64 @@
         <v>0</v>
       </c>
       <c r="X495" s="1">
-        <v>90502</v>
+        <v>90501</v>
       </c>
       <c r="Y495" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z495" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA495" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB495" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="AE495" s="51"/>
+      <c r="AF495" s="51"/>
+      <c r="AG495" s="51"/>
+      <c r="AH495" s="51"/>
+      <c r="AI495" s="51"/>
+      <c r="AL495" s="51"/>
+      <c r="AM495" s="51"/>
     </row>
     <row r="496" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B496" s="1">
-        <v>800013</v>
+        <v>800012</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="E496" s="41" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="G496" s="1" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="H496" s="42" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I496" s="42" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="J496" s="46" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="K496" s="42" t="s">
-        <v>4232</v>
+        <v>4231</v>
       </c>
       <c r="L496" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="M496" s="48">
-        <v>3</v>
+        <v>249</v>
+      </c>
+      <c r="M496" s="47">
+        <v>2</v>
       </c>
       <c r="N496" s="1">
         <v>0</v>
@@ -77064,10 +77399,10 @@
         <v>12</v>
       </c>
       <c r="P496" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R496" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="T496" s="1">
         <v>0</v>
@@ -77076,7 +77411,7 @@
         <v>0</v>
       </c>
       <c r="X496" s="1">
-        <v>90503</v>
+        <v>90502</v>
       </c>
       <c r="Y496" s="1" t="s">
         <v>237</v>
@@ -77085,7 +77420,7 @@
         <v>250</v>
       </c>
       <c r="AA496" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB496" s="1" t="s">
         <v>239</v>
@@ -77093,40 +77428,40 @@
     </row>
     <row r="497" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B497" s="1">
-        <v>800014</v>
+        <v>800013</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E497" s="41" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G497" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H497" s="42" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I497" s="42" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="J497" s="46" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="K497" s="42" t="s">
-        <v>269</v>
+        <v>4232</v>
       </c>
       <c r="L497" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M497" s="47">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="M497" s="48">
+        <v>3</v>
       </c>
       <c r="N497" s="1">
         <v>0</v>
@@ -77135,10 +77470,10 @@
         <v>12</v>
       </c>
       <c r="P497" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R497" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="T497" s="1">
         <v>0</v>
@@ -77147,57 +77482,57 @@
         <v>0</v>
       </c>
       <c r="X497" s="1">
-        <v>90504</v>
+        <v>90503</v>
       </c>
       <c r="Y497" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z497" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA497" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB497" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="498" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B498" s="1">
-        <v>800015</v>
+        <v>800014</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="E498" s="41" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="G498" s="1" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="H498" s="42" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I498" s="42" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="J498" s="46" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="K498" s="42" t="s">
-        <v>4233</v>
+        <v>269</v>
       </c>
       <c r="L498" s="42" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="M498" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N498" s="1">
         <v>0</v>
@@ -77206,10 +77541,10 @@
         <v>12</v>
       </c>
       <c r="P498" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R498" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="T498" s="1">
         <v>0</v>
@@ -77218,16 +77553,16 @@
         <v>0</v>
       </c>
       <c r="X498" s="1">
-        <v>90505</v>
+        <v>90504</v>
       </c>
       <c r="Y498" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z498" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA498" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB498" s="1" t="s">
         <v>271</v>
@@ -77235,40 +77570,40 @@
     </row>
     <row r="499" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B499" s="1">
-        <v>800016</v>
+        <v>800015</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E499" s="43" t="s">
-        <v>284</v>
+        <v>273</v>
+      </c>
+      <c r="E499" s="41" t="s">
+        <v>274</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G499" s="1" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="H499" s="42" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I499" s="42" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J499" s="46" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="K499" s="42" t="s">
-        <v>4234</v>
+        <v>4233</v>
       </c>
       <c r="L499" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="M499" s="48">
-        <v>3</v>
+        <v>281</v>
+      </c>
+      <c r="M499" s="47">
+        <v>2</v>
       </c>
       <c r="N499" s="1">
         <v>0</v>
@@ -77277,10 +77612,10 @@
         <v>12</v>
       </c>
       <c r="P499" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R499" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="T499" s="1">
         <v>0</v>
@@ -77289,7 +77624,7 @@
         <v>0</v>
       </c>
       <c r="X499" s="1">
-        <v>90506</v>
+        <v>90505</v>
       </c>
       <c r="Y499" s="1" t="s">
         <v>237</v>
@@ -77298,7 +77633,7 @@
         <v>250</v>
       </c>
       <c r="AA499" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB499" s="1" t="s">
         <v>271</v>
@@ -77306,40 +77641,40 @@
     </row>
     <row r="500" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B500" s="1">
-        <v>800017</v>
+        <v>800016</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="E500" s="43" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="H500" s="42" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I500" s="42" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="J500" s="46" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="K500" s="42" t="s">
-        <v>300</v>
+        <v>4234</v>
       </c>
       <c r="L500" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="M500" s="47">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="M500" s="48">
+        <v>3</v>
       </c>
       <c r="N500" s="1">
         <v>0</v>
@@ -77348,10 +77683,10 @@
         <v>12</v>
       </c>
       <c r="P500" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R500" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="T500" s="1">
         <v>0</v>
@@ -77360,54 +77695,54 @@
         <v>0</v>
       </c>
       <c r="X500" s="1">
-        <v>90507</v>
+        <v>90506</v>
       </c>
       <c r="Y500" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z500" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA500" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB500" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="501" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B501" s="1">
-        <v>800018</v>
+        <v>800017</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="E501" s="41" t="s">
-        <v>305</v>
+        <v>293</v>
+      </c>
+      <c r="E501" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="H501" s="42" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="I501" s="42" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="J501" s="46" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="K501" s="42" t="s">
-        <v>4235</v>
+        <v>300</v>
       </c>
       <c r="L501" s="42" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="M501" s="47">
         <v>1</v>
@@ -77419,10 +77754,10 @@
         <v>12</v>
       </c>
       <c r="P501" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R501" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="T501" s="1">
         <v>0</v>
@@ -77431,16 +77766,16 @@
         <v>0</v>
       </c>
       <c r="X501" s="1">
-        <v>90508</v>
+        <v>90507</v>
       </c>
       <c r="Y501" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z501" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA501" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB501" s="1" t="s">
         <v>302</v>
@@ -77448,40 +77783,40 @@
     </row>
     <row r="502" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B502" s="1">
-        <v>800019</v>
+        <v>800018</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E502" s="41" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="H502" s="42" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="I502" s="42" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="J502" s="46" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="K502" s="42" t="s">
-        <v>4236</v>
+        <v>4235</v>
       </c>
       <c r="L502" s="42" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="M502" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N502" s="1">
         <v>0</v>
@@ -77490,10 +77825,10 @@
         <v>12</v>
       </c>
       <c r="P502" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R502" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="T502" s="1">
         <v>0</v>
@@ -77502,7 +77837,7 @@
         <v>0</v>
       </c>
       <c r="X502" s="1">
-        <v>90509</v>
+        <v>90508</v>
       </c>
       <c r="Y502" s="1" t="s">
         <v>237</v>
@@ -77511,7 +77846,7 @@
         <v>250</v>
       </c>
       <c r="AA502" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB502" s="1" t="s">
         <v>302</v>
@@ -77519,40 +77854,40 @@
     </row>
     <row r="503" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B503" s="1">
-        <v>800020</v>
+        <v>800019</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E503" s="41" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="H503" s="42" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="I503" s="42" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="J503" s="46" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="K503" s="42" t="s">
-        <v>331</v>
+        <v>4236</v>
       </c>
       <c r="L503" s="42" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="M503" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N503" s="1">
         <v>0</v>
@@ -77561,10 +77896,10 @@
         <v>12</v>
       </c>
       <c r="P503" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R503" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="T503" s="1">
         <v>0</v>
@@ -77573,57 +77908,57 @@
         <v>0</v>
       </c>
       <c r="X503" s="1">
-        <v>90510</v>
+        <v>90509</v>
       </c>
       <c r="Y503" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z503" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA503" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB503" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="504" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B504" s="1">
-        <v>800021</v>
+        <v>800020</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="E504" s="41" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="H504" s="42" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="I504" s="42" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="J504" s="46" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="K504" s="42" t="s">
-        <v>4237</v>
+        <v>331</v>
       </c>
       <c r="L504" s="42" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="M504" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N504" s="1">
         <v>0</v>
@@ -77632,10 +77967,10 @@
         <v>12</v>
       </c>
       <c r="P504" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R504" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="T504" s="1">
         <v>0</v>
@@ -77644,7 +77979,7 @@
         <v>0</v>
       </c>
       <c r="X504" s="1">
-        <v>90511</v>
+        <v>90510</v>
       </c>
       <c r="Y504" s="1" t="s">
         <v>237</v>
@@ -77653,7 +77988,7 @@
         <v>333</v>
       </c>
       <c r="AA504" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB504" s="1" t="s">
         <v>239</v>
@@ -77661,40 +77996,40 @@
     </row>
     <row r="505" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B505" s="1">
-        <v>800022</v>
+        <v>800021</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E505" s="41" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="H505" s="42" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="I505" s="42" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J505" s="46" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="K505" s="42" t="s">
-        <v>4238</v>
+        <v>4237</v>
       </c>
       <c r="L505" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="M505" s="48">
-        <v>3</v>
+        <v>343</v>
+      </c>
+      <c r="M505" s="47">
+        <v>2</v>
       </c>
       <c r="N505" s="1">
         <v>0</v>
@@ -77703,10 +78038,10 @@
         <v>12</v>
       </c>
       <c r="P505" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R505" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="T505" s="1">
         <v>0</v>
@@ -77715,7 +78050,7 @@
         <v>0</v>
       </c>
       <c r="X505" s="1">
-        <v>90512</v>
+        <v>90511</v>
       </c>
       <c r="Y505" s="1" t="s">
         <v>237</v>
@@ -77724,7 +78059,7 @@
         <v>333</v>
       </c>
       <c r="AA505" s="42">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB505" s="1" t="s">
         <v>239</v>
@@ -77732,40 +78067,40 @@
     </row>
     <row r="506" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B506" s="1">
-        <v>800023</v>
+        <v>800022</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E506" s="41" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="H506" s="42" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I506" s="42" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="J506" s="46" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="K506" s="42" t="s">
-        <v>362</v>
+        <v>4238</v>
       </c>
       <c r="L506" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="M506" s="47">
-        <v>1</v>
+        <v>353</v>
+      </c>
+      <c r="M506" s="48">
+        <v>3</v>
       </c>
       <c r="N506" s="1">
         <v>0</v>
@@ -77774,10 +78109,10 @@
         <v>12</v>
       </c>
       <c r="P506" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R506" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="T506" s="1">
         <v>0</v>
@@ -77786,7 +78121,7 @@
         <v>0</v>
       </c>
       <c r="X506" s="1">
-        <v>90513</v>
+        <v>90512</v>
       </c>
       <c r="Y506" s="1" t="s">
         <v>237</v>
@@ -77795,45 +78130,45 @@
         <v>333</v>
       </c>
       <c r="AA506" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB506" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="507" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B507" s="1">
-        <v>800024</v>
+        <v>800023</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E507" s="41" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="H507" s="42" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I507" s="42" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="J507" s="46" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="K507" s="42" t="s">
-        <v>4239</v>
+        <v>362</v>
       </c>
       <c r="L507" s="42" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="M507" s="47">
         <v>1</v>
@@ -77845,10 +78180,10 @@
         <v>12</v>
       </c>
       <c r="P507" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R507" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="T507" s="1">
         <v>0</v>
@@ -77857,7 +78192,7 @@
         <v>0</v>
       </c>
       <c r="X507" s="1">
-        <v>90514</v>
+        <v>90513</v>
       </c>
       <c r="Y507" s="1" t="s">
         <v>237</v>
@@ -77866,7 +78201,7 @@
         <v>333</v>
       </c>
       <c r="AA507" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB507" s="1" t="s">
         <v>271</v>
@@ -77874,40 +78209,40 @@
     </row>
     <row r="508" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B508" s="1">
-        <v>800025</v>
+        <v>800024</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E508" s="41" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="H508" s="42" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="I508" s="42" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="J508" s="46" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K508" s="42" t="s">
-        <v>4240</v>
+        <v>4239</v>
       </c>
       <c r="L508" s="42" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="M508" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N508" s="1">
         <v>0</v>
@@ -77916,10 +78251,10 @@
         <v>12</v>
       </c>
       <c r="P508" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R508" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="T508" s="1">
         <v>0</v>
@@ -77928,7 +78263,7 @@
         <v>0</v>
       </c>
       <c r="X508" s="1">
-        <v>90515</v>
+        <v>90514</v>
       </c>
       <c r="Y508" s="1" t="s">
         <v>237</v>
@@ -77937,116 +78272,119 @@
         <v>333</v>
       </c>
       <c r="AA508" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB508" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="509" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="A509" s="87" t="s">
-        <v>4833</v>
-      </c>
-      <c r="B509" s="85">
-        <v>800031</v>
-      </c>
-      <c r="C509" s="88" t="s">
-        <v>4834</v>
-      </c>
-      <c r="D509" s="88" t="s">
-        <v>4835</v>
-      </c>
-      <c r="E509" s="101" t="s">
-        <v>5320</v>
-      </c>
-      <c r="F509" s="101" t="s">
-        <v>5073</v>
-      </c>
-      <c r="G509" s="101" t="s">
-        <v>5074</v>
-      </c>
-      <c r="H509" s="90" t="s">
-        <v>4836</v>
-      </c>
-      <c r="I509" s="107" t="s">
-        <v>5338</v>
-      </c>
-      <c r="J509" s="109" t="s">
-        <v>5332</v>
-      </c>
-      <c r="K509" s="101" t="s">
-        <v>5077</v>
-      </c>
-      <c r="L509" s="102" t="s">
-        <v>5078</v>
-      </c>
-      <c r="M509" s="92">
-        <v>1</v>
-      </c>
-      <c r="N509" s="85">
-        <v>0</v>
-      </c>
-      <c r="O509" s="85">
-        <v>13</v>
-      </c>
-      <c r="P509" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q509">
-        <v>1059</v>
-      </c>
-      <c r="R509" s="93">
-        <v>94501</v>
-      </c>
-      <c r="T509" s="85">
-        <v>0</v>
-      </c>
-      <c r="U509" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z509" s="94"/>
-      <c r="AA509" s="94"/>
-      <c r="AE509" s="95"/>
-      <c r="AF509" s="95"/>
-      <c r="AG509" s="95"/>
-      <c r="AH509" s="95"/>
-      <c r="AI509" s="95"/>
-      <c r="AL509" s="95"/>
-      <c r="AM509" s="95"/>
+    <row r="509" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B509" s="1">
+        <v>800025</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D509" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E509" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F509" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G509" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H509" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="I509" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="J509" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="K509" s="42" t="s">
+        <v>4240</v>
+      </c>
+      <c r="L509" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="M509" s="47">
+        <v>2</v>
+      </c>
+      <c r="N509" s="1">
+        <v>0</v>
+      </c>
+      <c r="O509" s="1">
+        <v>12</v>
+      </c>
+      <c r="P509" s="1">
+        <v>15</v>
+      </c>
+      <c r="R509" s="1">
+        <v>90515</v>
+      </c>
+      <c r="T509" s="1">
+        <v>0</v>
+      </c>
+      <c r="U509" s="1">
+        <v>0</v>
+      </c>
+      <c r="X509" s="1">
+        <v>90515</v>
+      </c>
+      <c r="Y509" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z509" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA509" s="42">
+        <v>10</v>
+      </c>
+      <c r="AB509" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="510" spans="1:39" s="85" customFormat="1" ht="33">
+      <c r="A510" s="87" t="s">
+        <v>4833</v>
+      </c>
       <c r="B510" s="85">
-        <v>800032</v>
+        <v>800031</v>
       </c>
       <c r="C510" s="88" t="s">
-        <v>4837</v>
+        <v>4834</v>
       </c>
       <c r="D510" s="88" t="s">
-        <v>4838</v>
+        <v>4835</v>
       </c>
       <c r="E510" s="101" t="s">
-        <v>5322</v>
+        <v>5320</v>
       </c>
       <c r="F510" s="101" t="s">
-        <v>5081</v>
+        <v>5073</v>
       </c>
       <c r="G510" s="101" t="s">
-        <v>5075</v>
+        <v>5074</v>
       </c>
       <c r="H510" s="90" t="s">
-        <v>4839</v>
-      </c>
-      <c r="I510" s="90" t="s">
-        <v>4840</v>
+        <v>4836</v>
+      </c>
+      <c r="I510" s="107" t="s">
+        <v>5338</v>
       </c>
       <c r="J510" s="109" t="s">
-        <v>5333</v>
+        <v>5332</v>
       </c>
       <c r="K510" s="101" t="s">
-        <v>5087</v>
+        <v>5077</v>
       </c>
       <c r="L510" s="102" t="s">
-        <v>5089</v>
+        <v>5078</v>
       </c>
       <c r="M510" s="92">
         <v>1</v>
@@ -78058,13 +78396,13 @@
         <v>13</v>
       </c>
       <c r="P510" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q510">
         <v>1059</v>
       </c>
       <c r="R510" s="93">
-        <v>94502</v>
+        <v>94501</v>
       </c>
       <c r="T510" s="85">
         <v>0</v>
@@ -78074,43 +78412,50 @@
       </c>
       <c r="Z510" s="94"/>
       <c r="AA510" s="94"/>
+      <c r="AE510" s="95"/>
+      <c r="AF510" s="95"/>
+      <c r="AG510" s="95"/>
+      <c r="AH510" s="95"/>
+      <c r="AI510" s="95"/>
+      <c r="AL510" s="95"/>
+      <c r="AM510" s="95"/>
     </row>
-    <row r="511" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="511" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B511" s="85">
-        <v>800033</v>
+        <v>800032</v>
       </c>
       <c r="C511" s="88" t="s">
-        <v>4841</v>
+        <v>4837</v>
       </c>
       <c r="D511" s="88" t="s">
-        <v>4842</v>
+        <v>4838</v>
       </c>
       <c r="E511" s="101" t="s">
-        <v>5324</v>
+        <v>5322</v>
       </c>
       <c r="F511" s="101" t="s">
-        <v>5084</v>
+        <v>5081</v>
       </c>
       <c r="G511" s="101" t="s">
-        <v>5076</v>
+        <v>5075</v>
       </c>
       <c r="H511" s="90" t="s">
-        <v>4843</v>
+        <v>4839</v>
       </c>
       <c r="I511" s="90" t="s">
-        <v>4844</v>
+        <v>4840</v>
       </c>
       <c r="J511" s="109" t="s">
-        <v>5334</v>
+        <v>5333</v>
       </c>
       <c r="K511" s="101" t="s">
-        <v>5088</v>
+        <v>5087</v>
       </c>
       <c r="L511" s="102" t="s">
-        <v>5090</v>
-      </c>
-      <c r="M511" s="96">
-        <v>2</v>
+        <v>5089</v>
+      </c>
+      <c r="M511" s="92">
+        <v>1</v>
       </c>
       <c r="N511" s="85">
         <v>0</v>
@@ -78119,13 +78464,13 @@
         <v>13</v>
       </c>
       <c r="P511" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q511">
         <v>1059</v>
       </c>
       <c r="R511" s="93">
-        <v>94503</v>
+        <v>94502</v>
       </c>
       <c r="T511" s="85">
         <v>0</v>
@@ -78136,42 +78481,42 @@
       <c r="Z511" s="94"/>
       <c r="AA511" s="94"/>
     </row>
-    <row r="512" spans="1:39" s="85" customFormat="1" ht="33">
+    <row r="512" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B512" s="85">
-        <v>800034</v>
+        <v>800033</v>
       </c>
       <c r="C512" s="88" t="s">
-        <v>4845</v>
+        <v>4841</v>
       </c>
       <c r="D512" s="88" t="s">
-        <v>4846</v>
-      </c>
-      <c r="E512" s="110" t="s">
-        <v>5321</v>
+        <v>4842</v>
+      </c>
+      <c r="E512" s="101" t="s">
+        <v>5324</v>
       </c>
       <c r="F512" s="101" t="s">
-        <v>5079</v>
+        <v>5084</v>
       </c>
       <c r="G512" s="101" t="s">
-        <v>5080</v>
+        <v>5076</v>
       </c>
       <c r="H512" s="90" t="s">
-        <v>4847</v>
+        <v>4843</v>
       </c>
       <c r="I512" s="90" t="s">
-        <v>4848</v>
+        <v>4844</v>
       </c>
       <c r="J512" s="109" t="s">
-        <v>5326</v>
-      </c>
-      <c r="K512" s="91" t="s">
-        <v>5091</v>
-      </c>
-      <c r="L512" s="103" t="s">
-        <v>5094</v>
-      </c>
-      <c r="M512" s="92">
-        <v>1</v>
+        <v>5334</v>
+      </c>
+      <c r="K512" s="101" t="s">
+        <v>5088</v>
+      </c>
+      <c r="L512" s="102" t="s">
+        <v>5090</v>
+      </c>
+      <c r="M512" s="96">
+        <v>2</v>
       </c>
       <c r="N512" s="85">
         <v>0</v>
@@ -78180,13 +78525,13 @@
         <v>13</v>
       </c>
       <c r="P512" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q512">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R512" s="93">
-        <v>94504</v>
+        <v>94503</v>
       </c>
       <c r="T512" s="85">
         <v>0</v>
@@ -78199,37 +78544,37 @@
     </row>
     <row r="513" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B513" s="85">
-        <v>800035</v>
+        <v>800034</v>
       </c>
       <c r="C513" s="88" t="s">
-        <v>4849</v>
+        <v>4845</v>
       </c>
       <c r="D513" s="88" t="s">
-        <v>4850</v>
+        <v>4846</v>
       </c>
       <c r="E513" s="110" t="s">
-        <v>5323</v>
+        <v>5321</v>
       </c>
       <c r="F513" s="101" t="s">
-        <v>5082</v>
-      </c>
-      <c r="G513" s="102" t="s">
-        <v>5083</v>
+        <v>5079</v>
+      </c>
+      <c r="G513" s="101" t="s">
+        <v>5080</v>
       </c>
       <c r="H513" s="90" t="s">
-        <v>4851</v>
+        <v>4847</v>
       </c>
       <c r="I513" s="90" t="s">
-        <v>4852</v>
+        <v>4848</v>
       </c>
       <c r="J513" s="109" t="s">
-        <v>5327</v>
+        <v>5326</v>
       </c>
       <c r="K513" s="91" t="s">
-        <v>5092</v>
+        <v>5091</v>
       </c>
       <c r="L513" s="103" t="s">
-        <v>5095</v>
+        <v>5094</v>
       </c>
       <c r="M513" s="92">
         <v>1</v>
@@ -78241,13 +78586,13 @@
         <v>13</v>
       </c>
       <c r="P513" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q513">
         <v>1060</v>
       </c>
       <c r="R513" s="93">
-        <v>94505</v>
+        <v>94504</v>
       </c>
       <c r="T513" s="85">
         <v>0</v>
@@ -78258,42 +78603,42 @@
       <c r="Z513" s="94"/>
       <c r="AA513" s="94"/>
     </row>
-    <row r="514" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="514" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B514" s="85">
-        <v>800036</v>
+        <v>800035</v>
       </c>
       <c r="C514" s="88" t="s">
-        <v>4853</v>
+        <v>4849</v>
       </c>
       <c r="D514" s="88" t="s">
-        <v>4854</v>
+        <v>4850</v>
       </c>
       <c r="E514" s="110" t="s">
-        <v>5325</v>
+        <v>5323</v>
       </c>
       <c r="F514" s="101" t="s">
-        <v>5085</v>
+        <v>5082</v>
       </c>
       <c r="G514" s="102" t="s">
-        <v>5086</v>
+        <v>5083</v>
       </c>
       <c r="H514" s="90" t="s">
-        <v>4855</v>
+        <v>4851</v>
       </c>
       <c r="I514" s="90" t="s">
-        <v>4856</v>
+        <v>4852</v>
       </c>
       <c r="J514" s="109" t="s">
-        <v>5328</v>
+        <v>5327</v>
       </c>
       <c r="K514" s="91" t="s">
-        <v>5093</v>
+        <v>5092</v>
       </c>
       <c r="L514" s="103" t="s">
-        <v>5096</v>
-      </c>
-      <c r="M514" s="96">
-        <v>2</v>
+        <v>5095</v>
+      </c>
+      <c r="M514" s="92">
+        <v>1</v>
       </c>
       <c r="N514" s="85">
         <v>0</v>
@@ -78302,13 +78647,13 @@
         <v>13</v>
       </c>
       <c r="P514" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q514">
         <v>1060</v>
       </c>
       <c r="R514" s="93">
-        <v>94506</v>
+        <v>94505</v>
       </c>
       <c r="T514" s="85">
         <v>0</v>
@@ -78319,42 +78664,42 @@
       <c r="Z514" s="94"/>
       <c r="AA514" s="94"/>
     </row>
-    <row r="515" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="515" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B515" s="85">
-        <v>800037</v>
+        <v>800036</v>
       </c>
       <c r="C515" s="88" t="s">
-        <v>4857</v>
+        <v>4853</v>
       </c>
       <c r="D515" s="88" t="s">
-        <v>4858</v>
+        <v>4854</v>
       </c>
       <c r="E515" s="110" t="s">
-        <v>5329</v>
-      </c>
-      <c r="F515" s="89" t="s">
-        <v>5097</v>
-      </c>
-      <c r="G515" s="104" t="s">
-        <v>5098</v>
+        <v>5325</v>
+      </c>
+      <c r="F515" s="101" t="s">
+        <v>5085</v>
+      </c>
+      <c r="G515" s="102" t="s">
+        <v>5086</v>
       </c>
       <c r="H515" s="90" t="s">
-        <v>4859</v>
+        <v>4855</v>
       </c>
       <c r="I515" s="90" t="s">
-        <v>4860</v>
+        <v>4856</v>
       </c>
       <c r="J515" s="109" t="s">
-        <v>5335</v>
+        <v>5328</v>
       </c>
       <c r="K515" s="91" t="s">
-        <v>5208</v>
-      </c>
-      <c r="L515" s="102" t="s">
-        <v>5211</v>
-      </c>
-      <c r="M515" s="92">
-        <v>1</v>
+        <v>5093</v>
+      </c>
+      <c r="L515" s="103" t="s">
+        <v>5096</v>
+      </c>
+      <c r="M515" s="96">
+        <v>2</v>
       </c>
       <c r="N515" s="85">
         <v>0</v>
@@ -78363,13 +78708,13 @@
         <v>13</v>
       </c>
       <c r="P515" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q515">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R515" s="93">
-        <v>94507</v>
+        <v>94506</v>
       </c>
       <c r="T515" s="85">
         <v>0</v>
@@ -78382,37 +78727,37 @@
     </row>
     <row r="516" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B516" s="85">
-        <v>800038</v>
+        <v>800037</v>
       </c>
       <c r="C516" s="88" t="s">
-        <v>4861</v>
+        <v>4857</v>
       </c>
       <c r="D516" s="88" t="s">
-        <v>4862</v>
+        <v>4858</v>
       </c>
       <c r="E516" s="110" t="s">
-        <v>5331</v>
+        <v>5329</v>
       </c>
       <c r="F516" s="89" t="s">
-        <v>5100</v>
+        <v>5097</v>
       </c>
       <c r="G516" s="104" t="s">
-        <v>5101</v>
+        <v>5098</v>
       </c>
       <c r="H516" s="90" t="s">
-        <v>4863</v>
+        <v>4859</v>
       </c>
       <c r="I516" s="90" t="s">
-        <v>4864</v>
+        <v>4860</v>
       </c>
       <c r="J516" s="109" t="s">
-        <v>5336</v>
+        <v>5335</v>
       </c>
       <c r="K516" s="91" t="s">
-        <v>5209</v>
+        <v>5208</v>
       </c>
       <c r="L516" s="102" t="s">
-        <v>5212</v>
+        <v>5211</v>
       </c>
       <c r="M516" s="92">
         <v>1</v>
@@ -78424,13 +78769,13 @@
         <v>13</v>
       </c>
       <c r="P516" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q516">
         <v>1061</v>
       </c>
       <c r="R516" s="93">
-        <v>94508</v>
+        <v>94507</v>
       </c>
       <c r="T516" s="85">
         <v>0</v>
@@ -78443,40 +78788,40 @@
     </row>
     <row r="517" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B517" s="85">
-        <v>800039</v>
+        <v>800038</v>
       </c>
       <c r="C517" s="88" t="s">
-        <v>4865</v>
-      </c>
-      <c r="D517" s="107" t="s">
-        <v>5179</v>
+        <v>4861</v>
+      </c>
+      <c r="D517" s="88" t="s">
+        <v>4862</v>
       </c>
       <c r="E517" s="110" t="s">
-        <v>5330</v>
+        <v>5331</v>
       </c>
       <c r="F517" s="89" t="s">
-        <v>5099</v>
+        <v>5100</v>
       </c>
       <c r="G517" s="104" t="s">
-        <v>5102</v>
+        <v>5101</v>
       </c>
       <c r="H517" s="90" t="s">
-        <v>4866</v>
+        <v>4863</v>
       </c>
       <c r="I517" s="90" t="s">
-        <v>4867</v>
+        <v>4864</v>
       </c>
       <c r="J517" s="109" t="s">
-        <v>5337</v>
+        <v>5336</v>
       </c>
       <c r="K517" s="91" t="s">
-        <v>5210</v>
+        <v>5209</v>
       </c>
       <c r="L517" s="102" t="s">
-        <v>5213</v>
+        <v>5212</v>
       </c>
       <c r="M517" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N517" s="85">
         <v>0</v>
@@ -78485,13 +78830,13 @@
         <v>13</v>
       </c>
       <c r="P517" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q517">
         <v>1061</v>
       </c>
       <c r="R517" s="93">
-        <v>94509</v>
+        <v>94508</v>
       </c>
       <c r="T517" s="85">
         <v>0</v>
@@ -78504,40 +78849,40 @@
     </row>
     <row r="518" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B518" s="85">
-        <v>800040</v>
+        <v>800039</v>
       </c>
       <c r="C518" s="88" t="s">
-        <v>4868</v>
-      </c>
-      <c r="D518" s="88" t="s">
-        <v>4869</v>
+        <v>4865</v>
+      </c>
+      <c r="D518" s="107" t="s">
+        <v>5179</v>
       </c>
       <c r="E518" s="110" t="s">
-        <v>5339</v>
-      </c>
-      <c r="F518" s="101" t="s">
-        <v>5103</v>
-      </c>
-      <c r="G518" s="105" t="s">
-        <v>5104</v>
+        <v>5330</v>
+      </c>
+      <c r="F518" s="89" t="s">
+        <v>5099</v>
+      </c>
+      <c r="G518" s="104" t="s">
+        <v>5102</v>
       </c>
       <c r="H518" s="90" t="s">
-        <v>4870</v>
+        <v>4866</v>
       </c>
       <c r="I518" s="90" t="s">
-        <v>4871</v>
-      </c>
-      <c r="J518" s="111" t="s">
-        <v>5341</v>
+        <v>4867</v>
+      </c>
+      <c r="J518" s="109" t="s">
+        <v>5337</v>
       </c>
       <c r="K518" s="91" t="s">
-        <v>5214</v>
-      </c>
-      <c r="L518" s="103" t="s">
-        <v>5215</v>
+        <v>5210</v>
+      </c>
+      <c r="L518" s="102" t="s">
+        <v>5213</v>
       </c>
       <c r="M518" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N518" s="85">
         <v>0</v>
@@ -78546,10 +78891,13 @@
         <v>13</v>
       </c>
       <c r="P518" s="85">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="Q518">
+        <v>1061</v>
       </c>
       <c r="R518" s="93">
-        <v>94510</v>
+        <v>94509</v>
       </c>
       <c r="T518" s="85">
         <v>0</v>
@@ -78562,37 +78910,37 @@
     </row>
     <row r="519" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B519" s="85">
-        <v>800041</v>
+        <v>800040</v>
       </c>
       <c r="C519" s="88" t="s">
-        <v>4872</v>
+        <v>4868</v>
       </c>
       <c r="D519" s="88" t="s">
-        <v>4873</v>
+        <v>4869</v>
       </c>
       <c r="E519" s="110" t="s">
-        <v>5340</v>
+        <v>5339</v>
       </c>
       <c r="F519" s="101" t="s">
-        <v>5105</v>
-      </c>
-      <c r="G519" s="101" t="s">
-        <v>5106</v>
+        <v>5103</v>
+      </c>
+      <c r="G519" s="105" t="s">
+        <v>5104</v>
       </c>
       <c r="H519" s="90" t="s">
-        <v>4874</v>
+        <v>4870</v>
       </c>
       <c r="I519" s="90" t="s">
-        <v>4875</v>
+        <v>4871</v>
       </c>
       <c r="J519" s="111" t="s">
-        <v>5342</v>
+        <v>5341</v>
       </c>
       <c r="K519" s="91" t="s">
-        <v>5216</v>
+        <v>5214</v>
       </c>
       <c r="L519" s="103" t="s">
-        <v>5217</v>
+        <v>5215</v>
       </c>
       <c r="M519" s="92">
         <v>1</v>
@@ -78604,10 +78952,10 @@
         <v>13</v>
       </c>
       <c r="P519" s="85">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R519" s="93">
-        <v>94511</v>
+        <v>94510</v>
       </c>
       <c r="T519" s="85">
         <v>0</v>
@@ -78618,41 +78966,41 @@
       <c r="Z519" s="94"/>
       <c r="AA519" s="94"/>
     </row>
-    <row r="520" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="520" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B520" s="85">
-        <v>800042</v>
-      </c>
-      <c r="C520" s="97" t="s">
-        <v>4876</v>
-      </c>
-      <c r="D520" s="97" t="s">
-        <v>4876</v>
+        <v>800041</v>
+      </c>
+      <c r="C520" s="88" t="s">
+        <v>4872</v>
+      </c>
+      <c r="D520" s="88" t="s">
+        <v>4873</v>
       </c>
       <c r="E520" s="110" t="s">
-        <v>5343</v>
+        <v>5340</v>
       </c>
       <c r="F520" s="101" t="s">
-        <v>5180</v>
+        <v>5105</v>
       </c>
       <c r="G520" s="101" t="s">
-        <v>5107</v>
-      </c>
-      <c r="H520" s="97" t="s">
-        <v>4877</v>
-      </c>
-      <c r="I520" s="97" t="s">
-        <v>4878</v>
-      </c>
-      <c r="J520" s="109" t="s">
-        <v>5346</v>
-      </c>
-      <c r="K520" s="101" t="s">
-        <v>5218</v>
-      </c>
-      <c r="L520" s="102" t="s">
-        <v>5219</v>
-      </c>
-      <c r="M520" s="96">
+        <v>5106</v>
+      </c>
+      <c r="H520" s="90" t="s">
+        <v>4874</v>
+      </c>
+      <c r="I520" s="90" t="s">
+        <v>4875</v>
+      </c>
+      <c r="J520" s="111" t="s">
+        <v>5342</v>
+      </c>
+      <c r="K520" s="91" t="s">
+        <v>5216</v>
+      </c>
+      <c r="L520" s="103" t="s">
+        <v>5217</v>
+      </c>
+      <c r="M520" s="92">
         <v>1</v>
       </c>
       <c r="N520" s="85">
@@ -78662,13 +79010,10 @@
         <v>13</v>
       </c>
       <c r="P520" s="85">
-        <v>12</v>
-      </c>
-      <c r="Q520">
-        <v>1062</v>
+        <v>11</v>
       </c>
       <c r="R520" s="93">
-        <v>94512</v>
+        <v>94511</v>
       </c>
       <c r="T520" s="85">
         <v>0</v>
@@ -78679,41 +79024,41 @@
       <c r="Z520" s="94"/>
       <c r="AA520" s="94"/>
     </row>
-    <row r="521" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="521" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B521" s="85">
-        <v>800043</v>
+        <v>800042</v>
       </c>
       <c r="C521" s="97" t="s">
-        <v>4879</v>
+        <v>4876</v>
       </c>
       <c r="D521" s="97" t="s">
-        <v>4879</v>
+        <v>4876</v>
       </c>
       <c r="E521" s="110" t="s">
-        <v>5344</v>
+        <v>5343</v>
       </c>
       <c r="F521" s="101" t="s">
-        <v>5181</v>
-      </c>
-      <c r="G521" s="102" t="s">
-        <v>5184</v>
+        <v>5180</v>
+      </c>
+      <c r="G521" s="101" t="s">
+        <v>5107</v>
       </c>
       <c r="H521" s="97" t="s">
-        <v>4880</v>
+        <v>4877</v>
       </c>
       <c r="I521" s="97" t="s">
-        <v>4881</v>
+        <v>4878</v>
       </c>
       <c r="J521" s="109" t="s">
-        <v>5347</v>
+        <v>5346</v>
       </c>
       <c r="K521" s="101" t="s">
-        <v>5220</v>
+        <v>5218</v>
       </c>
       <c r="L521" s="102" t="s">
-        <v>5221</v>
-      </c>
-      <c r="M521" s="92">
+        <v>5219</v>
+      </c>
+      <c r="M521" s="96">
         <v>1</v>
       </c>
       <c r="N521" s="85">
@@ -78723,13 +79068,13 @@
         <v>13</v>
       </c>
       <c r="P521" s="85">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q521">
         <v>1062</v>
       </c>
       <c r="R521" s="93">
-        <v>94513</v>
+        <v>94512</v>
       </c>
       <c r="T521" s="85">
         <v>0</v>
@@ -78742,40 +79087,40 @@
     </row>
     <row r="522" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B522" s="85">
-        <v>800044</v>
+        <v>800043</v>
       </c>
       <c r="C522" s="97" t="s">
-        <v>4882</v>
+        <v>4879</v>
       </c>
       <c r="D522" s="97" t="s">
-        <v>4882</v>
+        <v>4879</v>
       </c>
       <c r="E522" s="110" t="s">
-        <v>5345</v>
+        <v>5344</v>
       </c>
       <c r="F522" s="101" t="s">
-        <v>5182</v>
+        <v>5181</v>
       </c>
       <c r="G522" s="102" t="s">
-        <v>5183</v>
+        <v>5184</v>
       </c>
       <c r="H522" s="97" t="s">
-        <v>4883</v>
+        <v>4880</v>
       </c>
       <c r="I522" s="97" t="s">
-        <v>4884</v>
+        <v>4881</v>
       </c>
       <c r="J522" s="109" t="s">
-        <v>5348</v>
+        <v>5347</v>
       </c>
       <c r="K522" s="101" t="s">
-        <v>5222</v>
+        <v>5220</v>
       </c>
       <c r="L522" s="102" t="s">
-        <v>5223</v>
+        <v>5221</v>
       </c>
       <c r="M522" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N522" s="85">
         <v>0</v>
@@ -78784,13 +79129,13 @@
         <v>13</v>
       </c>
       <c r="P522" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q522">
         <v>1062</v>
       </c>
       <c r="R522" s="93">
-        <v>94514</v>
+        <v>94513</v>
       </c>
       <c r="T522" s="85">
         <v>0</v>
@@ -78803,40 +79148,40 @@
     </row>
     <row r="523" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B523" s="85">
-        <v>800045</v>
+        <v>800044</v>
       </c>
       <c r="C523" s="97" t="s">
-        <v>4885</v>
+        <v>4882</v>
       </c>
       <c r="D523" s="97" t="s">
-        <v>4886</v>
+        <v>4882</v>
       </c>
       <c r="E523" s="110" t="s">
-        <v>5349</v>
-      </c>
-      <c r="F523" s="105" t="s">
-        <v>5108</v>
-      </c>
-      <c r="G523" s="101" t="s">
-        <v>5109</v>
+        <v>5345</v>
+      </c>
+      <c r="F523" s="101" t="s">
+        <v>5182</v>
+      </c>
+      <c r="G523" s="102" t="s">
+        <v>5183</v>
       </c>
       <c r="H523" s="97" t="s">
-        <v>4887</v>
+        <v>4883</v>
       </c>
       <c r="I523" s="97" t="s">
-        <v>4888</v>
+        <v>4884</v>
       </c>
       <c r="J523" s="109" t="s">
-        <v>5352</v>
+        <v>5348</v>
       </c>
       <c r="K523" s="101" t="s">
-        <v>5224</v>
+        <v>5222</v>
       </c>
       <c r="L523" s="102" t="s">
-        <v>5225</v>
+        <v>5223</v>
       </c>
       <c r="M523" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N523" s="85">
         <v>0</v>
@@ -78845,13 +79190,13 @@
         <v>13</v>
       </c>
       <c r="P523" s="85">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q523">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R523" s="93">
-        <v>94515</v>
+        <v>94514</v>
       </c>
       <c r="T523" s="85">
         <v>0</v>
@@ -78862,41 +79207,41 @@
       <c r="Z523" s="94"/>
       <c r="AA523" s="94"/>
     </row>
-    <row r="524" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="524" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B524" s="85">
-        <v>800046</v>
+        <v>800045</v>
       </c>
       <c r="C524" s="97" t="s">
-        <v>4889</v>
+        <v>4885</v>
       </c>
       <c r="D524" s="97" t="s">
-        <v>4890</v>
+        <v>4886</v>
       </c>
       <c r="E524" s="110" t="s">
-        <v>5350</v>
+        <v>5349</v>
       </c>
       <c r="F524" s="105" t="s">
-        <v>5185</v>
-      </c>
-      <c r="G524" s="102" t="s">
-        <v>5186</v>
+        <v>5108</v>
+      </c>
+      <c r="G524" s="101" t="s">
+        <v>5109</v>
       </c>
       <c r="H524" s="97" t="s">
-        <v>4891</v>
+        <v>4887</v>
       </c>
       <c r="I524" s="97" t="s">
-        <v>4892</v>
+        <v>4888</v>
       </c>
       <c r="J524" s="109" t="s">
-        <v>5353</v>
+        <v>5352</v>
       </c>
       <c r="K524" s="101" t="s">
-        <v>5226</v>
+        <v>5224</v>
       </c>
       <c r="L524" s="102" t="s">
-        <v>5227</v>
-      </c>
-      <c r="M524" s="96">
+        <v>5225</v>
+      </c>
+      <c r="M524" s="92">
         <v>1</v>
       </c>
       <c r="N524" s="85">
@@ -78906,13 +79251,13 @@
         <v>13</v>
       </c>
       <c r="P524" s="85">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q524">
         <v>1063</v>
       </c>
       <c r="R524" s="93">
-        <v>94516</v>
+        <v>94515</v>
       </c>
       <c r="T524" s="85">
         <v>0</v>
@@ -78923,42 +79268,42 @@
       <c r="Z524" s="94"/>
       <c r="AA524" s="94"/>
     </row>
-    <row r="525" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="525" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B525" s="85">
-        <v>800047</v>
+        <v>800046</v>
       </c>
       <c r="C525" s="97" t="s">
-        <v>4893</v>
+        <v>4889</v>
       </c>
       <c r="D525" s="97" t="s">
-        <v>4894</v>
+        <v>4890</v>
       </c>
       <c r="E525" s="110" t="s">
-        <v>5351</v>
+        <v>5350</v>
       </c>
       <c r="F525" s="105" t="s">
-        <v>5187</v>
+        <v>5185</v>
       </c>
       <c r="G525" s="102" t="s">
-        <v>5188</v>
+        <v>5186</v>
       </c>
       <c r="H525" s="97" t="s">
-        <v>4895</v>
+        <v>4891</v>
       </c>
       <c r="I525" s="97" t="s">
-        <v>4896</v>
+        <v>4892</v>
       </c>
       <c r="J525" s="109" t="s">
-        <v>5354</v>
+        <v>5353</v>
       </c>
       <c r="K525" s="101" t="s">
-        <v>5228</v>
+        <v>5226</v>
       </c>
       <c r="L525" s="102" t="s">
-        <v>5229</v>
-      </c>
-      <c r="M525" s="92">
-        <v>2</v>
+        <v>5227</v>
+      </c>
+      <c r="M525" s="96">
+        <v>1</v>
       </c>
       <c r="N525" s="85">
         <v>0</v>
@@ -78967,13 +79312,13 @@
         <v>13</v>
       </c>
       <c r="P525" s="85">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q525">
         <v>1063</v>
       </c>
       <c r="R525" s="93">
-        <v>94517</v>
+        <v>94516</v>
       </c>
       <c r="T525" s="85">
         <v>0</v>
@@ -78986,40 +79331,40 @@
     </row>
     <row r="526" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B526" s="85">
-        <v>800048</v>
+        <v>800047</v>
       </c>
       <c r="C526" s="97" t="s">
-        <v>4897</v>
+        <v>4893</v>
       </c>
       <c r="D526" s="97" t="s">
-        <v>4898</v>
+        <v>4894</v>
       </c>
       <c r="E526" s="110" t="s">
-        <v>5355</v>
+        <v>5351</v>
       </c>
       <c r="F526" s="105" t="s">
-        <v>5110</v>
-      </c>
-      <c r="G526" s="101" t="s">
-        <v>5111</v>
+        <v>5187</v>
+      </c>
+      <c r="G526" s="102" t="s">
+        <v>5188</v>
       </c>
       <c r="H526" s="97" t="s">
-        <v>4899</v>
+        <v>4895</v>
       </c>
       <c r="I526" s="97" t="s">
-        <v>4900</v>
+        <v>4896</v>
       </c>
       <c r="J526" s="109" t="s">
-        <v>5358</v>
+        <v>5354</v>
       </c>
       <c r="K526" s="101" t="s">
-        <v>5230</v>
+        <v>5228</v>
       </c>
       <c r="L526" s="102" t="s">
-        <v>5233</v>
+        <v>5229</v>
       </c>
       <c r="M526" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N526" s="85">
         <v>0</v>
@@ -79028,13 +79373,13 @@
         <v>13</v>
       </c>
       <c r="P526" s="85">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q526">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R526" s="93">
-        <v>94518</v>
+        <v>94517</v>
       </c>
       <c r="T526" s="85">
         <v>0</v>
@@ -79047,37 +79392,37 @@
     </row>
     <row r="527" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B527" s="85">
-        <v>800049</v>
+        <v>800048</v>
       </c>
       <c r="C527" s="97" t="s">
-        <v>4901</v>
+        <v>4897</v>
       </c>
       <c r="D527" s="97" t="s">
-        <v>4902</v>
+        <v>4898</v>
       </c>
       <c r="E527" s="110" t="s">
-        <v>5356</v>
+        <v>5355</v>
       </c>
       <c r="F527" s="105" t="s">
-        <v>5189</v>
-      </c>
-      <c r="G527" s="102" t="s">
-        <v>5190</v>
+        <v>5110</v>
+      </c>
+      <c r="G527" s="101" t="s">
+        <v>5111</v>
       </c>
       <c r="H527" s="97" t="s">
-        <v>4903</v>
+        <v>4899</v>
       </c>
       <c r="I527" s="97" t="s">
-        <v>4904</v>
+        <v>4900</v>
       </c>
       <c r="J527" s="109" t="s">
-        <v>5359</v>
+        <v>5358</v>
       </c>
       <c r="K527" s="101" t="s">
-        <v>5231</v>
+        <v>5230</v>
       </c>
       <c r="L527" s="102" t="s">
-        <v>5235</v>
+        <v>5233</v>
       </c>
       <c r="M527" s="92">
         <v>1</v>
@@ -79089,13 +79434,13 @@
         <v>13</v>
       </c>
       <c r="P527" s="85">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q527">
         <v>1064</v>
       </c>
       <c r="R527" s="93">
-        <v>94519</v>
+        <v>94518</v>
       </c>
       <c r="T527" s="85">
         <v>0</v>
@@ -79106,42 +79451,42 @@
       <c r="Z527" s="94"/>
       <c r="AA527" s="94"/>
     </row>
-    <row r="528" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="528" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B528" s="85">
-        <v>800050</v>
+        <v>800049</v>
       </c>
       <c r="C528" s="97" t="s">
-        <v>4905</v>
+        <v>4901</v>
       </c>
       <c r="D528" s="97" t="s">
-        <v>4906</v>
+        <v>4902</v>
       </c>
       <c r="E528" s="110" t="s">
-        <v>5357</v>
+        <v>5356</v>
       </c>
       <c r="F528" s="105" t="s">
-        <v>5191</v>
+        <v>5189</v>
       </c>
       <c r="G528" s="102" t="s">
-        <v>5192</v>
+        <v>5190</v>
       </c>
       <c r="H528" s="97" t="s">
-        <v>4907</v>
+        <v>4903</v>
       </c>
       <c r="I528" s="97" t="s">
-        <v>4908</v>
+        <v>4904</v>
       </c>
       <c r="J528" s="109" t="s">
-        <v>5360</v>
+        <v>5359</v>
       </c>
       <c r="K528" s="101" t="s">
-        <v>5232</v>
+        <v>5231</v>
       </c>
       <c r="L528" s="102" t="s">
-        <v>5234</v>
-      </c>
-      <c r="M528" s="96">
-        <v>2</v>
+        <v>5235</v>
+      </c>
+      <c r="M528" s="92">
+        <v>1</v>
       </c>
       <c r="N528" s="85">
         <v>0</v>
@@ -79150,13 +79495,13 @@
         <v>13</v>
       </c>
       <c r="P528" s="85">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q528">
         <v>1064</v>
       </c>
       <c r="R528" s="93">
-        <v>94520</v>
+        <v>94519</v>
       </c>
       <c r="T528" s="85">
         <v>0</v>
@@ -79167,42 +79512,42 @@
       <c r="Z528" s="94"/>
       <c r="AA528" s="94"/>
     </row>
-    <row r="529" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="529" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B529" s="85">
-        <v>800051</v>
+        <v>800050</v>
       </c>
       <c r="C529" s="97" t="s">
-        <v>4909</v>
-      </c>
-      <c r="D529" s="112" t="s">
-        <v>5443</v>
-      </c>
-      <c r="E529" s="101" t="s">
-        <v>5361</v>
+        <v>4905</v>
+      </c>
+      <c r="D529" s="97" t="s">
+        <v>4906</v>
+      </c>
+      <c r="E529" s="110" t="s">
+        <v>5357</v>
       </c>
       <c r="F529" s="105" t="s">
-        <v>5112</v>
-      </c>
-      <c r="G529" s="101" t="s">
-        <v>5113</v>
+        <v>5191</v>
+      </c>
+      <c r="G529" s="102" t="s">
+        <v>5192</v>
       </c>
       <c r="H529" s="97" t="s">
-        <v>4910</v>
-      </c>
-      <c r="I529" s="112" t="s">
-        <v>5446</v>
-      </c>
-      <c r="J529" s="101" t="s">
-        <v>5375</v>
+        <v>4907</v>
+      </c>
+      <c r="I529" s="97" t="s">
+        <v>4908</v>
+      </c>
+      <c r="J529" s="109" t="s">
+        <v>5360</v>
       </c>
       <c r="K529" s="101" t="s">
-        <v>5236</v>
-      </c>
-      <c r="L529" s="101" t="s">
-        <v>5237</v>
-      </c>
-      <c r="M529" s="92">
-        <v>1</v>
+        <v>5232</v>
+      </c>
+      <c r="L529" s="102" t="s">
+        <v>5234</v>
+      </c>
+      <c r="M529" s="96">
+        <v>2</v>
       </c>
       <c r="N529" s="85">
         <v>0</v>
@@ -79211,10 +79556,13 @@
         <v>13</v>
       </c>
       <c r="P529" s="85">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="Q529">
+        <v>1064</v>
       </c>
       <c r="R529" s="93">
-        <v>94521</v>
+        <v>94520</v>
       </c>
       <c r="T529" s="85">
         <v>0</v>
@@ -79227,37 +79575,37 @@
     </row>
     <row r="530" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B530" s="85">
-        <v>800052</v>
+        <v>800051</v>
       </c>
       <c r="C530" s="97" t="s">
-        <v>4911</v>
+        <v>4909</v>
       </c>
       <c r="D530" s="112" t="s">
-        <v>5444</v>
+        <v>5443</v>
       </c>
       <c r="E530" s="101" t="s">
-        <v>5362</v>
+        <v>5361</v>
       </c>
       <c r="F530" s="105" t="s">
-        <v>5114</v>
+        <v>5112</v>
       </c>
       <c r="G530" s="101" t="s">
-        <v>5115</v>
+        <v>5113</v>
       </c>
       <c r="H530" s="97" t="s">
-        <v>4912</v>
+        <v>4910</v>
       </c>
       <c r="I530" s="112" t="s">
-        <v>5447</v>
+        <v>5446</v>
       </c>
       <c r="J530" s="101" t="s">
-        <v>5376</v>
+        <v>5375</v>
       </c>
       <c r="K530" s="101" t="s">
-        <v>5238</v>
+        <v>5236</v>
       </c>
       <c r="L530" s="101" t="s">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="M530" s="92">
         <v>1</v>
@@ -79269,10 +79617,10 @@
         <v>13</v>
       </c>
       <c r="P530" s="85">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R530" s="93">
-        <v>94522</v>
+        <v>94521</v>
       </c>
       <c r="T530" s="85">
         <v>0</v>
@@ -79285,37 +79633,37 @@
     </row>
     <row r="531" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B531" s="85">
-        <v>800053</v>
+        <v>800052</v>
       </c>
       <c r="C531" s="97" t="s">
-        <v>4913</v>
-      </c>
-      <c r="D531" s="97" t="s">
-        <v>4914</v>
+        <v>4911</v>
+      </c>
+      <c r="D531" s="112" t="s">
+        <v>5444</v>
       </c>
       <c r="E531" s="101" t="s">
-        <v>5363</v>
+        <v>5362</v>
       </c>
       <c r="F531" s="105" t="s">
-        <v>5116</v>
+        <v>5114</v>
       </c>
       <c r="G531" s="101" t="s">
-        <v>5117</v>
+        <v>5115</v>
       </c>
       <c r="H531" s="97" t="s">
-        <v>4915</v>
-      </c>
-      <c r="I531" s="97" t="s">
-        <v>4916</v>
+        <v>4912</v>
+      </c>
+      <c r="I531" s="112" t="s">
+        <v>5447</v>
       </c>
       <c r="J531" s="101" t="s">
-        <v>5377</v>
+        <v>5376</v>
       </c>
       <c r="K531" s="101" t="s">
-        <v>5240</v>
+        <v>5238</v>
       </c>
       <c r="L531" s="101" t="s">
-        <v>5241</v>
+        <v>5239</v>
       </c>
       <c r="M531" s="92">
         <v>1</v>
@@ -79327,10 +79675,10 @@
         <v>13</v>
       </c>
       <c r="P531" s="85">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R531" s="93">
-        <v>94523</v>
+        <v>94522</v>
       </c>
       <c r="T531" s="85">
         <v>0</v>
@@ -79341,41 +79689,41 @@
       <c r="Z531" s="94"/>
       <c r="AA531" s="94"/>
     </row>
-    <row r="532" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="532" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B532" s="85">
-        <v>800054</v>
+        <v>800053</v>
       </c>
       <c r="C532" s="97" t="s">
-        <v>4917</v>
-      </c>
-      <c r="D532" s="112" t="s">
-        <v>5445</v>
+        <v>4913</v>
+      </c>
+      <c r="D532" s="97" t="s">
+        <v>4914</v>
       </c>
       <c r="E532" s="101" t="s">
-        <v>5364</v>
+        <v>5363</v>
       </c>
       <c r="F532" s="105" t="s">
-        <v>5118</v>
+        <v>5116</v>
       </c>
       <c r="G532" s="101" t="s">
-        <v>5119</v>
+        <v>5117</v>
       </c>
       <c r="H532" s="97" t="s">
-        <v>4918</v>
-      </c>
-      <c r="I532" s="112" t="s">
-        <v>5448</v>
+        <v>4915</v>
+      </c>
+      <c r="I532" s="97" t="s">
+        <v>4916</v>
       </c>
       <c r="J532" s="101" t="s">
-        <v>5378</v>
+        <v>5377</v>
       </c>
       <c r="K532" s="101" t="s">
-        <v>5242</v>
+        <v>5240</v>
       </c>
       <c r="L532" s="101" t="s">
-        <v>5243</v>
-      </c>
-      <c r="M532" s="96">
+        <v>5241</v>
+      </c>
+      <c r="M532" s="92">
         <v>1</v>
       </c>
       <c r="N532" s="85">
@@ -79385,10 +79733,10 @@
         <v>13</v>
       </c>
       <c r="P532" s="85">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R532" s="93">
-        <v>94524</v>
+        <v>94523</v>
       </c>
       <c r="T532" s="85">
         <v>0</v>
@@ -79399,41 +79747,41 @@
       <c r="Z532" s="94"/>
       <c r="AA532" s="94"/>
     </row>
-    <row r="533" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="533" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B533" s="85">
-        <v>800055</v>
+        <v>800054</v>
       </c>
       <c r="C533" s="97" t="s">
-        <v>4919</v>
+        <v>4917</v>
       </c>
       <c r="D533" s="112" t="s">
-        <v>5450</v>
+        <v>5445</v>
       </c>
       <c r="E533" s="101" t="s">
-        <v>5365</v>
+        <v>5364</v>
       </c>
       <c r="F533" s="105" t="s">
-        <v>5120</v>
+        <v>5118</v>
       </c>
       <c r="G533" s="101" t="s">
-        <v>5121</v>
+        <v>5119</v>
       </c>
       <c r="H533" s="97" t="s">
-        <v>4920</v>
-      </c>
-      <c r="I533" s="97" t="s">
-        <v>4921</v>
+        <v>4918</v>
+      </c>
+      <c r="I533" s="112" t="s">
+        <v>5448</v>
       </c>
       <c r="J533" s="101" t="s">
-        <v>5379</v>
+        <v>5378</v>
       </c>
       <c r="K533" s="101" t="s">
-        <v>5244</v>
+        <v>5242</v>
       </c>
       <c r="L533" s="101" t="s">
-        <v>5245</v>
-      </c>
-      <c r="M533" s="92">
+        <v>5243</v>
+      </c>
+      <c r="M533" s="96">
         <v>1</v>
       </c>
       <c r="N533" s="85">
@@ -79443,10 +79791,10 @@
         <v>13</v>
       </c>
       <c r="P533" s="85">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R533" s="93">
-        <v>94525</v>
+        <v>94524</v>
       </c>
       <c r="T533" s="85">
         <v>0</v>
@@ -79459,40 +79807,40 @@
     </row>
     <row r="534" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B534" s="85">
-        <v>800056</v>
+        <v>800055</v>
       </c>
       <c r="C534" s="97" t="s">
-        <v>4922</v>
-      </c>
-      <c r="D534" s="97" t="s">
-        <v>4923</v>
+        <v>4919</v>
+      </c>
+      <c r="D534" s="112" t="s">
+        <v>5450</v>
       </c>
       <c r="E534" s="101" t="s">
-        <v>5366</v>
+        <v>5365</v>
       </c>
       <c r="F534" s="105" t="s">
-        <v>5122</v>
+        <v>5120</v>
       </c>
       <c r="G534" s="101" t="s">
-        <v>5123</v>
+        <v>5121</v>
       </c>
       <c r="H534" s="97" t="s">
-        <v>4924</v>
+        <v>4920</v>
       </c>
       <c r="I534" s="97" t="s">
-        <v>4925</v>
+        <v>4921</v>
       </c>
       <c r="J534" s="101" t="s">
-        <v>5380</v>
+        <v>5379</v>
       </c>
       <c r="K534" s="101" t="s">
-        <v>5246</v>
+        <v>5244</v>
       </c>
       <c r="L534" s="101" t="s">
-        <v>5247</v>
+        <v>5245</v>
       </c>
       <c r="M534" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N534" s="85">
         <v>0</v>
@@ -79501,10 +79849,10 @@
         <v>13</v>
       </c>
       <c r="P534" s="85">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R534" s="93">
-        <v>94526</v>
+        <v>94525</v>
       </c>
       <c r="T534" s="85">
         <v>0</v>
@@ -79517,40 +79865,40 @@
     </row>
     <row r="535" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B535" s="85">
-        <v>800057</v>
+        <v>800056</v>
       </c>
       <c r="C535" s="97" t="s">
-        <v>4926</v>
+        <v>4922</v>
       </c>
       <c r="D535" s="97" t="s">
-        <v>4927</v>
+        <v>4923</v>
       </c>
       <c r="E535" s="101" t="s">
-        <v>5367</v>
+        <v>5366</v>
       </c>
       <c r="F535" s="105" t="s">
-        <v>5124</v>
+        <v>5122</v>
       </c>
       <c r="G535" s="101" t="s">
-        <v>5125</v>
+        <v>5123</v>
       </c>
       <c r="H535" s="97" t="s">
-        <v>4928</v>
+        <v>4924</v>
       </c>
       <c r="I535" s="97" t="s">
-        <v>4929</v>
+        <v>4925</v>
       </c>
       <c r="J535" s="101" t="s">
-        <v>5381</v>
+        <v>5380</v>
       </c>
       <c r="K535" s="101" t="s">
-        <v>5248</v>
+        <v>5246</v>
       </c>
       <c r="L535" s="101" t="s">
-        <v>5249</v>
+        <v>5247</v>
       </c>
       <c r="M535" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N535" s="85">
         <v>0</v>
@@ -79559,10 +79907,10 @@
         <v>13</v>
       </c>
       <c r="P535" s="85">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R535" s="93">
-        <v>94527</v>
+        <v>94526</v>
       </c>
       <c r="T535" s="85">
         <v>0</v>
@@ -79573,41 +79921,41 @@
       <c r="Z535" s="94"/>
       <c r="AA535" s="94"/>
     </row>
-    <row r="536" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="536" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B536" s="85">
-        <v>800058</v>
+        <v>800057</v>
       </c>
       <c r="C536" s="97" t="s">
-        <v>4930</v>
-      </c>
-      <c r="D536" s="112" t="s">
-        <v>5449</v>
+        <v>4926</v>
+      </c>
+      <c r="D536" s="97" t="s">
+        <v>4927</v>
       </c>
       <c r="E536" s="101" t="s">
-        <v>5368</v>
+        <v>5367</v>
       </c>
       <c r="F536" s="105" t="s">
-        <v>5126</v>
+        <v>5124</v>
       </c>
       <c r="G536" s="101" t="s">
-        <v>5127</v>
+        <v>5125</v>
       </c>
       <c r="H536" s="97" t="s">
-        <v>4931</v>
+        <v>4928</v>
       </c>
       <c r="I536" s="97" t="s">
-        <v>4932</v>
+        <v>4929</v>
       </c>
       <c r="J536" s="101" t="s">
-        <v>5382</v>
+        <v>5381</v>
       </c>
       <c r="K536" s="101" t="s">
-        <v>5250</v>
+        <v>5248</v>
       </c>
       <c r="L536" s="101" t="s">
-        <v>5251</v>
-      </c>
-      <c r="M536" s="96">
+        <v>5249</v>
+      </c>
+      <c r="M536" s="92">
         <v>1</v>
       </c>
       <c r="N536" s="85">
@@ -79617,10 +79965,10 @@
         <v>13</v>
       </c>
       <c r="P536" s="85">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R536" s="93">
-        <v>94528</v>
+        <v>94527</v>
       </c>
       <c r="T536" s="85">
         <v>0</v>
@@ -79631,41 +79979,41 @@
       <c r="Z536" s="94"/>
       <c r="AA536" s="94"/>
     </row>
-    <row r="537" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="537" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B537" s="85">
-        <v>800059</v>
+        <v>800058</v>
       </c>
       <c r="C537" s="97" t="s">
-        <v>4933</v>
+        <v>4930</v>
       </c>
       <c r="D537" s="112" t="s">
-        <v>5451</v>
+        <v>5449</v>
       </c>
       <c r="E537" s="101" t="s">
-        <v>5369</v>
+        <v>5368</v>
       </c>
       <c r="F537" s="105" t="s">
-        <v>5128</v>
+        <v>5126</v>
       </c>
       <c r="G537" s="101" t="s">
-        <v>5129</v>
+        <v>5127</v>
       </c>
       <c r="H537" s="97" t="s">
-        <v>4934</v>
-      </c>
-      <c r="I537" s="112" t="s">
-        <v>5452</v>
+        <v>4931</v>
+      </c>
+      <c r="I537" s="97" t="s">
+        <v>4932</v>
       </c>
       <c r="J537" s="101" t="s">
-        <v>5383</v>
+        <v>5382</v>
       </c>
       <c r="K537" s="101" t="s">
-        <v>5252</v>
+        <v>5250</v>
       </c>
       <c r="L537" s="101" t="s">
-        <v>5253</v>
-      </c>
-      <c r="M537" s="92">
+        <v>5251</v>
+      </c>
+      <c r="M537" s="96">
         <v>1</v>
       </c>
       <c r="N537" s="85">
@@ -79675,10 +80023,10 @@
         <v>13</v>
       </c>
       <c r="P537" s="85">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R537" s="93">
-        <v>94529</v>
+        <v>94528</v>
       </c>
       <c r="T537" s="85">
         <v>0</v>
@@ -79691,40 +80039,40 @@
     </row>
     <row r="538" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B538" s="85">
-        <v>800060</v>
-      </c>
-      <c r="C538" s="98" t="s">
-        <v>4935</v>
-      </c>
-      <c r="D538" s="98" t="s">
-        <v>4936</v>
+        <v>800059</v>
+      </c>
+      <c r="C538" s="97" t="s">
+        <v>4933</v>
+      </c>
+      <c r="D538" s="112" t="s">
+        <v>5451</v>
       </c>
       <c r="E538" s="101" t="s">
-        <v>5370</v>
+        <v>5369</v>
       </c>
       <c r="F538" s="105" t="s">
-        <v>5130</v>
+        <v>5128</v>
       </c>
       <c r="G538" s="101" t="s">
-        <v>5131</v>
+        <v>5129</v>
       </c>
       <c r="H538" s="97" t="s">
-        <v>4937</v>
-      </c>
-      <c r="I538" s="97" t="s">
-        <v>4938</v>
+        <v>4934</v>
+      </c>
+      <c r="I538" s="112" t="s">
+        <v>5452</v>
       </c>
       <c r="J538" s="101" t="s">
-        <v>5384</v>
+        <v>5383</v>
       </c>
       <c r="K538" s="101" t="s">
-        <v>5254</v>
+        <v>5252</v>
       </c>
       <c r="L538" s="101" t="s">
-        <v>5255</v>
+        <v>5253</v>
       </c>
       <c r="M538" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N538" s="85">
         <v>0</v>
@@ -79733,10 +80081,10 @@
         <v>13</v>
       </c>
       <c r="P538" s="85">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R538" s="93">
-        <v>94530</v>
+        <v>94529</v>
       </c>
       <c r="T538" s="85">
         <v>0</v>
@@ -79749,37 +80097,37 @@
     </row>
     <row r="539" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B539" s="85">
-        <v>800061</v>
-      </c>
-      <c r="C539" s="97" t="s">
-        <v>4939</v>
-      </c>
-      <c r="D539" s="97" t="s">
-        <v>4940</v>
+        <v>800060</v>
+      </c>
+      <c r="C539" s="98" t="s">
+        <v>4935</v>
+      </c>
+      <c r="D539" s="98" t="s">
+        <v>4936</v>
       </c>
       <c r="E539" s="101" t="s">
-        <v>5371</v>
+        <v>5370</v>
       </c>
       <c r="F539" s="105" t="s">
-        <v>5132</v>
+        <v>5130</v>
       </c>
       <c r="G539" s="101" t="s">
-        <v>5133</v>
+        <v>5131</v>
       </c>
       <c r="H539" s="97" t="s">
-        <v>4941</v>
+        <v>4937</v>
       </c>
       <c r="I539" s="97" t="s">
-        <v>4942</v>
+        <v>4938</v>
       </c>
       <c r="J539" s="101" t="s">
-        <v>5385</v>
+        <v>5384</v>
       </c>
       <c r="K539" s="101" t="s">
-        <v>5256</v>
+        <v>5254</v>
       </c>
       <c r="L539" s="101" t="s">
-        <v>5257</v>
+        <v>5255</v>
       </c>
       <c r="M539" s="92">
         <v>2</v>
@@ -79791,10 +80139,10 @@
         <v>13</v>
       </c>
       <c r="P539" s="85">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R539" s="93">
-        <v>94531</v>
+        <v>94530</v>
       </c>
       <c r="T539" s="85">
         <v>0</v>
@@ -79805,41 +80153,41 @@
       <c r="Z539" s="94"/>
       <c r="AA539" s="94"/>
     </row>
-    <row r="540" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="540" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B540" s="85">
-        <v>800062</v>
+        <v>800061</v>
       </c>
       <c r="C540" s="97" t="s">
-        <v>4943</v>
+        <v>4939</v>
       </c>
       <c r="D540" s="97" t="s">
-        <v>4944</v>
+        <v>4940</v>
       </c>
       <c r="E540" s="101" t="s">
-        <v>5372</v>
+        <v>5371</v>
       </c>
       <c r="F540" s="105" t="s">
-        <v>5134</v>
+        <v>5132</v>
       </c>
       <c r="G540" s="101" t="s">
-        <v>5135</v>
+        <v>5133</v>
       </c>
       <c r="H540" s="97" t="s">
-        <v>4945</v>
+        <v>4941</v>
       </c>
       <c r="I540" s="97" t="s">
-        <v>4946</v>
+        <v>4942</v>
       </c>
       <c r="J540" s="101" t="s">
-        <v>5386</v>
+        <v>5385</v>
       </c>
       <c r="K540" s="101" t="s">
-        <v>5258</v>
+        <v>5256</v>
       </c>
       <c r="L540" s="101" t="s">
-        <v>5259</v>
-      </c>
-      <c r="M540" s="96">
+        <v>5257</v>
+      </c>
+      <c r="M540" s="92">
         <v>2</v>
       </c>
       <c r="N540" s="85">
@@ -79849,10 +80197,10 @@
         <v>13</v>
       </c>
       <c r="P540" s="85">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R540" s="93">
-        <v>94532</v>
+        <v>94531</v>
       </c>
       <c r="T540" s="85">
         <v>0</v>
@@ -79863,41 +80211,41 @@
       <c r="Z540" s="94"/>
       <c r="AA540" s="94"/>
     </row>
-    <row r="541" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="541" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B541" s="85">
-        <v>800063</v>
+        <v>800062</v>
       </c>
       <c r="C541" s="97" t="s">
-        <v>4947</v>
+        <v>4943</v>
       </c>
       <c r="D541" s="97" t="s">
-        <v>4947</v>
+        <v>4944</v>
       </c>
       <c r="E541" s="101" t="s">
-        <v>5373</v>
+        <v>5372</v>
       </c>
       <c r="F541" s="105" t="s">
-        <v>5136</v>
+        <v>5134</v>
       </c>
       <c r="G541" s="101" t="s">
-        <v>5137</v>
+        <v>5135</v>
       </c>
       <c r="H541" s="97" t="s">
-        <v>4948</v>
+        <v>4945</v>
       </c>
       <c r="I541" s="97" t="s">
-        <v>4949</v>
+        <v>4946</v>
       </c>
       <c r="J541" s="101" t="s">
-        <v>5387</v>
+        <v>5386</v>
       </c>
       <c r="K541" s="101" t="s">
-        <v>5260</v>
+        <v>5258</v>
       </c>
       <c r="L541" s="101" t="s">
-        <v>5261</v>
-      </c>
-      <c r="M541" s="92">
+        <v>5259</v>
+      </c>
+      <c r="M541" s="96">
         <v>2</v>
       </c>
       <c r="N541" s="85">
@@ -79907,10 +80255,10 @@
         <v>13</v>
       </c>
       <c r="P541" s="85">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R541" s="93">
-        <v>94533</v>
+        <v>94532</v>
       </c>
       <c r="T541" s="85">
         <v>0</v>
@@ -79923,37 +80271,37 @@
     </row>
     <row r="542" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B542" s="85">
-        <v>800064</v>
+        <v>800063</v>
       </c>
       <c r="C542" s="97" t="s">
-        <v>4950</v>
+        <v>4947</v>
       </c>
       <c r="D542" s="97" t="s">
-        <v>4950</v>
+        <v>4947</v>
       </c>
       <c r="E542" s="101" t="s">
-        <v>5374</v>
+        <v>5373</v>
       </c>
       <c r="F542" s="105" t="s">
-        <v>5138</v>
+        <v>5136</v>
       </c>
       <c r="G542" s="101" t="s">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="H542" s="97" t="s">
-        <v>4951</v>
+        <v>4948</v>
       </c>
       <c r="I542" s="97" t="s">
-        <v>4952</v>
+        <v>4949</v>
       </c>
       <c r="J542" s="101" t="s">
-        <v>5388</v>
+        <v>5387</v>
       </c>
       <c r="K542" s="101" t="s">
-        <v>5262</v>
+        <v>5260</v>
       </c>
       <c r="L542" s="101" t="s">
-        <v>5263</v>
+        <v>5261</v>
       </c>
       <c r="M542" s="92">
         <v>2</v>
@@ -79965,10 +80313,10 @@
         <v>13</v>
       </c>
       <c r="P542" s="85">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R542" s="93">
-        <v>94534</v>
+        <v>94533</v>
       </c>
       <c r="T542" s="85">
         <v>0</v>
@@ -79979,42 +80327,42 @@
       <c r="Z542" s="94"/>
       <c r="AA542" s="94"/>
     </row>
-    <row r="543" spans="2:27" s="85" customFormat="1" ht="16.5">
+    <row r="543" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B543" s="85">
-        <v>800065</v>
+        <v>800064</v>
       </c>
       <c r="C543" s="97" t="s">
-        <v>4953</v>
+        <v>4950</v>
       </c>
       <c r="D543" s="97" t="s">
-        <v>4954</v>
+        <v>4950</v>
       </c>
       <c r="E543" s="101" t="s">
-        <v>5389</v>
-      </c>
-      <c r="F543" s="101" t="s">
-        <v>5140</v>
+        <v>5374</v>
+      </c>
+      <c r="F543" s="105" t="s">
+        <v>5138</v>
       </c>
       <c r="G543" s="101" t="s">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="H543" s="97" t="s">
-        <v>4955</v>
+        <v>4951</v>
       </c>
       <c r="I543" s="97" t="s">
-        <v>4956</v>
+        <v>4952</v>
       </c>
       <c r="J543" s="101" t="s">
-        <v>5393</v>
+        <v>5388</v>
       </c>
       <c r="K543" s="101" t="s">
-        <v>5264</v>
+        <v>5262</v>
       </c>
       <c r="L543" s="101" t="s">
-        <v>5265</v>
+        <v>5263</v>
       </c>
       <c r="M543" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N543" s="85">
         <v>0</v>
@@ -80023,10 +80371,10 @@
         <v>13</v>
       </c>
       <c r="P543" s="85">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R543" s="93">
-        <v>94535</v>
+        <v>94534</v>
       </c>
       <c r="T543" s="85">
         <v>0</v>
@@ -80037,41 +80385,41 @@
       <c r="Z543" s="94"/>
       <c r="AA543" s="94"/>
     </row>
-    <row r="544" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="544" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B544" s="85">
-        <v>800066</v>
+        <v>800065</v>
       </c>
       <c r="C544" s="97" t="s">
-        <v>4957</v>
+        <v>4953</v>
       </c>
       <c r="D544" s="97" t="s">
-        <v>4958</v>
+        <v>4954</v>
       </c>
       <c r="E544" s="101" t="s">
-        <v>5390</v>
+        <v>5389</v>
       </c>
       <c r="F544" s="101" t="s">
-        <v>5142</v>
+        <v>5140</v>
       </c>
       <c r="G544" s="101" t="s">
-        <v>5143</v>
+        <v>5141</v>
       </c>
       <c r="H544" s="97" t="s">
-        <v>4959</v>
+        <v>4955</v>
       </c>
       <c r="I544" s="97" t="s">
-        <v>4960</v>
+        <v>4956</v>
       </c>
       <c r="J544" s="101" t="s">
-        <v>5394</v>
+        <v>5393</v>
       </c>
       <c r="K544" s="101" t="s">
-        <v>5266</v>
+        <v>5264</v>
       </c>
       <c r="L544" s="101" t="s">
-        <v>5267</v>
-      </c>
-      <c r="M544" s="96">
+        <v>5265</v>
+      </c>
+      <c r="M544" s="92">
         <v>1</v>
       </c>
       <c r="N544" s="85">
@@ -80081,13 +80429,10 @@
         <v>13</v>
       </c>
       <c r="P544" s="85">
-        <v>36</v>
-      </c>
-      <c r="Q544">
-        <v>1065</v>
+        <v>35</v>
       </c>
       <c r="R544" s="93">
-        <v>94536</v>
+        <v>94535</v>
       </c>
       <c r="T544" s="85">
         <v>0</v>
@@ -80098,42 +80443,42 @@
       <c r="Z544" s="94"/>
       <c r="AA544" s="94"/>
     </row>
-    <row r="545" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="545" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B545" s="85">
-        <v>800067</v>
+        <v>800066</v>
       </c>
       <c r="C545" s="97" t="s">
-        <v>4961</v>
+        <v>4957</v>
       </c>
       <c r="D545" s="97" t="s">
-        <v>4962</v>
+        <v>4958</v>
       </c>
       <c r="E545" s="101" t="s">
-        <v>5391</v>
+        <v>5390</v>
       </c>
       <c r="F545" s="101" t="s">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="G545" s="101" t="s">
-        <v>5145</v>
+        <v>5143</v>
       </c>
       <c r="H545" s="97" t="s">
-        <v>4963</v>
+        <v>4959</v>
       </c>
       <c r="I545" s="97" t="s">
-        <v>4964</v>
+        <v>4960</v>
       </c>
       <c r="J545" s="101" t="s">
-        <v>5395</v>
+        <v>5394</v>
       </c>
       <c r="K545" s="101" t="s">
-        <v>5268</v>
+        <v>5266</v>
       </c>
       <c r="L545" s="101" t="s">
-        <v>5269</v>
-      </c>
-      <c r="M545" s="92">
-        <v>2</v>
+        <v>5267</v>
+      </c>
+      <c r="M545" s="96">
+        <v>1</v>
       </c>
       <c r="N545" s="85">
         <v>0</v>
@@ -80142,13 +80487,13 @@
         <v>13</v>
       </c>
       <c r="P545" s="85">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q545">
         <v>1065</v>
       </c>
       <c r="R545" s="93">
-        <v>94537</v>
+        <v>94536</v>
       </c>
       <c r="T545" s="85">
         <v>0</v>
@@ -80161,40 +80506,40 @@
     </row>
     <row r="546" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B546" s="85">
-        <v>800068</v>
+        <v>800067</v>
       </c>
       <c r="C546" s="97" t="s">
-        <v>4965</v>
+        <v>4961</v>
       </c>
       <c r="D546" s="97" t="s">
-        <v>4966</v>
+        <v>4962</v>
       </c>
       <c r="E546" s="101" t="s">
-        <v>5392</v>
+        <v>5391</v>
       </c>
       <c r="F546" s="101" t="s">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="G546" s="101" t="s">
-        <v>5147</v>
+        <v>5145</v>
       </c>
       <c r="H546" s="97" t="s">
-        <v>4967</v>
+        <v>4963</v>
       </c>
       <c r="I546" s="97" t="s">
-        <v>4968</v>
+        <v>4964</v>
       </c>
       <c r="J546" s="101" t="s">
-        <v>5396</v>
+        <v>5395</v>
       </c>
       <c r="K546" s="101" t="s">
-        <v>5270</v>
+        <v>5268</v>
       </c>
       <c r="L546" s="101" t="s">
-        <v>5271</v>
+        <v>5269</v>
       </c>
       <c r="M546" s="92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N546" s="85">
         <v>0</v>
@@ -80203,13 +80548,13 @@
         <v>13</v>
       </c>
       <c r="P546" s="85">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q546">
         <v>1065</v>
       </c>
       <c r="R546" s="93">
-        <v>94538</v>
+        <v>94537</v>
       </c>
       <c r="T546" s="85">
         <v>0</v>
@@ -80222,40 +80567,40 @@
     </row>
     <row r="547" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B547" s="85">
-        <v>800069</v>
+        <v>800068</v>
       </c>
       <c r="C547" s="97" t="s">
-        <v>4969</v>
+        <v>4965</v>
       </c>
       <c r="D547" s="97" t="s">
-        <v>4970</v>
-      </c>
-      <c r="E547" s="110" t="s">
-        <v>5397</v>
+        <v>4966</v>
+      </c>
+      <c r="E547" s="101" t="s">
+        <v>5392</v>
       </c>
       <c r="F547" s="101" t="s">
-        <v>5148</v>
+        <v>5146</v>
       </c>
       <c r="G547" s="101" t="s">
-        <v>5149</v>
+        <v>5147</v>
       </c>
       <c r="H547" s="97" t="s">
-        <v>4971</v>
+        <v>4967</v>
       </c>
       <c r="I547" s="97" t="s">
-        <v>4972</v>
-      </c>
-      <c r="J547" s="109" t="s">
-        <v>5432</v>
+        <v>4968</v>
+      </c>
+      <c r="J547" s="101" t="s">
+        <v>5396</v>
       </c>
       <c r="K547" s="101" t="s">
-        <v>5272</v>
-      </c>
-      <c r="L547" s="102" t="s">
-        <v>5275</v>
+        <v>5270</v>
+      </c>
+      <c r="L547" s="101" t="s">
+        <v>5271</v>
       </c>
       <c r="M547" s="92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N547" s="85">
         <v>0</v>
@@ -80264,13 +80609,13 @@
         <v>13</v>
       </c>
       <c r="P547" s="85">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q547">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R547" s="93">
-        <v>94539</v>
+        <v>94538</v>
       </c>
       <c r="T547" s="85">
         <v>0</v>
@@ -80281,41 +80626,41 @@
       <c r="Z547" s="94"/>
       <c r="AA547" s="94"/>
     </row>
-    <row r="548" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="548" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B548" s="85">
-        <v>800070</v>
+        <v>800069</v>
       </c>
       <c r="C548" s="97" t="s">
-        <v>4973</v>
+        <v>4969</v>
       </c>
       <c r="D548" s="97" t="s">
-        <v>4974</v>
+        <v>4970</v>
       </c>
       <c r="E548" s="110" t="s">
-        <v>5398</v>
+        <v>5397</v>
       </c>
       <c r="F548" s="101" t="s">
-        <v>5195</v>
-      </c>
-      <c r="G548" s="102" t="s">
-        <v>5196</v>
+        <v>5148</v>
+      </c>
+      <c r="G548" s="101" t="s">
+        <v>5149</v>
       </c>
       <c r="H548" s="97" t="s">
-        <v>4975</v>
+        <v>4971</v>
       </c>
       <c r="I548" s="97" t="s">
-        <v>4976</v>
+        <v>4972</v>
       </c>
       <c r="J548" s="109" t="s">
-        <v>5433</v>
+        <v>5432</v>
       </c>
       <c r="K548" s="101" t="s">
-        <v>5273</v>
+        <v>5272</v>
       </c>
       <c r="L548" s="102" t="s">
-        <v>5276</v>
-      </c>
-      <c r="M548" s="96">
+        <v>5275</v>
+      </c>
+      <c r="M548" s="92">
         <v>1</v>
       </c>
       <c r="N548" s="85">
@@ -80325,13 +80670,13 @@
         <v>13</v>
       </c>
       <c r="P548" s="85">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q548">
         <v>1066</v>
       </c>
       <c r="R548" s="93">
-        <v>94540</v>
+        <v>94539</v>
       </c>
       <c r="T548" s="85">
         <v>0</v>
@@ -80342,42 +80687,42 @@
       <c r="Z548" s="94"/>
       <c r="AA548" s="94"/>
     </row>
-    <row r="549" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="549" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B549" s="85">
-        <v>800071</v>
+        <v>800070</v>
       </c>
       <c r="C549" s="97" t="s">
-        <v>4977</v>
+        <v>4973</v>
       </c>
       <c r="D549" s="97" t="s">
-        <v>4978</v>
+        <v>4974</v>
       </c>
       <c r="E549" s="110" t="s">
-        <v>5399</v>
+        <v>5398</v>
       </c>
       <c r="F549" s="101" t="s">
-        <v>5193</v>
+        <v>5195</v>
       </c>
       <c r="G549" s="102" t="s">
-        <v>5194</v>
+        <v>5196</v>
       </c>
       <c r="H549" s="97" t="s">
-        <v>4979</v>
+        <v>4975</v>
       </c>
       <c r="I549" s="97" t="s">
-        <v>4980</v>
+        <v>4976</v>
       </c>
       <c r="J549" s="109" t="s">
-        <v>5434</v>
+        <v>5433</v>
       </c>
       <c r="K549" s="101" t="s">
-        <v>5274</v>
+        <v>5273</v>
       </c>
       <c r="L549" s="102" t="s">
-        <v>5277</v>
-      </c>
-      <c r="M549" s="92">
-        <v>2</v>
+        <v>5276</v>
+      </c>
+      <c r="M549" s="96">
+        <v>1</v>
       </c>
       <c r="N549" s="85">
         <v>0</v>
@@ -80386,13 +80731,13 @@
         <v>13</v>
       </c>
       <c r="P549" s="85">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q549">
         <v>1066</v>
       </c>
       <c r="R549" s="93">
-        <v>94541</v>
+        <v>94540</v>
       </c>
       <c r="T549" s="85">
         <v>0</v>
@@ -80405,40 +80750,40 @@
     </row>
     <row r="550" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B550" s="85">
-        <v>800072</v>
+        <v>800071</v>
       </c>
       <c r="C550" s="97" t="s">
-        <v>4981</v>
+        <v>4977</v>
       </c>
       <c r="D550" s="97" t="s">
-        <v>4982</v>
+        <v>4978</v>
       </c>
       <c r="E550" s="110" t="s">
-        <v>5400</v>
+        <v>5399</v>
       </c>
       <c r="F550" s="101" t="s">
-        <v>5199</v>
-      </c>
-      <c r="G550" s="101" t="s">
-        <v>5150</v>
+        <v>5193</v>
+      </c>
+      <c r="G550" s="102" t="s">
+        <v>5194</v>
       </c>
       <c r="H550" s="97" t="s">
-        <v>4983</v>
+        <v>4979</v>
       </c>
       <c r="I550" s="97" t="s">
-        <v>4984</v>
+        <v>4980</v>
       </c>
       <c r="J550" s="109" t="s">
-        <v>5435</v>
+        <v>5434</v>
       </c>
       <c r="K550" s="101" t="s">
-        <v>5278</v>
+        <v>5274</v>
       </c>
       <c r="L550" s="102" t="s">
-        <v>5279</v>
+        <v>5277</v>
       </c>
       <c r="M550" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N550" s="85">
         <v>0</v>
@@ -80447,13 +80792,13 @@
         <v>13</v>
       </c>
       <c r="P550" s="85">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q550">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R550" s="93">
-        <v>94542</v>
+        <v>94541</v>
       </c>
       <c r="T550" s="85">
         <v>0</v>
@@ -80466,37 +80811,37 @@
     </row>
     <row r="551" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B551" s="85">
-        <v>800073</v>
+        <v>800072</v>
       </c>
       <c r="C551" s="97" t="s">
-        <v>4985</v>
+        <v>4981</v>
       </c>
       <c r="D551" s="97" t="s">
-        <v>4986</v>
+        <v>4982</v>
       </c>
       <c r="E551" s="110" t="s">
-        <v>5401</v>
+        <v>5400</v>
       </c>
       <c r="F551" s="101" t="s">
-        <v>5197</v>
-      </c>
-      <c r="G551" s="102" t="s">
-        <v>5198</v>
+        <v>5199</v>
+      </c>
+      <c r="G551" s="101" t="s">
+        <v>5150</v>
       </c>
       <c r="H551" s="97" t="s">
-        <v>4987</v>
+        <v>4983</v>
       </c>
       <c r="I551" s="97" t="s">
-        <v>4988</v>
+        <v>4984</v>
       </c>
       <c r="J551" s="109" t="s">
-        <v>5436</v>
+        <v>5435</v>
       </c>
       <c r="K551" s="101" t="s">
-        <v>5280</v>
+        <v>5278</v>
       </c>
       <c r="L551" s="102" t="s">
-        <v>5281</v>
+        <v>5279</v>
       </c>
       <c r="M551" s="92">
         <v>1</v>
@@ -80508,13 +80853,13 @@
         <v>13</v>
       </c>
       <c r="P551" s="85">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q551">
         <v>1067</v>
       </c>
       <c r="R551" s="93">
-        <v>94543</v>
+        <v>94542</v>
       </c>
       <c r="T551" s="85">
         <v>0</v>
@@ -80525,42 +80870,42 @@
       <c r="Z551" s="94"/>
       <c r="AA551" s="94"/>
     </row>
-    <row r="552" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="552" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B552" s="85">
-        <v>800074</v>
+        <v>800073</v>
       </c>
       <c r="C552" s="97" t="s">
-        <v>4989</v>
+        <v>4985</v>
       </c>
       <c r="D552" s="97" t="s">
-        <v>4990</v>
+        <v>4986</v>
       </c>
       <c r="E552" s="110" t="s">
-        <v>5402</v>
+        <v>5401</v>
       </c>
       <c r="F552" s="101" t="s">
-        <v>5200</v>
+        <v>5197</v>
       </c>
       <c r="G552" s="102" t="s">
-        <v>5201</v>
+        <v>5198</v>
       </c>
       <c r="H552" s="97" t="s">
-        <v>4991</v>
+        <v>4987</v>
       </c>
       <c r="I552" s="97" t="s">
-        <v>4992</v>
+        <v>4988</v>
       </c>
       <c r="J552" s="109" t="s">
-        <v>5437</v>
+        <v>5436</v>
       </c>
       <c r="K552" s="101" t="s">
-        <v>5282</v>
+        <v>5280</v>
       </c>
       <c r="L552" s="102" t="s">
-        <v>5283</v>
-      </c>
-      <c r="M552" s="96">
-        <v>2</v>
+        <v>5281</v>
+      </c>
+      <c r="M552" s="92">
+        <v>1</v>
       </c>
       <c r="N552" s="85">
         <v>0</v>
@@ -80569,13 +80914,13 @@
         <v>13</v>
       </c>
       <c r="P552" s="85">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q552">
         <v>1067</v>
       </c>
       <c r="R552" s="93">
-        <v>94544</v>
+        <v>94543</v>
       </c>
       <c r="T552" s="85">
         <v>0</v>
@@ -80586,42 +80931,42 @@
       <c r="Z552" s="94"/>
       <c r="AA552" s="94"/>
     </row>
-    <row r="553" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="553" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B553" s="85">
-        <v>800075</v>
+        <v>800074</v>
       </c>
       <c r="C553" s="97" t="s">
-        <v>4993</v>
+        <v>4989</v>
       </c>
       <c r="D553" s="97" t="s">
-        <v>4994</v>
+        <v>4990</v>
       </c>
       <c r="E553" s="110" t="s">
-        <v>5403</v>
+        <v>5402</v>
       </c>
       <c r="F553" s="101" t="s">
-        <v>5151</v>
-      </c>
-      <c r="G553" s="101" t="s">
-        <v>5152</v>
+        <v>5200</v>
+      </c>
+      <c r="G553" s="102" t="s">
+        <v>5201</v>
       </c>
       <c r="H553" s="97" t="s">
-        <v>4995</v>
+        <v>4991</v>
       </c>
       <c r="I553" s="97" t="s">
-        <v>4996</v>
+        <v>4992</v>
       </c>
       <c r="J553" s="109" t="s">
-        <v>5438</v>
+        <v>5437</v>
       </c>
       <c r="K553" s="101" t="s">
-        <v>5284</v>
+        <v>5282</v>
       </c>
       <c r="L553" s="102" t="s">
-        <v>5287</v>
-      </c>
-      <c r="M553" s="92">
-        <v>1</v>
+        <v>5283</v>
+      </c>
+      <c r="M553" s="96">
+        <v>2</v>
       </c>
       <c r="N553" s="85">
         <v>0</v>
@@ -80630,13 +80975,13 @@
         <v>13</v>
       </c>
       <c r="P553" s="85">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q553">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R553" s="93">
-        <v>94545</v>
+        <v>94544</v>
       </c>
       <c r="T553" s="85">
         <v>0</v>
@@ -80649,37 +80994,37 @@
     </row>
     <row r="554" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B554" s="85">
-        <v>800076</v>
+        <v>800075</v>
       </c>
       <c r="C554" s="97" t="s">
-        <v>4997</v>
+        <v>4993</v>
       </c>
       <c r="D554" s="97" t="s">
-        <v>4998</v>
+        <v>4994</v>
       </c>
       <c r="E554" s="110" t="s">
-        <v>5404</v>
+        <v>5403</v>
       </c>
       <c r="F554" s="101" t="s">
-        <v>5204</v>
-      </c>
-      <c r="G554" s="102" t="s">
-        <v>5205</v>
+        <v>5151</v>
+      </c>
+      <c r="G554" s="101" t="s">
+        <v>5152</v>
       </c>
       <c r="H554" s="97" t="s">
-        <v>4999</v>
+        <v>4995</v>
       </c>
       <c r="I554" s="97" t="s">
-        <v>5000</v>
+        <v>4996</v>
       </c>
       <c r="J554" s="109" t="s">
-        <v>5439</v>
+        <v>5438</v>
       </c>
       <c r="K554" s="101" t="s">
-        <v>5285</v>
+        <v>5284</v>
       </c>
       <c r="L554" s="102" t="s">
-        <v>5289</v>
+        <v>5287</v>
       </c>
       <c r="M554" s="92">
         <v>1</v>
@@ -80691,13 +81036,13 @@
         <v>13</v>
       </c>
       <c r="P554" s="85">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q554">
         <v>1068</v>
       </c>
       <c r="R554" s="93">
-        <v>94546</v>
+        <v>94545</v>
       </c>
       <c r="T554" s="85">
         <v>0</v>
@@ -80710,40 +81055,40 @@
     </row>
     <row r="555" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B555" s="85">
-        <v>800077</v>
+        <v>800076</v>
       </c>
       <c r="C555" s="97" t="s">
-        <v>5001</v>
+        <v>4997</v>
       </c>
       <c r="D555" s="97" t="s">
-        <v>5002</v>
+        <v>4998</v>
       </c>
       <c r="E555" s="110" t="s">
-        <v>5405</v>
+        <v>5404</v>
       </c>
       <c r="F555" s="101" t="s">
-        <v>5202</v>
+        <v>5204</v>
       </c>
       <c r="G555" s="102" t="s">
-        <v>5203</v>
+        <v>5205</v>
       </c>
       <c r="H555" s="97" t="s">
-        <v>5003</v>
+        <v>4999</v>
       </c>
       <c r="I555" s="97" t="s">
-        <v>5004</v>
+        <v>5000</v>
       </c>
       <c r="J555" s="109" t="s">
-        <v>5440</v>
+        <v>5439</v>
       </c>
       <c r="K555" s="101" t="s">
-        <v>5286</v>
+        <v>5285</v>
       </c>
       <c r="L555" s="102" t="s">
-        <v>5288</v>
+        <v>5289</v>
       </c>
       <c r="M555" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N555" s="85">
         <v>0</v>
@@ -80752,13 +81097,13 @@
         <v>13</v>
       </c>
       <c r="P555" s="85">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q555">
         <v>1068</v>
       </c>
       <c r="R555" s="93">
-        <v>94547</v>
+        <v>94546</v>
       </c>
       <c r="T555" s="85">
         <v>0</v>
@@ -80769,42 +81114,42 @@
       <c r="Z555" s="94"/>
       <c r="AA555" s="94"/>
     </row>
-    <row r="556" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="556" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B556" s="85">
-        <v>800078</v>
+        <v>800077</v>
       </c>
       <c r="C556" s="97" t="s">
-        <v>5005</v>
+        <v>5001</v>
       </c>
       <c r="D556" s="97" t="s">
-        <v>5006</v>
+        <v>5002</v>
       </c>
       <c r="E556" s="110" t="s">
-        <v>5406</v>
+        <v>5405</v>
       </c>
       <c r="F556" s="101" t="s">
-        <v>5177</v>
-      </c>
-      <c r="G556" s="101" t="s">
-        <v>5153</v>
+        <v>5202</v>
+      </c>
+      <c r="G556" s="102" t="s">
+        <v>5203</v>
       </c>
       <c r="H556" s="97" t="s">
-        <v>5007</v>
+        <v>5003</v>
       </c>
       <c r="I556" s="97" t="s">
-        <v>5008</v>
+        <v>5004</v>
       </c>
       <c r="J556" s="109" t="s">
-        <v>5441</v>
+        <v>5440</v>
       </c>
       <c r="K556" s="101" t="s">
-        <v>5290</v>
+        <v>5286</v>
       </c>
       <c r="L556" s="102" t="s">
-        <v>5292</v>
-      </c>
-      <c r="M556" s="96">
-        <v>1</v>
+        <v>5288</v>
+      </c>
+      <c r="M556" s="92">
+        <v>2</v>
       </c>
       <c r="N556" s="85">
         <v>0</v>
@@ -80813,13 +81158,13 @@
         <v>13</v>
       </c>
       <c r="P556" s="85">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q556">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R556" s="93">
-        <v>94548</v>
+        <v>94547</v>
       </c>
       <c r="T556" s="85">
         <v>0</v>
@@ -80830,42 +81175,42 @@
       <c r="Z556" s="94"/>
       <c r="AA556" s="94"/>
     </row>
-    <row r="557" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="557" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B557" s="85">
-        <v>800079</v>
+        <v>800078</v>
       </c>
       <c r="C557" s="97" t="s">
-        <v>5009</v>
+        <v>5005</v>
       </c>
       <c r="D557" s="97" t="s">
-        <v>5010</v>
+        <v>5006</v>
       </c>
       <c r="E557" s="110" t="s">
-        <v>5407</v>
+        <v>5406</v>
       </c>
       <c r="F557" s="101" t="s">
-        <v>5206</v>
-      </c>
-      <c r="G557" s="102" t="s">
-        <v>5207</v>
+        <v>5177</v>
+      </c>
+      <c r="G557" s="101" t="s">
+        <v>5153</v>
       </c>
       <c r="H557" s="97" t="s">
-        <v>5011</v>
+        <v>5007</v>
       </c>
       <c r="I557" s="97" t="s">
-        <v>5012</v>
+        <v>5008</v>
       </c>
       <c r="J557" s="109" t="s">
-        <v>5442</v>
+        <v>5441</v>
       </c>
       <c r="K557" s="101" t="s">
-        <v>5291</v>
+        <v>5290</v>
       </c>
       <c r="L557" s="102" t="s">
-        <v>5293</v>
-      </c>
-      <c r="M557" s="92">
-        <v>2</v>
+        <v>5292</v>
+      </c>
+      <c r="M557" s="96">
+        <v>1</v>
       </c>
       <c r="N557" s="85">
         <v>0</v>
@@ -80874,13 +81219,13 @@
         <v>13</v>
       </c>
       <c r="P557" s="85">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q557">
         <v>1069</v>
       </c>
       <c r="R557" s="93">
-        <v>94549</v>
+        <v>94548</v>
       </c>
       <c r="T557" s="85">
         <v>0</v>
@@ -80893,40 +81238,40 @@
     </row>
     <row r="558" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B558" s="85">
-        <v>800080</v>
+        <v>800079</v>
       </c>
       <c r="C558" s="97" t="s">
-        <v>5013</v>
+        <v>5009</v>
       </c>
       <c r="D558" s="97" t="s">
-        <v>5014</v>
+        <v>5010</v>
       </c>
       <c r="E558" s="110" t="s">
-        <v>5408</v>
+        <v>5407</v>
       </c>
       <c r="F558" s="101" t="s">
-        <v>5154</v>
-      </c>
-      <c r="G558" s="101" t="s">
-        <v>5155</v>
+        <v>5206</v>
+      </c>
+      <c r="G558" s="102" t="s">
+        <v>5207</v>
       </c>
       <c r="H558" s="97" t="s">
-        <v>5015</v>
+        <v>5011</v>
       </c>
       <c r="I558" s="97" t="s">
-        <v>5016</v>
-      </c>
-      <c r="J558" s="91" t="s">
-        <v>5410</v>
+        <v>5012</v>
+      </c>
+      <c r="J558" s="109" t="s">
+        <v>5442</v>
       </c>
       <c r="K558" s="101" t="s">
-        <v>5294</v>
-      </c>
-      <c r="L558" s="101" t="s">
-        <v>5295</v>
+        <v>5291</v>
+      </c>
+      <c r="L558" s="102" t="s">
+        <v>5293</v>
       </c>
       <c r="M558" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N558" s="85">
         <v>0</v>
@@ -80935,13 +81280,13 @@
         <v>13</v>
       </c>
       <c r="P558" s="85">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q558">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="R558" s="93">
-        <v>94550</v>
+        <v>94549</v>
       </c>
       <c r="T558" s="85">
         <v>0</v>
@@ -80954,40 +81299,40 @@
     </row>
     <row r="559" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B559" s="85">
-        <v>800081</v>
+        <v>800080</v>
       </c>
       <c r="C559" s="97" t="s">
-        <v>5017</v>
+        <v>5013</v>
       </c>
       <c r="D559" s="97" t="s">
-        <v>5018</v>
+        <v>5014</v>
       </c>
       <c r="E559" s="110" t="s">
-        <v>5409</v>
+        <v>5408</v>
       </c>
       <c r="F559" s="101" t="s">
-        <v>5156</v>
+        <v>5154</v>
       </c>
       <c r="G559" s="101" t="s">
-        <v>5157</v>
+        <v>5155</v>
       </c>
       <c r="H559" s="97" t="s">
-        <v>5019</v>
+        <v>5015</v>
       </c>
       <c r="I559" s="97" t="s">
-        <v>5020</v>
+        <v>5016</v>
       </c>
       <c r="J559" s="91" t="s">
-        <v>5411</v>
+        <v>5410</v>
       </c>
       <c r="K559" s="101" t="s">
-        <v>5296</v>
-      </c>
-      <c r="L559" s="102" t="s">
-        <v>5297</v>
+        <v>5294</v>
+      </c>
+      <c r="L559" s="101" t="s">
+        <v>5295</v>
       </c>
       <c r="M559" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N559" s="85">
         <v>0</v>
@@ -80996,13 +81341,13 @@
         <v>13</v>
       </c>
       <c r="P559" s="85">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q559">
         <v>1070</v>
       </c>
       <c r="R559" s="93">
-        <v>94551</v>
+        <v>94550</v>
       </c>
       <c r="T559" s="85">
         <v>0</v>
@@ -81013,54 +81358,57 @@
       <c r="Z559" s="94"/>
       <c r="AA559" s="94"/>
     </row>
-    <row r="560" spans="2:27" s="85" customFormat="1" ht="18.75">
+    <row r="560" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B560" s="85">
-        <v>800101</v>
+        <v>800081</v>
       </c>
       <c r="C560" s="97" t="s">
-        <v>5021</v>
+        <v>5017</v>
       </c>
       <c r="D560" s="97" t="s">
-        <v>5022</v>
-      </c>
-      <c r="E560" s="101" t="s">
-        <v>5412</v>
+        <v>5018</v>
+      </c>
+      <c r="E560" s="110" t="s">
+        <v>5409</v>
       </c>
       <c r="F560" s="101" t="s">
-        <v>5158</v>
-      </c>
-      <c r="G560" s="106" t="s">
-        <v>5159</v>
+        <v>5156</v>
+      </c>
+      <c r="G560" s="101" t="s">
+        <v>5157</v>
       </c>
       <c r="H560" s="97" t="s">
-        <v>5023</v>
+        <v>5019</v>
       </c>
       <c r="I560" s="97" t="s">
-        <v>5024</v>
-      </c>
-      <c r="J560" s="111" t="s">
-        <v>5422</v>
+        <v>5020</v>
+      </c>
+      <c r="J560" s="91" t="s">
+        <v>5411</v>
       </c>
       <c r="K560" s="101" t="s">
-        <v>5298</v>
-      </c>
-      <c r="L560" s="108" t="s">
-        <v>5317</v>
+        <v>5296</v>
+      </c>
+      <c r="L560" s="102" t="s">
+        <v>5297</v>
       </c>
       <c r="M560" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N560" s="85">
         <v>0</v>
       </c>
       <c r="O560" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P560" s="85">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="Q560">
+        <v>1070</v>
       </c>
       <c r="R560" s="93">
-        <v>95001</v>
+        <v>94551</v>
       </c>
       <c r="T560" s="85">
         <v>0</v>
@@ -81071,41 +81419,41 @@
       <c r="Z560" s="94"/>
       <c r="AA560" s="94"/>
     </row>
-    <row r="561" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="561" spans="1:27" s="85" customFormat="1" ht="18.75">
       <c r="B561" s="85">
-        <v>800102</v>
+        <v>800101</v>
       </c>
       <c r="C561" s="97" t="s">
-        <v>5025</v>
+        <v>5021</v>
       </c>
       <c r="D561" s="97" t="s">
-        <v>5026</v>
+        <v>5022</v>
       </c>
       <c r="E561" s="101" t="s">
-        <v>5413</v>
+        <v>5412</v>
       </c>
       <c r="F561" s="101" t="s">
-        <v>5160</v>
+        <v>5158</v>
       </c>
       <c r="G561" s="106" t="s">
-        <v>5161</v>
+        <v>5159</v>
       </c>
       <c r="H561" s="97" t="s">
-        <v>5027</v>
+        <v>5023</v>
       </c>
       <c r="I561" s="97" t="s">
-        <v>5028</v>
-      </c>
-      <c r="J561" s="91" t="s">
-        <v>5423</v>
+        <v>5024</v>
+      </c>
+      <c r="J561" s="111" t="s">
+        <v>5422</v>
       </c>
       <c r="K561" s="101" t="s">
-        <v>5299</v>
-      </c>
-      <c r="L561" s="102" t="s">
-        <v>5300</v>
-      </c>
-      <c r="M561" s="96">
+        <v>5298</v>
+      </c>
+      <c r="L561" s="108" t="s">
+        <v>5317</v>
+      </c>
+      <c r="M561" s="92">
         <v>1</v>
       </c>
       <c r="N561" s="85">
@@ -81115,10 +81463,10 @@
         <v>14</v>
       </c>
       <c r="P561" s="85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R561" s="93">
-        <v>95002</v>
+        <v>95001</v>
       </c>
       <c r="T561" s="85">
         <v>0</v>
@@ -81129,41 +81477,41 @@
       <c r="Z561" s="94"/>
       <c r="AA561" s="94"/>
     </row>
-    <row r="562" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="562" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B562" s="85">
-        <v>800103</v>
+        <v>800102</v>
       </c>
       <c r="C562" s="97" t="s">
-        <v>5029</v>
+        <v>5025</v>
       </c>
       <c r="D562" s="97" t="s">
-        <v>5030</v>
+        <v>5026</v>
       </c>
       <c r="E562" s="101" t="s">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="F562" s="101" t="s">
-        <v>5178</v>
+        <v>5160</v>
       </c>
       <c r="G562" s="106" t="s">
-        <v>5162</v>
+        <v>5161</v>
       </c>
       <c r="H562" s="97" t="s">
-        <v>5031</v>
+        <v>5027</v>
       </c>
       <c r="I562" s="97" t="s">
-        <v>5032</v>
+        <v>5028</v>
       </c>
       <c r="J562" s="91" t="s">
-        <v>5424</v>
-      </c>
-      <c r="K562" s="91" t="s">
-        <v>5301</v>
-      </c>
-      <c r="L562" s="91" t="s">
-        <v>5302</v>
-      </c>
-      <c r="M562" s="92">
+        <v>5423</v>
+      </c>
+      <c r="K562" s="101" t="s">
+        <v>5299</v>
+      </c>
+      <c r="L562" s="102" t="s">
+        <v>5300</v>
+      </c>
+      <c r="M562" s="96">
         <v>1</v>
       </c>
       <c r="N562" s="85">
@@ -81173,10 +81521,10 @@
         <v>14</v>
       </c>
       <c r="P562" s="85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R562" s="93">
-        <v>95003</v>
+        <v>95002</v>
       </c>
       <c r="T562" s="85">
         <v>0</v>
@@ -81189,37 +81537,37 @@
     </row>
     <row r="563" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B563" s="85">
-        <v>800104</v>
+        <v>800103</v>
       </c>
       <c r="C563" s="97" t="s">
-        <v>5033</v>
+        <v>5029</v>
       </c>
       <c r="D563" s="97" t="s">
-        <v>5034</v>
+        <v>5030</v>
       </c>
       <c r="E563" s="101" t="s">
-        <v>5415</v>
+        <v>5414</v>
       </c>
       <c r="F563" s="101" t="s">
-        <v>5163</v>
+        <v>5178</v>
       </c>
       <c r="G563" s="106" t="s">
-        <v>5164</v>
+        <v>5162</v>
       </c>
       <c r="H563" s="97" t="s">
-        <v>5035</v>
+        <v>5031</v>
       </c>
       <c r="I563" s="97" t="s">
-        <v>5036</v>
+        <v>5032</v>
       </c>
       <c r="J563" s="91" t="s">
-        <v>5425</v>
+        <v>5424</v>
       </c>
       <c r="K563" s="91" t="s">
-        <v>5303</v>
+        <v>5301</v>
       </c>
       <c r="L563" s="91" t="s">
-        <v>5304</v>
+        <v>5302</v>
       </c>
       <c r="M563" s="92">
         <v>1</v>
@@ -81231,10 +81579,10 @@
         <v>14</v>
       </c>
       <c r="P563" s="85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R563" s="93">
-        <v>95004</v>
+        <v>95003</v>
       </c>
       <c r="T563" s="85">
         <v>0</v>
@@ -81247,37 +81595,37 @@
     </row>
     <row r="564" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B564" s="85">
-        <v>800105</v>
+        <v>800104</v>
       </c>
       <c r="C564" s="97" t="s">
-        <v>5037</v>
+        <v>5033</v>
       </c>
       <c r="D564" s="97" t="s">
-        <v>5038</v>
+        <v>5034</v>
       </c>
       <c r="E564" s="101" t="s">
-        <v>5416</v>
+        <v>5415</v>
       </c>
       <c r="F564" s="101" t="s">
-        <v>5165</v>
+        <v>5163</v>
       </c>
       <c r="G564" s="106" t="s">
-        <v>5166</v>
+        <v>5164</v>
       </c>
       <c r="H564" s="97" t="s">
-        <v>5039</v>
+        <v>5035</v>
       </c>
       <c r="I564" s="97" t="s">
-        <v>5040</v>
+        <v>5036</v>
       </c>
       <c r="J564" s="91" t="s">
-        <v>5426</v>
+        <v>5425</v>
       </c>
       <c r="K564" s="91" t="s">
-        <v>5305</v>
+        <v>5303</v>
       </c>
       <c r="L564" s="91" t="s">
-        <v>5306</v>
+        <v>5304</v>
       </c>
       <c r="M564" s="92">
         <v>1</v>
@@ -81289,10 +81637,10 @@
         <v>14</v>
       </c>
       <c r="P564" s="85">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R564" s="93">
-        <v>95005</v>
+        <v>95004</v>
       </c>
       <c r="T564" s="85">
         <v>0</v>
@@ -81303,41 +81651,41 @@
       <c r="Z564" s="94"/>
       <c r="AA564" s="94"/>
     </row>
-    <row r="565" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="565" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B565" s="85">
-        <v>800106</v>
+        <v>800105</v>
       </c>
       <c r="C565" s="97" t="s">
-        <v>5041</v>
+        <v>5037</v>
       </c>
       <c r="D565" s="97" t="s">
-        <v>5042</v>
+        <v>5038</v>
       </c>
       <c r="E565" s="101" t="s">
-        <v>5417</v>
+        <v>5416</v>
       </c>
       <c r="F565" s="101" t="s">
-        <v>5167</v>
+        <v>5165</v>
       </c>
       <c r="G565" s="106" t="s">
-        <v>5168</v>
+        <v>5166</v>
       </c>
       <c r="H565" s="97" t="s">
-        <v>5043</v>
+        <v>5039</v>
       </c>
       <c r="I565" s="97" t="s">
-        <v>5044</v>
+        <v>5040</v>
       </c>
       <c r="J565" s="91" t="s">
-        <v>5427</v>
+        <v>5426</v>
       </c>
       <c r="K565" s="91" t="s">
-        <v>5307</v>
+        <v>5305</v>
       </c>
       <c r="L565" s="91" t="s">
-        <v>5308</v>
-      </c>
-      <c r="M565" s="96">
+        <v>5306</v>
+      </c>
+      <c r="M565" s="92">
         <v>1</v>
       </c>
       <c r="N565" s="85">
@@ -81347,10 +81695,10 @@
         <v>14</v>
       </c>
       <c r="P565" s="85">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R565" s="93">
-        <v>95006</v>
+        <v>95005</v>
       </c>
       <c r="T565" s="85">
         <v>0</v>
@@ -81361,42 +81709,42 @@
       <c r="Z565" s="94"/>
       <c r="AA565" s="94"/>
     </row>
-    <row r="566" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="566" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B566" s="85">
-        <v>800107</v>
+        <v>800106</v>
       </c>
       <c r="C566" s="97" t="s">
-        <v>5045</v>
+        <v>5041</v>
       </c>
       <c r="D566" s="97" t="s">
-        <v>5046</v>
+        <v>5042</v>
       </c>
       <c r="E566" s="101" t="s">
-        <v>5418</v>
+        <v>5417</v>
       </c>
       <c r="F566" s="101" t="s">
-        <v>5169</v>
+        <v>5167</v>
       </c>
       <c r="G566" s="106" t="s">
-        <v>5170</v>
+        <v>5168</v>
       </c>
       <c r="H566" s="97" t="s">
-        <v>5047</v>
+        <v>5043</v>
       </c>
       <c r="I566" s="97" t="s">
-        <v>5048</v>
+        <v>5044</v>
       </c>
       <c r="J566" s="91" t="s">
-        <v>5428</v>
+        <v>5427</v>
       </c>
       <c r="K566" s="91" t="s">
-        <v>5309</v>
+        <v>5307</v>
       </c>
       <c r="L566" s="91" t="s">
-        <v>5310</v>
-      </c>
-      <c r="M566" s="92">
-        <v>2</v>
+        <v>5308</v>
+      </c>
+      <c r="M566" s="96">
+        <v>1</v>
       </c>
       <c r="N566" s="85">
         <v>0</v>
@@ -81405,10 +81753,10 @@
         <v>14</v>
       </c>
       <c r="P566" s="85">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R566" s="93">
-        <v>95007</v>
+        <v>95006</v>
       </c>
       <c r="T566" s="85">
         <v>0</v>
@@ -81421,37 +81769,37 @@
     </row>
     <row r="567" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B567" s="85">
-        <v>800108</v>
+        <v>800107</v>
       </c>
       <c r="C567" s="97" t="s">
-        <v>5049</v>
+        <v>5045</v>
       </c>
       <c r="D567" s="97" t="s">
-        <v>5050</v>
+        <v>5046</v>
       </c>
       <c r="E567" s="101" t="s">
-        <v>5419</v>
+        <v>5418</v>
       </c>
       <c r="F567" s="101" t="s">
-        <v>5171</v>
+        <v>5169</v>
       </c>
       <c r="G567" s="106" t="s">
-        <v>5172</v>
+        <v>5170</v>
       </c>
       <c r="H567" s="97" t="s">
-        <v>5051</v>
+        <v>5047</v>
       </c>
       <c r="I567" s="97" t="s">
-        <v>5052</v>
+        <v>5048</v>
       </c>
       <c r="J567" s="91" t="s">
-        <v>5429</v>
+        <v>5428</v>
       </c>
       <c r="K567" s="91" t="s">
-        <v>5311</v>
+        <v>5309</v>
       </c>
       <c r="L567" s="91" t="s">
-        <v>5312</v>
+        <v>5310</v>
       </c>
       <c r="M567" s="92">
         <v>2</v>
@@ -81463,10 +81811,10 @@
         <v>14</v>
       </c>
       <c r="P567" s="85">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R567" s="93">
-        <v>95008</v>
+        <v>95007</v>
       </c>
       <c r="T567" s="85">
         <v>0</v>
@@ -81479,37 +81827,37 @@
     </row>
     <row r="568" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B568" s="85">
-        <v>800109</v>
+        <v>800108</v>
       </c>
       <c r="C568" s="97" t="s">
-        <v>5053</v>
+        <v>5049</v>
       </c>
       <c r="D568" s="97" t="s">
-        <v>5054</v>
+        <v>5050</v>
       </c>
       <c r="E568" s="101" t="s">
-        <v>5420</v>
+        <v>5419</v>
       </c>
       <c r="F568" s="101" t="s">
-        <v>5173</v>
+        <v>5171</v>
       </c>
       <c r="G568" s="106" t="s">
-        <v>5174</v>
+        <v>5172</v>
       </c>
       <c r="H568" s="97" t="s">
-        <v>5055</v>
+        <v>5051</v>
       </c>
       <c r="I568" s="97" t="s">
-        <v>5056</v>
+        <v>5052</v>
       </c>
       <c r="J568" s="91" t="s">
-        <v>5430</v>
+        <v>5429</v>
       </c>
       <c r="K568" s="91" t="s">
-        <v>5313</v>
+        <v>5311</v>
       </c>
       <c r="L568" s="91" t="s">
-        <v>5314</v>
+        <v>5312</v>
       </c>
       <c r="M568" s="92">
         <v>2</v>
@@ -81521,10 +81869,10 @@
         <v>14</v>
       </c>
       <c r="P568" s="85">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R568" s="93">
-        <v>95009</v>
+        <v>95008</v>
       </c>
       <c r="T568" s="85">
         <v>0</v>
@@ -81535,42 +81883,42 @@
       <c r="Z568" s="94"/>
       <c r="AA568" s="94"/>
     </row>
-    <row r="569" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="569" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B569" s="85">
-        <v>800110</v>
+        <v>800109</v>
       </c>
       <c r="C569" s="97" t="s">
-        <v>5057</v>
+        <v>5053</v>
       </c>
       <c r="D569" s="97" t="s">
-        <v>5058</v>
+        <v>5054</v>
       </c>
       <c r="E569" s="101" t="s">
-        <v>5421</v>
+        <v>5420</v>
       </c>
       <c r="F569" s="101" t="s">
-        <v>5175</v>
+        <v>5173</v>
       </c>
       <c r="G569" s="106" t="s">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="H569" s="97" t="s">
-        <v>5059</v>
+        <v>5055</v>
       </c>
       <c r="I569" s="97" t="s">
-        <v>5060</v>
+        <v>5056</v>
       </c>
       <c r="J569" s="91" t="s">
-        <v>5431</v>
+        <v>5430</v>
       </c>
       <c r="K569" s="91" t="s">
-        <v>5315</v>
+        <v>5313</v>
       </c>
       <c r="L569" s="91" t="s">
-        <v>5316</v>
-      </c>
-      <c r="M569" s="96">
-        <v>3</v>
+        <v>5314</v>
+      </c>
+      <c r="M569" s="92">
+        <v>2</v>
       </c>
       <c r="N569" s="85">
         <v>0</v>
@@ -81579,10 +81927,10 @@
         <v>14</v>
       </c>
       <c r="P569" s="85">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R569" s="93">
-        <v>95010</v>
+        <v>95009</v>
       </c>
       <c r="T569" s="85">
         <v>0</v>
@@ -81593,37 +81941,95 @@
       <c r="Z569" s="94"/>
       <c r="AA569" s="94"/>
     </row>
-    <row r="570" spans="1:27" s="2" customFormat="1">
-      <c r="A570" s="2" t="s">
+    <row r="570" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+      <c r="B570" s="85">
+        <v>800110</v>
+      </c>
+      <c r="C570" s="97" t="s">
+        <v>5057</v>
+      </c>
+      <c r="D570" s="97" t="s">
+        <v>5058</v>
+      </c>
+      <c r="E570" s="101" t="s">
+        <v>5421</v>
+      </c>
+      <c r="F570" s="101" t="s">
+        <v>5175</v>
+      </c>
+      <c r="G570" s="106" t="s">
+        <v>5176</v>
+      </c>
+      <c r="H570" s="97" t="s">
+        <v>5059</v>
+      </c>
+      <c r="I570" s="97" t="s">
+        <v>5060</v>
+      </c>
+      <c r="J570" s="91" t="s">
+        <v>5431</v>
+      </c>
+      <c r="K570" s="91" t="s">
+        <v>5315</v>
+      </c>
+      <c r="L570" s="91" t="s">
+        <v>5316</v>
+      </c>
+      <c r="M570" s="96">
+        <v>3</v>
+      </c>
+      <c r="N570" s="85">
+        <v>0</v>
+      </c>
+      <c r="O570" s="85">
+        <v>14</v>
+      </c>
+      <c r="P570" s="85">
+        <v>10</v>
+      </c>
+      <c r="R570" s="93">
+        <v>95010</v>
+      </c>
+      <c r="T570" s="85">
+        <v>0</v>
+      </c>
+      <c r="U570" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z570" s="94"/>
+      <c r="AA570" s="94"/>
+    </row>
+    <row r="571" spans="1:27" s="2" customFormat="1">
+      <c r="A571" s="2" t="s">
         <v>4241</v>
       </c>
-      <c r="B570" s="2">
+      <c r="B571" s="2">
         <v>900001</v>
       </c>
-      <c r="M570" s="2">
-        <v>0</v>
-      </c>
-      <c r="N570" s="2">
-        <v>0</v>
-      </c>
-      <c r="O570" s="2">
+      <c r="M571" s="2">
+        <v>0</v>
+      </c>
+      <c r="N571" s="2">
+        <v>0</v>
+      </c>
+      <c r="O571" s="2">
         <v>2</v>
       </c>
-      <c r="P570" s="2">
+      <c r="P571" s="2">
         <v>999</v>
       </c>
-      <c r="R570" s="2">
+      <c r="R571" s="2">
         <v>98001</v>
       </c>
-      <c r="T570" s="2">
+      <c r="T571" s="2">
         <v>1</v>
       </c>
-      <c r="U570" s="2">
+      <c r="U571" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U509" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:U510" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="38" type="noConversion"/>
   <conditionalFormatting sqref="N1:N445 N449:N459 N462:N479 N482:N1048576">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">

--- a/source/bin/excel/achievement.xlsx
+++ b/source/bin/excel/achievement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\liqi-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A9A297-C44A-42B2-9ED9-0144255DFFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD78FBBA-32DC-49BF-89B3-D898850AE038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="export" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="badge_group" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$511</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">achievement!$A$1:$U$515</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6752" uniqueCount="5841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6792" uniqueCount="5881">
   <si>
     <t>sheet</t>
   </si>
@@ -42342,6 +42342,394 @@
   <si>
     <t>獲得雀士伊芙·克里斯特</t>
     <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>与赤麟的邂逅</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>與赤麟的邂逅</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赤麟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>との出会い</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得雀士赤麟</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>獲得雀士赤麟</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤麟的契约者</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤麟的契約者</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>赤麟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の契約者</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>与赤麟签订契约</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>與赤麟簽訂契約</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>An Encounter with Chi Lin</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonded with Chi Lin</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아카리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="BatangChe"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="BatangChe"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만남</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아카리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="BatangChe"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="BatangChe"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계약자</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤麟を入手する</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤麟と契約を結ぶ</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>Obtain Jyanshi Chi Lin</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bond with Chi Lin</t>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아카리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>획득하기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아카리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>계약</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>맺기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="38" type="noConversion"/>
+  </si>
+  <si>
+    <t>与墨菲的邂逅</t>
+  </si>
+  <si>
+    <t>與墨菲的邂逅</t>
+  </si>
+  <si>
+    <t>モフィーとの出会い</t>
+  </si>
+  <si>
+    <t>An Encounter with Murphy</t>
+  </si>
+  <si>
+    <t>머피와의 만남</t>
+  </si>
+  <si>
+    <t>获得雀士墨菲</t>
+  </si>
+  <si>
+    <t>獲得雀士墨菲</t>
+  </si>
+  <si>
+    <t>モフィーを入手する</t>
+  </si>
+  <si>
+    <t>Obtain Jyanshi Murphy</t>
+  </si>
+  <si>
+    <t>머피 획득하기.</t>
+  </si>
+  <si>
+    <t>墨菲的契约者</t>
+  </si>
+  <si>
+    <t>墨菲的契約者</t>
+  </si>
+  <si>
+    <t>モフィーの契約者</t>
+  </si>
+  <si>
+    <t>Bonded with Murphy</t>
+  </si>
+  <si>
+    <t>머피의 계약자</t>
+  </si>
+  <si>
+    <t>与墨菲签订契约</t>
+  </si>
+  <si>
+    <t>與墨菲簽訂契約</t>
+  </si>
+  <si>
+    <t>モフィーと契約を結ぶ</t>
+  </si>
+  <si>
+    <t>Bond with Murphy</t>
+  </si>
+  <si>
+    <t>머피와(과) 계약 맺기.</t>
   </si>
 </sst>
 </file>
@@ -43460,7 +43848,27 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -44529,7 +44937,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AM572"/>
+  <dimension ref="A1:AM576"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.75" customWidth="1"/>
@@ -76826,7 +77234,7 @@
       <c r="Z480" s="27"/>
       <c r="AA480" s="27"/>
     </row>
-    <row r="481" spans="1:39" ht="16.5">
+    <row r="481" spans="1:31" ht="16.5">
       <c r="B481">
         <v>100483</v>
       </c>
@@ -76886,7 +77294,7 @@
       <c r="Z481" s="27"/>
       <c r="AA481" s="27"/>
     </row>
-    <row r="482" spans="1:39" ht="16.5">
+    <row r="482" spans="1:31" ht="16.5">
       <c r="A482">
         <v>18</v>
       </c>
@@ -76952,7 +77360,7 @@
       <c r="Z482" s="27"/>
       <c r="AA482" s="27"/>
     </row>
-    <row r="483" spans="1:39">
+    <row r="483" spans="1:31">
       <c r="A483">
         <v>19</v>
       </c>
@@ -77018,7 +77426,7 @@
       <c r="Z483" s="27"/>
       <c r="AA483" s="27"/>
     </row>
-    <row r="484" spans="1:39" ht="16.5">
+    <row r="484" spans="1:31" ht="16.5">
       <c r="B484">
         <v>100486</v>
       </c>
@@ -77079,7 +77487,7 @@
       <c r="Z484" s="27"/>
       <c r="AA484" s="27"/>
     </row>
-    <row r="485" spans="1:39" ht="16.5">
+    <row r="485" spans="1:31" ht="16.5">
       <c r="B485">
         <v>100487</v>
       </c>
@@ -77140,7 +77548,7 @@
       <c r="Z485" s="27"/>
       <c r="AA485" s="27"/>
     </row>
-    <row r="486" spans="1:39" ht="16.5">
+    <row r="486" spans="1:31" ht="16.5">
       <c r="B486">
         <v>100488</v>
       </c>
@@ -77201,7 +77609,7 @@
       <c r="Z486" s="27"/>
       <c r="AA486" s="27"/>
     </row>
-    <row r="487" spans="1:39" ht="16.5">
+    <row r="487" spans="1:31" ht="16.5">
       <c r="B487">
         <v>100489</v>
       </c>
@@ -77262,7 +77670,7 @@
       <c r="Z487" s="27"/>
       <c r="AA487" s="27"/>
     </row>
-    <row r="488" spans="1:39" ht="16.5" customHeight="1">
+    <row r="488" spans="1:31" ht="16.5" customHeight="1">
       <c r="B488">
         <v>100490</v>
       </c>
@@ -77326,7 +77734,7 @@
       <c r="AD488" s="49"/>
       <c r="AE488" s="27"/>
     </row>
-    <row r="489" spans="1:39" ht="16.5">
+    <row r="489" spans="1:31" ht="16.5">
       <c r="B489">
         <v>100491</v>
       </c>
@@ -77390,7 +77798,7 @@
       <c r="AD489" s="49"/>
       <c r="AE489" s="27"/>
     </row>
-    <row r="490" spans="1:39" ht="16.5" customHeight="1">
+    <row r="490" spans="1:31" ht="16.5" customHeight="1">
       <c r="B490">
         <v>100492</v>
       </c>
@@ -77454,7 +77862,7 @@
       <c r="AD490" s="49"/>
       <c r="AE490" s="27"/>
     </row>
-    <row r="491" spans="1:39" ht="16.5">
+    <row r="491" spans="1:31" ht="16.5">
       <c r="B491">
         <v>100493</v>
       </c>
@@ -77518,7 +77926,7 @@
       <c r="AD491" s="49"/>
       <c r="AE491" s="27"/>
     </row>
-    <row r="492" spans="1:39" ht="16.5">
+    <row r="492" spans="1:31" ht="16.5">
       <c r="A492">
         <v>20</v>
       </c>
@@ -77584,7 +77992,7 @@
       <c r="Z492" s="27"/>
       <c r="AA492" s="27"/>
     </row>
-    <row r="493" spans="1:39" ht="16.5">
+    <row r="493" spans="1:31" ht="16.5">
       <c r="A493">
         <v>21</v>
       </c>
@@ -77650,7 +78058,7 @@
       <c r="Z493" s="27"/>
       <c r="AA493" s="27"/>
     </row>
-    <row r="494" spans="1:39">
+    <row r="494" spans="1:31">
       <c r="A494">
         <v>22</v>
       </c>
@@ -77716,7 +78124,7 @@
       <c r="Z494" s="27"/>
       <c r="AA494" s="27"/>
     </row>
-    <row r="495" spans="1:39" ht="16.5">
+    <row r="495" spans="1:31" ht="16.5">
       <c r="A495">
         <v>23</v>
       </c>
@@ -77782,336 +78190,301 @@
       <c r="Z495" s="27"/>
       <c r="AA495" s="27"/>
     </row>
-    <row r="496" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="A496" s="1" t="s">
-        <v>4230</v>
-      </c>
-      <c r="B496" s="1">
-        <v>800011</v>
-      </c>
-      <c r="C496" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D496" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E496" s="41" t="s">
-        <v>229</v>
-      </c>
-      <c r="F496" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="G496" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="H496" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I496" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J496" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="K496" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="L496" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="M496" s="47">
+    <row r="496" spans="1:31" ht="16.5">
+      <c r="B496">
+        <v>100498</v>
+      </c>
+      <c r="C496" s="29" t="s">
+        <v>5841</v>
+      </c>
+      <c r="D496" s="29" t="s">
+        <v>5842</v>
+      </c>
+      <c r="E496" s="62" t="s">
+        <v>5843</v>
+      </c>
+      <c r="F496" s="63" t="s">
+        <v>5851</v>
+      </c>
+      <c r="G496" s="73" t="s">
+        <v>5853</v>
+      </c>
+      <c r="H496" s="60" t="s">
+        <v>5844</v>
+      </c>
+      <c r="I496" s="29" t="s">
+        <v>5845</v>
+      </c>
+      <c r="J496" s="63" t="s">
+        <v>5855</v>
+      </c>
+      <c r="K496" s="60" t="s">
+        <v>5857</v>
+      </c>
+      <c r="L496" s="79" t="s">
+        <v>5859</v>
+      </c>
+      <c r="M496" s="66">
+        <v>2</v>
+      </c>
+      <c r="N496">
+        <v>0</v>
+      </c>
+      <c r="O496">
+        <v>10</v>
+      </c>
+      <c r="P496" s="85">
+        <v>174</v>
+      </c>
+      <c r="R496" s="123">
+        <v>99186</v>
+      </c>
+      <c r="T496">
+        <v>0</v>
+      </c>
+      <c r="U496">
+        <v>0</v>
+      </c>
+      <c r="X496" s="27"/>
+      <c r="Y496" s="27"/>
+      <c r="Z496" s="27"/>
+      <c r="AA496" s="27"/>
+      <c r="AB496" s="27"/>
+      <c r="AC496" s="27"/>
+      <c r="AD496" s="49"/>
+      <c r="AE496" s="27"/>
+    </row>
+    <row r="497" spans="1:39" ht="16.5">
+      <c r="B497">
+        <v>100499</v>
+      </c>
+      <c r="C497" s="29" t="s">
+        <v>5846</v>
+      </c>
+      <c r="D497" s="29" t="s">
+        <v>5847</v>
+      </c>
+      <c r="E497" s="62" t="s">
+        <v>5848</v>
+      </c>
+      <c r="F497" s="63" t="s">
+        <v>5852</v>
+      </c>
+      <c r="G497" s="73" t="s">
+        <v>5854</v>
+      </c>
+      <c r="H497" s="60" t="s">
+        <v>5849</v>
+      </c>
+      <c r="I497" s="29" t="s">
+        <v>5850</v>
+      </c>
+      <c r="J497" s="63" t="s">
+        <v>5856</v>
+      </c>
+      <c r="K497" s="29" t="s">
+        <v>5858</v>
+      </c>
+      <c r="L497" s="78" t="s">
+        <v>5860</v>
+      </c>
+      <c r="M497" s="66">
+        <v>2</v>
+      </c>
+      <c r="N497">
+        <v>0</v>
+      </c>
+      <c r="O497">
+        <v>10</v>
+      </c>
+      <c r="P497" s="86">
+        <v>376</v>
+      </c>
+      <c r="R497" s="123">
+        <v>99187</v>
+      </c>
+      <c r="T497">
+        <v>0</v>
+      </c>
+      <c r="U497">
+        <v>0</v>
+      </c>
+      <c r="X497" s="27"/>
+      <c r="Y497" s="27"/>
+      <c r="Z497" s="27"/>
+      <c r="AA497" s="27"/>
+      <c r="AB497" s="27"/>
+      <c r="AC497" s="27"/>
+      <c r="AD497" s="49"/>
+      <c r="AE497" s="27"/>
+    </row>
+    <row r="498" spans="1:39">
+      <c r="B498">
+        <v>100500</v>
+      </c>
+      <c r="C498" s="29" t="s">
+        <v>5861</v>
+      </c>
+      <c r="D498" s="29" t="s">
+        <v>5862</v>
+      </c>
+      <c r="E498" s="62" t="s">
+        <v>5863</v>
+      </c>
+      <c r="F498" s="63" t="s">
+        <v>5864</v>
+      </c>
+      <c r="G498" s="137" t="s">
+        <v>5865</v>
+      </c>
+      <c r="H498" s="60" t="s">
+        <v>5866</v>
+      </c>
+      <c r="I498" s="29" t="s">
+        <v>5867</v>
+      </c>
+      <c r="J498" s="63" t="s">
+        <v>5868</v>
+      </c>
+      <c r="K498" s="60" t="s">
+        <v>5869</v>
+      </c>
+      <c r="L498" s="79" t="s">
+        <v>5870</v>
+      </c>
+      <c r="M498" s="66">
         <v>1</v>
       </c>
-      <c r="N496" s="1">
-        <v>0</v>
-      </c>
-      <c r="O496" s="1">
-        <v>12</v>
-      </c>
-      <c r="P496" s="1">
+      <c r="N498">
+        <v>0</v>
+      </c>
+      <c r="O498">
+        <v>10</v>
+      </c>
+      <c r="P498" s="85">
+        <v>175</v>
+      </c>
+      <c r="R498" s="123">
+        <v>99188</v>
+      </c>
+      <c r="T498">
+        <v>0</v>
+      </c>
+      <c r="U498">
+        <v>0</v>
+      </c>
+      <c r="X498" s="27"/>
+      <c r="Y498" s="27"/>
+      <c r="Z498" s="27"/>
+      <c r="AA498" s="27"/>
+      <c r="AB498" s="27"/>
+      <c r="AC498" s="27"/>
+      <c r="AD498" s="49"/>
+      <c r="AE498" s="27"/>
+    </row>
+    <row r="499" spans="1:39">
+      <c r="B499">
+        <v>100501</v>
+      </c>
+      <c r="C499" s="29" t="s">
+        <v>5871</v>
+      </c>
+      <c r="D499" s="29" t="s">
+        <v>5872</v>
+      </c>
+      <c r="E499" s="62" t="s">
+        <v>5873</v>
+      </c>
+      <c r="F499" s="63" t="s">
+        <v>5874</v>
+      </c>
+      <c r="G499" s="137" t="s">
+        <v>5875</v>
+      </c>
+      <c r="H499" s="60" t="s">
+        <v>5876</v>
+      </c>
+      <c r="I499" s="29" t="s">
+        <v>5877</v>
+      </c>
+      <c r="J499" s="63" t="s">
+        <v>5878</v>
+      </c>
+      <c r="K499" s="29" t="s">
+        <v>5879</v>
+      </c>
+      <c r="L499" s="138" t="s">
+        <v>5880</v>
+      </c>
+      <c r="M499" s="66">
         <v>1</v>
       </c>
-      <c r="R496" s="1">
-        <v>90501</v>
-      </c>
-      <c r="T496" s="1">
-        <v>0</v>
-      </c>
-      <c r="U496" s="1">
-        <v>0</v>
-      </c>
-      <c r="X496" s="1">
-        <v>90501</v>
-      </c>
-      <c r="Y496" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z496" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA496" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB496" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE496" s="51"/>
-      <c r="AF496" s="51"/>
-      <c r="AG496" s="51"/>
-      <c r="AH496" s="51"/>
-      <c r="AI496" s="51"/>
-      <c r="AL496" s="51"/>
-      <c r="AM496" s="51"/>
-    </row>
-    <row r="497" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B497" s="1">
-        <v>800012</v>
-      </c>
-      <c r="C497" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D497" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E497" s="41" t="s">
-        <v>242</v>
-      </c>
-      <c r="F497" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G497" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="H497" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="I497" s="42" t="s">
-        <v>246</v>
-      </c>
-      <c r="J497" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="K497" s="42" t="s">
-        <v>4231</v>
-      </c>
-      <c r="L497" s="42" t="s">
-        <v>249</v>
-      </c>
-      <c r="M497" s="47">
-        <v>2</v>
-      </c>
-      <c r="N497" s="1">
-        <v>0</v>
-      </c>
-      <c r="O497" s="1">
-        <v>12</v>
-      </c>
-      <c r="P497" s="1">
-        <v>2</v>
-      </c>
-      <c r="R497" s="1">
-        <v>90502</v>
-      </c>
-      <c r="T497" s="1">
-        <v>0</v>
-      </c>
-      <c r="U497" s="1">
-        <v>0</v>
-      </c>
-      <c r="X497" s="1">
-        <v>90502</v>
-      </c>
-      <c r="Y497" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z497" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA497" s="42">
-        <v>3</v>
-      </c>
-      <c r="AB497" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="498" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B498" s="1">
-        <v>800013</v>
-      </c>
-      <c r="C498" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D498" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="E498" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="F498" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G498" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="H498" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="I498" s="42" t="s">
-        <v>257</v>
-      </c>
-      <c r="J498" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="K498" s="42" t="s">
-        <v>4232</v>
-      </c>
-      <c r="L498" s="42" t="s">
-        <v>260</v>
-      </c>
-      <c r="M498" s="48">
-        <v>3</v>
-      </c>
-      <c r="N498" s="1">
-        <v>0</v>
-      </c>
-      <c r="O498" s="1">
-        <v>12</v>
-      </c>
-      <c r="P498" s="1">
-        <v>3</v>
-      </c>
-      <c r="R498" s="1">
-        <v>90503</v>
-      </c>
-      <c r="T498" s="1">
-        <v>0</v>
-      </c>
-      <c r="U498" s="1">
-        <v>0</v>
-      </c>
-      <c r="X498" s="1">
-        <v>90503</v>
-      </c>
-      <c r="Y498" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z498" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA498" s="42">
-        <v>5</v>
-      </c>
-      <c r="AB498" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="499" spans="1:39" s="1" customFormat="1" ht="15">
-      <c r="B499" s="1">
-        <v>800014</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E499" s="41" t="s">
-        <v>263</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="G499" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="H499" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="I499" s="42" t="s">
-        <v>267</v>
-      </c>
-      <c r="J499" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="K499" s="42" t="s">
-        <v>269</v>
-      </c>
-      <c r="L499" s="42" t="s">
-        <v>270</v>
-      </c>
-      <c r="M499" s="47">
-        <v>1</v>
-      </c>
-      <c r="N499" s="1">
-        <v>0</v>
-      </c>
-      <c r="O499" s="1">
-        <v>12</v>
-      </c>
-      <c r="P499" s="1">
-        <v>4</v>
-      </c>
-      <c r="R499" s="1">
-        <v>90504</v>
-      </c>
-      <c r="T499" s="1">
-        <v>0</v>
-      </c>
-      <c r="U499" s="1">
-        <v>0</v>
-      </c>
-      <c r="X499" s="1">
-        <v>90504</v>
-      </c>
-      <c r="Y499" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z499" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA499" s="42">
-        <v>1</v>
-      </c>
-      <c r="AB499" s="1" t="s">
-        <v>271</v>
-      </c>
+      <c r="N499">
+        <v>0</v>
+      </c>
+      <c r="O499">
+        <v>10</v>
+      </c>
+      <c r="P499" s="86">
+        <v>377</v>
+      </c>
+      <c r="R499" s="123">
+        <v>99189</v>
+      </c>
+      <c r="T499">
+        <v>0</v>
+      </c>
+      <c r="U499">
+        <v>0</v>
+      </c>
+      <c r="X499" s="27"/>
+      <c r="Y499" s="27"/>
+      <c r="Z499" s="27"/>
+      <c r="AA499" s="27"/>
+      <c r="AB499" s="27"/>
+      <c r="AC499" s="27"/>
+      <c r="AD499" s="49"/>
+      <c r="AE499" s="27"/>
     </row>
     <row r="500" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="A500" s="1" t="s">
+        <v>4230</v>
+      </c>
       <c r="B500" s="1">
-        <v>800015</v>
+        <v>800011</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>272</v>
+        <v>227</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>273</v>
+        <v>228</v>
       </c>
       <c r="E500" s="41" t="s">
-        <v>274</v>
+        <v>229</v>
       </c>
       <c r="F500" s="1" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="G500" s="1" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="H500" s="42" t="s">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="I500" s="42" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="J500" s="46" t="s">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="K500" s="42" t="s">
-        <v>4233</v>
+        <v>235</v>
       </c>
       <c r="L500" s="42" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="M500" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N500" s="1">
         <v>0</v>
@@ -78120,10 +78493,10 @@
         <v>12</v>
       </c>
       <c r="P500" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R500" s="1">
-        <v>90505</v>
+        <v>90501</v>
       </c>
       <c r="T500" s="1">
         <v>0</v>
@@ -78132,57 +78505,64 @@
         <v>0</v>
       </c>
       <c r="X500" s="1">
-        <v>90505</v>
+        <v>90501</v>
       </c>
       <c r="Y500" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z500" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA500" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB500" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="AE500" s="51"/>
+      <c r="AF500" s="51"/>
+      <c r="AG500" s="51"/>
+      <c r="AH500" s="51"/>
+      <c r="AI500" s="51"/>
+      <c r="AL500" s="51"/>
+      <c r="AM500" s="51"/>
     </row>
     <row r="501" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B501" s="1">
-        <v>800016</v>
+        <v>800012</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="E501" s="43" t="s">
-        <v>284</v>
+        <v>241</v>
+      </c>
+      <c r="E501" s="41" t="s">
+        <v>242</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="G501" s="1" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="H501" s="42" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="I501" s="42" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="J501" s="46" t="s">
-        <v>289</v>
+        <v>247</v>
       </c>
       <c r="K501" s="42" t="s">
-        <v>4234</v>
+        <v>4231</v>
       </c>
       <c r="L501" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="M501" s="48">
-        <v>3</v>
+        <v>249</v>
+      </c>
+      <c r="M501" s="47">
+        <v>2</v>
       </c>
       <c r="N501" s="1">
         <v>0</v>
@@ -78191,10 +78571,10 @@
         <v>12</v>
       </c>
       <c r="P501" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R501" s="1">
-        <v>90506</v>
+        <v>90502</v>
       </c>
       <c r="T501" s="1">
         <v>0</v>
@@ -78203,7 +78583,7 @@
         <v>0</v>
       </c>
       <c r="X501" s="1">
-        <v>90506</v>
+        <v>90502</v>
       </c>
       <c r="Y501" s="1" t="s">
         <v>237</v>
@@ -78212,48 +78592,48 @@
         <v>250</v>
       </c>
       <c r="AA501" s="42">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AB501" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="502" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B502" s="1">
-        <v>800017</v>
+        <v>800013</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E502" s="43" t="s">
-        <v>294</v>
+        <v>252</v>
+      </c>
+      <c r="E502" s="41" t="s">
+        <v>253</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="G502" s="1" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="H502" s="42" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="I502" s="42" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="J502" s="46" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="K502" s="42" t="s">
-        <v>300</v>
+        <v>4232</v>
       </c>
       <c r="L502" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="M502" s="47">
-        <v>1</v>
+        <v>260</v>
+      </c>
+      <c r="M502" s="48">
+        <v>3</v>
       </c>
       <c r="N502" s="1">
         <v>0</v>
@@ -78262,10 +78642,10 @@
         <v>12</v>
       </c>
       <c r="P502" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R502" s="1">
-        <v>90507</v>
+        <v>90503</v>
       </c>
       <c r="T502" s="1">
         <v>0</v>
@@ -78274,54 +78654,54 @@
         <v>0</v>
       </c>
       <c r="X502" s="1">
-        <v>90507</v>
+        <v>90503</v>
       </c>
       <c r="Y502" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z502" s="42" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AA502" s="42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB502" s="1" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
     </row>
     <row r="503" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B503" s="1">
-        <v>800018</v>
+        <v>800014</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="E503" s="41" t="s">
-        <v>305</v>
+        <v>263</v>
       </c>
       <c r="F503" s="1" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="G503" s="1" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="H503" s="42" t="s">
-        <v>308</v>
+        <v>266</v>
       </c>
       <c r="I503" s="42" t="s">
-        <v>309</v>
+        <v>267</v>
       </c>
       <c r="J503" s="46" t="s">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="K503" s="42" t="s">
-        <v>4235</v>
+        <v>269</v>
       </c>
       <c r="L503" s="42" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="M503" s="47">
         <v>1</v>
@@ -78333,10 +78713,10 @@
         <v>12</v>
       </c>
       <c r="P503" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R503" s="1">
-        <v>90508</v>
+        <v>90504</v>
       </c>
       <c r="T503" s="1">
         <v>0</v>
@@ -78345,54 +78725,54 @@
         <v>0</v>
       </c>
       <c r="X503" s="1">
-        <v>90508</v>
+        <v>90504</v>
       </c>
       <c r="Y503" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z503" s="42" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AA503" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB503" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="504" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B504" s="1">
-        <v>800019</v>
+        <v>800015</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="E504" s="41" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="G504" s="1" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="H504" s="42" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="I504" s="42" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="J504" s="46" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="K504" s="42" t="s">
-        <v>4236</v>
+        <v>4233</v>
       </c>
       <c r="L504" s="42" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="M504" s="47">
         <v>2</v>
@@ -78404,10 +78784,10 @@
         <v>12</v>
       </c>
       <c r="P504" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R504" s="1">
-        <v>90509</v>
+        <v>90505</v>
       </c>
       <c r="T504" s="1">
         <v>0</v>
@@ -78416,7 +78796,7 @@
         <v>0</v>
       </c>
       <c r="X504" s="1">
-        <v>90509</v>
+        <v>90505</v>
       </c>
       <c r="Y504" s="1" t="s">
         <v>237</v>
@@ -78425,48 +78805,48 @@
         <v>250</v>
       </c>
       <c r="AA504" s="42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB504" s="1" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="505" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B505" s="1">
-        <v>800020</v>
+        <v>800016</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E505" s="41" t="s">
-        <v>325</v>
+        <v>283</v>
+      </c>
+      <c r="E505" s="43" t="s">
+        <v>284</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="G505" s="1" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="H505" s="42" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="I505" s="42" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="J505" s="46" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="K505" s="42" t="s">
-        <v>331</v>
+        <v>4234</v>
       </c>
       <c r="L505" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="M505" s="47">
-        <v>1</v>
+        <v>291</v>
+      </c>
+      <c r="M505" s="48">
+        <v>3</v>
       </c>
       <c r="N505" s="1">
         <v>0</v>
@@ -78475,10 +78855,10 @@
         <v>12</v>
       </c>
       <c r="P505" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R505" s="1">
-        <v>90510</v>
+        <v>90506</v>
       </c>
       <c r="T505" s="1">
         <v>0</v>
@@ -78487,57 +78867,57 @@
         <v>0</v>
       </c>
       <c r="X505" s="1">
-        <v>90510</v>
+        <v>90506</v>
       </c>
       <c r="Y505" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z505" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA505" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB505" s="1" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="506" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B506" s="1">
-        <v>800021</v>
+        <v>800017</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>334</v>
+        <v>292</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E506" s="41" t="s">
-        <v>336</v>
+        <v>293</v>
+      </c>
+      <c r="E506" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>337</v>
+        <v>295</v>
       </c>
       <c r="G506" s="1" t="s">
-        <v>338</v>
+        <v>296</v>
       </c>
       <c r="H506" s="42" t="s">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="I506" s="42" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="J506" s="46" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="K506" s="42" t="s">
-        <v>4237</v>
+        <v>300</v>
       </c>
       <c r="L506" s="42" t="s">
-        <v>343</v>
+        <v>301</v>
       </c>
       <c r="M506" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N506" s="1">
         <v>0</v>
@@ -78546,10 +78926,10 @@
         <v>12</v>
       </c>
       <c r="P506" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R506" s="1">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="T506" s="1">
         <v>0</v>
@@ -78558,57 +78938,57 @@
         <v>0</v>
       </c>
       <c r="X506" s="1">
-        <v>90511</v>
+        <v>90507</v>
       </c>
       <c r="Y506" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z506" s="42" t="s">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="AA506" s="42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB506" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="507" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B507" s="1">
-        <v>800022</v>
+        <v>800018</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="E507" s="41" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="G507" s="1" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="H507" s="42" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="I507" s="42" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="J507" s="46" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="K507" s="42" t="s">
-        <v>4238</v>
+        <v>4235</v>
       </c>
       <c r="L507" s="42" t="s">
-        <v>353</v>
-      </c>
-      <c r="M507" s="48">
-        <v>3</v>
+        <v>312</v>
+      </c>
+      <c r="M507" s="47">
+        <v>1</v>
       </c>
       <c r="N507" s="1">
         <v>0</v>
@@ -78617,10 +78997,10 @@
         <v>12</v>
       </c>
       <c r="P507" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R507" s="1">
-        <v>90512</v>
+        <v>90508</v>
       </c>
       <c r="T507" s="1">
         <v>0</v>
@@ -78629,57 +79009,57 @@
         <v>0</v>
       </c>
       <c r="X507" s="1">
-        <v>90512</v>
+        <v>90508</v>
       </c>
       <c r="Y507" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z507" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA507" s="42">
         <v>5</v>
       </c>
       <c r="AB507" s="1" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="508" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B508" s="1">
-        <v>800023</v>
+        <v>800019</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="E508" s="41" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="F508" s="1" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="G508" s="1" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="H508" s="42" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="I508" s="42" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="J508" s="46" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="K508" s="42" t="s">
-        <v>362</v>
+        <v>4236</v>
       </c>
       <c r="L508" s="42" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="M508" s="47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N508" s="1">
         <v>0</v>
@@ -78688,10 +79068,10 @@
         <v>12</v>
       </c>
       <c r="P508" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R508" s="1">
-        <v>90513</v>
+        <v>90509</v>
       </c>
       <c r="T508" s="1">
         <v>0</v>
@@ -78700,54 +79080,54 @@
         <v>0</v>
       </c>
       <c r="X508" s="1">
-        <v>90513</v>
+        <v>90509</v>
       </c>
       <c r="Y508" s="1" t="s">
         <v>237</v>
       </c>
       <c r="Z508" s="42" t="s">
-        <v>333</v>
+        <v>250</v>
       </c>
       <c r="AA508" s="42">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AB508" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="509" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B509" s="1">
-        <v>800024</v>
+        <v>800020</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="E509" s="41" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="F509" s="1" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="G509" s="1" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="H509" s="42" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="I509" s="42" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="J509" s="46" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="K509" s="42" t="s">
-        <v>4239</v>
+        <v>331</v>
       </c>
       <c r="L509" s="42" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="M509" s="47">
         <v>1</v>
@@ -78759,10 +79139,10 @@
         <v>12</v>
       </c>
       <c r="P509" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R509" s="1">
-        <v>90514</v>
+        <v>90510</v>
       </c>
       <c r="T509" s="1">
         <v>0</v>
@@ -78771,7 +79151,7 @@
         <v>0</v>
       </c>
       <c r="X509" s="1">
-        <v>90514</v>
+        <v>90510</v>
       </c>
       <c r="Y509" s="1" t="s">
         <v>237</v>
@@ -78780,45 +79160,45 @@
         <v>333</v>
       </c>
       <c r="AA509" s="42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB509" s="1" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="510" spans="1:39" s="1" customFormat="1" ht="15">
       <c r="B510" s="1">
-        <v>800025</v>
+        <v>800021</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="E510" s="41" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="F510" s="1" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="G510" s="1" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="H510" s="42" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="I510" s="42" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="J510" s="46" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="K510" s="42" t="s">
-        <v>4240</v>
+        <v>4237</v>
       </c>
       <c r="L510" s="42" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="M510" s="47">
         <v>2</v>
@@ -78830,10 +79210,10 @@
         <v>12</v>
       </c>
       <c r="P510" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R510" s="1">
-        <v>90515</v>
+        <v>90511</v>
       </c>
       <c r="T510" s="1">
         <v>0</v>
@@ -78842,7 +79222,7 @@
         <v>0</v>
       </c>
       <c r="X510" s="1">
-        <v>90515</v>
+        <v>90511</v>
       </c>
       <c r="Y510" s="1" t="s">
         <v>237</v>
@@ -78851,299 +79231,332 @@
         <v>333</v>
       </c>
       <c r="AA510" s="42">
+        <v>3</v>
+      </c>
+      <c r="AB510" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="511" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B511" s="1">
+        <v>800022</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D511" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E511" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="F511" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G511" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H511" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="I511" s="42" t="s">
+        <v>350</v>
+      </c>
+      <c r="J511" s="46" t="s">
+        <v>351</v>
+      </c>
+      <c r="K511" s="42" t="s">
+        <v>4238</v>
+      </c>
+      <c r="L511" s="42" t="s">
+        <v>353</v>
+      </c>
+      <c r="M511" s="48">
+        <v>3</v>
+      </c>
+      <c r="N511" s="1">
+        <v>0</v>
+      </c>
+      <c r="O511" s="1">
+        <v>12</v>
+      </c>
+      <c r="P511" s="1">
+        <v>12</v>
+      </c>
+      <c r="R511" s="1">
+        <v>90512</v>
+      </c>
+      <c r="T511" s="1">
+        <v>0</v>
+      </c>
+      <c r="U511" s="1">
+        <v>0</v>
+      </c>
+      <c r="X511" s="1">
+        <v>90512</v>
+      </c>
+      <c r="Y511" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z511" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA511" s="42">
+        <v>5</v>
+      </c>
+      <c r="AB511" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="512" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B512" s="1">
+        <v>800023</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="D512" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E512" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="F512" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G512" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H512" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="I512" s="42" t="s">
+        <v>360</v>
+      </c>
+      <c r="J512" s="46" t="s">
+        <v>361</v>
+      </c>
+      <c r="K512" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="L512" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="M512" s="47">
+        <v>1</v>
+      </c>
+      <c r="N512" s="1">
+        <v>0</v>
+      </c>
+      <c r="O512" s="1">
+        <v>12</v>
+      </c>
+      <c r="P512" s="1">
+        <v>13</v>
+      </c>
+      <c r="R512" s="1">
+        <v>90513</v>
+      </c>
+      <c r="T512" s="1">
+        <v>0</v>
+      </c>
+      <c r="U512" s="1">
+        <v>0</v>
+      </c>
+      <c r="X512" s="1">
+        <v>90513</v>
+      </c>
+      <c r="Y512" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z512" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA512" s="42">
+        <v>1</v>
+      </c>
+      <c r="AB512" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="513" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B513" s="1">
+        <v>800024</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D513" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E513" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="F513" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G513" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H513" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="I513" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="J513" s="46" t="s">
+        <v>371</v>
+      </c>
+      <c r="K513" s="42" t="s">
+        <v>4239</v>
+      </c>
+      <c r="L513" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="M513" s="47">
+        <v>1</v>
+      </c>
+      <c r="N513" s="1">
+        <v>0</v>
+      </c>
+      <c r="O513" s="1">
+        <v>12</v>
+      </c>
+      <c r="P513" s="1">
+        <v>14</v>
+      </c>
+      <c r="R513" s="1">
+        <v>90514</v>
+      </c>
+      <c r="T513" s="1">
+        <v>0</v>
+      </c>
+      <c r="U513" s="1">
+        <v>0</v>
+      </c>
+      <c r="X513" s="1">
+        <v>90514</v>
+      </c>
+      <c r="Y513" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z513" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA513" s="42">
+        <v>5</v>
+      </c>
+      <c r="AB513" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="514" spans="1:39" s="1" customFormat="1" ht="15">
+      <c r="B514" s="1">
+        <v>800025</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D514" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E514" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="F514" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G514" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H514" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="I514" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="J514" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="K514" s="42" t="s">
+        <v>4240</v>
+      </c>
+      <c r="L514" s="42" t="s">
+        <v>383</v>
+      </c>
+      <c r="M514" s="47">
+        <v>2</v>
+      </c>
+      <c r="N514" s="1">
+        <v>0</v>
+      </c>
+      <c r="O514" s="1">
+        <v>12</v>
+      </c>
+      <c r="P514" s="1">
+        <v>15</v>
+      </c>
+      <c r="R514" s="1">
+        <v>90515</v>
+      </c>
+      <c r="T514" s="1">
+        <v>0</v>
+      </c>
+      <c r="U514" s="1">
+        <v>0</v>
+      </c>
+      <c r="X514" s="1">
+        <v>90515</v>
+      </c>
+      <c r="Y514" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="Z514" s="42" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA514" s="42">
         <v>10</v>
       </c>
-      <c r="AB510" s="1" t="s">
+      <c r="AB514" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="511" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="A511" s="87" t="s">
+    <row r="515" spans="1:39" s="85" customFormat="1" ht="33">
+      <c r="A515" s="87" t="s">
         <v>4827</v>
       </c>
-      <c r="B511" s="85">
+      <c r="B515" s="85">
         <v>800031</v>
       </c>
-      <c r="C511" s="88" t="s">
+      <c r="C515" s="88" t="s">
         <v>4828</v>
       </c>
-      <c r="D511" s="88" t="s">
+      <c r="D515" s="88" t="s">
         <v>4829</v>
       </c>
-      <c r="E511" s="101" t="s">
+      <c r="E515" s="101" t="s">
         <v>5314</v>
       </c>
-      <c r="F511" s="101" t="s">
+      <c r="F515" s="101" t="s">
         <v>5067</v>
       </c>
-      <c r="G511" s="101" t="s">
+      <c r="G515" s="101" t="s">
         <v>5068</v>
       </c>
-      <c r="H511" s="90" t="s">
+      <c r="H515" s="90" t="s">
         <v>4830</v>
       </c>
-      <c r="I511" s="107" t="s">
+      <c r="I515" s="107" t="s">
         <v>5332</v>
       </c>
-      <c r="J511" s="109" t="s">
+      <c r="J515" s="109" t="s">
         <v>5326</v>
       </c>
-      <c r="K511" s="101" t="s">
+      <c r="K515" s="101" t="s">
         <v>5071</v>
       </c>
-      <c r="L511" s="102" t="s">
+      <c r="L515" s="102" t="s">
         <v>5072</v>
-      </c>
-      <c r="M511" s="92">
-        <v>1</v>
-      </c>
-      <c r="N511" s="85">
-        <v>0</v>
-      </c>
-      <c r="O511" s="85">
-        <v>13</v>
-      </c>
-      <c r="P511" s="85">
-        <v>1</v>
-      </c>
-      <c r="Q511">
-        <v>1059</v>
-      </c>
-      <c r="R511" s="93">
-        <v>94501</v>
-      </c>
-      <c r="T511" s="85">
-        <v>0</v>
-      </c>
-      <c r="U511" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z511" s="94"/>
-      <c r="AA511" s="94"/>
-      <c r="AE511" s="95"/>
-      <c r="AF511" s="95"/>
-      <c r="AG511" s="95"/>
-      <c r="AH511" s="95"/>
-      <c r="AI511" s="95"/>
-      <c r="AL511" s="95"/>
-      <c r="AM511" s="95"/>
-    </row>
-    <row r="512" spans="1:39" s="85" customFormat="1" ht="33">
-      <c r="B512" s="85">
-        <v>800032</v>
-      </c>
-      <c r="C512" s="88" t="s">
-        <v>4831</v>
-      </c>
-      <c r="D512" s="88" t="s">
-        <v>4832</v>
-      </c>
-      <c r="E512" s="101" t="s">
-        <v>5316</v>
-      </c>
-      <c r="F512" s="101" t="s">
-        <v>5075</v>
-      </c>
-      <c r="G512" s="101" t="s">
-        <v>5069</v>
-      </c>
-      <c r="H512" s="90" t="s">
-        <v>4833</v>
-      </c>
-      <c r="I512" s="90" t="s">
-        <v>4834</v>
-      </c>
-      <c r="J512" s="109" t="s">
-        <v>5327</v>
-      </c>
-      <c r="K512" s="101" t="s">
-        <v>5081</v>
-      </c>
-      <c r="L512" s="102" t="s">
-        <v>5083</v>
-      </c>
-      <c r="M512" s="92">
-        <v>1</v>
-      </c>
-      <c r="N512" s="85">
-        <v>0</v>
-      </c>
-      <c r="O512" s="85">
-        <v>13</v>
-      </c>
-      <c r="P512" s="85">
-        <v>2</v>
-      </c>
-      <c r="Q512">
-        <v>1059</v>
-      </c>
-      <c r="R512" s="93">
-        <v>94502</v>
-      </c>
-      <c r="T512" s="85">
-        <v>0</v>
-      </c>
-      <c r="U512" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z512" s="94"/>
-      <c r="AA512" s="94"/>
-    </row>
-    <row r="513" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
-      <c r="B513" s="85">
-        <v>800033</v>
-      </c>
-      <c r="C513" s="88" t="s">
-        <v>4835</v>
-      </c>
-      <c r="D513" s="88" t="s">
-        <v>4836</v>
-      </c>
-      <c r="E513" s="101" t="s">
-        <v>5318</v>
-      </c>
-      <c r="F513" s="101" t="s">
-        <v>5078</v>
-      </c>
-      <c r="G513" s="101" t="s">
-        <v>5070</v>
-      </c>
-      <c r="H513" s="90" t="s">
-        <v>4837</v>
-      </c>
-      <c r="I513" s="90" t="s">
-        <v>4838</v>
-      </c>
-      <c r="J513" s="109" t="s">
-        <v>5328</v>
-      </c>
-      <c r="K513" s="101" t="s">
-        <v>5082</v>
-      </c>
-      <c r="L513" s="102" t="s">
-        <v>5084</v>
-      </c>
-      <c r="M513" s="96">
-        <v>2</v>
-      </c>
-      <c r="N513" s="85">
-        <v>0</v>
-      </c>
-      <c r="O513" s="85">
-        <v>13</v>
-      </c>
-      <c r="P513" s="85">
-        <v>3</v>
-      </c>
-      <c r="Q513">
-        <v>1059</v>
-      </c>
-      <c r="R513" s="93">
-        <v>94503</v>
-      </c>
-      <c r="T513" s="85">
-        <v>0</v>
-      </c>
-      <c r="U513" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z513" s="94"/>
-      <c r="AA513" s="94"/>
-    </row>
-    <row r="514" spans="2:27" s="85" customFormat="1" ht="33">
-      <c r="B514" s="85">
-        <v>800034</v>
-      </c>
-      <c r="C514" s="88" t="s">
-        <v>4839</v>
-      </c>
-      <c r="D514" s="88" t="s">
-        <v>4840</v>
-      </c>
-      <c r="E514" s="110" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F514" s="101" t="s">
-        <v>5073</v>
-      </c>
-      <c r="G514" s="101" t="s">
-        <v>5074</v>
-      </c>
-      <c r="H514" s="90" t="s">
-        <v>4841</v>
-      </c>
-      <c r="I514" s="90" t="s">
-        <v>4842</v>
-      </c>
-      <c r="J514" s="109" t="s">
-        <v>5320</v>
-      </c>
-      <c r="K514" s="91" t="s">
-        <v>5085</v>
-      </c>
-      <c r="L514" s="103" t="s">
-        <v>5088</v>
-      </c>
-      <c r="M514" s="92">
-        <v>1</v>
-      </c>
-      <c r="N514" s="85">
-        <v>0</v>
-      </c>
-      <c r="O514" s="85">
-        <v>13</v>
-      </c>
-      <c r="P514" s="85">
-        <v>4</v>
-      </c>
-      <c r="Q514">
-        <v>1060</v>
-      </c>
-      <c r="R514" s="93">
-        <v>94504</v>
-      </c>
-      <c r="T514" s="85">
-        <v>0</v>
-      </c>
-      <c r="U514" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z514" s="94"/>
-      <c r="AA514" s="94"/>
-    </row>
-    <row r="515" spans="2:27" s="85" customFormat="1" ht="33">
-      <c r="B515" s="85">
-        <v>800035</v>
-      </c>
-      <c r="C515" s="88" t="s">
-        <v>4843</v>
-      </c>
-      <c r="D515" s="88" t="s">
-        <v>4844</v>
-      </c>
-      <c r="E515" s="110" t="s">
-        <v>5317</v>
-      </c>
-      <c r="F515" s="101" t="s">
-        <v>5076</v>
-      </c>
-      <c r="G515" s="102" t="s">
-        <v>5077</v>
-      </c>
-      <c r="H515" s="90" t="s">
-        <v>4845</v>
-      </c>
-      <c r="I515" s="90" t="s">
-        <v>4846</v>
-      </c>
-      <c r="J515" s="109" t="s">
-        <v>5321</v>
-      </c>
-      <c r="K515" s="91" t="s">
-        <v>5086</v>
-      </c>
-      <c r="L515" s="103" t="s">
-        <v>5089</v>
       </c>
       <c r="M515" s="92">
         <v>1</v>
@@ -79155,13 +79568,13 @@
         <v>13</v>
       </c>
       <c r="P515" s="85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q515">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R515" s="93">
-        <v>94505</v>
+        <v>94501</v>
       </c>
       <c r="T515" s="85">
         <v>0</v>
@@ -79171,43 +79584,50 @@
       </c>
       <c r="Z515" s="94"/>
       <c r="AA515" s="94"/>
+      <c r="AE515" s="95"/>
+      <c r="AF515" s="95"/>
+      <c r="AG515" s="95"/>
+      <c r="AH515" s="95"/>
+      <c r="AI515" s="95"/>
+      <c r="AL515" s="95"/>
+      <c r="AM515" s="95"/>
     </row>
-    <row r="516" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="516" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B516" s="85">
-        <v>800036</v>
+        <v>800032</v>
       </c>
       <c r="C516" s="88" t="s">
-        <v>4847</v>
+        <v>4831</v>
       </c>
       <c r="D516" s="88" t="s">
-        <v>4848</v>
-      </c>
-      <c r="E516" s="110" t="s">
-        <v>5319</v>
+        <v>4832</v>
+      </c>
+      <c r="E516" s="101" t="s">
+        <v>5316</v>
       </c>
       <c r="F516" s="101" t="s">
-        <v>5079</v>
-      </c>
-      <c r="G516" s="102" t="s">
-        <v>5080</v>
+        <v>5075</v>
+      </c>
+      <c r="G516" s="101" t="s">
+        <v>5069</v>
       </c>
       <c r="H516" s="90" t="s">
-        <v>4849</v>
+        <v>4833</v>
       </c>
       <c r="I516" s="90" t="s">
-        <v>4850</v>
+        <v>4834</v>
       </c>
       <c r="J516" s="109" t="s">
-        <v>5322</v>
-      </c>
-      <c r="K516" s="91" t="s">
-        <v>5087</v>
-      </c>
-      <c r="L516" s="103" t="s">
-        <v>5090</v>
-      </c>
-      <c r="M516" s="96">
-        <v>2</v>
+        <v>5327</v>
+      </c>
+      <c r="K516" s="101" t="s">
+        <v>5081</v>
+      </c>
+      <c r="L516" s="102" t="s">
+        <v>5083</v>
+      </c>
+      <c r="M516" s="92">
+        <v>1</v>
       </c>
       <c r="N516" s="85">
         <v>0</v>
@@ -79216,13 +79636,13 @@
         <v>13</v>
       </c>
       <c r="P516" s="85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q516">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R516" s="93">
-        <v>94506</v>
+        <v>94502</v>
       </c>
       <c r="T516" s="85">
         <v>0</v>
@@ -79233,42 +79653,42 @@
       <c r="Z516" s="94"/>
       <c r="AA516" s="94"/>
     </row>
-    <row r="517" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="517" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B517" s="85">
-        <v>800037</v>
+        <v>800033</v>
       </c>
       <c r="C517" s="88" t="s">
-        <v>4851</v>
+        <v>4835</v>
       </c>
       <c r="D517" s="88" t="s">
-        <v>4852</v>
-      </c>
-      <c r="E517" s="110" t="s">
-        <v>5323</v>
-      </c>
-      <c r="F517" s="89" t="s">
-        <v>5091</v>
-      </c>
-      <c r="G517" s="104" t="s">
-        <v>5092</v>
+        <v>4836</v>
+      </c>
+      <c r="E517" s="101" t="s">
+        <v>5318</v>
+      </c>
+      <c r="F517" s="101" t="s">
+        <v>5078</v>
+      </c>
+      <c r="G517" s="101" t="s">
+        <v>5070</v>
       </c>
       <c r="H517" s="90" t="s">
-        <v>4853</v>
+        <v>4837</v>
       </c>
       <c r="I517" s="90" t="s">
-        <v>4854</v>
+        <v>4838</v>
       </c>
       <c r="J517" s="109" t="s">
-        <v>5329</v>
-      </c>
-      <c r="K517" s="91" t="s">
-        <v>5202</v>
+        <v>5328</v>
+      </c>
+      <c r="K517" s="101" t="s">
+        <v>5082</v>
       </c>
       <c r="L517" s="102" t="s">
-        <v>5205</v>
-      </c>
-      <c r="M517" s="92">
-        <v>1</v>
+        <v>5084</v>
+      </c>
+      <c r="M517" s="96">
+        <v>2</v>
       </c>
       <c r="N517" s="85">
         <v>0</v>
@@ -79277,13 +79697,13 @@
         <v>13</v>
       </c>
       <c r="P517" s="85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q517">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="R517" s="93">
-        <v>94507</v>
+        <v>94503</v>
       </c>
       <c r="T517" s="85">
         <v>0</v>
@@ -79294,39 +79714,39 @@
       <c r="Z517" s="94"/>
       <c r="AA517" s="94"/>
     </row>
-    <row r="518" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="518" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B518" s="85">
-        <v>800038</v>
+        <v>800034</v>
       </c>
       <c r="C518" s="88" t="s">
-        <v>4855</v>
+        <v>4839</v>
       </c>
       <c r="D518" s="88" t="s">
-        <v>4856</v>
+        <v>4840</v>
       </c>
       <c r="E518" s="110" t="s">
-        <v>5325</v>
-      </c>
-      <c r="F518" s="89" t="s">
-        <v>5094</v>
-      </c>
-      <c r="G518" s="104" t="s">
-        <v>5095</v>
+        <v>5315</v>
+      </c>
+      <c r="F518" s="101" t="s">
+        <v>5073</v>
+      </c>
+      <c r="G518" s="101" t="s">
+        <v>5074</v>
       </c>
       <c r="H518" s="90" t="s">
-        <v>4857</v>
+        <v>4841</v>
       </c>
       <c r="I518" s="90" t="s">
-        <v>4858</v>
+        <v>4842</v>
       </c>
       <c r="J518" s="109" t="s">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="K518" s="91" t="s">
-        <v>5203</v>
-      </c>
-      <c r="L518" s="102" t="s">
-        <v>5206</v>
+        <v>5085</v>
+      </c>
+      <c r="L518" s="103" t="s">
+        <v>5088</v>
       </c>
       <c r="M518" s="92">
         <v>1</v>
@@ -79338,13 +79758,13 @@
         <v>13</v>
       </c>
       <c r="P518" s="85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q518">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R518" s="93">
-        <v>94508</v>
+        <v>94504</v>
       </c>
       <c r="T518" s="85">
         <v>0</v>
@@ -79355,42 +79775,42 @@
       <c r="Z518" s="94"/>
       <c r="AA518" s="94"/>
     </row>
-    <row r="519" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="519" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B519" s="85">
-        <v>800039</v>
+        <v>800035</v>
       </c>
       <c r="C519" s="88" t="s">
-        <v>4859</v>
-      </c>
-      <c r="D519" s="107" t="s">
-        <v>5173</v>
+        <v>4843</v>
+      </c>
+      <c r="D519" s="88" t="s">
+        <v>4844</v>
       </c>
       <c r="E519" s="110" t="s">
-        <v>5324</v>
-      </c>
-      <c r="F519" s="89" t="s">
-        <v>5093</v>
-      </c>
-      <c r="G519" s="104" t="s">
-        <v>5096</v>
+        <v>5317</v>
+      </c>
+      <c r="F519" s="101" t="s">
+        <v>5076</v>
+      </c>
+      <c r="G519" s="102" t="s">
+        <v>5077</v>
       </c>
       <c r="H519" s="90" t="s">
-        <v>4860</v>
+        <v>4845</v>
       </c>
       <c r="I519" s="90" t="s">
-        <v>4861</v>
+        <v>4846</v>
       </c>
       <c r="J519" s="109" t="s">
-        <v>5331</v>
+        <v>5321</v>
       </c>
       <c r="K519" s="91" t="s">
-        <v>5204</v>
-      </c>
-      <c r="L519" s="102" t="s">
-        <v>5207</v>
+        <v>5086</v>
+      </c>
+      <c r="L519" s="103" t="s">
+        <v>5089</v>
       </c>
       <c r="M519" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N519" s="85">
         <v>0</v>
@@ -79399,13 +79819,13 @@
         <v>13</v>
       </c>
       <c r="P519" s="85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q519">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="R519" s="93">
-        <v>94509</v>
+        <v>94505</v>
       </c>
       <c r="T519" s="85">
         <v>0</v>
@@ -79416,42 +79836,42 @@
       <c r="Z519" s="94"/>
       <c r="AA519" s="94"/>
     </row>
-    <row r="520" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="520" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B520" s="85">
-        <v>800040</v>
+        <v>800036</v>
       </c>
       <c r="C520" s="88" t="s">
-        <v>4862</v>
+        <v>4847</v>
       </c>
       <c r="D520" s="88" t="s">
-        <v>4863</v>
+        <v>4848</v>
       </c>
       <c r="E520" s="110" t="s">
-        <v>5333</v>
+        <v>5319</v>
       </c>
       <c r="F520" s="101" t="s">
-        <v>5097</v>
-      </c>
-      <c r="G520" s="105" t="s">
-        <v>5098</v>
+        <v>5079</v>
+      </c>
+      <c r="G520" s="102" t="s">
+        <v>5080</v>
       </c>
       <c r="H520" s="90" t="s">
-        <v>4864</v>
+        <v>4849</v>
       </c>
       <c r="I520" s="90" t="s">
-        <v>4865</v>
-      </c>
-      <c r="J520" s="111" t="s">
-        <v>5335</v>
+        <v>4850</v>
+      </c>
+      <c r="J520" s="109" t="s">
+        <v>5322</v>
       </c>
       <c r="K520" s="91" t="s">
-        <v>5208</v>
+        <v>5087</v>
       </c>
       <c r="L520" s="103" t="s">
-        <v>5209</v>
-      </c>
-      <c r="M520" s="92">
-        <v>1</v>
+        <v>5090</v>
+      </c>
+      <c r="M520" s="96">
+        <v>2</v>
       </c>
       <c r="N520" s="85">
         <v>0</v>
@@ -79460,10 +79880,13 @@
         <v>13</v>
       </c>
       <c r="P520" s="85">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="Q520">
+        <v>1060</v>
       </c>
       <c r="R520" s="93">
-        <v>94510</v>
+        <v>94506</v>
       </c>
       <c r="T520" s="85">
         <v>0</v>
@@ -79474,39 +79897,39 @@
       <c r="Z520" s="94"/>
       <c r="AA520" s="94"/>
     </row>
-    <row r="521" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="521" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B521" s="85">
-        <v>800041</v>
+        <v>800037</v>
       </c>
       <c r="C521" s="88" t="s">
-        <v>4866</v>
+        <v>4851</v>
       </c>
       <c r="D521" s="88" t="s">
-        <v>4867</v>
+        <v>4852</v>
       </c>
       <c r="E521" s="110" t="s">
-        <v>5334</v>
-      </c>
-      <c r="F521" s="101" t="s">
-        <v>5099</v>
-      </c>
-      <c r="G521" s="101" t="s">
-        <v>5100</v>
+        <v>5323</v>
+      </c>
+      <c r="F521" s="89" t="s">
+        <v>5091</v>
+      </c>
+      <c r="G521" s="104" t="s">
+        <v>5092</v>
       </c>
       <c r="H521" s="90" t="s">
-        <v>4868</v>
+        <v>4853</v>
       </c>
       <c r="I521" s="90" t="s">
-        <v>4869</v>
-      </c>
-      <c r="J521" s="111" t="s">
-        <v>5336</v>
+        <v>4854</v>
+      </c>
+      <c r="J521" s="109" t="s">
+        <v>5329</v>
       </c>
       <c r="K521" s="91" t="s">
-        <v>5210</v>
-      </c>
-      <c r="L521" s="103" t="s">
-        <v>5211</v>
+        <v>5202</v>
+      </c>
+      <c r="L521" s="102" t="s">
+        <v>5205</v>
       </c>
       <c r="M521" s="92">
         <v>1</v>
@@ -79518,10 +79941,13 @@
         <v>13</v>
       </c>
       <c r="P521" s="85">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="Q521">
+        <v>1061</v>
       </c>
       <c r="R521" s="93">
-        <v>94511</v>
+        <v>94507</v>
       </c>
       <c r="T521" s="85">
         <v>0</v>
@@ -79532,41 +79958,41 @@
       <c r="Z521" s="94"/>
       <c r="AA521" s="94"/>
     </row>
-    <row r="522" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="522" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B522" s="85">
-        <v>800042</v>
-      </c>
-      <c r="C522" s="97" t="s">
-        <v>4870</v>
-      </c>
-      <c r="D522" s="97" t="s">
-        <v>4870</v>
+        <v>800038</v>
+      </c>
+      <c r="C522" s="88" t="s">
+        <v>4855</v>
+      </c>
+      <c r="D522" s="88" t="s">
+        <v>4856</v>
       </c>
       <c r="E522" s="110" t="s">
-        <v>5337</v>
-      </c>
-      <c r="F522" s="101" t="s">
-        <v>5174</v>
-      </c>
-      <c r="G522" s="101" t="s">
-        <v>5101</v>
-      </c>
-      <c r="H522" s="97" t="s">
-        <v>4871</v>
-      </c>
-      <c r="I522" s="97" t="s">
-        <v>4872</v>
+        <v>5325</v>
+      </c>
+      <c r="F522" s="89" t="s">
+        <v>5094</v>
+      </c>
+      <c r="G522" s="104" t="s">
+        <v>5095</v>
+      </c>
+      <c r="H522" s="90" t="s">
+        <v>4857</v>
+      </c>
+      <c r="I522" s="90" t="s">
+        <v>4858</v>
       </c>
       <c r="J522" s="109" t="s">
-        <v>5340</v>
-      </c>
-      <c r="K522" s="101" t="s">
-        <v>5212</v>
+        <v>5330</v>
+      </c>
+      <c r="K522" s="91" t="s">
+        <v>5203</v>
       </c>
       <c r="L522" s="102" t="s">
-        <v>5213</v>
-      </c>
-      <c r="M522" s="96">
+        <v>5206</v>
+      </c>
+      <c r="M522" s="92">
         <v>1</v>
       </c>
       <c r="N522" s="85">
@@ -79576,13 +80002,13 @@
         <v>13</v>
       </c>
       <c r="P522" s="85">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q522">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="R522" s="93">
-        <v>94512</v>
+        <v>94508</v>
       </c>
       <c r="T522" s="85">
         <v>0</v>
@@ -79593,42 +80019,42 @@
       <c r="Z522" s="94"/>
       <c r="AA522" s="94"/>
     </row>
-    <row r="523" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="523" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B523" s="85">
-        <v>800043</v>
-      </c>
-      <c r="C523" s="97" t="s">
-        <v>4873</v>
-      </c>
-      <c r="D523" s="97" t="s">
-        <v>4873</v>
+        <v>800039</v>
+      </c>
+      <c r="C523" s="88" t="s">
+        <v>4859</v>
+      </c>
+      <c r="D523" s="107" t="s">
+        <v>5173</v>
       </c>
       <c r="E523" s="110" t="s">
-        <v>5338</v>
-      </c>
-      <c r="F523" s="101" t="s">
-        <v>5175</v>
-      </c>
-      <c r="G523" s="102" t="s">
-        <v>5178</v>
-      </c>
-      <c r="H523" s="97" t="s">
-        <v>4874</v>
-      </c>
-      <c r="I523" s="97" t="s">
-        <v>4875</v>
+        <v>5324</v>
+      </c>
+      <c r="F523" s="89" t="s">
+        <v>5093</v>
+      </c>
+      <c r="G523" s="104" t="s">
+        <v>5096</v>
+      </c>
+      <c r="H523" s="90" t="s">
+        <v>4860</v>
+      </c>
+      <c r="I523" s="90" t="s">
+        <v>4861</v>
       </c>
       <c r="J523" s="109" t="s">
-        <v>5341</v>
-      </c>
-      <c r="K523" s="101" t="s">
-        <v>5214</v>
+        <v>5331</v>
+      </c>
+      <c r="K523" s="91" t="s">
+        <v>5204</v>
       </c>
       <c r="L523" s="102" t="s">
-        <v>5215</v>
+        <v>5207</v>
       </c>
       <c r="M523" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N523" s="85">
         <v>0</v>
@@ -79637,13 +80063,13 @@
         <v>13</v>
       </c>
       <c r="P523" s="85">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q523">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="R523" s="93">
-        <v>94513</v>
+        <v>94509</v>
       </c>
       <c r="T523" s="85">
         <v>0</v>
@@ -79654,42 +80080,42 @@
       <c r="Z523" s="94"/>
       <c r="AA523" s="94"/>
     </row>
-    <row r="524" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="524" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B524" s="85">
-        <v>800044</v>
-      </c>
-      <c r="C524" s="97" t="s">
-        <v>4876</v>
-      </c>
-      <c r="D524" s="97" t="s">
-        <v>4876</v>
+        <v>800040</v>
+      </c>
+      <c r="C524" s="88" t="s">
+        <v>4862</v>
+      </c>
+      <c r="D524" s="88" t="s">
+        <v>4863</v>
       </c>
       <c r="E524" s="110" t="s">
-        <v>5339</v>
+        <v>5333</v>
       </c>
       <c r="F524" s="101" t="s">
-        <v>5176</v>
-      </c>
-      <c r="G524" s="102" t="s">
-        <v>5177</v>
-      </c>
-      <c r="H524" s="97" t="s">
-        <v>4877</v>
-      </c>
-      <c r="I524" s="97" t="s">
-        <v>4878</v>
-      </c>
-      <c r="J524" s="109" t="s">
-        <v>5342</v>
-      </c>
-      <c r="K524" s="101" t="s">
-        <v>5216</v>
-      </c>
-      <c r="L524" s="102" t="s">
-        <v>5217</v>
+        <v>5097</v>
+      </c>
+      <c r="G524" s="105" t="s">
+        <v>5098</v>
+      </c>
+      <c r="H524" s="90" t="s">
+        <v>4864</v>
+      </c>
+      <c r="I524" s="90" t="s">
+        <v>4865</v>
+      </c>
+      <c r="J524" s="111" t="s">
+        <v>5335</v>
+      </c>
+      <c r="K524" s="91" t="s">
+        <v>5208</v>
+      </c>
+      <c r="L524" s="103" t="s">
+        <v>5209</v>
       </c>
       <c r="M524" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N524" s="85">
         <v>0</v>
@@ -79698,13 +80124,10 @@
         <v>13</v>
       </c>
       <c r="P524" s="85">
-        <v>14</v>
-      </c>
-      <c r="Q524">
-        <v>1062</v>
+        <v>10</v>
       </c>
       <c r="R524" s="93">
-        <v>94514</v>
+        <v>94510</v>
       </c>
       <c r="T524" s="85">
         <v>0</v>
@@ -79715,39 +80138,39 @@
       <c r="Z524" s="94"/>
       <c r="AA524" s="94"/>
     </row>
-    <row r="525" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="525" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B525" s="85">
-        <v>800045</v>
-      </c>
-      <c r="C525" s="97" t="s">
-        <v>4879</v>
-      </c>
-      <c r="D525" s="97" t="s">
-        <v>4880</v>
+        <v>800041</v>
+      </c>
+      <c r="C525" s="88" t="s">
+        <v>4866</v>
+      </c>
+      <c r="D525" s="88" t="s">
+        <v>4867</v>
       </c>
       <c r="E525" s="110" t="s">
-        <v>5343</v>
-      </c>
-      <c r="F525" s="105" t="s">
-        <v>5102</v>
+        <v>5334</v>
+      </c>
+      <c r="F525" s="101" t="s">
+        <v>5099</v>
       </c>
       <c r="G525" s="101" t="s">
-        <v>5103</v>
-      </c>
-      <c r="H525" s="97" t="s">
-        <v>4881</v>
-      </c>
-      <c r="I525" s="97" t="s">
-        <v>4882</v>
-      </c>
-      <c r="J525" s="109" t="s">
-        <v>5346</v>
-      </c>
-      <c r="K525" s="101" t="s">
-        <v>5218</v>
-      </c>
-      <c r="L525" s="102" t="s">
-        <v>5219</v>
+        <v>5100</v>
+      </c>
+      <c r="H525" s="90" t="s">
+        <v>4868</v>
+      </c>
+      <c r="I525" s="90" t="s">
+        <v>4869</v>
+      </c>
+      <c r="J525" s="111" t="s">
+        <v>5336</v>
+      </c>
+      <c r="K525" s="91" t="s">
+        <v>5210</v>
+      </c>
+      <c r="L525" s="103" t="s">
+        <v>5211</v>
       </c>
       <c r="M525" s="92">
         <v>1</v>
@@ -79759,13 +80182,10 @@
         <v>13</v>
       </c>
       <c r="P525" s="85">
-        <v>15</v>
-      </c>
-      <c r="Q525">
-        <v>1063</v>
+        <v>11</v>
       </c>
       <c r="R525" s="93">
-        <v>94515</v>
+        <v>94511</v>
       </c>
       <c r="T525" s="85">
         <v>0</v>
@@ -79776,39 +80196,39 @@
       <c r="Z525" s="94"/>
       <c r="AA525" s="94"/>
     </row>
-    <row r="526" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
+    <row r="526" spans="1:39" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B526" s="85">
-        <v>800046</v>
+        <v>800042</v>
       </c>
       <c r="C526" s="97" t="s">
-        <v>4883</v>
+        <v>4870</v>
       </c>
       <c r="D526" s="97" t="s">
-        <v>4884</v>
+        <v>4870</v>
       </c>
       <c r="E526" s="110" t="s">
-        <v>5344</v>
-      </c>
-      <c r="F526" s="105" t="s">
-        <v>5179</v>
-      </c>
-      <c r="G526" s="102" t="s">
-        <v>5180</v>
+        <v>5337</v>
+      </c>
+      <c r="F526" s="101" t="s">
+        <v>5174</v>
+      </c>
+      <c r="G526" s="101" t="s">
+        <v>5101</v>
       </c>
       <c r="H526" s="97" t="s">
-        <v>4885</v>
+        <v>4871</v>
       </c>
       <c r="I526" s="97" t="s">
-        <v>4886</v>
+        <v>4872</v>
       </c>
       <c r="J526" s="109" t="s">
-        <v>5347</v>
+        <v>5340</v>
       </c>
       <c r="K526" s="101" t="s">
-        <v>5220</v>
+        <v>5212</v>
       </c>
       <c r="L526" s="102" t="s">
-        <v>5221</v>
+        <v>5213</v>
       </c>
       <c r="M526" s="96">
         <v>1</v>
@@ -79820,13 +80240,13 @@
         <v>13</v>
       </c>
       <c r="P526" s="85">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q526">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R526" s="93">
-        <v>94516</v>
+        <v>94512</v>
       </c>
       <c r="T526" s="85">
         <v>0</v>
@@ -79837,42 +80257,42 @@
       <c r="Z526" s="94"/>
       <c r="AA526" s="94"/>
     </row>
-    <row r="527" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="527" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B527" s="85">
-        <v>800047</v>
+        <v>800043</v>
       </c>
       <c r="C527" s="97" t="s">
-        <v>4887</v>
+        <v>4873</v>
       </c>
       <c r="D527" s="97" t="s">
-        <v>4888</v>
+        <v>4873</v>
       </c>
       <c r="E527" s="110" t="s">
-        <v>5345</v>
-      </c>
-      <c r="F527" s="105" t="s">
-        <v>5181</v>
+        <v>5338</v>
+      </c>
+      <c r="F527" s="101" t="s">
+        <v>5175</v>
       </c>
       <c r="G527" s="102" t="s">
-        <v>5182</v>
+        <v>5178</v>
       </c>
       <c r="H527" s="97" t="s">
-        <v>4889</v>
+        <v>4874</v>
       </c>
       <c r="I527" s="97" t="s">
-        <v>4890</v>
+        <v>4875</v>
       </c>
       <c r="J527" s="109" t="s">
-        <v>5348</v>
+        <v>5341</v>
       </c>
       <c r="K527" s="101" t="s">
-        <v>5222</v>
+        <v>5214</v>
       </c>
       <c r="L527" s="102" t="s">
-        <v>5223</v>
+        <v>5215</v>
       </c>
       <c r="M527" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N527" s="85">
         <v>0</v>
@@ -79881,13 +80301,13 @@
         <v>13</v>
       </c>
       <c r="P527" s="85">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q527">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R527" s="93">
-        <v>94517</v>
+        <v>94513</v>
       </c>
       <c r="T527" s="85">
         <v>0</v>
@@ -79898,42 +80318,42 @@
       <c r="Z527" s="94"/>
       <c r="AA527" s="94"/>
     </row>
-    <row r="528" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="528" spans="1:39" s="85" customFormat="1" ht="33">
       <c r="B528" s="85">
-        <v>800048</v>
+        <v>800044</v>
       </c>
       <c r="C528" s="97" t="s">
-        <v>4891</v>
+        <v>4876</v>
       </c>
       <c r="D528" s="97" t="s">
-        <v>4892</v>
+        <v>4876</v>
       </c>
       <c r="E528" s="110" t="s">
-        <v>5349</v>
-      </c>
-      <c r="F528" s="105" t="s">
-        <v>5104</v>
-      </c>
-      <c r="G528" s="101" t="s">
-        <v>5105</v>
+        <v>5339</v>
+      </c>
+      <c r="F528" s="101" t="s">
+        <v>5176</v>
+      </c>
+      <c r="G528" s="102" t="s">
+        <v>5177</v>
       </c>
       <c r="H528" s="97" t="s">
-        <v>4893</v>
+        <v>4877</v>
       </c>
       <c r="I528" s="97" t="s">
-        <v>4894</v>
+        <v>4878</v>
       </c>
       <c r="J528" s="109" t="s">
-        <v>5352</v>
+        <v>5342</v>
       </c>
       <c r="K528" s="101" t="s">
-        <v>5224</v>
+        <v>5216</v>
       </c>
       <c r="L528" s="102" t="s">
-        <v>5227</v>
+        <v>5217</v>
       </c>
       <c r="M528" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N528" s="85">
         <v>0</v>
@@ -79942,13 +80362,13 @@
         <v>13</v>
       </c>
       <c r="P528" s="85">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Q528">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="R528" s="93">
-        <v>94518</v>
+        <v>94514</v>
       </c>
       <c r="T528" s="85">
         <v>0</v>
@@ -79961,37 +80381,37 @@
     </row>
     <row r="529" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B529" s="85">
-        <v>800049</v>
+        <v>800045</v>
       </c>
       <c r="C529" s="97" t="s">
-        <v>4895</v>
+        <v>4879</v>
       </c>
       <c r="D529" s="97" t="s">
-        <v>4896</v>
+        <v>4880</v>
       </c>
       <c r="E529" s="110" t="s">
-        <v>5350</v>
+        <v>5343</v>
       </c>
       <c r="F529" s="105" t="s">
-        <v>5183</v>
-      </c>
-      <c r="G529" s="102" t="s">
-        <v>5184</v>
+        <v>5102</v>
+      </c>
+      <c r="G529" s="101" t="s">
+        <v>5103</v>
       </c>
       <c r="H529" s="97" t="s">
-        <v>4897</v>
+        <v>4881</v>
       </c>
       <c r="I529" s="97" t="s">
-        <v>4898</v>
+        <v>4882</v>
       </c>
       <c r="J529" s="109" t="s">
-        <v>5353</v>
+        <v>5346</v>
       </c>
       <c r="K529" s="101" t="s">
-        <v>5225</v>
+        <v>5218</v>
       </c>
       <c r="L529" s="102" t="s">
-        <v>5229</v>
+        <v>5219</v>
       </c>
       <c r="M529" s="92">
         <v>1</v>
@@ -80003,13 +80423,13 @@
         <v>13</v>
       </c>
       <c r="P529" s="85">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q529">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R529" s="93">
-        <v>94519</v>
+        <v>94515</v>
       </c>
       <c r="T529" s="85">
         <v>0</v>
@@ -80022,40 +80442,40 @@
     </row>
     <row r="530" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B530" s="85">
-        <v>800050</v>
+        <v>800046</v>
       </c>
       <c r="C530" s="97" t="s">
-        <v>4899</v>
+        <v>4883</v>
       </c>
       <c r="D530" s="97" t="s">
-        <v>4900</v>
+        <v>4884</v>
       </c>
       <c r="E530" s="110" t="s">
-        <v>5351</v>
+        <v>5344</v>
       </c>
       <c r="F530" s="105" t="s">
-        <v>5185</v>
+        <v>5179</v>
       </c>
       <c r="G530" s="102" t="s">
-        <v>5186</v>
+        <v>5180</v>
       </c>
       <c r="H530" s="97" t="s">
-        <v>4901</v>
+        <v>4885</v>
       </c>
       <c r="I530" s="97" t="s">
-        <v>4902</v>
+        <v>4886</v>
       </c>
       <c r="J530" s="109" t="s">
-        <v>5354</v>
+        <v>5347</v>
       </c>
       <c r="K530" s="101" t="s">
-        <v>5226</v>
+        <v>5220</v>
       </c>
       <c r="L530" s="102" t="s">
-        <v>5228</v>
+        <v>5221</v>
       </c>
       <c r="M530" s="96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N530" s="85">
         <v>0</v>
@@ -80064,13 +80484,13 @@
         <v>13</v>
       </c>
       <c r="P530" s="85">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Q530">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="R530" s="93">
-        <v>94520</v>
+        <v>94516</v>
       </c>
       <c r="T530" s="85">
         <v>0</v>
@@ -80083,40 +80503,40 @@
     </row>
     <row r="531" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B531" s="85">
-        <v>800051</v>
+        <v>800047</v>
       </c>
       <c r="C531" s="97" t="s">
-        <v>4903</v>
-      </c>
-      <c r="D531" s="112" t="s">
-        <v>5437</v>
-      </c>
-      <c r="E531" s="101" t="s">
-        <v>5355</v>
+        <v>4887</v>
+      </c>
+      <c r="D531" s="97" t="s">
+        <v>4888</v>
+      </c>
+      <c r="E531" s="110" t="s">
+        <v>5345</v>
       </c>
       <c r="F531" s="105" t="s">
-        <v>5106</v>
-      </c>
-      <c r="G531" s="101" t="s">
-        <v>5107</v>
+        <v>5181</v>
+      </c>
+      <c r="G531" s="102" t="s">
+        <v>5182</v>
       </c>
       <c r="H531" s="97" t="s">
-        <v>4904</v>
-      </c>
-      <c r="I531" s="112" t="s">
-        <v>5440</v>
-      </c>
-      <c r="J531" s="101" t="s">
-        <v>5369</v>
+        <v>4889</v>
+      </c>
+      <c r="I531" s="97" t="s">
+        <v>4890</v>
+      </c>
+      <c r="J531" s="109" t="s">
+        <v>5348</v>
       </c>
       <c r="K531" s="101" t="s">
-        <v>5230</v>
-      </c>
-      <c r="L531" s="101" t="s">
-        <v>5231</v>
+        <v>5222</v>
+      </c>
+      <c r="L531" s="102" t="s">
+        <v>5223</v>
       </c>
       <c r="M531" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N531" s="85">
         <v>0</v>
@@ -80125,10 +80545,13 @@
         <v>13</v>
       </c>
       <c r="P531" s="85">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="Q531">
+        <v>1063</v>
       </c>
       <c r="R531" s="93">
-        <v>94521</v>
+        <v>94517</v>
       </c>
       <c r="T531" s="85">
         <v>0</v>
@@ -80141,37 +80564,37 @@
     </row>
     <row r="532" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B532" s="85">
-        <v>800052</v>
+        <v>800048</v>
       </c>
       <c r="C532" s="97" t="s">
-        <v>4905</v>
-      </c>
-      <c r="D532" s="112" t="s">
-        <v>5438</v>
-      </c>
-      <c r="E532" s="101" t="s">
-        <v>5356</v>
+        <v>4891</v>
+      </c>
+      <c r="D532" s="97" t="s">
+        <v>4892</v>
+      </c>
+      <c r="E532" s="110" t="s">
+        <v>5349</v>
       </c>
       <c r="F532" s="105" t="s">
-        <v>5108</v>
+        <v>5104</v>
       </c>
       <c r="G532" s="101" t="s">
-        <v>5109</v>
+        <v>5105</v>
       </c>
       <c r="H532" s="97" t="s">
-        <v>4906</v>
-      </c>
-      <c r="I532" s="112" t="s">
-        <v>5441</v>
-      </c>
-      <c r="J532" s="101" t="s">
-        <v>5370</v>
+        <v>4893</v>
+      </c>
+      <c r="I532" s="97" t="s">
+        <v>4894</v>
+      </c>
+      <c r="J532" s="109" t="s">
+        <v>5352</v>
       </c>
       <c r="K532" s="101" t="s">
-        <v>5232</v>
-      </c>
-      <c r="L532" s="101" t="s">
-        <v>5233</v>
+        <v>5224</v>
+      </c>
+      <c r="L532" s="102" t="s">
+        <v>5227</v>
       </c>
       <c r="M532" s="92">
         <v>1</v>
@@ -80183,10 +80606,13 @@
         <v>13</v>
       </c>
       <c r="P532" s="85">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="Q532">
+        <v>1064</v>
       </c>
       <c r="R532" s="93">
-        <v>94522</v>
+        <v>94518</v>
       </c>
       <c r="T532" s="85">
         <v>0</v>
@@ -80199,37 +80625,37 @@
     </row>
     <row r="533" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B533" s="85">
-        <v>800053</v>
+        <v>800049</v>
       </c>
       <c r="C533" s="97" t="s">
-        <v>4907</v>
+        <v>4895</v>
       </c>
       <c r="D533" s="97" t="s">
-        <v>4908</v>
-      </c>
-      <c r="E533" s="101" t="s">
-        <v>5357</v>
+        <v>4896</v>
+      </c>
+      <c r="E533" s="110" t="s">
+        <v>5350</v>
       </c>
       <c r="F533" s="105" t="s">
-        <v>5110</v>
-      </c>
-      <c r="G533" s="101" t="s">
-        <v>5111</v>
+        <v>5183</v>
+      </c>
+      <c r="G533" s="102" t="s">
+        <v>5184</v>
       </c>
       <c r="H533" s="97" t="s">
-        <v>4909</v>
+        <v>4897</v>
       </c>
       <c r="I533" s="97" t="s">
-        <v>4910</v>
-      </c>
-      <c r="J533" s="101" t="s">
-        <v>5371</v>
+        <v>4898</v>
+      </c>
+      <c r="J533" s="109" t="s">
+        <v>5353</v>
       </c>
       <c r="K533" s="101" t="s">
-        <v>5234</v>
-      </c>
-      <c r="L533" s="101" t="s">
-        <v>5235</v>
+        <v>5225</v>
+      </c>
+      <c r="L533" s="102" t="s">
+        <v>5229</v>
       </c>
       <c r="M533" s="92">
         <v>1</v>
@@ -80241,10 +80667,13 @@
         <v>13</v>
       </c>
       <c r="P533" s="85">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="Q533">
+        <v>1064</v>
       </c>
       <c r="R533" s="93">
-        <v>94523</v>
+        <v>94519</v>
       </c>
       <c r="T533" s="85">
         <v>0</v>
@@ -80257,40 +80686,40 @@
     </row>
     <row r="534" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B534" s="85">
-        <v>800054</v>
+        <v>800050</v>
       </c>
       <c r="C534" s="97" t="s">
-        <v>4911</v>
-      </c>
-      <c r="D534" s="112" t="s">
-        <v>5439</v>
-      </c>
-      <c r="E534" s="101" t="s">
-        <v>5358</v>
+        <v>4899</v>
+      </c>
+      <c r="D534" s="97" t="s">
+        <v>4900</v>
+      </c>
+      <c r="E534" s="110" t="s">
+        <v>5351</v>
       </c>
       <c r="F534" s="105" t="s">
-        <v>5112</v>
-      </c>
-      <c r="G534" s="101" t="s">
-        <v>5113</v>
+        <v>5185</v>
+      </c>
+      <c r="G534" s="102" t="s">
+        <v>5186</v>
       </c>
       <c r="H534" s="97" t="s">
-        <v>4912</v>
-      </c>
-      <c r="I534" s="112" t="s">
-        <v>5442</v>
-      </c>
-      <c r="J534" s="101" t="s">
-        <v>5372</v>
+        <v>4901</v>
+      </c>
+      <c r="I534" s="97" t="s">
+        <v>4902</v>
+      </c>
+      <c r="J534" s="109" t="s">
+        <v>5354</v>
       </c>
       <c r="K534" s="101" t="s">
-        <v>5236</v>
-      </c>
-      <c r="L534" s="101" t="s">
-        <v>5237</v>
+        <v>5226</v>
+      </c>
+      <c r="L534" s="102" t="s">
+        <v>5228</v>
       </c>
       <c r="M534" s="96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N534" s="85">
         <v>0</v>
@@ -80299,10 +80728,13 @@
         <v>13</v>
       </c>
       <c r="P534" s="85">
-        <v>24</v>
+        <v>20</v>
+      </c>
+      <c r="Q534">
+        <v>1064</v>
       </c>
       <c r="R534" s="93">
-        <v>94524</v>
+        <v>94520</v>
       </c>
       <c r="T534" s="85">
         <v>0</v>
@@ -80315,37 +80747,37 @@
     </row>
     <row r="535" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B535" s="85">
-        <v>800055</v>
+        <v>800051</v>
       </c>
       <c r="C535" s="97" t="s">
-        <v>4913</v>
+        <v>4903</v>
       </c>
       <c r="D535" s="112" t="s">
-        <v>5444</v>
+        <v>5437</v>
       </c>
       <c r="E535" s="101" t="s">
-        <v>5359</v>
+        <v>5355</v>
       </c>
       <c r="F535" s="105" t="s">
-        <v>5114</v>
+        <v>5106</v>
       </c>
       <c r="G535" s="101" t="s">
-        <v>5115</v>
+        <v>5107</v>
       </c>
       <c r="H535" s="97" t="s">
-        <v>4914</v>
-      </c>
-      <c r="I535" s="97" t="s">
-        <v>4915</v>
+        <v>4904</v>
+      </c>
+      <c r="I535" s="112" t="s">
+        <v>5440</v>
       </c>
       <c r="J535" s="101" t="s">
-        <v>5373</v>
+        <v>5369</v>
       </c>
       <c r="K535" s="101" t="s">
-        <v>5238</v>
+        <v>5230</v>
       </c>
       <c r="L535" s="101" t="s">
-        <v>5239</v>
+        <v>5231</v>
       </c>
       <c r="M535" s="92">
         <v>1</v>
@@ -80357,10 +80789,10 @@
         <v>13</v>
       </c>
       <c r="P535" s="85">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R535" s="93">
-        <v>94525</v>
+        <v>94521</v>
       </c>
       <c r="T535" s="85">
         <v>0</v>
@@ -80373,40 +80805,40 @@
     </row>
     <row r="536" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B536" s="85">
-        <v>800056</v>
+        <v>800052</v>
       </c>
       <c r="C536" s="97" t="s">
-        <v>4916</v>
-      </c>
-      <c r="D536" s="97" t="s">
-        <v>4917</v>
+        <v>4905</v>
+      </c>
+      <c r="D536" s="112" t="s">
+        <v>5438</v>
       </c>
       <c r="E536" s="101" t="s">
-        <v>5360</v>
+        <v>5356</v>
       </c>
       <c r="F536" s="105" t="s">
-        <v>5116</v>
+        <v>5108</v>
       </c>
       <c r="G536" s="101" t="s">
-        <v>5117</v>
+        <v>5109</v>
       </c>
       <c r="H536" s="97" t="s">
-        <v>4918</v>
-      </c>
-      <c r="I536" s="97" t="s">
-        <v>4919</v>
+        <v>4906</v>
+      </c>
+      <c r="I536" s="112" t="s">
+        <v>5441</v>
       </c>
       <c r="J536" s="101" t="s">
-        <v>5374</v>
+        <v>5370</v>
       </c>
       <c r="K536" s="101" t="s">
-        <v>5240</v>
+        <v>5232</v>
       </c>
       <c r="L536" s="101" t="s">
-        <v>5241</v>
+        <v>5233</v>
       </c>
       <c r="M536" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N536" s="85">
         <v>0</v>
@@ -80415,10 +80847,10 @@
         <v>13</v>
       </c>
       <c r="P536" s="85">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="R536" s="93">
-        <v>94526</v>
+        <v>94522</v>
       </c>
       <c r="T536" s="85">
         <v>0</v>
@@ -80431,37 +80863,37 @@
     </row>
     <row r="537" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B537" s="85">
-        <v>800057</v>
+        <v>800053</v>
       </c>
       <c r="C537" s="97" t="s">
-        <v>4920</v>
+        <v>4907</v>
       </c>
       <c r="D537" s="97" t="s">
-        <v>4921</v>
+        <v>4908</v>
       </c>
       <c r="E537" s="101" t="s">
-        <v>5361</v>
+        <v>5357</v>
       </c>
       <c r="F537" s="105" t="s">
-        <v>5118</v>
+        <v>5110</v>
       </c>
       <c r="G537" s="101" t="s">
-        <v>5119</v>
+        <v>5111</v>
       </c>
       <c r="H537" s="97" t="s">
-        <v>4922</v>
+        <v>4909</v>
       </c>
       <c r="I537" s="97" t="s">
-        <v>4923</v>
+        <v>4910</v>
       </c>
       <c r="J537" s="101" t="s">
-        <v>5375</v>
+        <v>5371</v>
       </c>
       <c r="K537" s="101" t="s">
-        <v>5242</v>
+        <v>5234</v>
       </c>
       <c r="L537" s="101" t="s">
-        <v>5243</v>
+        <v>5235</v>
       </c>
       <c r="M537" s="92">
         <v>1</v>
@@ -80473,10 +80905,10 @@
         <v>13</v>
       </c>
       <c r="P537" s="85">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="R537" s="93">
-        <v>94527</v>
+        <v>94523</v>
       </c>
       <c r="T537" s="85">
         <v>0</v>
@@ -80489,37 +80921,37 @@
     </row>
     <row r="538" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B538" s="85">
-        <v>800058</v>
+        <v>800054</v>
       </c>
       <c r="C538" s="97" t="s">
-        <v>4924</v>
+        <v>4911</v>
       </c>
       <c r="D538" s="112" t="s">
-        <v>5443</v>
+        <v>5439</v>
       </c>
       <c r="E538" s="101" t="s">
-        <v>5362</v>
+        <v>5358</v>
       </c>
       <c r="F538" s="105" t="s">
-        <v>5120</v>
+        <v>5112</v>
       </c>
       <c r="G538" s="101" t="s">
-        <v>5121</v>
+        <v>5113</v>
       </c>
       <c r="H538" s="97" t="s">
-        <v>4925</v>
-      </c>
-      <c r="I538" s="97" t="s">
-        <v>4926</v>
+        <v>4912</v>
+      </c>
+      <c r="I538" s="112" t="s">
+        <v>5442</v>
       </c>
       <c r="J538" s="101" t="s">
-        <v>5376</v>
+        <v>5372</v>
       </c>
       <c r="K538" s="101" t="s">
-        <v>5244</v>
+        <v>5236</v>
       </c>
       <c r="L538" s="101" t="s">
-        <v>5245</v>
+        <v>5237</v>
       </c>
       <c r="M538" s="96">
         <v>1</v>
@@ -80531,10 +80963,10 @@
         <v>13</v>
       </c>
       <c r="P538" s="85">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="R538" s="93">
-        <v>94528</v>
+        <v>94524</v>
       </c>
       <c r="T538" s="85">
         <v>0</v>
@@ -80547,37 +80979,37 @@
     </row>
     <row r="539" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B539" s="85">
-        <v>800059</v>
+        <v>800055</v>
       </c>
       <c r="C539" s="97" t="s">
-        <v>4927</v>
+        <v>4913</v>
       </c>
       <c r="D539" s="112" t="s">
-        <v>5445</v>
+        <v>5444</v>
       </c>
       <c r="E539" s="101" t="s">
-        <v>5363</v>
+        <v>5359</v>
       </c>
       <c r="F539" s="105" t="s">
-        <v>5122</v>
+        <v>5114</v>
       </c>
       <c r="G539" s="101" t="s">
-        <v>5123</v>
+        <v>5115</v>
       </c>
       <c r="H539" s="97" t="s">
-        <v>4928</v>
-      </c>
-      <c r="I539" s="112" t="s">
-        <v>5446</v>
+        <v>4914</v>
+      </c>
+      <c r="I539" s="97" t="s">
+        <v>4915</v>
       </c>
       <c r="J539" s="101" t="s">
-        <v>5377</v>
+        <v>5373</v>
       </c>
       <c r="K539" s="101" t="s">
-        <v>5246</v>
+        <v>5238</v>
       </c>
       <c r="L539" s="101" t="s">
-        <v>5247</v>
+        <v>5239</v>
       </c>
       <c r="M539" s="92">
         <v>1</v>
@@ -80589,10 +81021,10 @@
         <v>13</v>
       </c>
       <c r="P539" s="85">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R539" s="93">
-        <v>94529</v>
+        <v>94525</v>
       </c>
       <c r="T539" s="85">
         <v>0</v>
@@ -80605,37 +81037,37 @@
     </row>
     <row r="540" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B540" s="85">
-        <v>800060</v>
-      </c>
-      <c r="C540" s="98" t="s">
-        <v>4929</v>
-      </c>
-      <c r="D540" s="98" t="s">
-        <v>4930</v>
+        <v>800056</v>
+      </c>
+      <c r="C540" s="97" t="s">
+        <v>4916</v>
+      </c>
+      <c r="D540" s="97" t="s">
+        <v>4917</v>
       </c>
       <c r="E540" s="101" t="s">
-        <v>5364</v>
+        <v>5360</v>
       </c>
       <c r="F540" s="105" t="s">
-        <v>5124</v>
+        <v>5116</v>
       </c>
       <c r="G540" s="101" t="s">
-        <v>5125</v>
+        <v>5117</v>
       </c>
       <c r="H540" s="97" t="s">
-        <v>4931</v>
+        <v>4918</v>
       </c>
       <c r="I540" s="97" t="s">
-        <v>4932</v>
+        <v>4919</v>
       </c>
       <c r="J540" s="101" t="s">
-        <v>5378</v>
+        <v>5374</v>
       </c>
       <c r="K540" s="101" t="s">
-        <v>5248</v>
+        <v>5240</v>
       </c>
       <c r="L540" s="101" t="s">
-        <v>5249</v>
+        <v>5241</v>
       </c>
       <c r="M540" s="92">
         <v>2</v>
@@ -80647,10 +81079,10 @@
         <v>13</v>
       </c>
       <c r="P540" s="85">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="R540" s="93">
-        <v>94530</v>
+        <v>94526</v>
       </c>
       <c r="T540" s="85">
         <v>0</v>
@@ -80663,40 +81095,40 @@
     </row>
     <row r="541" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B541" s="85">
-        <v>800061</v>
+        <v>800057</v>
       </c>
       <c r="C541" s="97" t="s">
-        <v>4933</v>
+        <v>4920</v>
       </c>
       <c r="D541" s="97" t="s">
-        <v>4934</v>
+        <v>4921</v>
       </c>
       <c r="E541" s="101" t="s">
-        <v>5365</v>
+        <v>5361</v>
       </c>
       <c r="F541" s="105" t="s">
-        <v>5126</v>
+        <v>5118</v>
       </c>
       <c r="G541" s="101" t="s">
-        <v>5127</v>
+        <v>5119</v>
       </c>
       <c r="H541" s="97" t="s">
-        <v>4935</v>
+        <v>4922</v>
       </c>
       <c r="I541" s="97" t="s">
-        <v>4936</v>
+        <v>4923</v>
       </c>
       <c r="J541" s="101" t="s">
-        <v>5379</v>
+        <v>5375</v>
       </c>
       <c r="K541" s="101" t="s">
-        <v>5250</v>
+        <v>5242</v>
       </c>
       <c r="L541" s="101" t="s">
-        <v>5251</v>
+        <v>5243</v>
       </c>
       <c r="M541" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N541" s="85">
         <v>0</v>
@@ -80705,10 +81137,10 @@
         <v>13</v>
       </c>
       <c r="P541" s="85">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R541" s="93">
-        <v>94531</v>
+        <v>94527</v>
       </c>
       <c r="T541" s="85">
         <v>0</v>
@@ -80721,40 +81153,40 @@
     </row>
     <row r="542" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B542" s="85">
-        <v>800062</v>
+        <v>800058</v>
       </c>
       <c r="C542" s="97" t="s">
-        <v>4937</v>
-      </c>
-      <c r="D542" s="97" t="s">
-        <v>4938</v>
+        <v>4924</v>
+      </c>
+      <c r="D542" s="112" t="s">
+        <v>5443</v>
       </c>
       <c r="E542" s="101" t="s">
-        <v>5366</v>
+        <v>5362</v>
       </c>
       <c r="F542" s="105" t="s">
-        <v>5128</v>
+        <v>5120</v>
       </c>
       <c r="G542" s="101" t="s">
-        <v>5129</v>
+        <v>5121</v>
       </c>
       <c r="H542" s="97" t="s">
-        <v>4939</v>
+        <v>4925</v>
       </c>
       <c r="I542" s="97" t="s">
-        <v>4940</v>
+        <v>4926</v>
       </c>
       <c r="J542" s="101" t="s">
-        <v>5380</v>
+        <v>5376</v>
       </c>
       <c r="K542" s="101" t="s">
-        <v>5252</v>
+        <v>5244</v>
       </c>
       <c r="L542" s="101" t="s">
-        <v>5253</v>
+        <v>5245</v>
       </c>
       <c r="M542" s="96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N542" s="85">
         <v>0</v>
@@ -80763,10 +81195,10 @@
         <v>13</v>
       </c>
       <c r="P542" s="85">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R542" s="93">
-        <v>94532</v>
+        <v>94528</v>
       </c>
       <c r="T542" s="85">
         <v>0</v>
@@ -80779,40 +81211,40 @@
     </row>
     <row r="543" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B543" s="85">
-        <v>800063</v>
+        <v>800059</v>
       </c>
       <c r="C543" s="97" t="s">
-        <v>4941</v>
-      </c>
-      <c r="D543" s="97" t="s">
-        <v>4941</v>
+        <v>4927</v>
+      </c>
+      <c r="D543" s="112" t="s">
+        <v>5445</v>
       </c>
       <c r="E543" s="101" t="s">
-        <v>5367</v>
+        <v>5363</v>
       </c>
       <c r="F543" s="105" t="s">
-        <v>5130</v>
+        <v>5122</v>
       </c>
       <c r="G543" s="101" t="s">
-        <v>5131</v>
+        <v>5123</v>
       </c>
       <c r="H543" s="97" t="s">
-        <v>4942</v>
-      </c>
-      <c r="I543" s="97" t="s">
-        <v>4943</v>
+        <v>4928</v>
+      </c>
+      <c r="I543" s="112" t="s">
+        <v>5446</v>
       </c>
       <c r="J543" s="101" t="s">
-        <v>5381</v>
+        <v>5377</v>
       </c>
       <c r="K543" s="101" t="s">
-        <v>5254</v>
+        <v>5246</v>
       </c>
       <c r="L543" s="101" t="s">
-        <v>5255</v>
+        <v>5247</v>
       </c>
       <c r="M543" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N543" s="85">
         <v>0</v>
@@ -80821,10 +81253,10 @@
         <v>13</v>
       </c>
       <c r="P543" s="85">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R543" s="93">
-        <v>94533</v>
+        <v>94529</v>
       </c>
       <c r="T543" s="85">
         <v>0</v>
@@ -80837,37 +81269,37 @@
     </row>
     <row r="544" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B544" s="85">
-        <v>800064</v>
-      </c>
-      <c r="C544" s="97" t="s">
-        <v>4944</v>
-      </c>
-      <c r="D544" s="97" t="s">
-        <v>4944</v>
+        <v>800060</v>
+      </c>
+      <c r="C544" s="98" t="s">
+        <v>4929</v>
+      </c>
+      <c r="D544" s="98" t="s">
+        <v>4930</v>
       </c>
       <c r="E544" s="101" t="s">
-        <v>5368</v>
+        <v>5364</v>
       </c>
       <c r="F544" s="105" t="s">
-        <v>5132</v>
+        <v>5124</v>
       </c>
       <c r="G544" s="101" t="s">
-        <v>5133</v>
+        <v>5125</v>
       </c>
       <c r="H544" s="97" t="s">
-        <v>4945</v>
+        <v>4931</v>
       </c>
       <c r="I544" s="97" t="s">
-        <v>4946</v>
+        <v>4932</v>
       </c>
       <c r="J544" s="101" t="s">
-        <v>5382</v>
+        <v>5378</v>
       </c>
       <c r="K544" s="101" t="s">
-        <v>5256</v>
+        <v>5248</v>
       </c>
       <c r="L544" s="101" t="s">
-        <v>5257</v>
+        <v>5249</v>
       </c>
       <c r="M544" s="92">
         <v>2</v>
@@ -80879,10 +81311,10 @@
         <v>13</v>
       </c>
       <c r="P544" s="85">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R544" s="93">
-        <v>94534</v>
+        <v>94530</v>
       </c>
       <c r="T544" s="85">
         <v>0</v>
@@ -80893,42 +81325,42 @@
       <c r="Z544" s="94"/>
       <c r="AA544" s="94"/>
     </row>
-    <row r="545" spans="2:27" s="85" customFormat="1" ht="16.5">
+    <row r="545" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B545" s="85">
-        <v>800065</v>
+        <v>800061</v>
       </c>
       <c r="C545" s="97" t="s">
-        <v>4947</v>
+        <v>4933</v>
       </c>
       <c r="D545" s="97" t="s">
-        <v>4948</v>
+        <v>4934</v>
       </c>
       <c r="E545" s="101" t="s">
-        <v>5383</v>
-      </c>
-      <c r="F545" s="101" t="s">
-        <v>5134</v>
+        <v>5365</v>
+      </c>
+      <c r="F545" s="105" t="s">
+        <v>5126</v>
       </c>
       <c r="G545" s="101" t="s">
-        <v>5135</v>
+        <v>5127</v>
       </c>
       <c r="H545" s="97" t="s">
-        <v>4949</v>
+        <v>4935</v>
       </c>
       <c r="I545" s="97" t="s">
-        <v>4950</v>
+        <v>4936</v>
       </c>
       <c r="J545" s="101" t="s">
-        <v>5387</v>
+        <v>5379</v>
       </c>
       <c r="K545" s="101" t="s">
-        <v>5258</v>
+        <v>5250</v>
       </c>
       <c r="L545" s="101" t="s">
-        <v>5259</v>
+        <v>5251</v>
       </c>
       <c r="M545" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N545" s="85">
         <v>0</v>
@@ -80937,10 +81369,10 @@
         <v>13</v>
       </c>
       <c r="P545" s="85">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R545" s="93">
-        <v>94535</v>
+        <v>94531</v>
       </c>
       <c r="T545" s="85">
         <v>0</v>
@@ -80953,40 +81385,40 @@
     </row>
     <row r="546" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B546" s="85">
-        <v>800066</v>
+        <v>800062</v>
       </c>
       <c r="C546" s="97" t="s">
-        <v>4951</v>
+        <v>4937</v>
       </c>
       <c r="D546" s="97" t="s">
-        <v>4952</v>
+        <v>4938</v>
       </c>
       <c r="E546" s="101" t="s">
-        <v>5384</v>
-      </c>
-      <c r="F546" s="101" t="s">
-        <v>5136</v>
+        <v>5366</v>
+      </c>
+      <c r="F546" s="105" t="s">
+        <v>5128</v>
       </c>
       <c r="G546" s="101" t="s">
-        <v>5137</v>
+        <v>5129</v>
       </c>
       <c r="H546" s="97" t="s">
-        <v>4953</v>
+        <v>4939</v>
       </c>
       <c r="I546" s="97" t="s">
-        <v>4954</v>
+        <v>4940</v>
       </c>
       <c r="J546" s="101" t="s">
-        <v>5388</v>
+        <v>5380</v>
       </c>
       <c r="K546" s="101" t="s">
-        <v>5260</v>
+        <v>5252</v>
       </c>
       <c r="L546" s="101" t="s">
-        <v>5261</v>
+        <v>5253</v>
       </c>
       <c r="M546" s="96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N546" s="85">
         <v>0</v>
@@ -80995,13 +81427,10 @@
         <v>13</v>
       </c>
       <c r="P546" s="85">
-        <v>36</v>
-      </c>
-      <c r="Q546">
-        <v>1065</v>
+        <v>32</v>
       </c>
       <c r="R546" s="93">
-        <v>94536</v>
+        <v>94532</v>
       </c>
       <c r="T546" s="85">
         <v>0</v>
@@ -81014,37 +81443,37 @@
     </row>
     <row r="547" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B547" s="85">
-        <v>800067</v>
+        <v>800063</v>
       </c>
       <c r="C547" s="97" t="s">
-        <v>4955</v>
+        <v>4941</v>
       </c>
       <c r="D547" s="97" t="s">
-        <v>4956</v>
+        <v>4941</v>
       </c>
       <c r="E547" s="101" t="s">
-        <v>5385</v>
-      </c>
-      <c r="F547" s="101" t="s">
-        <v>5138</v>
+        <v>5367</v>
+      </c>
+      <c r="F547" s="105" t="s">
+        <v>5130</v>
       </c>
       <c r="G547" s="101" t="s">
-        <v>5139</v>
+        <v>5131</v>
       </c>
       <c r="H547" s="97" t="s">
-        <v>4957</v>
+        <v>4942</v>
       </c>
       <c r="I547" s="97" t="s">
-        <v>4958</v>
+        <v>4943</v>
       </c>
       <c r="J547" s="101" t="s">
-        <v>5389</v>
+        <v>5381</v>
       </c>
       <c r="K547" s="101" t="s">
-        <v>5262</v>
+        <v>5254</v>
       </c>
       <c r="L547" s="101" t="s">
-        <v>5263</v>
+        <v>5255</v>
       </c>
       <c r="M547" s="92">
         <v>2</v>
@@ -81056,13 +81485,10 @@
         <v>13</v>
       </c>
       <c r="P547" s="85">
-        <v>37</v>
-      </c>
-      <c r="Q547">
-        <v>1065</v>
+        <v>33</v>
       </c>
       <c r="R547" s="93">
-        <v>94537</v>
+        <v>94533</v>
       </c>
       <c r="T547" s="85">
         <v>0</v>
@@ -81075,40 +81501,40 @@
     </row>
     <row r="548" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B548" s="85">
-        <v>800068</v>
+        <v>800064</v>
       </c>
       <c r="C548" s="97" t="s">
-        <v>4959</v>
+        <v>4944</v>
       </c>
       <c r="D548" s="97" t="s">
-        <v>4960</v>
+        <v>4944</v>
       </c>
       <c r="E548" s="101" t="s">
-        <v>5386</v>
-      </c>
-      <c r="F548" s="101" t="s">
-        <v>5140</v>
+        <v>5368</v>
+      </c>
+      <c r="F548" s="105" t="s">
+        <v>5132</v>
       </c>
       <c r="G548" s="101" t="s">
-        <v>5141</v>
+        <v>5133</v>
       </c>
       <c r="H548" s="97" t="s">
-        <v>4961</v>
+        <v>4945</v>
       </c>
       <c r="I548" s="97" t="s">
-        <v>4962</v>
+        <v>4946</v>
       </c>
       <c r="J548" s="101" t="s">
-        <v>5390</v>
+        <v>5382</v>
       </c>
       <c r="K548" s="101" t="s">
-        <v>5264</v>
+        <v>5256</v>
       </c>
       <c r="L548" s="101" t="s">
-        <v>5265</v>
+        <v>5257</v>
       </c>
       <c r="M548" s="92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N548" s="85">
         <v>0</v>
@@ -81117,13 +81543,10 @@
         <v>13</v>
       </c>
       <c r="P548" s="85">
-        <v>38</v>
-      </c>
-      <c r="Q548">
-        <v>1065</v>
+        <v>34</v>
       </c>
       <c r="R548" s="93">
-        <v>94538</v>
+        <v>94534</v>
       </c>
       <c r="T548" s="85">
         <v>0</v>
@@ -81134,39 +81557,39 @@
       <c r="Z548" s="94"/>
       <c r="AA548" s="94"/>
     </row>
-    <row r="549" spans="2:27" s="85" customFormat="1" ht="33">
+    <row r="549" spans="2:27" s="85" customFormat="1" ht="16.5">
       <c r="B549" s="85">
-        <v>800069</v>
+        <v>800065</v>
       </c>
       <c r="C549" s="97" t="s">
-        <v>4963</v>
+        <v>4947</v>
       </c>
       <c r="D549" s="97" t="s">
-        <v>4964</v>
-      </c>
-      <c r="E549" s="110" t="s">
-        <v>5391</v>
+        <v>4948</v>
+      </c>
+      <c r="E549" s="101" t="s">
+        <v>5383</v>
       </c>
       <c r="F549" s="101" t="s">
-        <v>5142</v>
+        <v>5134</v>
       </c>
       <c r="G549" s="101" t="s">
-        <v>5143</v>
+        <v>5135</v>
       </c>
       <c r="H549" s="97" t="s">
-        <v>4965</v>
+        <v>4949</v>
       </c>
       <c r="I549" s="97" t="s">
-        <v>4966</v>
-      </c>
-      <c r="J549" s="109" t="s">
-        <v>5426</v>
+        <v>4950</v>
+      </c>
+      <c r="J549" s="101" t="s">
+        <v>5387</v>
       </c>
       <c r="K549" s="101" t="s">
-        <v>5266</v>
-      </c>
-      <c r="L549" s="102" t="s">
-        <v>5269</v>
+        <v>5258</v>
+      </c>
+      <c r="L549" s="101" t="s">
+        <v>5259</v>
       </c>
       <c r="M549" s="92">
         <v>1</v>
@@ -81178,13 +81601,10 @@
         <v>13</v>
       </c>
       <c r="P549" s="85">
-        <v>39</v>
-      </c>
-      <c r="Q549">
-        <v>1066</v>
+        <v>35</v>
       </c>
       <c r="R549" s="93">
-        <v>94539</v>
+        <v>94535</v>
       </c>
       <c r="T549" s="85">
         <v>0</v>
@@ -81197,37 +81617,37 @@
     </row>
     <row r="550" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B550" s="85">
-        <v>800070</v>
+        <v>800066</v>
       </c>
       <c r="C550" s="97" t="s">
-        <v>4967</v>
+        <v>4951</v>
       </c>
       <c r="D550" s="97" t="s">
-        <v>4968</v>
-      </c>
-      <c r="E550" s="110" t="s">
-        <v>5392</v>
+        <v>4952</v>
+      </c>
+      <c r="E550" s="101" t="s">
+        <v>5384</v>
       </c>
       <c r="F550" s="101" t="s">
-        <v>5189</v>
-      </c>
-      <c r="G550" s="102" t="s">
-        <v>5190</v>
+        <v>5136</v>
+      </c>
+      <c r="G550" s="101" t="s">
+        <v>5137</v>
       </c>
       <c r="H550" s="97" t="s">
-        <v>4969</v>
+        <v>4953</v>
       </c>
       <c r="I550" s="97" t="s">
-        <v>4970</v>
-      </c>
-      <c r="J550" s="109" t="s">
-        <v>5427</v>
+        <v>4954</v>
+      </c>
+      <c r="J550" s="101" t="s">
+        <v>5388</v>
       </c>
       <c r="K550" s="101" t="s">
-        <v>5267</v>
-      </c>
-      <c r="L550" s="102" t="s">
-        <v>5270</v>
+        <v>5260</v>
+      </c>
+      <c r="L550" s="101" t="s">
+        <v>5261</v>
       </c>
       <c r="M550" s="96">
         <v>1</v>
@@ -81239,13 +81659,13 @@
         <v>13</v>
       </c>
       <c r="P550" s="85">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q550">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R550" s="93">
-        <v>94540</v>
+        <v>94536</v>
       </c>
       <c r="T550" s="85">
         <v>0</v>
@@ -81258,37 +81678,37 @@
     </row>
     <row r="551" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B551" s="85">
-        <v>800071</v>
+        <v>800067</v>
       </c>
       <c r="C551" s="97" t="s">
-        <v>4971</v>
+        <v>4955</v>
       </c>
       <c r="D551" s="97" t="s">
-        <v>4972</v>
-      </c>
-      <c r="E551" s="110" t="s">
-        <v>5393</v>
+        <v>4956</v>
+      </c>
+      <c r="E551" s="101" t="s">
+        <v>5385</v>
       </c>
       <c r="F551" s="101" t="s">
-        <v>5187</v>
-      </c>
-      <c r="G551" s="102" t="s">
-        <v>5188</v>
+        <v>5138</v>
+      </c>
+      <c r="G551" s="101" t="s">
+        <v>5139</v>
       </c>
       <c r="H551" s="97" t="s">
-        <v>4973</v>
+        <v>4957</v>
       </c>
       <c r="I551" s="97" t="s">
-        <v>4974</v>
-      </c>
-      <c r="J551" s="109" t="s">
-        <v>5428</v>
+        <v>4958</v>
+      </c>
+      <c r="J551" s="101" t="s">
+        <v>5389</v>
       </c>
       <c r="K551" s="101" t="s">
-        <v>5268</v>
-      </c>
-      <c r="L551" s="102" t="s">
-        <v>5271</v>
+        <v>5262</v>
+      </c>
+      <c r="L551" s="101" t="s">
+        <v>5263</v>
       </c>
       <c r="M551" s="92">
         <v>2</v>
@@ -81300,13 +81720,13 @@
         <v>13</v>
       </c>
       <c r="P551" s="85">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q551">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R551" s="93">
-        <v>94541</v>
+        <v>94537</v>
       </c>
       <c r="T551" s="85">
         <v>0</v>
@@ -81319,40 +81739,40 @@
     </row>
     <row r="552" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B552" s="85">
-        <v>800072</v>
+        <v>800068</v>
       </c>
       <c r="C552" s="97" t="s">
-        <v>4975</v>
+        <v>4959</v>
       </c>
       <c r="D552" s="97" t="s">
-        <v>4976</v>
-      </c>
-      <c r="E552" s="110" t="s">
-        <v>5394</v>
+        <v>4960</v>
+      </c>
+      <c r="E552" s="101" t="s">
+        <v>5386</v>
       </c>
       <c r="F552" s="101" t="s">
-        <v>5193</v>
+        <v>5140</v>
       </c>
       <c r="G552" s="101" t="s">
-        <v>5144</v>
+        <v>5141</v>
       </c>
       <c r="H552" s="97" t="s">
-        <v>4977</v>
+        <v>4961</v>
       </c>
       <c r="I552" s="97" t="s">
-        <v>4978</v>
-      </c>
-      <c r="J552" s="109" t="s">
-        <v>5429</v>
+        <v>4962</v>
+      </c>
+      <c r="J552" s="101" t="s">
+        <v>5390</v>
       </c>
       <c r="K552" s="101" t="s">
-        <v>5272</v>
-      </c>
-      <c r="L552" s="102" t="s">
-        <v>5273</v>
+        <v>5264</v>
+      </c>
+      <c r="L552" s="101" t="s">
+        <v>5265</v>
       </c>
       <c r="M552" s="92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N552" s="85">
         <v>0</v>
@@ -81361,13 +81781,13 @@
         <v>13</v>
       </c>
       <c r="P552" s="85">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q552">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="R552" s="93">
-        <v>94542</v>
+        <v>94538</v>
       </c>
       <c r="T552" s="85">
         <v>0</v>
@@ -81380,37 +81800,37 @@
     </row>
     <row r="553" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B553" s="85">
-        <v>800073</v>
+        <v>800069</v>
       </c>
       <c r="C553" s="97" t="s">
-        <v>4979</v>
+        <v>4963</v>
       </c>
       <c r="D553" s="97" t="s">
-        <v>4980</v>
+        <v>4964</v>
       </c>
       <c r="E553" s="110" t="s">
-        <v>5395</v>
+        <v>5391</v>
       </c>
       <c r="F553" s="101" t="s">
-        <v>5191</v>
-      </c>
-      <c r="G553" s="102" t="s">
-        <v>5192</v>
+        <v>5142</v>
+      </c>
+      <c r="G553" s="101" t="s">
+        <v>5143</v>
       </c>
       <c r="H553" s="97" t="s">
-        <v>4981</v>
+        <v>4965</v>
       </c>
       <c r="I553" s="97" t="s">
-        <v>4982</v>
+        <v>4966</v>
       </c>
       <c r="J553" s="109" t="s">
-        <v>5430</v>
+        <v>5426</v>
       </c>
       <c r="K553" s="101" t="s">
-        <v>5274</v>
+        <v>5266</v>
       </c>
       <c r="L553" s="102" t="s">
-        <v>5275</v>
+        <v>5269</v>
       </c>
       <c r="M553" s="92">
         <v>1</v>
@@ -81422,13 +81842,13 @@
         <v>13</v>
       </c>
       <c r="P553" s="85">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q553">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R553" s="93">
-        <v>94543</v>
+        <v>94539</v>
       </c>
       <c r="T553" s="85">
         <v>0</v>
@@ -81441,40 +81861,40 @@
     </row>
     <row r="554" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B554" s="85">
-        <v>800074</v>
+        <v>800070</v>
       </c>
       <c r="C554" s="97" t="s">
-        <v>4983</v>
+        <v>4967</v>
       </c>
       <c r="D554" s="97" t="s">
-        <v>4984</v>
+        <v>4968</v>
       </c>
       <c r="E554" s="110" t="s">
-        <v>5396</v>
+        <v>5392</v>
       </c>
       <c r="F554" s="101" t="s">
-        <v>5194</v>
+        <v>5189</v>
       </c>
       <c r="G554" s="102" t="s">
-        <v>5195</v>
+        <v>5190</v>
       </c>
       <c r="H554" s="97" t="s">
-        <v>4985</v>
+        <v>4969</v>
       </c>
       <c r="I554" s="97" t="s">
-        <v>4986</v>
+        <v>4970</v>
       </c>
       <c r="J554" s="109" t="s">
-        <v>5431</v>
+        <v>5427</v>
       </c>
       <c r="K554" s="101" t="s">
-        <v>5276</v>
+        <v>5267</v>
       </c>
       <c r="L554" s="102" t="s">
-        <v>5277</v>
+        <v>5270</v>
       </c>
       <c r="M554" s="96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N554" s="85">
         <v>0</v>
@@ -81483,13 +81903,13 @@
         <v>13</v>
       </c>
       <c r="P554" s="85">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q554">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="R554" s="93">
-        <v>94544</v>
+        <v>94540</v>
       </c>
       <c r="T554" s="85">
         <v>0</v>
@@ -81502,40 +81922,40 @@
     </row>
     <row r="555" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B555" s="85">
-        <v>800075</v>
+        <v>800071</v>
       </c>
       <c r="C555" s="97" t="s">
-        <v>4987</v>
+        <v>4971</v>
       </c>
       <c r="D555" s="97" t="s">
-        <v>4988</v>
+        <v>4972</v>
       </c>
       <c r="E555" s="110" t="s">
-        <v>5397</v>
+        <v>5393</v>
       </c>
       <c r="F555" s="101" t="s">
-        <v>5145</v>
-      </c>
-      <c r="G555" s="101" t="s">
-        <v>5146</v>
+        <v>5187</v>
+      </c>
+      <c r="G555" s="102" t="s">
+        <v>5188</v>
       </c>
       <c r="H555" s="97" t="s">
-        <v>4989</v>
+        <v>4973</v>
       </c>
       <c r="I555" s="97" t="s">
-        <v>4990</v>
+        <v>4974</v>
       </c>
       <c r="J555" s="109" t="s">
-        <v>5432</v>
+        <v>5428</v>
       </c>
       <c r="K555" s="101" t="s">
-        <v>5278</v>
+        <v>5268</v>
       </c>
       <c r="L555" s="102" t="s">
-        <v>5281</v>
+        <v>5271</v>
       </c>
       <c r="M555" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N555" s="85">
         <v>0</v>
@@ -81544,13 +81964,13 @@
         <v>13</v>
       </c>
       <c r="P555" s="85">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q555">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="R555" s="93">
-        <v>94545</v>
+        <v>94541</v>
       </c>
       <c r="T555" s="85">
         <v>0</v>
@@ -81563,37 +81983,37 @@
     </row>
     <row r="556" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B556" s="85">
-        <v>800076</v>
+        <v>800072</v>
       </c>
       <c r="C556" s="97" t="s">
-        <v>4991</v>
+        <v>4975</v>
       </c>
       <c r="D556" s="97" t="s">
-        <v>4992</v>
+        <v>4976</v>
       </c>
       <c r="E556" s="110" t="s">
-        <v>5398</v>
+        <v>5394</v>
       </c>
       <c r="F556" s="101" t="s">
-        <v>5198</v>
-      </c>
-      <c r="G556" s="102" t="s">
-        <v>5199</v>
+        <v>5193</v>
+      </c>
+      <c r="G556" s="101" t="s">
+        <v>5144</v>
       </c>
       <c r="H556" s="97" t="s">
-        <v>4993</v>
+        <v>4977</v>
       </c>
       <c r="I556" s="97" t="s">
-        <v>4994</v>
+        <v>4978</v>
       </c>
       <c r="J556" s="109" t="s">
-        <v>5433</v>
+        <v>5429</v>
       </c>
       <c r="K556" s="101" t="s">
-        <v>5279</v>
+        <v>5272</v>
       </c>
       <c r="L556" s="102" t="s">
-        <v>5283</v>
+        <v>5273</v>
       </c>
       <c r="M556" s="92">
         <v>1</v>
@@ -81605,13 +82025,13 @@
         <v>13</v>
       </c>
       <c r="P556" s="85">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q556">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R556" s="93">
-        <v>94546</v>
+        <v>94542</v>
       </c>
       <c r="T556" s="85">
         <v>0</v>
@@ -81624,40 +82044,40 @@
     </row>
     <row r="557" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B557" s="85">
-        <v>800077</v>
+        <v>800073</v>
       </c>
       <c r="C557" s="97" t="s">
-        <v>4995</v>
+        <v>4979</v>
       </c>
       <c r="D557" s="97" t="s">
-        <v>4996</v>
+        <v>4980</v>
       </c>
       <c r="E557" s="110" t="s">
-        <v>5399</v>
+        <v>5395</v>
       </c>
       <c r="F557" s="101" t="s">
-        <v>5196</v>
+        <v>5191</v>
       </c>
       <c r="G557" s="102" t="s">
-        <v>5197</v>
+        <v>5192</v>
       </c>
       <c r="H557" s="97" t="s">
-        <v>4997</v>
+        <v>4981</v>
       </c>
       <c r="I557" s="97" t="s">
-        <v>4998</v>
+        <v>4982</v>
       </c>
       <c r="J557" s="109" t="s">
-        <v>5434</v>
+        <v>5430</v>
       </c>
       <c r="K557" s="101" t="s">
-        <v>5280</v>
+        <v>5274</v>
       </c>
       <c r="L557" s="102" t="s">
-        <v>5282</v>
+        <v>5275</v>
       </c>
       <c r="M557" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N557" s="85">
         <v>0</v>
@@ -81666,13 +82086,13 @@
         <v>13</v>
       </c>
       <c r="P557" s="85">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q557">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="R557" s="93">
-        <v>94547</v>
+        <v>94543</v>
       </c>
       <c r="T557" s="85">
         <v>0</v>
@@ -81685,40 +82105,40 @@
     </row>
     <row r="558" spans="2:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B558" s="85">
-        <v>800078</v>
+        <v>800074</v>
       </c>
       <c r="C558" s="97" t="s">
-        <v>4999</v>
+        <v>4983</v>
       </c>
       <c r="D558" s="97" t="s">
-        <v>5000</v>
+        <v>4984</v>
       </c>
       <c r="E558" s="110" t="s">
-        <v>5400</v>
+        <v>5396</v>
       </c>
       <c r="F558" s="101" t="s">
-        <v>5171</v>
-      </c>
-      <c r="G558" s="101" t="s">
-        <v>5147</v>
+        <v>5194</v>
+      </c>
+      <c r="G558" s="102" t="s">
+        <v>5195</v>
       </c>
       <c r="H558" s="97" t="s">
-        <v>5001</v>
+        <v>4985</v>
       </c>
       <c r="I558" s="97" t="s">
-        <v>5002</v>
+        <v>4986</v>
       </c>
       <c r="J558" s="109" t="s">
-        <v>5435</v>
+        <v>5431</v>
       </c>
       <c r="K558" s="101" t="s">
-        <v>5284</v>
+        <v>5276</v>
       </c>
       <c r="L558" s="102" t="s">
-        <v>5286</v>
+        <v>5277</v>
       </c>
       <c r="M558" s="96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N558" s="85">
         <v>0</v>
@@ -81727,13 +82147,13 @@
         <v>13</v>
       </c>
       <c r="P558" s="85">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q558">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="R558" s="93">
-        <v>94548</v>
+        <v>94544</v>
       </c>
       <c r="T558" s="85">
         <v>0</v>
@@ -81746,40 +82166,40 @@
     </row>
     <row r="559" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B559" s="85">
-        <v>800079</v>
+        <v>800075</v>
       </c>
       <c r="C559" s="97" t="s">
-        <v>5003</v>
+        <v>4987</v>
       </c>
       <c r="D559" s="97" t="s">
-        <v>5004</v>
+        <v>4988</v>
       </c>
       <c r="E559" s="110" t="s">
-        <v>5401</v>
+        <v>5397</v>
       </c>
       <c r="F559" s="101" t="s">
-        <v>5200</v>
-      </c>
-      <c r="G559" s="102" t="s">
-        <v>5201</v>
+        <v>5145</v>
+      </c>
+      <c r="G559" s="101" t="s">
+        <v>5146</v>
       </c>
       <c r="H559" s="97" t="s">
-        <v>5005</v>
+        <v>4989</v>
       </c>
       <c r="I559" s="97" t="s">
-        <v>5006</v>
+        <v>4990</v>
       </c>
       <c r="J559" s="109" t="s">
-        <v>5436</v>
+        <v>5432</v>
       </c>
       <c r="K559" s="101" t="s">
-        <v>5285</v>
+        <v>5278</v>
       </c>
       <c r="L559" s="102" t="s">
-        <v>5287</v>
+        <v>5281</v>
       </c>
       <c r="M559" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N559" s="85">
         <v>0</v>
@@ -81788,13 +82208,13 @@
         <v>13</v>
       </c>
       <c r="P559" s="85">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Q559">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R559" s="93">
-        <v>94549</v>
+        <v>94545</v>
       </c>
       <c r="T559" s="85">
         <v>0</v>
@@ -81807,37 +82227,37 @@
     </row>
     <row r="560" spans="2:27" s="85" customFormat="1" ht="33">
       <c r="B560" s="85">
-        <v>800080</v>
+        <v>800076</v>
       </c>
       <c r="C560" s="97" t="s">
-        <v>5007</v>
+        <v>4991</v>
       </c>
       <c r="D560" s="97" t="s">
-        <v>5008</v>
+        <v>4992</v>
       </c>
       <c r="E560" s="110" t="s">
-        <v>5402</v>
+        <v>5398</v>
       </c>
       <c r="F560" s="101" t="s">
-        <v>5148</v>
-      </c>
-      <c r="G560" s="101" t="s">
-        <v>5149</v>
+        <v>5198</v>
+      </c>
+      <c r="G560" s="102" t="s">
+        <v>5199</v>
       </c>
       <c r="H560" s="97" t="s">
-        <v>5009</v>
+        <v>4993</v>
       </c>
       <c r="I560" s="97" t="s">
-        <v>5010</v>
-      </c>
-      <c r="J560" s="91" t="s">
-        <v>5404</v>
+        <v>4994</v>
+      </c>
+      <c r="J560" s="109" t="s">
+        <v>5433</v>
       </c>
       <c r="K560" s="101" t="s">
-        <v>5288</v>
-      </c>
-      <c r="L560" s="101" t="s">
-        <v>5289</v>
+        <v>5279</v>
+      </c>
+      <c r="L560" s="102" t="s">
+        <v>5283</v>
       </c>
       <c r="M560" s="92">
         <v>1</v>
@@ -81849,13 +82269,13 @@
         <v>13</v>
       </c>
       <c r="P560" s="85">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q560">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="R560" s="93">
-        <v>94550</v>
+        <v>94546</v>
       </c>
       <c r="T560" s="85">
         <v>0</v>
@@ -81868,37 +82288,37 @@
     </row>
     <row r="561" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B561" s="85">
-        <v>800081</v>
+        <v>800077</v>
       </c>
       <c r="C561" s="97" t="s">
-        <v>5011</v>
+        <v>4995</v>
       </c>
       <c r="D561" s="97" t="s">
-        <v>5012</v>
+        <v>4996</v>
       </c>
       <c r="E561" s="110" t="s">
-        <v>5403</v>
+        <v>5399</v>
       </c>
       <c r="F561" s="101" t="s">
-        <v>5150</v>
-      </c>
-      <c r="G561" s="101" t="s">
-        <v>5151</v>
+        <v>5196</v>
+      </c>
+      <c r="G561" s="102" t="s">
+        <v>5197</v>
       </c>
       <c r="H561" s="97" t="s">
-        <v>5013</v>
+        <v>4997</v>
       </c>
       <c r="I561" s="97" t="s">
-        <v>5014</v>
-      </c>
-      <c r="J561" s="91" t="s">
-        <v>5405</v>
+        <v>4998</v>
+      </c>
+      <c r="J561" s="109" t="s">
+        <v>5434</v>
       </c>
       <c r="K561" s="101" t="s">
-        <v>5290</v>
+        <v>5280</v>
       </c>
       <c r="L561" s="102" t="s">
-        <v>5291</v>
+        <v>5282</v>
       </c>
       <c r="M561" s="92">
         <v>2</v>
@@ -81910,13 +82330,13 @@
         <v>13</v>
       </c>
       <c r="P561" s="85">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Q561">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="R561" s="93">
-        <v>94551</v>
+        <v>94547</v>
       </c>
       <c r="T561" s="85">
         <v>0</v>
@@ -81927,54 +82347,57 @@
       <c r="Z561" s="94"/>
       <c r="AA561" s="94"/>
     </row>
-    <row r="562" spans="1:27" s="85" customFormat="1" ht="18.75">
+    <row r="562" spans="1:27" s="85" customFormat="1" ht="33.75" thickBot="1">
       <c r="B562" s="85">
-        <v>800101</v>
+        <v>800078</v>
       </c>
       <c r="C562" s="97" t="s">
-        <v>5015</v>
+        <v>4999</v>
       </c>
       <c r="D562" s="97" t="s">
-        <v>5016</v>
-      </c>
-      <c r="E562" s="101" t="s">
-        <v>5406</v>
+        <v>5000</v>
+      </c>
+      <c r="E562" s="110" t="s">
+        <v>5400</v>
       </c>
       <c r="F562" s="101" t="s">
-        <v>5152</v>
-      </c>
-      <c r="G562" s="106" t="s">
-        <v>5153</v>
+        <v>5171</v>
+      </c>
+      <c r="G562" s="101" t="s">
+        <v>5147</v>
       </c>
       <c r="H562" s="97" t="s">
-        <v>5017</v>
+        <v>5001</v>
       </c>
       <c r="I562" s="97" t="s">
-        <v>5018</v>
-      </c>
-      <c r="J562" s="111" t="s">
-        <v>5416</v>
+        <v>5002</v>
+      </c>
+      <c r="J562" s="109" t="s">
+        <v>5435</v>
       </c>
       <c r="K562" s="101" t="s">
-        <v>5292</v>
-      </c>
-      <c r="L562" s="108" t="s">
-        <v>5311</v>
-      </c>
-      <c r="M562" s="92">
+        <v>5284</v>
+      </c>
+      <c r="L562" s="102" t="s">
+        <v>5286</v>
+      </c>
+      <c r="M562" s="96">
         <v>1</v>
       </c>
       <c r="N562" s="85">
         <v>0</v>
       </c>
       <c r="O562" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P562" s="85">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="Q562">
+        <v>1069</v>
       </c>
       <c r="R562" s="93">
-        <v>95001</v>
+        <v>94548</v>
       </c>
       <c r="T562" s="85">
         <v>0</v>
@@ -81985,54 +82408,57 @@
       <c r="Z562" s="94"/>
       <c r="AA562" s="94"/>
     </row>
-    <row r="563" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+    <row r="563" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B563" s="85">
-        <v>800102</v>
+        <v>800079</v>
       </c>
       <c r="C563" s="97" t="s">
-        <v>5019</v>
+        <v>5003</v>
       </c>
       <c r="D563" s="97" t="s">
-        <v>5020</v>
-      </c>
-      <c r="E563" s="101" t="s">
-        <v>5407</v>
+        <v>5004</v>
+      </c>
+      <c r="E563" s="110" t="s">
+        <v>5401</v>
       </c>
       <c r="F563" s="101" t="s">
-        <v>5154</v>
-      </c>
-      <c r="G563" s="106" t="s">
-        <v>5155</v>
+        <v>5200</v>
+      </c>
+      <c r="G563" s="102" t="s">
+        <v>5201</v>
       </c>
       <c r="H563" s="97" t="s">
-        <v>5021</v>
+        <v>5005</v>
       </c>
       <c r="I563" s="97" t="s">
-        <v>5022</v>
-      </c>
-      <c r="J563" s="91" t="s">
-        <v>5417</v>
+        <v>5006</v>
+      </c>
+      <c r="J563" s="109" t="s">
+        <v>5436</v>
       </c>
       <c r="K563" s="101" t="s">
-        <v>5293</v>
+        <v>5285</v>
       </c>
       <c r="L563" s="102" t="s">
-        <v>5294</v>
-      </c>
-      <c r="M563" s="96">
-        <v>1</v>
+        <v>5287</v>
+      </c>
+      <c r="M563" s="92">
+        <v>2</v>
       </c>
       <c r="N563" s="85">
         <v>0</v>
       </c>
       <c r="O563" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P563" s="85">
-        <v>2</v>
+        <v>49</v>
+      </c>
+      <c r="Q563">
+        <v>1069</v>
       </c>
       <c r="R563" s="93">
-        <v>95002</v>
+        <v>94549</v>
       </c>
       <c r="T563" s="85">
         <v>0</v>
@@ -82043,39 +82469,39 @@
       <c r="Z563" s="94"/>
       <c r="AA563" s="94"/>
     </row>
-    <row r="564" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="564" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B564" s="85">
-        <v>800103</v>
+        <v>800080</v>
       </c>
       <c r="C564" s="97" t="s">
-        <v>5023</v>
+        <v>5007</v>
       </c>
       <c r="D564" s="97" t="s">
-        <v>5024</v>
-      </c>
-      <c r="E564" s="101" t="s">
-        <v>5408</v>
+        <v>5008</v>
+      </c>
+      <c r="E564" s="110" t="s">
+        <v>5402</v>
       </c>
       <c r="F564" s="101" t="s">
-        <v>5172</v>
-      </c>
-      <c r="G564" s="106" t="s">
-        <v>5156</v>
+        <v>5148</v>
+      </c>
+      <c r="G564" s="101" t="s">
+        <v>5149</v>
       </c>
       <c r="H564" s="97" t="s">
-        <v>5025</v>
+        <v>5009</v>
       </c>
       <c r="I564" s="97" t="s">
-        <v>5026</v>
+        <v>5010</v>
       </c>
       <c r="J564" s="91" t="s">
-        <v>5418</v>
-      </c>
-      <c r="K564" s="91" t="s">
-        <v>5295</v>
-      </c>
-      <c r="L564" s="91" t="s">
-        <v>5296</v>
+        <v>5404</v>
+      </c>
+      <c r="K564" s="101" t="s">
+        <v>5288</v>
+      </c>
+      <c r="L564" s="101" t="s">
+        <v>5289</v>
       </c>
       <c r="M564" s="92">
         <v>1</v>
@@ -82084,13 +82510,16 @@
         <v>0</v>
       </c>
       <c r="O564" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P564" s="85">
-        <v>3</v>
+        <v>50</v>
+      </c>
+      <c r="Q564">
+        <v>1070</v>
       </c>
       <c r="R564" s="93">
-        <v>95003</v>
+        <v>94550</v>
       </c>
       <c r="T564" s="85">
         <v>0</v>
@@ -82101,54 +82530,57 @@
       <c r="Z564" s="94"/>
       <c r="AA564" s="94"/>
     </row>
-    <row r="565" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="565" spans="1:27" s="85" customFormat="1" ht="33">
       <c r="B565" s="85">
-        <v>800104</v>
+        <v>800081</v>
       </c>
       <c r="C565" s="97" t="s">
-        <v>5027</v>
+        <v>5011</v>
       </c>
       <c r="D565" s="97" t="s">
-        <v>5028</v>
-      </c>
-      <c r="E565" s="101" t="s">
-        <v>5409</v>
+        <v>5012</v>
+      </c>
+      <c r="E565" s="110" t="s">
+        <v>5403</v>
       </c>
       <c r="F565" s="101" t="s">
-        <v>5157</v>
-      </c>
-      <c r="G565" s="106" t="s">
-        <v>5158</v>
+        <v>5150</v>
+      </c>
+      <c r="G565" s="101" t="s">
+        <v>5151</v>
       </c>
       <c r="H565" s="97" t="s">
-        <v>5029</v>
+        <v>5013</v>
       </c>
       <c r="I565" s="97" t="s">
-        <v>5030</v>
+        <v>5014</v>
       </c>
       <c r="J565" s="91" t="s">
-        <v>5419</v>
-      </c>
-      <c r="K565" s="91" t="s">
-        <v>5297</v>
-      </c>
-      <c r="L565" s="91" t="s">
-        <v>5298</v>
+        <v>5405</v>
+      </c>
+      <c r="K565" s="101" t="s">
+        <v>5290</v>
+      </c>
+      <c r="L565" s="102" t="s">
+        <v>5291</v>
       </c>
       <c r="M565" s="92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N565" s="85">
         <v>0</v>
       </c>
       <c r="O565" s="85">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P565" s="85">
-        <v>4</v>
+        <v>51</v>
+      </c>
+      <c r="Q565">
+        <v>1070</v>
       </c>
       <c r="R565" s="93">
-        <v>95004</v>
+        <v>94551</v>
       </c>
       <c r="T565" s="85">
         <v>0</v>
@@ -82159,39 +82591,39 @@
       <c r="Z565" s="94"/>
       <c r="AA565" s="94"/>
     </row>
-    <row r="566" spans="1:27" s="85" customFormat="1" ht="16.5">
+    <row r="566" spans="1:27" s="85" customFormat="1" ht="18.75">
       <c r="B566" s="85">
-        <v>800105</v>
+        <v>800101</v>
       </c>
       <c r="C566" s="97" t="s">
-        <v>5031</v>
+        <v>5015</v>
       </c>
       <c r="D566" s="97" t="s">
-        <v>5032</v>
+        <v>5016</v>
       </c>
       <c r="E566" s="101" t="s">
-        <v>5410</v>
+        <v>5406</v>
       </c>
       <c r="F566" s="101" t="s">
-        <v>5159</v>
+        <v>5152</v>
       </c>
       <c r="G566" s="106" t="s">
-        <v>5160</v>
+        <v>5153</v>
       </c>
       <c r="H566" s="97" t="s">
-        <v>5033</v>
+        <v>5017</v>
       </c>
       <c r="I566" s="97" t="s">
-        <v>5034</v>
-      </c>
-      <c r="J566" s="91" t="s">
-        <v>5420</v>
-      </c>
-      <c r="K566" s="91" t="s">
-        <v>5299</v>
-      </c>
-      <c r="L566" s="91" t="s">
-        <v>5300</v>
+        <v>5018</v>
+      </c>
+      <c r="J566" s="111" t="s">
+        <v>5416</v>
+      </c>
+      <c r="K566" s="101" t="s">
+        <v>5292</v>
+      </c>
+      <c r="L566" s="108" t="s">
+        <v>5311</v>
       </c>
       <c r="M566" s="92">
         <v>1</v>
@@ -82203,10 +82635,10 @@
         <v>14</v>
       </c>
       <c r="P566" s="85">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R566" s="93">
-        <v>95005</v>
+        <v>95001</v>
       </c>
       <c r="T566" s="85">
         <v>0</v>
@@ -82219,37 +82651,37 @@
     </row>
     <row r="567" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B567" s="85">
-        <v>800106</v>
+        <v>800102</v>
       </c>
       <c r="C567" s="97" t="s">
-        <v>5035</v>
+        <v>5019</v>
       </c>
       <c r="D567" s="97" t="s">
-        <v>5036</v>
+        <v>5020</v>
       </c>
       <c r="E567" s="101" t="s">
-        <v>5411</v>
+        <v>5407</v>
       </c>
       <c r="F567" s="101" t="s">
-        <v>5161</v>
+        <v>5154</v>
       </c>
       <c r="G567" s="106" t="s">
-        <v>5162</v>
+        <v>5155</v>
       </c>
       <c r="H567" s="97" t="s">
-        <v>5037</v>
+        <v>5021</v>
       </c>
       <c r="I567" s="97" t="s">
-        <v>5038</v>
+        <v>5022</v>
       </c>
       <c r="J567" s="91" t="s">
-        <v>5421</v>
-      </c>
-      <c r="K567" s="91" t="s">
-        <v>5301</v>
-      </c>
-      <c r="L567" s="91" t="s">
-        <v>5302</v>
+        <v>5417</v>
+      </c>
+      <c r="K567" s="101" t="s">
+        <v>5293</v>
+      </c>
+      <c r="L567" s="102" t="s">
+        <v>5294</v>
       </c>
       <c r="M567" s="96">
         <v>1</v>
@@ -82261,10 +82693,10 @@
         <v>14</v>
       </c>
       <c r="P567" s="85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R567" s="93">
-        <v>95006</v>
+        <v>95002</v>
       </c>
       <c r="T567" s="85">
         <v>0</v>
@@ -82277,40 +82709,40 @@
     </row>
     <row r="568" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B568" s="85">
-        <v>800107</v>
+        <v>800103</v>
       </c>
       <c r="C568" s="97" t="s">
-        <v>5039</v>
+        <v>5023</v>
       </c>
       <c r="D568" s="97" t="s">
-        <v>5040</v>
+        <v>5024</v>
       </c>
       <c r="E568" s="101" t="s">
-        <v>5412</v>
+        <v>5408</v>
       </c>
       <c r="F568" s="101" t="s">
-        <v>5163</v>
+        <v>5172</v>
       </c>
       <c r="G568" s="106" t="s">
-        <v>5164</v>
+        <v>5156</v>
       </c>
       <c r="H568" s="97" t="s">
-        <v>5041</v>
+        <v>5025</v>
       </c>
       <c r="I568" s="97" t="s">
-        <v>5042</v>
+        <v>5026</v>
       </c>
       <c r="J568" s="91" t="s">
-        <v>5422</v>
+        <v>5418</v>
       </c>
       <c r="K568" s="91" t="s">
-        <v>5303</v>
+        <v>5295</v>
       </c>
       <c r="L568" s="91" t="s">
-        <v>5304</v>
+        <v>5296</v>
       </c>
       <c r="M568" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N568" s="85">
         <v>0</v>
@@ -82319,10 +82751,10 @@
         <v>14</v>
       </c>
       <c r="P568" s="85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R568" s="93">
-        <v>95007</v>
+        <v>95003</v>
       </c>
       <c r="T568" s="85">
         <v>0</v>
@@ -82335,40 +82767,40 @@
     </row>
     <row r="569" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B569" s="85">
-        <v>800108</v>
+        <v>800104</v>
       </c>
       <c r="C569" s="97" t="s">
-        <v>5043</v>
+        <v>5027</v>
       </c>
       <c r="D569" s="97" t="s">
-        <v>5044</v>
+        <v>5028</v>
       </c>
       <c r="E569" s="101" t="s">
-        <v>5413</v>
+        <v>5409</v>
       </c>
       <c r="F569" s="101" t="s">
-        <v>5165</v>
+        <v>5157</v>
       </c>
       <c r="G569" s="106" t="s">
-        <v>5166</v>
+        <v>5158</v>
       </c>
       <c r="H569" s="97" t="s">
-        <v>5045</v>
+        <v>5029</v>
       </c>
       <c r="I569" s="97" t="s">
-        <v>5046</v>
+        <v>5030</v>
       </c>
       <c r="J569" s="91" t="s">
-        <v>5423</v>
+        <v>5419</v>
       </c>
       <c r="K569" s="91" t="s">
-        <v>5305</v>
+        <v>5297</v>
       </c>
       <c r="L569" s="91" t="s">
-        <v>5306</v>
+        <v>5298</v>
       </c>
       <c r="M569" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N569" s="85">
         <v>0</v>
@@ -82377,10 +82809,10 @@
         <v>14</v>
       </c>
       <c r="P569" s="85">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R569" s="93">
-        <v>95008</v>
+        <v>95004</v>
       </c>
       <c r="T569" s="85">
         <v>0</v>
@@ -82393,40 +82825,40 @@
     </row>
     <row r="570" spans="1:27" s="85" customFormat="1" ht="16.5">
       <c r="B570" s="85">
-        <v>800109</v>
+        <v>800105</v>
       </c>
       <c r="C570" s="97" t="s">
-        <v>5047</v>
+        <v>5031</v>
       </c>
       <c r="D570" s="97" t="s">
-        <v>5048</v>
+        <v>5032</v>
       </c>
       <c r="E570" s="101" t="s">
-        <v>5414</v>
+        <v>5410</v>
       </c>
       <c r="F570" s="101" t="s">
-        <v>5167</v>
+        <v>5159</v>
       </c>
       <c r="G570" s="106" t="s">
-        <v>5168</v>
+        <v>5160</v>
       </c>
       <c r="H570" s="97" t="s">
-        <v>5049</v>
+        <v>5033</v>
       </c>
       <c r="I570" s="97" t="s">
-        <v>5050</v>
+        <v>5034</v>
       </c>
       <c r="J570" s="91" t="s">
-        <v>5424</v>
+        <v>5420</v>
       </c>
       <c r="K570" s="91" t="s">
-        <v>5307</v>
+        <v>5299</v>
       </c>
       <c r="L570" s="91" t="s">
-        <v>5308</v>
+        <v>5300</v>
       </c>
       <c r="M570" s="92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N570" s="85">
         <v>0</v>
@@ -82435,10 +82867,10 @@
         <v>14</v>
       </c>
       <c r="P570" s="85">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R570" s="93">
-        <v>95009</v>
+        <v>95005</v>
       </c>
       <c r="T570" s="85">
         <v>0</v>
@@ -82451,40 +82883,40 @@
     </row>
     <row r="571" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
       <c r="B571" s="85">
-        <v>800110</v>
+        <v>800106</v>
       </c>
       <c r="C571" s="97" t="s">
-        <v>5051</v>
+        <v>5035</v>
       </c>
       <c r="D571" s="97" t="s">
-        <v>5052</v>
+        <v>5036</v>
       </c>
       <c r="E571" s="101" t="s">
-        <v>5415</v>
+        <v>5411</v>
       </c>
       <c r="F571" s="101" t="s">
-        <v>5169</v>
+        <v>5161</v>
       </c>
       <c r="G571" s="106" t="s">
-        <v>5170</v>
+        <v>5162</v>
       </c>
       <c r="H571" s="97" t="s">
-        <v>5053</v>
+        <v>5037</v>
       </c>
       <c r="I571" s="97" t="s">
-        <v>5054</v>
+        <v>5038</v>
       </c>
       <c r="J571" s="91" t="s">
-        <v>5425</v>
+        <v>5421</v>
       </c>
       <c r="K571" s="91" t="s">
-        <v>5309</v>
+        <v>5301</v>
       </c>
       <c r="L571" s="91" t="s">
-        <v>5310</v>
+        <v>5302</v>
       </c>
       <c r="M571" s="96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N571" s="85">
         <v>0</v>
@@ -82493,10 +82925,10 @@
         <v>14</v>
       </c>
       <c r="P571" s="85">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R571" s="93">
-        <v>95010</v>
+        <v>95006</v>
       </c>
       <c r="T571" s="85">
         <v>0</v>
@@ -82507,54 +82939,306 @@
       <c r="Z571" s="94"/>
       <c r="AA571" s="94"/>
     </row>
-    <row r="572" spans="1:27" s="2" customFormat="1">
-      <c r="A572" s="2" t="s">
+    <row r="572" spans="1:27" s="85" customFormat="1" ht="16.5">
+      <c r="B572" s="85">
+        <v>800107</v>
+      </c>
+      <c r="C572" s="97" t="s">
+        <v>5039</v>
+      </c>
+      <c r="D572" s="97" t="s">
+        <v>5040</v>
+      </c>
+      <c r="E572" s="101" t="s">
+        <v>5412</v>
+      </c>
+      <c r="F572" s="101" t="s">
+        <v>5163</v>
+      </c>
+      <c r="G572" s="106" t="s">
+        <v>5164</v>
+      </c>
+      <c r="H572" s="97" t="s">
+        <v>5041</v>
+      </c>
+      <c r="I572" s="97" t="s">
+        <v>5042</v>
+      </c>
+      <c r="J572" s="91" t="s">
+        <v>5422</v>
+      </c>
+      <c r="K572" s="91" t="s">
+        <v>5303</v>
+      </c>
+      <c r="L572" s="91" t="s">
+        <v>5304</v>
+      </c>
+      <c r="M572" s="92">
+        <v>2</v>
+      </c>
+      <c r="N572" s="85">
+        <v>0</v>
+      </c>
+      <c r="O572" s="85">
+        <v>14</v>
+      </c>
+      <c r="P572" s="85">
+        <v>7</v>
+      </c>
+      <c r="R572" s="93">
+        <v>95007</v>
+      </c>
+      <c r="T572" s="85">
+        <v>0</v>
+      </c>
+      <c r="U572" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z572" s="94"/>
+      <c r="AA572" s="94"/>
+    </row>
+    <row r="573" spans="1:27" s="85" customFormat="1" ht="16.5">
+      <c r="B573" s="85">
+        <v>800108</v>
+      </c>
+      <c r="C573" s="97" t="s">
+        <v>5043</v>
+      </c>
+      <c r="D573" s="97" t="s">
+        <v>5044</v>
+      </c>
+      <c r="E573" s="101" t="s">
+        <v>5413</v>
+      </c>
+      <c r="F573" s="101" t="s">
+        <v>5165</v>
+      </c>
+      <c r="G573" s="106" t="s">
+        <v>5166</v>
+      </c>
+      <c r="H573" s="97" t="s">
+        <v>5045</v>
+      </c>
+      <c r="I573" s="97" t="s">
+        <v>5046</v>
+      </c>
+      <c r="J573" s="91" t="s">
+        <v>5423</v>
+      </c>
+      <c r="K573" s="91" t="s">
+        <v>5305</v>
+      </c>
+      <c r="L573" s="91" t="s">
+        <v>5306</v>
+      </c>
+      <c r="M573" s="92">
+        <v>2</v>
+      </c>
+      <c r="N573" s="85">
+        <v>0</v>
+      </c>
+      <c r="O573" s="85">
+        <v>14</v>
+      </c>
+      <c r="P573" s="85">
+        <v>8</v>
+      </c>
+      <c r="R573" s="93">
+        <v>95008</v>
+      </c>
+      <c r="T573" s="85">
+        <v>0</v>
+      </c>
+      <c r="U573" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z573" s="94"/>
+      <c r="AA573" s="94"/>
+    </row>
+    <row r="574" spans="1:27" s="85" customFormat="1" ht="16.5">
+      <c r="B574" s="85">
+        <v>800109</v>
+      </c>
+      <c r="C574" s="97" t="s">
+        <v>5047</v>
+      </c>
+      <c r="D574" s="97" t="s">
+        <v>5048</v>
+      </c>
+      <c r="E574" s="101" t="s">
+        <v>5414</v>
+      </c>
+      <c r="F574" s="101" t="s">
+        <v>5167</v>
+      </c>
+      <c r="G574" s="106" t="s">
+        <v>5168</v>
+      </c>
+      <c r="H574" s="97" t="s">
+        <v>5049</v>
+      </c>
+      <c r="I574" s="97" t="s">
+        <v>5050</v>
+      </c>
+      <c r="J574" s="91" t="s">
+        <v>5424</v>
+      </c>
+      <c r="K574" s="91" t="s">
+        <v>5307</v>
+      </c>
+      <c r="L574" s="91" t="s">
+        <v>5308</v>
+      </c>
+      <c r="M574" s="92">
+        <v>2</v>
+      </c>
+      <c r="N574" s="85">
+        <v>0</v>
+      </c>
+      <c r="O574" s="85">
+        <v>14</v>
+      </c>
+      <c r="P574" s="85">
+        <v>9</v>
+      </c>
+      <c r="R574" s="93">
+        <v>95009</v>
+      </c>
+      <c r="T574" s="85">
+        <v>0</v>
+      </c>
+      <c r="U574" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z574" s="94"/>
+      <c r="AA574" s="94"/>
+    </row>
+    <row r="575" spans="1:27" s="85" customFormat="1" ht="17.25" thickBot="1">
+      <c r="B575" s="85">
+        <v>800110</v>
+      </c>
+      <c r="C575" s="97" t="s">
+        <v>5051</v>
+      </c>
+      <c r="D575" s="97" t="s">
+        <v>5052</v>
+      </c>
+      <c r="E575" s="101" t="s">
+        <v>5415</v>
+      </c>
+      <c r="F575" s="101" t="s">
+        <v>5169</v>
+      </c>
+      <c r="G575" s="106" t="s">
+        <v>5170</v>
+      </c>
+      <c r="H575" s="97" t="s">
+        <v>5053</v>
+      </c>
+      <c r="I575" s="97" t="s">
+        <v>5054</v>
+      </c>
+      <c r="J575" s="91" t="s">
+        <v>5425</v>
+      </c>
+      <c r="K575" s="91" t="s">
+        <v>5309</v>
+      </c>
+      <c r="L575" s="91" t="s">
+        <v>5310</v>
+      </c>
+      <c r="M575" s="96">
+        <v>3</v>
+      </c>
+      <c r="N575" s="85">
+        <v>0</v>
+      </c>
+      <c r="O575" s="85">
+        <v>14</v>
+      </c>
+      <c r="P575" s="85">
+        <v>10</v>
+      </c>
+      <c r="R575" s="93">
+        <v>95010</v>
+      </c>
+      <c r="T575" s="85">
+        <v>0</v>
+      </c>
+      <c r="U575" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z575" s="94"/>
+      <c r="AA575" s="94"/>
+    </row>
+    <row r="576" spans="1:27" s="2" customFormat="1">
+      <c r="A576" s="2" t="s">
         <v>4241</v>
       </c>
-      <c r="B572" s="2">
+      <c r="B576" s="2">
         <v>900001</v>
       </c>
-      <c r="M572" s="2">
-        <v>0</v>
-      </c>
-      <c r="N572" s="2">
-        <v>0</v>
-      </c>
-      <c r="O572" s="2">
+      <c r="M576" s="2">
+        <v>0</v>
+      </c>
+      <c r="N576" s="2">
+        <v>0</v>
+      </c>
+      <c r="O576" s="2">
         <v>2</v>
       </c>
-      <c r="P572" s="2">
+      <c r="P576" s="2">
         <v>999</v>
       </c>
-      <c r="R572" s="2">
+      <c r="R576" s="2">
         <v>98001</v>
       </c>
-      <c r="T572" s="2">
+      <c r="T576" s="2">
         <v>1</v>
       </c>
-      <c r="U572" s="2">
+      <c r="U576" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U511" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:U515" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="38" type="noConversion"/>
-  <conditionalFormatting sqref="N1:N443 N449:N459 N462:N479 N482:N1048576 N445">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="N1:N445">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O1:O443 O449:O459 O462:O479 O482:O1048576 O445">
-    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+  <conditionalFormatting sqref="N449:N459 N462:N479">
+    <cfRule type="cellIs" dxfId="6" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N482:N497 N500:N1048576">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:O445">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N444">
+  <conditionalFormatting sqref="O449:O459 O462:O479">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+      <formula>9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O482:O497 O500:O1048576">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+      <formula>9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N498:N499">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O444">
+  <conditionalFormatting sqref="O498:O499">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>9</formula>
     </cfRule>
